--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>273.834282</v>
+        <v>274.834282</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>116.950278</v>
+        <v>117.950278</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>104.708322</v>
+        <v>105.708322</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>228.779942</v>
+        <v>229.779942</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>231.566493</v>
+        <v>232.566493</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>39.934039</v>
+        <v>40.934039</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>266.603993</v>
+        <v>267.603993</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>215.64463</v>
+        <v>216.64463</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>199.727917</v>
+        <v>200.727917</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>115.62456</v>
+        <v>116.62456</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>200.630289</v>
+        <v>201.630289</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>278.687986</v>
+        <v>279.687986</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>264.503137</v>
+        <v>265.503137</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>233.631667</v>
+        <v>234.631667</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>235.92897</v>
+        <v>236.92897</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>115.578785</v>
+        <v>116.578785</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>97.815046</v>
+        <v>98.815046</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>203.515799</v>
+        <v>204.515799</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>195.60456</v>
+        <v>196.60456</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>116.950706</v>
+        <v>117.950706</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>33.952731</v>
+        <v>34.952731</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>32.697928</v>
+        <v>33.697928</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>39.931458</v>
+        <v>40.931458</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>228.77941</v>
+        <v>229.77941</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>115.723623</v>
+        <v>116.723623</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>13.577778</v>
+        <v>14.577778</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>63.934433</v>
+        <v>64.934433</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>264.508646</v>
+        <v>265.508646</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>185.59213</v>
+        <v>186.59213</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>194.685613</v>
+        <v>195.685613</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>124.82566</v>
+        <v>125.82566</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>266.5989</v>
+        <v>267.5989</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>123.60706</v>
+        <v>124.60706</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>202.827616</v>
+        <v>203.827616</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>111.725405</v>
+        <v>112.725405</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>230.873414</v>
+        <v>231.873414</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>238.659155</v>
+        <v>239.659155</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7451,7 +7451,7 @@
         <v>46090.58235540509</v>
       </c>
       <c r="AQ39">
-        <v>0.689595</v>
+        <v>1.689595</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7632,7 +7632,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>125.891053</v>
+        <v>126.891053</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7813,7 +7813,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>104.705301</v>
+        <v>105.705301</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -7994,7 +7994,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>63.695035</v>
+        <v>64.695035</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8172,7 +8172,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>33.954722</v>
+        <v>34.954722</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8353,7 +8353,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>53.618681</v>
+        <v>54.618681</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8534,7 +8534,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>12.718715</v>
+        <v>13.718715</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8715,7 +8715,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>187.910417</v>
+        <v>188.910417</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8896,7 +8896,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>202.827002</v>
+        <v>203.827002</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9030,7 +9030,7 @@
         <v>46090.58140600695</v>
       </c>
       <c r="AQ48">
-        <v>0.690544</v>
+        <v>1.690544</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9214,7 +9214,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>153.943773</v>
+        <v>154.943773</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9395,7 +9395,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>153.942558</v>
+        <v>154.942558</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9563,7 +9563,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>11.592813</v>
+        <v>12.592813</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9744,7 +9744,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>230.874398</v>
+        <v>231.874398</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9922,7 +9922,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>231.567905</v>
+        <v>232.567905</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10106,7 +10106,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>138.710521</v>
+        <v>139.710521</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10287,7 +10287,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>244.783391</v>
+        <v>245.783391</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10465,7 +10465,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>11.592072</v>
+        <v>12.592072</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10649,7 +10649,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>222.540926</v>
+        <v>223.540926</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10783,7 +10783,7 @@
         <v>46090.58088335648</v>
       </c>
       <c r="AQ58">
-        <v>0.691065</v>
+        <v>1.691065</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -10961,7 +10961,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>269.645579</v>
+        <v>270.645579</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11139,7 +11139,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>259.694398</v>
+        <v>260.694398</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11320,7 +11320,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>89.796944</v>
+        <v>90.796944</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11498,7 +11498,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>54.688229</v>
+        <v>55.688229</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11676,7 +11676,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>231.567072</v>
+        <v>232.567072</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11857,7 +11857,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>125.895162</v>
+        <v>126.895162</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12038,7 +12038,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>105.514803</v>
+        <v>106.514803</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12219,7 +12219,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>167.568646</v>
+        <v>168.568646</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12397,7 +12397,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>234.822755</v>
+        <v>235.822755</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12575,7 +12575,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>195.6239</v>
+        <v>196.6239</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12759,7 +12759,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>115.623773</v>
+        <v>116.623773</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -12937,7 +12937,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>53.598322</v>
+        <v>54.598322</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13115,7 +13115,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>270.938715</v>
+        <v>271.938715</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13293,7 +13293,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>273.831609</v>
+        <v>274.831609</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13471,7 +13471,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>231.582847</v>
+        <v>232.582847</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13652,7 +13652,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>188.684375</v>
+        <v>189.684375</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13830,7 +13830,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>124.720972</v>
+        <v>125.720972</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14011,7 +14011,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>131.716933</v>
+        <v>132.716933</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14192,7 +14192,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>83.84463</v>
+        <v>84.84463</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14373,7 +14373,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>88.542176</v>
+        <v>89.542176</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14554,7 +14554,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>33.773565</v>
+        <v>34.773565</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14696,7 +14696,7 @@
         <v>46076.53149964121</v>
       </c>
       <c r="AQ80">
-        <v>14.740451</v>
+        <v>15.740451</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -14882,7 +14882,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>245.654282</v>
+        <v>246.654282</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15060,7 +15060,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>182.680498</v>
+        <v>183.680498</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15241,7 +15241,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>117.607488</v>
+        <v>118.607488</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15378,7 +15378,7 @@
         <v>46090.72432047454</v>
       </c>
       <c r="AQ84">
-        <v>0.547627</v>
+        <v>1.547627</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15562,7 +15562,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>186.889144</v>
+        <v>187.889144</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15743,7 +15743,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>104.695648</v>
+        <v>105.695648</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -15924,7 +15924,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>259.697789</v>
+        <v>260.697789</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16105,7 +16105,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>153.943553</v>
+        <v>154.943553</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16283,7 +16283,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>138.858912</v>
+        <v>139.858912</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16464,7 +16464,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>133.553669</v>
+        <v>134.553669</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16645,7 +16645,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>123.605718</v>
+        <v>124.605718</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16823,7 +16823,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>238.723113</v>
+        <v>239.723113</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17001,7 +17001,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>269.597859</v>
+        <v>270.597859</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17190,7 +17190,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>217.567523</v>
+        <v>218.567523</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17371,7 +17371,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>186.887431</v>
+        <v>187.887431</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17552,7 +17552,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>167.561493</v>
+        <v>168.561493</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17733,7 +17733,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>89.806308</v>
+        <v>90.806308</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17834,7 +17834,7 @@
         <v>46076.60414643519</v>
       </c>
       <c r="AK98">
-        <v>14.667801</v>
+        <v>15.667801</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18015,7 +18015,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>223.570035</v>
+        <v>224.570035</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18193,7 +18193,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>264.502755</v>
+        <v>265.502755</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18371,7 +18371,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>173.943183</v>
+        <v>174.943183</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18549,7 +18549,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>231.566296</v>
+        <v>232.566296</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18730,7 +18730,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>63.938056</v>
+        <v>64.938056</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -18908,7 +18908,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>270.939109</v>
+        <v>271.939109</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19086,7 +19086,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>182.553773</v>
+        <v>183.553773</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19267,7 +19267,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>104.708877</v>
+        <v>105.708877</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19448,7 +19448,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>200.622951</v>
+        <v>201.622951</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19629,7 +19629,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>192.698808</v>
+        <v>193.698808</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19807,7 +19807,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>32.722593</v>
+        <v>33.722593</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -19985,7 +19985,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>266.688715</v>
+        <v>267.688715</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20166,7 +20166,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>222.685706</v>
+        <v>223.685706</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20350,7 +20350,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>161.944456</v>
+        <v>162.944456</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20531,7 +20531,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>103.723773</v>
+        <v>104.723773</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20712,7 +20712,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>221.122581</v>
+        <v>222.122581</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -20893,7 +20893,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>229.7661</v>
+        <v>230.7661</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21074,7 +21074,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>182.609722</v>
+        <v>183.609722</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21255,7 +21255,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>131.698414</v>
+        <v>132.698414</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21436,7 +21436,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>104.694329</v>
+        <v>105.694329</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21617,7 +21617,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>63.936678</v>
+        <v>64.936678</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21798,7 +21798,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>40.72397</v>
+        <v>41.72397</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -21976,7 +21976,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>273.834572</v>
+        <v>274.834572</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22154,7 +22154,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>259.645451</v>
+        <v>260.645451</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22335,7 +22335,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>269.595995</v>
+        <v>270.595995</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22516,7 +22516,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>161.942859</v>
+        <v>162.942859</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22697,7 +22697,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>115.723137</v>
+        <v>116.723137</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -22878,7 +22878,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>133.544306</v>
+        <v>134.544306</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23056,7 +23056,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>52.588542</v>
+        <v>53.588542</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23237,7 +23237,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>248.564664</v>
+        <v>249.564664</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23421,7 +23421,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>222.705718</v>
+        <v>223.705718</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23599,7 +23599,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>200.576157</v>
+        <v>201.576157</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23712,7 +23712,7 @@
         <v>46079.66128135417</v>
       </c>
       <c r="AN131">
-        <v>11.610671</v>
+        <v>12.610671</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -23893,7 +23893,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW132">
-        <v>4.596667</v>
+        <v>5.596667</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24074,7 +24074,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW133">
-        <v>186.885278</v>
+        <v>187.885278</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24187,7 +24187,7 @@
         <v>46056.35300378472</v>
       </c>
       <c r="AN134">
-        <v>34.918947</v>
+        <v>35.918947</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24365,7 +24365,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW135">
-        <v>264.503368</v>
+        <v>265.503368</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24546,7 +24546,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW136">
-        <v>104.695752</v>
+        <v>105.695752</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -24727,7 +24727,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW137">
-        <v>88.54288200000001</v>
+        <v>89.54288200000001</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -24900,7 +24900,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW138">
-        <v>259.597963</v>
+        <v>260.597963</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25081,7 +25081,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW139">
-        <v>89.798391</v>
+        <v>90.798391</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25262,7 +25262,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW140">
-        <v>18.675081</v>
+        <v>19.675081</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25443,7 +25443,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW141">
-        <v>173.805532</v>
+        <v>174.805532</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25624,7 +25624,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW142">
-        <v>167.956944</v>
+        <v>168.956944</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -25802,7 +25802,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW143">
-        <v>277.647986</v>
+        <v>278.647986</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -25980,7 +25980,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW144">
-        <v>203.488345</v>
+        <v>204.488345</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26161,7 +26161,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW145">
-        <v>161.942315</v>
+        <v>162.942315</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26337,7 +26337,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW146">
-        <v>97.814815</v>
+        <v>98.814815</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26518,7 +26518,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW147">
-        <v>31.835752</v>
+        <v>32.835752</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -26696,7 +26696,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW148">
-        <v>259.648657</v>
+        <v>260.648657</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -26874,7 +26874,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW149">
-        <v>264.505023</v>
+        <v>265.505023</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27008,7 +27008,7 @@
         <v>46090.5815483912</v>
       </c>
       <c r="AQ150">
-        <v>0.690405</v>
+        <v>1.690405</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27189,7 +27189,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW151">
-        <v>200.685648</v>
+        <v>201.685648</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27367,7 +27367,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW152">
-        <v>234.822326</v>
+        <v>235.822326</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27545,7 +27545,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW153">
-        <v>231.566794</v>
+        <v>232.566794</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -27726,7 +27726,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW154">
-        <v>194.686644</v>
+        <v>195.686644</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -27907,7 +27907,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW155">
-        <v>53.604826</v>
+        <v>54.604826</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28088,7 +28088,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW156">
-        <v>166.818819</v>
+        <v>167.818819</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28269,7 +28269,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW157">
-        <v>166.618877</v>
+        <v>167.618877</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28447,7 +28447,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW158">
-        <v>33.951863</v>
+        <v>34.951863</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -28631,7 +28631,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW159">
-        <v>89.805938</v>
+        <v>90.805938</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -28812,7 +28812,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW160">
-        <v>188.517014</v>
+        <v>189.517014</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29001,7 +29001,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW161">
-        <v>178.582245</v>
+        <v>179.582245</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29169,7 +29169,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW162">
-        <v>208.652419</v>
+        <v>209.652419</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29350,7 +29350,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW163">
-        <v>161.94162</v>
+        <v>162.94162</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29531,7 +29531,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW164">
-        <v>105.515463</v>
+        <v>106.515463</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -29712,7 +29712,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW165">
-        <v>46.628484</v>
+        <v>47.628484</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -29893,7 +29893,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW166">
-        <v>230.874201</v>
+        <v>231.874201</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30074,7 +30074,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW167">
-        <v>186.890891</v>
+        <v>187.890891</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30255,7 +30255,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW168">
-        <v>110.538414</v>
+        <v>111.538414</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30433,7 +30433,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW169">
-        <v>33.956308</v>
+        <v>34.956308</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30611,7 +30611,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW170">
-        <v>220.897014</v>
+        <v>221.897014</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -30792,7 +30792,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW171">
-        <v>136.643461</v>
+        <v>137.643461</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -30970,7 +30970,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW172">
-        <v>104.692674</v>
+        <v>105.692674</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31151,7 +31151,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW173">
-        <v>4.597697</v>
+        <v>5.597697</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31329,7 +31329,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW174">
-        <v>269.598796</v>
+        <v>270.598796</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31510,7 +31510,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW175">
-        <v>245.949097</v>
+        <v>246.949097</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -31688,7 +31688,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW176">
-        <v>54.679653</v>
+        <v>55.679653</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -31866,7 +31866,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW177">
-        <v>27.724954</v>
+        <v>28.724954</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32039,7 +32039,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW178">
-        <v>185.591921</v>
+        <v>186.591921</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32220,7 +32220,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW179">
-        <v>63.936076</v>
+        <v>64.936076</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32398,7 +32398,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW180">
-        <v>13.571563</v>
+        <v>14.571563</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32576,7 +32576,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW181">
-        <v>220.901956</v>
+        <v>221.901956</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -32754,7 +32754,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW182">
-        <v>273.834965</v>
+        <v>274.834965</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -32932,7 +32932,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW183">
-        <v>195.603032</v>
+        <v>196.603032</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33110,7 +33110,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW184">
-        <v>266.598345</v>
+        <v>267.598345</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33288,7 +33288,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW185">
-        <v>257.705185</v>
+        <v>258.705185</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33466,7 +33466,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW186">
-        <v>195.623785</v>
+        <v>196.623785</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -33647,7 +33647,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW187">
-        <v>124.72081</v>
+        <v>125.72081</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -33789,7 +33789,7 @@
         <v>46076.53159934028</v>
       </c>
       <c r="AQ188">
-        <v>14.740347</v>
+        <v>15.740347</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -33967,7 +33967,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW189">
-        <v>266.597986</v>
+        <v>267.597986</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34148,7 +34148,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW190">
-        <v>222.701528</v>
+        <v>223.701528</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34329,7 +34329,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW191">
-        <v>167.956227</v>
+        <v>168.956227</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34510,7 +34510,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW192">
-        <v>200.515938</v>
+        <v>201.515938</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -34691,7 +34691,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW193">
-        <v>111.669282</v>
+        <v>112.669282</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -34869,7 +34869,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW194">
-        <v>33.954282</v>
+        <v>34.954282</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35047,7 +35047,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW195">
-        <v>273.842535</v>
+        <v>274.842535</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35215,7 +35215,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW196">
-        <v>208.664606</v>
+        <v>209.664606</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35396,7 +35396,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW197">
-        <v>186.888403</v>
+        <v>187.888403</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35580,7 +35580,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW198">
-        <v>167.959769</v>
+        <v>168.959769</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -35764,7 +35764,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW199">
-        <v>222.705347</v>
+        <v>223.705347</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -35945,7 +35945,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW200">
-        <v>89.797708</v>
+        <v>90.797708</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36123,7 +36123,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW201">
-        <v>266.688993</v>
+        <v>267.688993</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36301,7 +36301,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW202">
-        <v>280.909826</v>
+        <v>281.909826</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36482,7 +36482,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW203">
-        <v>186.894248</v>
+        <v>187.894248</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -36660,7 +36660,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW204">
-        <v>160.681644</v>
+        <v>161.681644</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -36841,7 +36841,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW205">
-        <v>253.925532</v>
+        <v>254.925532</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37019,7 +37019,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW206">
-        <v>264.503935</v>
+        <v>265.503935</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37197,7 +37197,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW207">
-        <v>192.607488</v>
+        <v>193.607488</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37375,7 +37375,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW208">
-        <v>17.60419</v>
+        <v>18.60419</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37556,7 +37556,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW209">
-        <v>248.561505</v>
+        <v>249.561505</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -37737,7 +37737,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW210">
-        <v>196.530926</v>
+        <v>197.530926</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -37915,7 +37915,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW211">
-        <v>54.685266</v>
+        <v>55.685266</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38093,7 +38093,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW212">
-        <v>269.57213</v>
+        <v>270.57213</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38206,7 +38206,7 @@
         <v>46079.66134925926</v>
       </c>
       <c r="AN213">
-        <v>11.610602</v>
+        <v>12.610602</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38384,7 +38384,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW214">
-        <v>266.688449</v>
+        <v>267.688449</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -38562,7 +38562,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW215">
-        <v>0.541829</v>
+        <v>1.541829</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -38740,7 +38740,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW216">
-        <v>265.610671</v>
+        <v>266.610671</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -38918,7 +38918,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW217">
-        <v>277.593252</v>
+        <v>278.593252</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39096,7 +39096,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW218">
-        <v>279.733646</v>
+        <v>280.733646</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39274,7 +39274,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW219">
-        <v>269.646829</v>
+        <v>270.646829</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39452,7 +39452,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW220">
-        <v>231.568519</v>
+        <v>232.568519</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -39633,7 +39633,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW221">
-        <v>231.586493</v>
+        <v>232.586493</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -39814,7 +39814,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW222">
-        <v>136.911528</v>
+        <v>137.911528</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -39956,7 +39956,7 @@
         <v>46076.53141864583</v>
       </c>
       <c r="AQ223">
-        <v>14.740532</v>
+        <v>15.740532</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40134,7 +40134,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW224">
-        <v>278.68897</v>
+        <v>279.68897</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40312,7 +40312,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW225">
-        <v>269.587894</v>
+        <v>270.587894</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -40490,7 +40490,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW226">
-        <v>278.684838</v>
+        <v>279.684838</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -40671,7 +40671,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW227">
-        <v>179.639144</v>
+        <v>180.639144</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -40852,7 +40852,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW228">
-        <v>111.693438</v>
+        <v>112.693438</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41033,7 +41033,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW229">
-        <v>104.711586</v>
+        <v>105.711586</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41214,7 +41214,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW230">
-        <v>39.933079</v>
+        <v>40.933079</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41395,7 +41395,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW231">
-        <v>39.934757</v>
+        <v>40.934757</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -41576,7 +41576,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW232">
-        <v>186.8936</v>
+        <v>187.8936</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -41757,7 +41757,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW233">
-        <v>238.659074</v>
+        <v>239.659074</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -41935,7 +41935,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW234">
-        <v>255.900382</v>
+        <v>256.900382</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42116,7 +42116,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW235">
-        <v>195.669988</v>
+        <v>196.669988</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42300,7 +42300,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW236">
-        <v>187.910185</v>
+        <v>188.910185</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42481,7 +42481,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW237">
-        <v>167.958079</v>
+        <v>168.958079</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -42659,7 +42659,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW238">
-        <v>118.886944</v>
+        <v>119.886944</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -42840,7 +42840,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW239">
-        <v>4.595556</v>
+        <v>5.595556</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43021,7 +43021,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW240">
-        <v>230.874734</v>
+        <v>231.874734</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43202,7 +43202,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW241">
-        <v>186.753194</v>
+        <v>187.753194</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43383,7 +43383,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW242">
-        <v>89.798935</v>
+        <v>90.798935</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -43561,7 +43561,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW243">
-        <v>54.6786</v>
+        <v>55.6786</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -43742,7 +43742,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW244">
-        <v>105.515961</v>
+        <v>106.515961</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -43923,7 +43923,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW245">
-        <v>220.900729</v>
+        <v>221.900729</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44096,7 +44096,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW246">
-        <v>266.573229</v>
+        <v>267.573229</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44274,7 +44274,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW247">
-        <v>231.567303</v>
+        <v>232.567303</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44458,7 +44458,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW248">
-        <v>195.601377</v>
+        <v>196.601377</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -44639,7 +44639,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW249">
-        <v>138.855961</v>
+        <v>139.855961</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -44823,7 +44823,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW250">
-        <v>167.660845</v>
+        <v>168.660845</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45004,7 +45004,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW251">
-        <v>161.940741</v>
+        <v>162.940741</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45185,7 +45185,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW252">
-        <v>12.719549</v>
+        <v>13.719549</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45363,7 +45363,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW253">
-        <v>231.567708</v>
+        <v>232.567708</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -45544,7 +45544,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW254">
-        <v>202.828241</v>
+        <v>203.828241</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -45725,7 +45725,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW255">
-        <v>39.678426</v>
+        <v>40.678426</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -45906,7 +45906,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW256">
-        <v>251.720903</v>
+        <v>252.720903</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46087,7 +46087,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW257">
-        <v>40.724387</v>
+        <v>41.724387</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46188,7 +46188,7 @@
         <v>46076.60415833333</v>
       </c>
       <c r="AK258">
-        <v>14.667789</v>
+        <v>15.667789</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46289,7 +46289,7 @@
         <v>46076.70991956018</v>
       </c>
       <c r="AK259">
-        <v>14.562025</v>
+        <v>15.562025</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46470,7 +46470,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW260">
-        <v>63.935359</v>
+        <v>64.93535900000001</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -46651,7 +46651,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW261">
-        <v>230.835313</v>
+        <v>231.835313</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -46829,7 +46829,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW262">
-        <v>161.950486</v>
+        <v>162.950486</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47010,7 +47010,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW263">
-        <v>161.948333</v>
+        <v>162.948333</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47188,7 +47188,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW264">
-        <v>136.532882</v>
+        <v>137.532882</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47364,7 +47364,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW265">
-        <v>228.779572</v>
+        <v>229.779572</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -47542,7 +47542,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW266">
-        <v>152.939051</v>
+        <v>153.939051</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -47726,7 +47726,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW267">
-        <v>138.711273</v>
+        <v>139.711273</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -47904,7 +47904,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW268">
-        <v>87.70796300000001</v>
+        <v>88.70796300000001</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48085,7 +48085,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW269">
-        <v>259.698009</v>
+        <v>260.698009</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48263,7 +48263,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW270">
-        <v>269.646088</v>
+        <v>270.646088</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48444,7 +48444,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW271">
-        <v>248.561852</v>
+        <v>249.561852</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -48625,7 +48625,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW272">
-        <v>124.720706</v>
+        <v>125.720706</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -48803,7 +48803,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW273">
-        <v>138.712083</v>
+        <v>139.712083</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -48984,7 +48984,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW274">
-        <v>104.695475</v>
+        <v>105.695475</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49165,7 +49165,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW275">
-        <v>248.562396</v>
+        <v>249.562396</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49343,7 +49343,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW276">
-        <v>167.952477</v>
+        <v>168.952477</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -49527,7 +49527,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW277">
-        <v>119.699317</v>
+        <v>120.699317</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -49708,7 +49708,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW278">
-        <v>258.591204</v>
+        <v>259.591204</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -49889,7 +49889,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW279">
-        <v>173.806725</v>
+        <v>174.806725</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50070,7 +50070,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW280">
-        <v>104.712245</v>
+        <v>105.712245</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50251,7 +50251,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW281">
-        <v>125.893333</v>
+        <v>126.893333</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50432,7 +50432,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW282">
-        <v>244.783194</v>
+        <v>245.783194</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -50639,7 +50639,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW283">
-        <v>124.826389</v>
+        <v>125.826389</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -50817,7 +50817,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW284">
-        <v>115.622396</v>
+        <v>116.622396</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -50998,7 +50998,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW285">
-        <v>98.65510399999999</v>
+        <v>99.65510399999999</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51182,7 +51182,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW286">
-        <v>153.942477</v>
+        <v>154.942477</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51316,7 +51316,7 @@
         <v>46090.58126142361</v>
       </c>
       <c r="AQ287">
-        <v>0.690694</v>
+        <v>1.690694</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -51494,7 +51494,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW288">
-        <v>245.949468</v>
+        <v>246.949468</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -51672,7 +51672,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW289">
-        <v>257.706134</v>
+        <v>258.706134</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -51850,7 +51850,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW290">
-        <v>220.901794</v>
+        <v>221.901794</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52031,7 +52031,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW291">
-        <v>200.629861</v>
+        <v>201.629861</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52215,7 +52215,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW292">
-        <v>141.95728</v>
+        <v>142.95728</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52396,7 +52396,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW293">
-        <v>119.692975</v>
+        <v>120.692975</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -52577,7 +52577,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW294">
-        <v>244.911863</v>
+        <v>245.911863</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -52755,7 +52755,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW295">
-        <v>258.911065</v>
+        <v>259.911065</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -52936,7 +52936,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW296">
-        <v>203.518958</v>
+        <v>204.518958</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53114,7 +53114,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW297">
-        <v>264.501968</v>
+        <v>265.501968</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53295,7 +53295,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW298">
-        <v>186.894815</v>
+        <v>187.894815</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -53309,7 +53309,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -53329,7 +53329,7 @@
         <v>46045.58498351852</v>
       </c>
       <c r="J299" s="2">
-        <v>46090.72899315972</v>
+        <v>46091.62691195602</v>
       </c>
       <c r="M299" s="2">
         <v>46075.58498351852</v>
@@ -53405,6 +53405,21 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.aspbfo3qvjqw</t>
         </is>
       </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
+        </is>
+      </c>
       <c r="AF299" t="inlineStr">
         <is>
           <t>Gestão</t>
@@ -53431,8 +53446,17 @@
       <c r="AO299" s="2">
         <v>46090.72898921296</v>
       </c>
+      <c r="AP299" s="2">
+        <v>46091.62691219908</v>
+      </c>
       <c r="AQ299">
-        <v>0.542963</v>
+        <v>0.897917</v>
+      </c>
+      <c r="AR299" s="2">
+        <v>46091.62691277778</v>
+      </c>
+      <c r="AT299">
+        <v>0.645035</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -53613,7 +53637,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW300">
-        <v>104.563704</v>
+        <v>105.563704</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -53791,7 +53815,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW301">
-        <v>231.569641</v>
+        <v>232.569641</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -53925,7 +53949,7 @@
         <v>46090.58068733796</v>
       </c>
       <c r="AQ302">
-        <v>0.691262</v>
+        <v>1.691262</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54114,7 +54138,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW303">
-        <v>255.900845</v>
+        <v>256.900845</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54295,7 +54319,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW304">
-        <v>186.887685</v>
+        <v>187.887685</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -54473,7 +54497,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW305">
-        <v>161.699155</v>
+        <v>162.699155</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -54654,7 +54678,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW306">
-        <v>83.84487300000001</v>
+        <v>84.84487300000001</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -54840,7 +54864,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW307">
-        <v>196.660625</v>
+        <v>197.660625</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55018,7 +55042,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW308">
-        <v>270.940567</v>
+        <v>271.940567</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55199,7 +55223,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW309">
-        <v>160.612778</v>
+        <v>161.612778</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -55380,7 +55404,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW310">
-        <v>115.722986</v>
+        <v>116.722986</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -55561,7 +55585,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW311">
-        <v>89.810451</v>
+        <v>90.810451</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -55742,7 +55766,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW312">
-        <v>63.937188</v>
+        <v>64.93718800000001</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -55923,7 +55947,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW313">
-        <v>160.611343</v>
+        <v>161.611343</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56104,7 +56128,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW314">
-        <v>160.613113</v>
+        <v>161.613113</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56205,7 +56229,7 @@
         <v>46076.70818526621</v>
       </c>
       <c r="AK315">
-        <v>14.563762</v>
+        <v>15.563762</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -56383,7 +56407,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW316">
-        <v>264.50235</v>
+        <v>265.50235</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -56561,7 +56585,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW317">
-        <v>33.958588</v>
+        <v>34.958588</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -56742,16 +56766,16 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW318">
-        <v>217.564039</v>
+        <v>218.564039</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319">
-        <v>1210318748</v>
+        <v>1289597864</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Curso: Pós Corte Online Turma: 21 Disciplina: Princípios da gestão eficiente Tópico: Gestão economico-financeira em fazendas Professor: Guilherme Campos De Arruda LamegoData: 45980</t>
+          <t>Curso: Pós Gestão Fazendas Online Turma: 1 Disciplina: Aplicação de ferramentas e métodos de gestão Tópico: Gestão da rotina de trabalho do dia a dia, qualidade, metas e rituais de gestão Professor: Rafael Silva Alves de OliveiraTipo de Conteúdo: Onli</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -56761,11 +56785,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Reprovado na Validação</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="E319" s="2">
-        <v>45979.875</v>
+        <v>46077.87559027778</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -56773,16 +56797,13 @@
         </is>
       </c>
       <c r="H319" s="2">
-        <v>45954.62754259259</v>
+        <v>46077.70090876157</v>
       </c>
       <c r="I319" s="2">
-        <v>45908.53443530093</v>
+        <v>46050.61468201389</v>
       </c>
       <c r="J319" s="2">
-        <v>45954.62754267361</v>
-      </c>
-      <c r="M319" s="2">
-        <v>45938.53443530093</v>
+        <v>46077.70090884259</v>
       </c>
       <c r="N319" t="b">
         <v>0</v>
@@ -56794,65 +56815,65 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Guilherme Campos De Arruda Lamego</t>
+          <t>Rafael Silva Alves de Oliveira</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>Curso: Pós Corte Online Turma: 21 Disciplina: Princípios da gestão eficiente Tópico: Gestão economico-financeira em fazendas Professor: Guilherme Campos De Arruda LamegoData: 45980</t>
+          <t>Curso: Pós Gestão Fazendas Online Turma: 1 Disciplina: Aplicação de ferramentas e métodos de gestão Tópico: Gestão da rotina de trabalho do dia a dia, qualidade, metas e rituais de gestão Professor: Rafael Silva Alves de OliveiraTipo de Conteúdo: Onli</t>
         </is>
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>Pós Corte Online</t>
+          <t>Pós Gestão Fazendas Online</t>
         </is>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>Princípios da gestão eficiente</t>
+          <t>Aplicação de ferramentas e métodos de gestão</t>
         </is>
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>Gestão economico-financeira em fazendas</t>
+          <t>Gestão da rotina de trabalho do dia a dia, qualidade, metas e rituais de gestão</t>
         </is>
       </c>
       <c r="X319" s="2">
-        <v>45979.875</v>
+        <v>46077.87559027778</v>
       </c>
       <c r="Y319" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>https://rehagro.instructure.com/courses/2941/modules</t>
+          <t>https://rehagro.instructure.com/courses/2974</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1xcQZxZVIuqxticMYNr2yoDazsNBgfX4BPdfry9LsfBo/edit?tab=t.19lbzndilb0h</t>
+          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.a7jzuflcbwlc</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -56872,67 +56893,67 @@
       </c>
       <c r="AF319" t="inlineStr">
         <is>
-          <t>Reprovado na Validação</t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="AG319" t="inlineStr">
         <is>
-          <t>01:47:00</t>
+          <t>01:49:00</t>
         </is>
       </c>
       <c r="AH319">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AI319" s="2">
-        <v>45908.53444015046</v>
+        <v>46050.61468837963</v>
       </c>
       <c r="AJ319" s="2">
-        <v>45947.59307728009</v>
+        <v>46072.42328466436</v>
       </c>
       <c r="AK319">
-        <v>39.058634</v>
+        <v>21.808588</v>
       </c>
       <c r="AL319" s="2">
-        <v>45947.59307776621</v>
+        <v>46072.42328561343</v>
       </c>
       <c r="AM319" s="2">
-        <v>45952.56312944445</v>
+        <v>46076.34390538195</v>
       </c>
       <c r="AN319">
-        <v>1.110625</v>
+        <v>3.920613</v>
       </c>
       <c r="AO319" s="2">
-        <v>45947.59427358797</v>
+        <v>46076.34390559028</v>
       </c>
       <c r="AP319" s="2">
-        <v>45952.67415577546</v>
+        <v>46077.68847505787</v>
       </c>
       <c r="AQ319">
-        <v>3.97044</v>
+        <v>1.34456</v>
       </c>
       <c r="AR319" s="2">
-        <v>45952.67415603009</v>
+        <v>46077.68847538195</v>
       </c>
       <c r="AS319" s="2">
-        <v>45954.62754299769</v>
+        <v>46077.70090915509</v>
       </c>
       <c r="AT319">
-        <v>1.95338</v>
+        <v>0.012431</v>
       </c>
       <c r="AU319" s="2">
-        <v>45954.62754329861</v>
+        <v>46077.70090952546</v>
       </c>
       <c r="AW319">
-        <v>136.64441</v>
+        <v>14.571042</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320">
-        <v>1289597864</v>
+        <v>1210318748</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Curso: Pós Gestão Fazendas Online Turma: 1 Disciplina: Aplicação de ferramentas e métodos de gestão Tópico: Gestão da rotina de trabalho do dia a dia, qualidade, metas e rituais de gestão Professor: Rafael Silva Alves de OliveiraTipo de Conteúdo: Onli</t>
+          <t>Curso: Pós Corte Online Turma: 21 Disciplina: Princípios da gestão eficiente Tópico: Gestão economico-financeira em fazendas Professor: Guilherme Campos De Arruda LamegoData: 45980</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -56942,11 +56963,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="E320" s="2">
-        <v>46077.87559027778</v>
+        <v>45979.875</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -56954,13 +56975,16 @@
         </is>
       </c>
       <c r="H320" s="2">
-        <v>46077.70090876157</v>
+        <v>45954.62754259259</v>
       </c>
       <c r="I320" s="2">
-        <v>46050.61468201389</v>
+        <v>45908.53443530093</v>
       </c>
       <c r="J320" s="2">
-        <v>46077.70090884259</v>
+        <v>45954.62754267361</v>
+      </c>
+      <c r="M320" s="2">
+        <v>45938.53443530093</v>
       </c>
       <c r="N320" t="b">
         <v>0</v>
@@ -56972,65 +56996,65 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Rafael Silva Alves de Oliveira</t>
+          <t>Guilherme Campos De Arruda Lamego</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Corte</t>
         </is>
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>Curso: Pós Gestão Fazendas Online Turma: 1 Disciplina: Aplicação de ferramentas e métodos de gestão Tópico: Gestão da rotina de trabalho do dia a dia, qualidade, metas e rituais de gestão Professor: Rafael Silva Alves de OliveiraTipo de Conteúdo: Onli</t>
+          <t>Curso: Pós Corte Online Turma: 21 Disciplina: Princípios da gestão eficiente Tópico: Gestão economico-financeira em fazendas Professor: Guilherme Campos De Arruda LamegoData: 45980</t>
         </is>
       </c>
       <c r="T320" t="inlineStr">
         <is>
-          <t>Pós Gestão Fazendas Online</t>
+          <t>Pós Corte Online</t>
         </is>
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>Aplicação de ferramentas e métodos de gestão</t>
+          <t>Princípios da gestão eficiente</t>
         </is>
       </c>
       <c r="W320" t="inlineStr">
         <is>
-          <t>Gestão da rotina de trabalho do dia a dia, qualidade, metas e rituais de gestão</t>
+          <t>Gestão economico-financeira em fazendas</t>
         </is>
       </c>
       <c r="X320" s="2">
-        <v>46077.87559027778</v>
+        <v>45979.875</v>
       </c>
       <c r="Y320" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>https://rehagro.instructure.com/courses/2974</t>
+          <t>https://rehagro.instructure.com/courses/2941/modules</t>
         </is>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.a7jzuflcbwlc</t>
+          <t>https://docs.google.com/document/d/1xcQZxZVIuqxticMYNr2yoDazsNBgfX4BPdfry9LsfBo/edit?tab=t.19lbzndilb0h</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -57050,58 +57074,58 @@
       </c>
       <c r="AF320" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="AG320" t="inlineStr">
         <is>
-          <t>01:49:00</t>
+          <t>01:47:00</t>
         </is>
       </c>
       <c r="AH320">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AI320" s="2">
-        <v>46050.61468837963</v>
+        <v>45908.53444015046</v>
       </c>
       <c r="AJ320" s="2">
-        <v>46072.42328466436</v>
+        <v>45947.59307728009</v>
       </c>
       <c r="AK320">
-        <v>21.808588</v>
+        <v>39.058634</v>
       </c>
       <c r="AL320" s="2">
-        <v>46072.42328561343</v>
+        <v>45947.59307776621</v>
       </c>
       <c r="AM320" s="2">
-        <v>46076.34390538195</v>
+        <v>45952.56312944445</v>
       </c>
       <c r="AN320">
-        <v>3.920613</v>
+        <v>1.110625</v>
       </c>
       <c r="AO320" s="2">
-        <v>46076.34390559028</v>
+        <v>45947.59427358797</v>
       </c>
       <c r="AP320" s="2">
-        <v>46077.68847505787</v>
+        <v>45952.67415577546</v>
       </c>
       <c r="AQ320">
-        <v>1.34456</v>
+        <v>3.97044</v>
       </c>
       <c r="AR320" s="2">
-        <v>46077.68847538195</v>
+        <v>45952.67415603009</v>
       </c>
       <c r="AS320" s="2">
-        <v>46077.70090915509</v>
+        <v>45954.62754299769</v>
       </c>
       <c r="AT320">
-        <v>0.012431</v>
+        <v>1.95338</v>
       </c>
       <c r="AU320" s="2">
-        <v>46077.70090952546</v>
+        <v>45954.62754329861</v>
       </c>
       <c r="AW320">
-        <v>13.571042</v>
+        <v>137.64441</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57235,7 +57259,7 @@
         <v>46090.58107568287</v>
       </c>
       <c r="AQ321">
-        <v>0.69088</v>
+        <v>1.69088</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -57249,7 +57273,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -57269,7 +57293,7 @@
         <v>46045.58499030092</v>
       </c>
       <c r="J322" s="2">
-        <v>46090.72972653935</v>
+        <v>46091.62671137732</v>
       </c>
       <c r="M322" s="2">
         <v>46075.58499030092</v>
@@ -57345,6 +57369,21 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.aspbfo3qvjqw</t>
         </is>
       </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
+        </is>
+      </c>
       <c r="AF322" t="inlineStr">
         <is>
           <t>Gestão</t>
@@ -57371,8 +57410,17 @@
       <c r="AO322" s="2">
         <v>46090.72972311343</v>
       </c>
+      <c r="AP322" s="2">
+        <v>46091.62671181713</v>
+      </c>
       <c r="AQ322">
-        <v>0.542222</v>
+        <v>0.896979</v>
+      </c>
+      <c r="AR322" s="2">
+        <v>46091.62671216435</v>
+      </c>
+      <c r="AT322">
+        <v>0.645243</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -57553,7 +57601,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW323">
-        <v>217.566829</v>
+        <v>218.566829</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -57734,7 +57782,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW324">
-        <v>230.872072</v>
+        <v>231.872072</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -57912,7 +57960,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW325">
-        <v>39.601979</v>
+        <v>40.601979</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58090,7 +58138,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW326">
-        <v>273.835417</v>
+        <v>274.835417</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -58271,7 +58319,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW327">
-        <v>167.95162</v>
+        <v>168.95162</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -58449,7 +58497,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW328">
-        <v>131.661701</v>
+        <v>132.661701</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -58630,7 +58678,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW329">
-        <v>119.696956</v>
+        <v>120.696956</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -58811,7 +58859,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW330">
-        <v>252.609468</v>
+        <v>253.609468</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -58992,7 +59040,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW331">
-        <v>207.668484</v>
+        <v>208.668484</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59173,7 +59221,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW332">
-        <v>89.81197899999999</v>
+        <v>90.81197899999999</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -59354,7 +59402,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW333">
-        <v>48.814595</v>
+        <v>49.814595</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -59532,7 +59580,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW334">
-        <v>200.575856</v>
+        <v>201.575856</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -59716,7 +59764,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW335">
-        <v>146.586574</v>
+        <v>147.586574</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -59894,7 +59942,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW336">
-        <v>231.56897</v>
+        <v>232.56897</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60075,7 +60123,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW337">
-        <v>125.889549</v>
+        <v>126.889549</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -60256,7 +60304,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW338">
-        <v>115.622824</v>
+        <v>116.622824</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -60434,7 +60482,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW339">
-        <v>210.593449</v>
+        <v>211.593449</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -60615,7 +60663,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW340">
-        <v>56.575313</v>
+        <v>57.575313</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -60796,7 +60844,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW341">
-        <v>202.824884</v>
+        <v>203.824884</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -60972,7 +61020,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW342">
-        <v>136.643924</v>
+        <v>137.643924</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61073,7 +61121,7 @@
         <v>46076.60422097222</v>
       </c>
       <c r="AK343">
-        <v>14.667731</v>
+        <v>15.667731</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -61113,7 +61161,7 @@
         <v>46080.60364699074</v>
       </c>
       <c r="N344" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -61210,7 +61258,7 @@
         <v>46079.38060059027</v>
       </c>
       <c r="AQ344">
-        <v>11.891354</v>
+        <v>12.891354</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -61388,7 +61436,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW345">
-        <v>278.693796</v>
+        <v>279.693796</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -61569,7 +61617,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW346">
-        <v>188.892766</v>
+        <v>189.892766</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -61750,7 +61798,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW347">
-        <v>167.958981</v>
+        <v>168.958981</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -61931,7 +61979,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW348">
-        <v>117.607002</v>
+        <v>118.607002</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62112,7 +62160,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW349">
-        <v>235.932141</v>
+        <v>236.932141</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -62293,7 +62341,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW350">
-        <v>33.77287</v>
+        <v>34.77287</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -62474,7 +62522,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW351">
-        <v>14.945313</v>
+        <v>15.945313</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -62655,7 +62703,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW352">
-        <v>98.65571799999999</v>
+        <v>99.65571799999999</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -62833,7 +62881,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW353">
-        <v>192.652523</v>
+        <v>193.652523</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63014,7 +63062,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW354">
-        <v>171.591042</v>
+        <v>172.591042</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -63192,7 +63240,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW355">
-        <v>136.645035</v>
+        <v>137.645035</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -63373,7 +63421,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW356">
-        <v>117.608229</v>
+        <v>118.608229</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -63554,7 +63602,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW357">
-        <v>244.912083</v>
+        <v>245.912083</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -63735,7 +63783,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW358">
-        <v>173.806273</v>
+        <v>174.806273</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -63916,7 +63964,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW359">
-        <v>161.939977</v>
+        <v>162.939977</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64097,7 +64145,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW360">
-        <v>168.012488</v>
+        <v>169.012488</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -64278,7 +64326,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW361">
-        <v>103.727234</v>
+        <v>104.727234</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -64459,7 +64507,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW362">
-        <v>53.606424</v>
+        <v>54.606424</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -64640,7 +64688,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW363">
-        <v>269.596701</v>
+        <v>270.596701</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -64818,7 +64866,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW364">
-        <v>270.938877</v>
+        <v>271.938877</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -64999,7 +65047,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW365">
-        <v>84.726169</v>
+        <v>85.726169</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -65180,7 +65228,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW366">
-        <v>39.740486</v>
+        <v>40.740486</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -65358,7 +65406,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW367">
-        <v>277.587546</v>
+        <v>278.587546</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -65539,7 +65587,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW368">
-        <v>167.960197</v>
+        <v>168.960197</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -65717,7 +65765,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW369">
-        <v>87.707882</v>
+        <v>88.707882</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -65898,7 +65946,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW370">
-        <v>248.562917</v>
+        <v>249.562917</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66079,7 +66127,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW371">
-        <v>138.857465</v>
+        <v>139.857465</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -66260,7 +66308,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW372">
-        <v>136.8925</v>
+        <v>137.8925</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -66438,7 +66486,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW373">
-        <v>264.501701</v>
+        <v>265.501701</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -66619,7 +66667,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW374">
-        <v>235.929456</v>
+        <v>236.929456</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -66797,7 +66845,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW375">
-        <v>154.529653</v>
+        <v>155.529653</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -66913,7 +66961,7 @@
         <v>46077.71026703704</v>
       </c>
       <c r="AN376">
-        <v>11.610671</v>
+        <v>12.610671</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67091,7 +67139,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW377">
-        <v>238.722014</v>
+        <v>239.722014</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -67272,7 +67320,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW378">
-        <v>186.889039</v>
+        <v>187.889039</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -67306,13 +67354,13 @@
         <v>46045.58497321759</v>
       </c>
       <c r="J379" s="2">
-        <v>46090.40562921297</v>
+        <v>46091.40575797453</v>
       </c>
       <c r="M379" s="2">
         <v>46075.58497321759</v>
       </c>
       <c r="N379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O379" t="inlineStr">
         <is>
@@ -67433,7 +67481,7 @@
         <v>46090.40563063657</v>
       </c>
       <c r="AT379">
-        <v>0.866319</v>
+        <v>1.866319</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -67611,7 +67659,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW380">
-        <v>273.727454</v>
+        <v>274.727454</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -67789,7 +67837,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW381">
-        <v>269.63331</v>
+        <v>270.63331</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -67970,7 +68018,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW382">
-        <v>117.613623</v>
+        <v>118.613623</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -68148,7 +68196,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW383">
-        <v>270.939676</v>
+        <v>271.939676</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -68326,7 +68374,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW384">
-        <v>248.563438</v>
+        <v>249.563438</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -68504,7 +68552,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW385">
-        <v>278.685197</v>
+        <v>279.685197</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -68682,7 +68730,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW386">
-        <v>126.621574</v>
+        <v>127.621574</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -68860,7 +68908,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW387">
-        <v>264.500231</v>
+        <v>265.500231</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69038,7 +69086,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW388">
-        <v>231.566111</v>
+        <v>232.566111</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -69219,7 +69267,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW389">
-        <v>222.698738</v>
+        <v>223.698738</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -69400,7 +69448,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW390">
-        <v>138.856782</v>
+        <v>139.856782</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -69581,7 +69629,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW391">
-        <v>83.843715</v>
+        <v>84.843715</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -69762,7 +69810,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW392">
-        <v>89.810903</v>
+        <v>90.810903</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -69935,7 +69983,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW393">
-        <v>185.592269</v>
+        <v>186.592269</v>
       </c>
     </row>
     <row r="394" ht="18" customHeight="1">
@@ -70108,7 +70156,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW394">
-        <v>185.591806</v>
+        <v>186.591806</v>
       </c>
     </row>
     <row r="395" ht="18" customHeight="1">
@@ -70289,7 +70337,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW395">
-        <v>89.80932900000001</v>
+        <v>90.80932900000001</v>
       </c>
     </row>
     <row r="396" ht="18" customHeight="1">
@@ -70470,7 +70518,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW396">
-        <v>104.70985</v>
+        <v>105.70985</v>
       </c>
     </row>
     <row r="397" ht="18" customHeight="1">
@@ -70651,7 +70699,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW397">
-        <v>117.607211</v>
+        <v>118.607211</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>276.834282</v>
+        <v>279.834294</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1025,7 +1025,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW3">
-        <v>107.708322</v>
+        <v>110.708333</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW4">
-        <v>119.950278</v>
+        <v>122.950289</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>231.779942</v>
+        <v>234.779954</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>234.566493</v>
+        <v>237.566505</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>42.934039</v>
+        <v>45.934051</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>269.603993</v>
+        <v>272.604005</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>218.64463</v>
+        <v>221.644641</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>202.727917</v>
+        <v>205.727928</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>118.62456</v>
+        <v>121.624572</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>203.630289</v>
+        <v>206.630301</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>281.687986</v>
+        <v>284.687998</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>267.503137</v>
+        <v>270.503148</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>236.631667</v>
+        <v>239.631678</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>238.92897</v>
+        <v>241.928981</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>118.578785</v>
+        <v>121.578796</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>100.815046</v>
+        <v>103.815058</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>206.515799</v>
+        <v>209.51581</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>198.60456</v>
+        <v>201.604572</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>119.950706</v>
+        <v>122.950718</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>36.952731</v>
+        <v>39.952743</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>35.697928</v>
+        <v>38.69794</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>42.931458</v>
+        <v>45.93147</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>231.77941</v>
+        <v>234.779421</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>118.723623</v>
+        <v>121.723634</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>16.577778</v>
+        <v>19.577789</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>66.934433</v>
+        <v>69.934444</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>267.508646</v>
+        <v>270.508657</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5878,7 +5878,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW30">
-        <v>197.685613</v>
+        <v>200.685625</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW31">
-        <v>188.59213</v>
+        <v>191.592141</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>127.82566</v>
+        <v>130.825671</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>269.5989</v>
+        <v>272.598912</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW34">
-        <v>205.827616</v>
+        <v>208.827627</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW35">
-        <v>126.60706</v>
+        <v>129.607072</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>114.725405</v>
+        <v>117.725417</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>233.873414</v>
+        <v>236.873426</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>241.659155</v>
+        <v>244.659167</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7351,7 +7351,7 @@
         <v>46076.71127025463</v>
       </c>
       <c r="J39" s="2">
-        <v>46090.58235930555</v>
+        <v>46094.65132420139</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -7424,6 +7424,11 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AF39" t="inlineStr">
         <is>
           <t>Gestão</t>
@@ -7451,7 +7456,7 @@
         <v>46090.58235540509</v>
       </c>
       <c r="AQ39">
-        <v>3.689595</v>
+        <v>6.689606</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7632,7 +7637,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>128.891053</v>
+        <v>131.891065</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7813,7 +7818,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>107.705301</v>
+        <v>110.705313</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -7994,7 +7999,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>66.695035</v>
+        <v>69.695046</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8175,7 +8180,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW43">
-        <v>56.618681</v>
+        <v>59.618692</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8353,7 +8358,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW44">
-        <v>36.954722</v>
+        <v>39.954734</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8534,7 +8539,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>15.718715</v>
+        <v>18.718727</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8715,7 +8720,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>190.910417</v>
+        <v>193.910428</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8896,7 +8901,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>205.827002</v>
+        <v>208.827014</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9030,7 +9035,7 @@
         <v>46090.58140600695</v>
       </c>
       <c r="AQ48">
-        <v>3.690544</v>
+        <v>6.690556</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9214,7 +9219,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>156.943773</v>
+        <v>159.943785</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9395,7 +9400,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>156.942558</v>
+        <v>159.942569</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9563,7 +9568,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>14.592813</v>
+        <v>17.592824</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9744,7 +9749,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>233.874398</v>
+        <v>236.87441</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9922,7 +9927,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>234.567905</v>
+        <v>237.567917</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10106,7 +10111,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>141.710521</v>
+        <v>144.710532</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10287,7 +10292,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>247.783391</v>
+        <v>250.783403</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10465,7 +10470,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>14.592072</v>
+        <v>17.592083</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10649,7 +10654,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>225.540926</v>
+        <v>228.540938</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10683,7 +10688,7 @@
         <v>46076.60419387731</v>
       </c>
       <c r="J58" s="2">
-        <v>46090.5808875463</v>
+        <v>46094.6509167824</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -10756,6 +10761,11 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Reprovado</t>
+        </is>
+      </c>
       <c r="AF58" t="inlineStr">
         <is>
           <t>Gestão</t>
@@ -10783,7 +10793,7 @@
         <v>46090.58088335648</v>
       </c>
       <c r="AQ58">
-        <v>3.691065</v>
+        <v>6.691076</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -10961,7 +10971,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>272.645579</v>
+        <v>275.64559</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11139,7 +11149,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>262.694398</v>
+        <v>265.69441</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11320,7 +11330,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>92.796944</v>
+        <v>95.79695599999999</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11498,7 +11508,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>57.688229</v>
+        <v>60.688241</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11676,7 +11686,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>234.567072</v>
+        <v>237.567083</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11857,7 +11867,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>128.895162</v>
+        <v>131.895174</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12038,7 +12048,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>108.514803</v>
+        <v>111.514815</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12216,7 +12226,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW66">
-        <v>237.822755</v>
+        <v>240.822766</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12400,7 +12410,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW67">
-        <v>118.623773</v>
+        <v>121.623785</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12578,7 +12588,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>198.6239</v>
+        <v>201.623912</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12759,7 +12769,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW69">
-        <v>170.568646</v>
+        <v>173.568657</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -12937,7 +12947,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>56.598322</v>
+        <v>59.598333</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13115,7 +13125,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>273.938715</v>
+        <v>276.938727</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13293,7 +13303,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>276.831609</v>
+        <v>279.83162</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13471,7 +13481,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>234.582847</v>
+        <v>237.582859</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13652,7 +13662,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>191.684375</v>
+        <v>194.684387</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13833,7 +13843,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW75">
-        <v>86.84463</v>
+        <v>89.844641</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14014,7 +14024,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>134.716933</v>
+        <v>137.716944</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14192,7 +14202,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW77">
-        <v>127.720972</v>
+        <v>130.720984</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14373,7 +14383,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>91.542176</v>
+        <v>94.542188</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14554,7 +14564,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>36.773565</v>
+        <v>39.773576</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14568,7 +14578,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14588,7 +14598,7 @@
         <v>46045.58500423611</v>
       </c>
       <c r="J80" s="2">
-        <v>46085.61974087963</v>
+        <v>46095.51319524305</v>
       </c>
       <c r="M80" s="2">
         <v>46075.58500423611</v>
@@ -14664,9 +14674,19 @@
           <t>https://docs.google.com/document/d/1pSj1GskLIM6lXszJuef1pijPC_LT3gIaWxqGmK-xmMQ/edit?tab=t.iolnz6jemwx9</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD80" t="inlineStr">
         <is>
           <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -14695,8 +14715,17 @@
       <c r="AO80" s="2">
         <v>46076.53149964121</v>
       </c>
+      <c r="AP80" s="2">
+        <v>46094.51261431713</v>
+      </c>
       <c r="AQ80">
-        <v>17.740451</v>
+        <v>17.981111</v>
+      </c>
+      <c r="AR80" s="2">
+        <v>46094.51261479167</v>
+      </c>
+      <c r="AT80">
+        <v>2.759352</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -14882,7 +14911,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>248.654282</v>
+        <v>251.654294</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15060,7 +15089,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>185.680498</v>
+        <v>188.680509</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15241,7 +15270,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>120.607488</v>
+        <v>123.6075</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15402,7 +15431,7 @@
         <v>46092.48987280093</v>
       </c>
       <c r="AT84">
-        <v>1.782072</v>
+        <v>4.782083</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15586,7 +15615,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>189.889144</v>
+        <v>192.889155</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15767,7 +15796,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>107.695648</v>
+        <v>110.69566</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -15948,7 +15977,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>262.697789</v>
+        <v>265.697801</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16126,7 +16155,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW88">
-        <v>141.858912</v>
+        <v>144.858924</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16307,7 +16336,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW89">
-        <v>156.943553</v>
+        <v>159.943565</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16488,7 +16517,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>136.553669</v>
+        <v>139.553681</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16669,7 +16698,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>126.605718</v>
+        <v>129.605729</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16847,7 +16876,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>241.723113</v>
+        <v>244.723125</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17025,7 +17054,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>272.597859</v>
+        <v>275.59787</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17214,7 +17243,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>220.567523</v>
+        <v>223.567535</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17395,7 +17424,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>189.887431</v>
+        <v>192.887442</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17576,7 +17605,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>170.561493</v>
+        <v>173.561505</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17757,7 +17786,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>92.806308</v>
+        <v>95.806319</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17858,7 +17887,7 @@
         <v>46076.60414643519</v>
       </c>
       <c r="AK98">
-        <v>17.667801</v>
+        <v>20.667813</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18039,7 +18068,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>226.570035</v>
+        <v>229.570046</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18217,7 +18246,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>267.502755</v>
+        <v>270.502766</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18395,7 +18424,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>176.943183</v>
+        <v>179.943194</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18573,7 +18602,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>234.566296</v>
+        <v>237.566308</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18754,7 +18783,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>66.938056</v>
+        <v>69.938067</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -18932,7 +18961,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>273.939109</v>
+        <v>276.93912</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19110,7 +19139,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>185.553773</v>
+        <v>188.553785</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19291,7 +19320,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>107.708877</v>
+        <v>110.708889</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19472,7 +19501,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>203.622951</v>
+        <v>206.622963</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19653,7 +19682,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>195.698808</v>
+        <v>198.698819</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19831,7 +19860,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>35.722593</v>
+        <v>38.722604</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20009,7 +20038,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>269.688715</v>
+        <v>272.688727</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20190,7 +20219,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>225.685706</v>
+        <v>228.685718</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20371,7 +20400,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW112">
-        <v>106.723773</v>
+        <v>109.723785</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20555,7 +20584,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW113">
-        <v>164.944456</v>
+        <v>167.944468</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20736,7 +20765,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW114">
-        <v>185.609722</v>
+        <v>188.609734</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -20917,7 +20946,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW115">
-        <v>224.122581</v>
+        <v>227.122593</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21098,7 +21127,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW116">
-        <v>232.7661</v>
+        <v>235.766111</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21279,7 +21308,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>134.698414</v>
+        <v>137.698426</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21460,7 +21489,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>107.694329</v>
+        <v>110.69434</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21641,7 +21670,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>66.936678</v>
+        <v>69.93669</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21822,7 +21851,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>43.72397</v>
+        <v>46.723981</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22000,7 +22029,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>276.834572</v>
+        <v>279.834583</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22181,7 +22210,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW122">
-        <v>272.595995</v>
+        <v>275.596007</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22359,7 +22388,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW123">
-        <v>262.645451</v>
+        <v>265.645463</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22540,7 +22569,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>164.942859</v>
+        <v>167.94287</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22721,7 +22750,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>118.723137</v>
+        <v>121.723148</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -22902,7 +22931,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>136.544306</v>
+        <v>139.544317</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23080,7 +23109,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>55.588542</v>
+        <v>58.588553</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23258,7 +23287,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW128">
-        <v>203.576157</v>
+        <v>206.576169</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23439,7 +23468,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW129">
-        <v>251.564664</v>
+        <v>254.564676</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23623,7 +23652,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW130">
-        <v>225.705718</v>
+        <v>228.705729</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23804,7 +23833,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>7.596667</v>
+        <v>10.596678</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -23985,7 +24014,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>189.885278</v>
+        <v>192.885289</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24098,7 +24127,7 @@
         <v>46056.35300378472</v>
       </c>
       <c r="AN133">
-        <v>37.918947</v>
+        <v>40.918958</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24276,7 +24305,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW134">
-        <v>267.503368</v>
+        <v>270.50338</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24457,7 +24486,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>91.54288200000001</v>
+        <v>94.542894</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24638,7 +24667,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW136">
-        <v>107.695752</v>
+        <v>110.695764</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -24811,7 +24840,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW137">
-        <v>262.597963</v>
+        <v>265.597975</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -24992,7 +25021,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW138">
-        <v>92.798391</v>
+        <v>95.79840299999999</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25173,7 +25202,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW139">
-        <v>21.675081</v>
+        <v>24.675093</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25354,7 +25383,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW140">
-        <v>176.805532</v>
+        <v>179.805544</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25535,7 +25564,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW141">
-        <v>170.956944</v>
+        <v>173.956956</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25713,7 +25742,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW142">
-        <v>280.647986</v>
+        <v>283.647998</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -25891,7 +25920,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW143">
-        <v>206.488345</v>
+        <v>209.488356</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26072,7 +26101,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW144">
-        <v>164.942315</v>
+        <v>167.942326</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26248,7 +26277,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW145">
-        <v>100.814815</v>
+        <v>103.814826</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26429,7 +26458,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW146">
-        <v>34.835752</v>
+        <v>37.835764</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26607,7 +26636,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW147">
-        <v>262.648657</v>
+        <v>265.648669</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -26785,7 +26814,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW148">
-        <v>267.505023</v>
+        <v>270.505035</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -26819,7 +26848,7 @@
         <v>46076.60416021991</v>
       </c>
       <c r="J149" s="2">
-        <v>46090.58155533565</v>
+        <v>46094.6511883912</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -26892,6 +26921,11 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AF149" t="inlineStr">
         <is>
           <t>Gestão</t>
@@ -26919,7 +26953,7 @@
         <v>46090.5815483912</v>
       </c>
       <c r="AQ149">
-        <v>3.690405</v>
+        <v>6.690417</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27100,7 +27134,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW150">
-        <v>203.685648</v>
+        <v>206.68566</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27278,7 +27312,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW151">
-        <v>237.822326</v>
+        <v>240.822338</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27456,7 +27490,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW152">
-        <v>234.566794</v>
+        <v>237.566806</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27637,7 +27671,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW153">
-        <v>197.686644</v>
+        <v>200.686655</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -27818,7 +27852,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW154">
-        <v>56.604826</v>
+        <v>59.604838</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -27999,7 +28033,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>169.618877</v>
+        <v>172.618889</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28180,7 +28214,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW156">
-        <v>169.818819</v>
+        <v>172.818831</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28358,7 +28392,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW157">
-        <v>36.951863</v>
+        <v>39.951875</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28542,7 +28576,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW158">
-        <v>92.805938</v>
+        <v>95.805949</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -28723,7 +28757,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW159">
-        <v>191.517014</v>
+        <v>194.517025</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -28912,7 +28946,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW160">
-        <v>181.582245</v>
+        <v>184.582257</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29080,7 +29114,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW161">
-        <v>211.652419</v>
+        <v>214.652431</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29261,7 +29295,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW162">
-        <v>164.94162</v>
+        <v>167.941632</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29442,7 +29476,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW163">
-        <v>108.515463</v>
+        <v>111.515475</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29623,7 +29657,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW164">
-        <v>49.628484</v>
+        <v>52.628495</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -29804,7 +29838,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW165">
-        <v>233.874201</v>
+        <v>236.874213</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -29985,7 +30019,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW166">
-        <v>189.890891</v>
+        <v>192.890903</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30166,7 +30200,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW167">
-        <v>113.538414</v>
+        <v>116.538426</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30344,7 +30378,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW168">
-        <v>36.956308</v>
+        <v>39.956319</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30522,7 +30556,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW169">
-        <v>223.897014</v>
+        <v>226.897025</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30703,7 +30737,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW170">
-        <v>139.643461</v>
+        <v>142.643472</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -30881,7 +30915,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW171">
-        <v>107.692674</v>
+        <v>110.692685</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31062,7 +31096,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW172">
-        <v>7.597697</v>
+        <v>10.597708</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31240,7 +31274,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW173">
-        <v>272.598796</v>
+        <v>275.598808</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31421,7 +31455,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW174">
-        <v>248.949097</v>
+        <v>251.949109</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31599,7 +31633,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW175">
-        <v>57.679653</v>
+        <v>60.679664</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -31777,7 +31811,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW176">
-        <v>30.724954</v>
+        <v>33.724965</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -31950,7 +31984,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW177">
-        <v>188.591921</v>
+        <v>191.591933</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32131,7 +32165,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW178">
-        <v>66.936076</v>
+        <v>69.936088</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32309,7 +32343,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW179">
-        <v>16.571563</v>
+        <v>19.571574</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32487,7 +32521,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW180">
-        <v>223.901956</v>
+        <v>226.901968</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32665,7 +32699,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW181">
-        <v>276.834965</v>
+        <v>279.834977</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -32843,7 +32877,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW182">
-        <v>198.603032</v>
+        <v>201.603044</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33021,7 +33055,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW183">
-        <v>269.598345</v>
+        <v>272.598356</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33199,7 +33233,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW184">
-        <v>260.705185</v>
+        <v>263.705197</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33377,7 +33411,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW185">
-        <v>198.623785</v>
+        <v>201.623796</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33558,7 +33592,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW186">
-        <v>127.72081</v>
+        <v>130.720822</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -33572,7 +33606,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -33592,7 +33626,7 @@
         <v>46045.58499743055</v>
       </c>
       <c r="J187" s="2">
-        <v>46085.62068180555</v>
+        <v>46095.51250278935</v>
       </c>
       <c r="M187" s="2">
         <v>46075.58499743055</v>
@@ -33668,9 +33702,19 @@
           <t>https://docs.google.com/document/d/1pSj1GskLIM6lXszJuef1pijPC_LT3gIaWxqGmK-xmMQ/edit?tab=t.iolnz6jemwx9</t>
         </is>
       </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD187" t="inlineStr">
         <is>
           <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -33699,8 +33743,17 @@
       <c r="AO187" s="2">
         <v>46076.53159934028</v>
       </c>
+      <c r="AP187" s="2">
+        <v>46094.51247393519</v>
+      </c>
       <c r="AQ187">
-        <v>17.740347</v>
+        <v>17.980868</v>
+      </c>
+      <c r="AR187" s="2">
+        <v>46094.5124747338</v>
+      </c>
+      <c r="AT187">
+        <v>2.759491</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -33878,7 +33931,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW188">
-        <v>269.597986</v>
+        <v>272.597998</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34059,7 +34112,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW189">
-        <v>225.701528</v>
+        <v>228.701539</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34240,7 +34293,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW190">
-        <v>170.956227</v>
+        <v>173.956238</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34421,7 +34474,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW191">
-        <v>203.515938</v>
+        <v>206.515949</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34602,7 +34655,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW192">
-        <v>114.669282</v>
+        <v>117.669294</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -34780,7 +34833,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW193">
-        <v>36.954282</v>
+        <v>39.954294</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -34958,7 +35011,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW194">
-        <v>276.842535</v>
+        <v>279.842546</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35126,7 +35179,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW195">
-        <v>211.664606</v>
+        <v>214.664618</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35307,7 +35360,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW196">
-        <v>189.888403</v>
+        <v>192.888414</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35491,7 +35544,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW197">
-        <v>170.959769</v>
+        <v>173.95978</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35675,7 +35728,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW198">
-        <v>225.705347</v>
+        <v>228.705359</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -35856,7 +35909,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW199">
-        <v>92.797708</v>
+        <v>95.79772</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36034,7 +36087,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>283.909826</v>
+        <v>286.909838</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36212,7 +36265,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW201">
-        <v>269.688993</v>
+        <v>272.689005</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36393,7 +36446,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW202">
-        <v>189.894248</v>
+        <v>192.894259</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36571,7 +36624,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW203">
-        <v>163.681644</v>
+        <v>166.681655</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -36752,7 +36805,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW204">
-        <v>256.925532</v>
+        <v>259.925544</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -36930,7 +36983,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW205">
-        <v>267.503935</v>
+        <v>270.503947</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37108,7 +37161,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW206">
-        <v>195.607488</v>
+        <v>198.6075</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37286,7 +37339,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW207">
-        <v>20.60419</v>
+        <v>23.604201</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37467,7 +37520,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW208">
-        <v>251.561505</v>
+        <v>254.561516</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37648,7 +37701,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW209">
-        <v>199.530926</v>
+        <v>202.530938</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -37826,7 +37879,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW210">
-        <v>57.685266</v>
+        <v>60.685278</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38004,7 +38057,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW211">
-        <v>272.57213</v>
+        <v>275.572141</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38182,7 +38235,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW212">
-        <v>269.688449</v>
+        <v>272.688461</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38360,7 +38413,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW213">
-        <v>3.541829</v>
+        <v>6.54184</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38538,7 +38591,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW214">
-        <v>282.733646</v>
+        <v>285.733657</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -38716,7 +38769,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW215">
-        <v>268.610671</v>
+        <v>271.610683</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -38894,7 +38947,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW216">
-        <v>280.593252</v>
+        <v>283.593264</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39072,7 +39125,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW217">
-        <v>272.646829</v>
+        <v>275.64684</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39253,7 +39306,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW218">
-        <v>139.911528</v>
+        <v>142.911539</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39431,7 +39484,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW219">
-        <v>234.568519</v>
+        <v>237.56853</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39612,7 +39665,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW220">
-        <v>234.586493</v>
+        <v>237.586505</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -39626,12 +39679,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Construção no Canvas</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Grãos</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="E221" s="2">
@@ -39646,7 +39699,7 @@
         <v>46045.58506547453</v>
       </c>
       <c r="J221" s="2">
-        <v>46085.61908604167</v>
+        <v>46094.5122262963</v>
       </c>
       <c r="M221" s="2">
         <v>46075.58506547453</v>
@@ -39722,14 +39775,24 @@
           <t>https://docs.google.com/document/d/1pSj1GskLIM6lXszJuef1pijPC_LT3gIaWxqGmK-xmMQ/edit?tab=t.iolnz6jemwx9</t>
         </is>
       </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Reprovado</t>
+        </is>
+      </c>
       <c r="AD221" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>
       </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>Reprovado: Realizar ajustes</t>
+        </is>
+      </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>Grãos</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="AI221" s="2">
@@ -39748,13 +39811,16 @@
         <v>46076.53141831019</v>
       </c>
       <c r="AN221">
-        <v>24.994213</v>
+        <v>27.753958</v>
       </c>
       <c r="AO221" s="2">
         <v>46076.53141864583</v>
       </c>
+      <c r="AP221" s="2">
+        <v>46094.51222321759</v>
+      </c>
       <c r="AQ221">
-        <v>17.740532</v>
+        <v>17.980799</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -39932,7 +39998,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW222">
-        <v>281.68897</v>
+        <v>284.688981</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40110,7 +40176,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW223">
-        <v>272.587894</v>
+        <v>275.587905</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40288,7 +40354,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW224">
-        <v>281.684838</v>
+        <v>284.68485</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40469,7 +40535,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW225">
-        <v>182.639144</v>
+        <v>185.639155</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -40650,7 +40716,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW226">
-        <v>114.693438</v>
+        <v>117.693449</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -40831,7 +40897,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW227">
-        <v>107.711586</v>
+        <v>110.711597</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41012,7 +41078,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>42.934757</v>
+        <v>45.934769</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41193,7 +41259,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW229">
-        <v>42.933079</v>
+        <v>45.93309</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41374,7 +41440,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW230">
-        <v>189.8936</v>
+        <v>192.893611</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41555,7 +41621,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW231">
-        <v>241.659074</v>
+        <v>244.659086</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -41733,7 +41799,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW232">
-        <v>258.900382</v>
+        <v>261.900394</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -41914,7 +41980,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW233">
-        <v>198.669988</v>
+        <v>201.67</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42098,7 +42164,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW234">
-        <v>190.910185</v>
+        <v>193.910197</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42279,7 +42345,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW235">
-        <v>170.958079</v>
+        <v>173.95809</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42457,7 +42523,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW236">
-        <v>121.886944</v>
+        <v>124.886956</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42638,7 +42704,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW237">
-        <v>7.595556</v>
+        <v>10.595567</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -42819,7 +42885,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW238">
-        <v>233.874734</v>
+        <v>236.874745</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43000,7 +43066,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW239">
-        <v>189.753194</v>
+        <v>192.753206</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43181,7 +43247,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW240">
-        <v>92.798935</v>
+        <v>95.798947</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43359,7 +43425,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW241">
-        <v>57.6786</v>
+        <v>60.678611</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43540,7 +43606,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW242">
-        <v>108.515961</v>
+        <v>111.515972</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -43721,7 +43787,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW243">
-        <v>223.900729</v>
+        <v>226.900741</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -43894,7 +43960,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW244">
-        <v>269.573229</v>
+        <v>272.573241</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44072,7 +44138,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW245">
-        <v>234.567303</v>
+        <v>237.567315</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44256,7 +44322,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW246">
-        <v>198.601377</v>
+        <v>201.601389</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44437,7 +44503,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW247">
-        <v>141.855961</v>
+        <v>144.855972</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44621,7 +44687,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW248">
-        <v>170.660845</v>
+        <v>173.660856</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -44802,7 +44868,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW249">
-        <v>164.940741</v>
+        <v>167.940752</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -44983,7 +45049,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW250">
-        <v>15.719549</v>
+        <v>18.71956</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45161,7 +45227,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW251">
-        <v>234.567708</v>
+        <v>237.56772</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45342,7 +45408,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW252">
-        <v>205.828241</v>
+        <v>208.828252</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45523,7 +45589,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW253">
-        <v>42.678426</v>
+        <v>45.678438</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -45704,7 +45770,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW254">
-        <v>254.720903</v>
+        <v>257.720914</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -45885,7 +45951,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW255">
-        <v>43.724387</v>
+        <v>46.724398</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -45986,7 +46052,7 @@
         <v>46076.70991956018</v>
       </c>
       <c r="AK256">
-        <v>17.562025</v>
+        <v>20.562037</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46087,7 +46153,7 @@
         <v>46076.60415833333</v>
       </c>
       <c r="AK257">
-        <v>17.667789</v>
+        <v>20.667801</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46268,7 +46334,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW258">
-        <v>66.93535900000001</v>
+        <v>69.93537000000001</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46449,7 +46515,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW259">
-        <v>233.835313</v>
+        <v>236.835324</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46630,7 +46696,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>164.948333</v>
+        <v>167.948345</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -46808,7 +46874,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW261">
-        <v>164.950486</v>
+        <v>167.950498</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -46986,7 +47052,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW262">
-        <v>139.532882</v>
+        <v>142.532894</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47162,7 +47228,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW263">
-        <v>231.779572</v>
+        <v>234.779583</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47340,7 +47406,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW264">
-        <v>155.939051</v>
+        <v>158.939063</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47524,7 +47590,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW265">
-        <v>141.711273</v>
+        <v>144.711285</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -47702,7 +47768,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW266">
-        <v>90.70796300000001</v>
+        <v>93.707975</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -47883,7 +47949,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW267">
-        <v>262.698009</v>
+        <v>265.698021</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48061,7 +48127,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW268">
-        <v>272.646088</v>
+        <v>275.6461</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48242,7 +48308,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW269">
-        <v>251.561852</v>
+        <v>254.561863</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48420,7 +48486,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>141.712083</v>
+        <v>144.712095</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48601,7 +48667,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW271">
-        <v>127.720706</v>
+        <v>130.720718</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -48782,7 +48848,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW272">
-        <v>107.695475</v>
+        <v>110.695486</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -48963,7 +49029,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW273">
-        <v>251.562396</v>
+        <v>254.562407</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49141,7 +49207,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW274">
-        <v>170.952477</v>
+        <v>173.952488</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49325,7 +49391,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW275">
-        <v>122.699317</v>
+        <v>125.699329</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49506,7 +49572,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW276">
-        <v>261.591204</v>
+        <v>264.591215</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -49687,7 +49753,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW277">
-        <v>176.806725</v>
+        <v>179.806736</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -49868,7 +49934,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>128.893333</v>
+        <v>131.893345</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50049,7 +50115,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>247.783194</v>
+        <v>250.783206</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50256,7 +50322,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>127.826389</v>
+        <v>130.8264</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50437,7 +50503,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW281">
-        <v>107.712245</v>
+        <v>110.712257</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50615,7 +50681,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW282">
-        <v>118.622396</v>
+        <v>121.622407</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -50799,7 +50865,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>156.942477</v>
+        <v>159.942488</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -50980,7 +51046,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW284">
-        <v>101.655104</v>
+        <v>104.655116</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51014,7 +51080,7 @@
         <v>46076.6041722338</v>
       </c>
       <c r="J285" s="2">
-        <v>46090.58126530092</v>
+        <v>46094.65110508102</v>
       </c>
       <c r="N285" t="b">
         <v>0</v>
@@ -51087,6 +51153,11 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AF285" t="inlineStr">
         <is>
           <t>Gestão</t>
@@ -51114,7 +51185,7 @@
         <v>46090.58126142361</v>
       </c>
       <c r="AQ285">
-        <v>3.690694</v>
+        <v>6.690706</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51292,7 +51363,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW286">
-        <v>248.949468</v>
+        <v>251.949479</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51470,7 +51541,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW287">
-        <v>260.706134</v>
+        <v>263.706146</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -51651,7 +51722,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>203.629861</v>
+        <v>206.629873</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -51829,7 +51900,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW289">
-        <v>223.901794</v>
+        <v>226.901806</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52013,7 +52084,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW290">
-        <v>144.95728</v>
+        <v>147.957292</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52194,7 +52265,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>247.911863</v>
+        <v>250.911875</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52375,7 +52446,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW292">
-        <v>122.692975</v>
+        <v>125.692986</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52553,7 +52624,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW293">
-        <v>261.911065</v>
+        <v>264.911076</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -52734,7 +52805,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW294">
-        <v>206.518958</v>
+        <v>209.51897</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -52912,7 +52983,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW295">
-        <v>267.501968</v>
+        <v>270.501979</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53093,7 +53164,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW296">
-        <v>189.894815</v>
+        <v>192.894826</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53254,7 +53325,7 @@
         <v>46091.62691277778</v>
       </c>
       <c r="AT297">
-        <v>2.645035</v>
+        <v>5.645046</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53435,7 +53506,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW298">
-        <v>107.563704</v>
+        <v>110.563715</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -53613,7 +53684,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW299">
-        <v>234.569641</v>
+        <v>237.569653</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -53647,7 +53718,7 @@
         <v>46076.60418768518</v>
       </c>
       <c r="J300" s="2">
-        <v>46090.58069163194</v>
+        <v>46094.65082283565</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -53720,6 +53791,11 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AF300" t="inlineStr">
         <is>
           <t>Gestão</t>
@@ -53747,7 +53823,7 @@
         <v>46090.58068733796</v>
       </c>
       <c r="AQ300">
-        <v>3.691262</v>
+        <v>6.691273</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -53936,7 +54012,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW301">
-        <v>258.900845</v>
+        <v>261.900856</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54117,7 +54193,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW302">
-        <v>189.887685</v>
+        <v>192.887697</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54295,7 +54371,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW303">
-        <v>164.699155</v>
+        <v>167.699167</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54476,7 +54552,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW304">
-        <v>86.84487300000001</v>
+        <v>89.84488399999999</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -54654,7 +54730,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>273.940567</v>
+        <v>276.940579</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -54835,7 +54911,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW306">
-        <v>118.722986</v>
+        <v>121.722998</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55021,7 +55097,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW307">
-        <v>199.660625</v>
+        <v>202.660637</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55202,7 +55278,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW308">
-        <v>163.612778</v>
+        <v>166.612789</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55383,7 +55459,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW309">
-        <v>92.810451</v>
+        <v>95.810463</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -55564,7 +55640,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW310">
-        <v>66.93718800000001</v>
+        <v>69.93719900000001</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -55745,7 +55821,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>163.613113</v>
+        <v>166.613125</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -55926,7 +56002,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW312">
-        <v>163.611343</v>
+        <v>166.611354</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56027,7 +56103,7 @@
         <v>46076.70818526621</v>
       </c>
       <c r="AK313">
-        <v>17.563762</v>
+        <v>20.563773</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56205,7 +56281,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW314">
-        <v>267.50235</v>
+        <v>270.502361</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56383,7 +56459,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW315">
-        <v>36.958588</v>
+        <v>39.9586</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -56564,7 +56640,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW316">
-        <v>220.564039</v>
+        <v>223.564051</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -56745,7 +56821,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>139.64441</v>
+        <v>142.644421</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -56923,21 +56999,21 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW318">
-        <v>16.571042</v>
+        <v>19.571053</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319">
-        <v>1301624302</v>
+        <v>1286617795</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Curso: Pós Gestão Fazendas Online Turma: 2 Disciplina: Operações e fundamentos do agronegócio Tópico: Jornada do gestor Professor: Guilherme Campos De Arruda LamegoTipo de Conteúdo: Online gravadaData: 46106</t>
+          <t>Curso: MBA Gestão do Agronegócio Turma: 6 Disciplina: Agronegócio e gestão da rotina e metas Tópico: Orientações para desenvolvimento de Projeto/Desafio Professor: Victoria Dalcomune Ferreira PiskeTipo de Conteúdo: Online gravadaData: 46093</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -56946,7 +57022,7 @@
         </is>
       </c>
       <c r="E319" s="2">
-        <v>46105.875</v>
+        <v>46092.875</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -56954,13 +57030,16 @@
         </is>
       </c>
       <c r="I319" s="2">
-        <v>46076.6041787037</v>
+        <v>46045.58499030092</v>
       </c>
       <c r="J319" s="2">
-        <v>46090.58108027778</v>
+        <v>46092.62702260417</v>
+      </c>
+      <c r="M319" s="2">
+        <v>46075.58499030092</v>
       </c>
       <c r="N319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -56969,12 +57048,12 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Guilherme Campos De Arruda Lamego</t>
+          <t>Victoria Dalcomune Ferreira Piske</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -56984,50 +57063,65 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>Curso: Pós Gestão Fazendas Online Turma: 2 Disciplina: Operações e fundamentos do agronegócio Tópico: Jornada do gestor Professor: Guilherme Campos De Arruda LamegoTipo de Conteúdo: Online gravadaData: 46106</t>
+          <t>Curso: MBA Gestão do Agronegócio Turma: 6 Disciplina: Agronegócio e gestão da rotina e metas Tópico: Orientações para desenvolvimento de Projeto/Desafio Professor: Victoria Dalcomune Ferreira PiskeTipo de Conteúdo: Online gravadaData: 46093</t>
         </is>
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>Pós Gestão Fazendas Online</t>
+          <t>MBA Gestão do Agronegócio</t>
         </is>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>Operações e fundamentos do agronegócio</t>
+          <t>Agronegócio e gestão da rotina e metas</t>
         </is>
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>Jornada do gestor</t>
+          <t>Orientações para desenvolvimento de Projeto/Desafio</t>
         </is>
       </c>
       <c r="X319" s="2">
-        <v>46105.875</v>
+        <v>46092.875</v>
       </c>
       <c r="Y319" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://rehagro.instructure.com/courses/3047 </t>
+          <t>https://rehagro.instructure.com/courses/2951/modules</t>
         </is>
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
+          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.aspbfo3qvjqw</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -57036,42 +57130,51 @@
         </is>
       </c>
       <c r="AI319" s="2">
-        <v>46076.60418275463</v>
+        <v>46045.58499524306</v>
       </c>
       <c r="AJ319" s="2">
-        <v>46090.58007364583</v>
+        <v>46086.70777142361</v>
       </c>
       <c r="AK319">
-        <v>13.97588</v>
+        <v>41.122766</v>
       </c>
       <c r="AL319" s="2">
-        <v>46090.58007386574</v>
+        <v>46086.70777230324</v>
       </c>
       <c r="AM319" s="2">
-        <v>46090.58107552084</v>
+        <v>46090.72972290509</v>
       </c>
       <c r="AN319">
-        <v>0.000995</v>
+        <v>4.021944</v>
       </c>
       <c r="AO319" s="2">
-        <v>46090.58107568287</v>
+        <v>46090.72972311343</v>
+      </c>
+      <c r="AP319" s="2">
+        <v>46091.62671181713</v>
       </c>
       <c r="AQ319">
-        <v>3.69088</v>
+        <v>0.896979</v>
+      </c>
+      <c r="AR319" s="2">
+        <v>46091.62671216435</v>
+      </c>
+      <c r="AT319">
+        <v>5.645255</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320">
-        <v>1286617795</v>
+        <v>1301624302</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Curso: MBA Gestão do Agronegócio Turma: 6 Disciplina: Agronegócio e gestão da rotina e metas Tópico: Orientações para desenvolvimento de Projeto/Desafio Professor: Victoria Dalcomune Ferreira PiskeTipo de Conteúdo: Online gravadaData: 46093</t>
+          <t>Curso: Pós Gestão Fazendas Online Turma: 2 Disciplina: Operações e fundamentos do agronegócio Tópico: Jornada do gestor Professor: Guilherme Campos De Arruda LamegoTipo de Conteúdo: Online gravadaData: 46106</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Validação</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -57080,7 +57183,7 @@
         </is>
       </c>
       <c r="E320" s="2">
-        <v>46092.875</v>
+        <v>46105.875</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -57088,16 +57191,13 @@
         </is>
       </c>
       <c r="I320" s="2">
-        <v>46045.58499030092</v>
+        <v>46076.6041787037</v>
       </c>
       <c r="J320" s="2">
-        <v>46092.62702260417</v>
-      </c>
-      <c r="M320" s="2">
-        <v>46075.58499030092</v>
+        <v>46094.65099866898</v>
       </c>
       <c r="N320" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -57106,119 +57206,100 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Victoria Dalcomune Ferreira Piske</t>
+          <t>Guilherme Campos De Arruda Lamego</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>Gestão</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>Curso: Pós Gestão Fazendas Online Turma: 2 Disciplina: Operações e fundamentos do agronegócio Tópico: Jornada do gestor Professor: Guilherme Campos De Arruda LamegoTipo de Conteúdo: Online gravadaData: 46106</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Pós Gestão Fazendas Online</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Operações e fundamentos do agronegócio</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>Jornada do gestor</t>
+        </is>
+      </c>
+      <c r="X320" s="2">
+        <v>46105.875</v>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="R320" t="inlineStr">
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rehagro.instructure.com/courses/3047 </t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>Reprovado</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
         <is>
           <t>Gestão</t>
         </is>
       </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>Curso: MBA Gestão do Agronegócio Turma: 6 Disciplina: Agronegócio e gestão da rotina e metas Tópico: Orientações para desenvolvimento de Projeto/Desafio Professor: Victoria Dalcomune Ferreira PiskeTipo de Conteúdo: Online gravadaData: 46093</t>
-        </is>
-      </c>
-      <c r="T320" t="inlineStr">
-        <is>
-          <t>MBA Gestão do Agronegócio</t>
-        </is>
-      </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>Agronegócio e gestão da rotina e metas</t>
-        </is>
-      </c>
-      <c r="W320" t="inlineStr">
-        <is>
-          <t>Orientações para desenvolvimento de Projeto/Desafio</t>
-        </is>
-      </c>
-      <c r="X320" s="2">
-        <v>46092.875</v>
-      </c>
-      <c r="Y320" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="AA320" t="inlineStr">
-        <is>
-          <t>https://rehagro.instructure.com/courses/2951/modules</t>
-        </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.aspbfo3qvjqw</t>
-        </is>
-      </c>
-      <c r="AC320" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="AD320" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="AE320" t="inlineStr">
-        <is>
-          <t>Aprovado: Publicar !</t>
-        </is>
-      </c>
-      <c r="AF320" t="inlineStr">
-        <is>
-          <t>Gestão</t>
-        </is>
-      </c>
       <c r="AI320" s="2">
-        <v>46045.58499524306</v>
+        <v>46076.60418275463</v>
       </c>
       <c r="AJ320" s="2">
-        <v>46086.70777142361</v>
+        <v>46090.58007364583</v>
       </c>
       <c r="AK320">
-        <v>41.122766</v>
+        <v>13.97588</v>
       </c>
       <c r="AL320" s="2">
-        <v>46086.70777230324</v>
+        <v>46090.58007386574</v>
       </c>
       <c r="AM320" s="2">
-        <v>46090.72972290509</v>
+        <v>46090.58107552084</v>
       </c>
       <c r="AN320">
-        <v>4.021944</v>
+        <v>0.000995</v>
       </c>
       <c r="AO320" s="2">
-        <v>46090.72972311343</v>
-      </c>
-      <c r="AP320" s="2">
-        <v>46091.62671181713</v>
+        <v>46090.58107568287</v>
       </c>
       <c r="AQ320">
-        <v>0.896979</v>
-      </c>
-      <c r="AR320" s="2">
-        <v>46091.62671216435</v>
-      </c>
-      <c r="AT320">
-        <v>2.645243</v>
+        <v>6.690891</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57399,7 +57480,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW321">
-        <v>220.566829</v>
+        <v>223.56684</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -57580,7 +57661,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW322">
-        <v>233.872072</v>
+        <v>236.872083</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -57758,7 +57839,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW323">
-        <v>42.601979</v>
+        <v>45.601991</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -57936,7 +58017,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW324">
-        <v>276.835417</v>
+        <v>279.835428</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58117,7 +58198,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW325">
-        <v>170.95162</v>
+        <v>173.951632</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58295,7 +58376,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW326">
-        <v>134.661701</v>
+        <v>137.661713</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -58476,7 +58557,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW327">
-        <v>122.696956</v>
+        <v>125.696968</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -58657,7 +58738,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW328">
-        <v>255.609468</v>
+        <v>258.609479</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -58838,7 +58919,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW329">
-        <v>210.668484</v>
+        <v>213.668495</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59019,7 +59100,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW330">
-        <v>92.81197899999999</v>
+        <v>95.81199100000001</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59200,7 +59281,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW331">
-        <v>51.814595</v>
+        <v>54.814606</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59378,7 +59459,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW332">
-        <v>203.575856</v>
+        <v>206.575868</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -59562,7 +59643,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW333">
-        <v>149.586574</v>
+        <v>152.586586</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -59743,7 +59824,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>128.889549</v>
+        <v>131.88956</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -59924,7 +60005,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>118.622824</v>
+        <v>121.622836</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60102,7 +60183,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW336">
-        <v>234.56897</v>
+        <v>237.568981</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60280,7 +60361,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW337">
-        <v>213.593449</v>
+        <v>216.593461</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -60461,7 +60542,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW338">
-        <v>59.575313</v>
+        <v>62.575324</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -60637,7 +60718,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>139.643924</v>
+        <v>142.643935</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -60818,7 +60899,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW340">
-        <v>205.824884</v>
+        <v>208.824896</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -60928,7 +61009,7 @@
         <v>46092.38034266204</v>
       </c>
       <c r="AN341">
-        <v>1.891609</v>
+        <v>4.89162</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61089,7 +61170,7 @@
         <v>46092.49037300926</v>
       </c>
       <c r="AT342">
-        <v>1.781574</v>
+        <v>4.781586</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61267,7 +61348,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW343">
-        <v>281.693796</v>
+        <v>284.693808</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -61448,7 +61529,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW344">
-        <v>191.892766</v>
+        <v>194.892778</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -61629,7 +61710,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW345">
-        <v>170.958981</v>
+        <v>173.958993</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -61810,7 +61891,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW346">
-        <v>120.607002</v>
+        <v>123.607014</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -61991,7 +62072,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW347">
-        <v>238.932141</v>
+        <v>241.932153</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62172,7 +62253,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW348">
-        <v>36.77287</v>
+        <v>39.772882</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62353,7 +62434,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW349">
-        <v>17.945313</v>
+        <v>20.945324</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -62534,7 +62615,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW350">
-        <v>101.655718</v>
+        <v>104.655729</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -62712,7 +62793,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW351">
-        <v>195.652523</v>
+        <v>198.652535</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -62893,7 +62974,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW352">
-        <v>174.591042</v>
+        <v>177.591053</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63071,7 +63152,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW353">
-        <v>139.645035</v>
+        <v>142.645046</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63252,7 +63333,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW354">
-        <v>120.608229</v>
+        <v>123.608241</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -63433,7 +63514,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW355">
-        <v>247.912083</v>
+        <v>250.912095</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -63614,7 +63695,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW356">
-        <v>176.806273</v>
+        <v>179.806285</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -63795,7 +63876,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW357">
-        <v>164.939977</v>
+        <v>167.939988</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -63976,7 +64057,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW358">
-        <v>171.012488</v>
+        <v>174.0125</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64157,7 +64238,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW359">
-        <v>106.727234</v>
+        <v>109.727245</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64338,7 +64419,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW360">
-        <v>56.606424</v>
+        <v>59.606435</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -64519,7 +64600,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW361">
-        <v>272.596701</v>
+        <v>275.596713</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -64697,7 +64778,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW362">
-        <v>273.938877</v>
+        <v>276.938889</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -64878,7 +64959,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW363">
-        <v>87.726169</v>
+        <v>90.726181</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65059,7 +65140,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW364">
-        <v>42.740486</v>
+        <v>45.740498</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65237,7 +65318,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW365">
-        <v>280.587546</v>
+        <v>283.587558</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -65418,7 +65499,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW366">
-        <v>170.960197</v>
+        <v>173.960208</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -65596,7 +65677,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW367">
-        <v>90.707882</v>
+        <v>93.707894</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -65777,7 +65858,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW368">
-        <v>251.562917</v>
+        <v>254.562928</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -65958,7 +66039,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW369">
-        <v>141.857465</v>
+        <v>144.857477</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66139,7 +66220,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW370">
-        <v>139.8925</v>
+        <v>142.892512</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66317,7 +66398,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW371">
-        <v>267.501701</v>
+        <v>270.501713</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -66498,7 +66579,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW372">
-        <v>238.929456</v>
+        <v>241.929468</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -66676,7 +66757,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW373">
-        <v>157.529653</v>
+        <v>160.529664</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -66854,7 +66935,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW374">
-        <v>241.722014</v>
+        <v>244.722025</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67035,7 +67116,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW375">
-        <v>189.889039</v>
+        <v>192.889051</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67196,7 +67277,7 @@
         <v>46090.40563063657</v>
       </c>
       <c r="AT376">
-        <v>3.866319</v>
+        <v>6.866331</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67374,7 +67455,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW377">
-        <v>276.727454</v>
+        <v>279.727465</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -67552,7 +67633,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW378">
-        <v>272.63331</v>
+        <v>275.633322</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -67733,7 +67814,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW379">
-        <v>120.613623</v>
+        <v>123.613634</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -67911,7 +67992,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW380">
-        <v>273.939676</v>
+        <v>276.939688</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68089,7 +68170,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW381">
-        <v>251.563438</v>
+        <v>254.563449</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -68267,7 +68348,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW382">
-        <v>281.685197</v>
+        <v>284.685208</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -68445,7 +68526,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW383">
-        <v>129.621574</v>
+        <v>132.621586</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -68623,7 +68704,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW384">
-        <v>267.500231</v>
+        <v>270.500243</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -68801,7 +68882,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW385">
-        <v>234.566111</v>
+        <v>237.566123</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -68982,7 +69063,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW386">
-        <v>225.698738</v>
+        <v>228.69875</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69163,7 +69244,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW387">
-        <v>141.856782</v>
+        <v>144.856794</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69344,7 +69425,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>92.810903</v>
+        <v>95.810914</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -69525,7 +69606,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW389">
-        <v>86.843715</v>
+        <v>89.843727</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -69698,7 +69779,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW390">
-        <v>188.592269</v>
+        <v>191.59228</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -69871,7 +69952,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW391">
-        <v>188.591806</v>
+        <v>191.591817</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70052,7 +70133,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW392">
-        <v>92.80932900000001</v>
+        <v>95.80934000000001</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70233,7 +70314,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>120.607211</v>
+        <v>123.607222</v>
       </c>
     </row>
     <row r="394" ht="18" customHeight="1">
@@ -70414,7 +70495,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW394">
-        <v>107.70985</v>
+        <v>110.709861</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>280.834282</v>
+        <v>281.834433</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>123.950278</v>
+        <v>124.950428</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>111.708322</v>
+        <v>112.708472</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>235.779942</v>
+        <v>236.780093</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>238.566493</v>
+        <v>239.566644</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>46.934039</v>
+        <v>47.93419</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>273.603993</v>
+        <v>274.604144</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>222.64463</v>
+        <v>223.64478</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>206.727917</v>
+        <v>207.728067</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>122.62456</v>
+        <v>123.624711</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>207.630289</v>
+        <v>208.63044</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>285.687986</v>
+        <v>286.688137</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>271.503137</v>
+        <v>272.503287</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>240.631667</v>
+        <v>241.631817</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>242.92897</v>
+        <v>243.92912</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>122.578785</v>
+        <v>123.578935</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>104.815046</v>
+        <v>105.815197</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>210.515799</v>
+        <v>211.515949</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>202.60456</v>
+        <v>203.604711</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>123.950706</v>
+        <v>124.950856</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>40.952731</v>
+        <v>41.952882</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>39.697928</v>
+        <v>40.698079</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>46.931458</v>
+        <v>47.931609</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>235.77941</v>
+        <v>236.77956</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>122.723623</v>
+        <v>123.723773</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>20.577778</v>
+        <v>21.577928</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>70.934433</v>
+        <v>71.934583</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>271.508646</v>
+        <v>272.508796</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>192.59213</v>
+        <v>193.59228</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>201.685613</v>
+        <v>202.685764</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>131.82566</v>
+        <v>132.82581</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>273.5989</v>
+        <v>274.599051</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>130.60706</v>
+        <v>131.607211</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>209.827616</v>
+        <v>210.827766</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>118.725405</v>
+        <v>119.725556</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>237.873414</v>
+        <v>238.873565</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>245.659155</v>
+        <v>246.659306</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7456,7 +7456,7 @@
         <v>46090.58235540509</v>
       </c>
       <c r="AQ39">
-        <v>7.689595</v>
+        <v>8.689745</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7637,7 +7637,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>132.891053</v>
+        <v>133.891204</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7818,7 +7818,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>111.705301</v>
+        <v>112.705451</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -7999,7 +7999,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>70.695035</v>
+        <v>71.695185</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8177,7 +8177,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>40.954722</v>
+        <v>41.954873</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8358,7 +8358,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>60.618681</v>
+        <v>61.618831</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8539,7 +8539,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>19.718715</v>
+        <v>20.718866</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8720,7 +8720,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>194.910417</v>
+        <v>195.910567</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8901,7 +8901,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>209.827002</v>
+        <v>210.827153</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9035,7 +9035,7 @@
         <v>46090.58140600695</v>
       </c>
       <c r="AQ48">
-        <v>7.690544</v>
+        <v>8.690694000000001</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9219,7 +9219,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>160.943773</v>
+        <v>161.943924</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9400,7 +9400,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>160.942558</v>
+        <v>161.942708</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9568,7 +9568,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>18.592813</v>
+        <v>19.592963</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9749,7 +9749,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>237.874398</v>
+        <v>238.874549</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9927,7 +9927,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>238.567905</v>
+        <v>239.568056</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10111,7 +10111,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>145.710521</v>
+        <v>146.710671</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10292,7 +10292,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>251.783391</v>
+        <v>252.783542</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10470,7 +10470,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>18.592072</v>
+        <v>19.592222</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10654,7 +10654,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>229.540926</v>
+        <v>230.541076</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10793,7 +10793,7 @@
         <v>46090.58088335648</v>
       </c>
       <c r="AQ58">
-        <v>7.691065</v>
+        <v>8.691215</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -10971,7 +10971,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>276.645579</v>
+        <v>277.645729</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11149,7 +11149,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>266.694398</v>
+        <v>267.694549</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11330,7 +11330,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>96.796944</v>
+        <v>97.797095</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11508,7 +11508,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>61.688229</v>
+        <v>62.68838</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11686,7 +11686,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>238.567072</v>
+        <v>239.567222</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11867,7 +11867,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>132.895162</v>
+        <v>133.895313</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12048,7 +12048,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>112.514803</v>
+        <v>113.514954</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12229,7 +12229,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>174.568646</v>
+        <v>175.568796</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12407,7 +12407,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>241.822755</v>
+        <v>242.822905</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12585,7 +12585,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>202.6239</v>
+        <v>203.624051</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12769,7 +12769,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>122.623773</v>
+        <v>123.623924</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -12947,7 +12947,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>60.598322</v>
+        <v>61.598472</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13125,7 +13125,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>277.938715</v>
+        <v>278.938866</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13303,7 +13303,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>280.831609</v>
+        <v>281.831759</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13481,7 +13481,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>238.582847</v>
+        <v>239.582998</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13662,7 +13662,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>195.684375</v>
+        <v>196.684525</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13840,7 +13840,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>131.720972</v>
+        <v>132.721123</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14021,7 +14021,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>138.716933</v>
+        <v>139.717083</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14202,7 +14202,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>90.84463</v>
+        <v>91.84478</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14383,7 +14383,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>95.542176</v>
+        <v>96.542326</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14564,7 +14564,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>40.773565</v>
+        <v>41.773715</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14745,7 +14745,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>0.879421</v>
+        <v>1.879572</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -14931,7 +14931,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>252.654282</v>
+        <v>253.654433</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15109,7 +15109,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>189.680498</v>
+        <v>190.680648</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15290,7 +15290,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>124.607488</v>
+        <v>125.607639</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15471,7 +15471,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>0.875046</v>
+        <v>1.875197</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15655,7 +15655,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>193.889144</v>
+        <v>194.889294</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15836,7 +15836,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>111.695648</v>
+        <v>112.695799</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16017,7 +16017,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>266.697789</v>
+        <v>267.69794</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16198,7 +16198,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>160.943553</v>
+        <v>161.943704</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16376,7 +16376,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>145.858912</v>
+        <v>146.859063</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16557,7 +16557,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>140.553669</v>
+        <v>141.553819</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16738,7 +16738,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>130.605718</v>
+        <v>131.605868</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16916,7 +16916,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>245.723113</v>
+        <v>246.723264</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17094,7 +17094,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>276.597859</v>
+        <v>277.598009</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17283,7 +17283,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>224.567523</v>
+        <v>225.567674</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17464,7 +17464,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>193.887431</v>
+        <v>194.887581</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17645,7 +17645,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>174.561493</v>
+        <v>175.561644</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17826,7 +17826,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>96.806308</v>
+        <v>97.80645800000001</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17936,7 +17936,7 @@
         <v>46097.3976521875</v>
       </c>
       <c r="AN98">
-        <v>0.874294</v>
+        <v>1.874444</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18117,7 +18117,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>230.570035</v>
+        <v>231.570185</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18295,7 +18295,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>271.502755</v>
+        <v>272.502905</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18473,7 +18473,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>180.943183</v>
+        <v>181.943333</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18651,7 +18651,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>238.566296</v>
+        <v>239.566447</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18832,7 +18832,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>70.938056</v>
+        <v>71.93820599999999</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19010,7 +19010,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>277.939109</v>
+        <v>278.939259</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19188,7 +19188,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>189.553773</v>
+        <v>190.553924</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19369,7 +19369,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>111.708877</v>
+        <v>112.709028</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19550,7 +19550,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>207.622951</v>
+        <v>208.623102</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19731,7 +19731,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>199.698808</v>
+        <v>200.698958</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19909,7 +19909,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>39.722593</v>
+        <v>40.722743</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20087,7 +20087,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>273.688715</v>
+        <v>274.688866</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20268,7 +20268,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>229.685706</v>
+        <v>230.685856</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20452,7 +20452,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>168.944456</v>
+        <v>169.944606</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20633,7 +20633,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>110.723773</v>
+        <v>111.723924</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20814,7 +20814,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>228.122581</v>
+        <v>229.122731</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -20995,7 +20995,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>236.7661</v>
+        <v>237.76625</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21176,7 +21176,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>189.609722</v>
+        <v>190.609873</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21357,7 +21357,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>138.698414</v>
+        <v>139.698565</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21538,7 +21538,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>111.694329</v>
+        <v>112.694479</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21719,7 +21719,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>70.936678</v>
+        <v>71.936829</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21900,7 +21900,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>47.72397</v>
+        <v>48.72412</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22078,7 +22078,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>280.834572</v>
+        <v>281.834722</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22256,7 +22256,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>266.645451</v>
+        <v>267.645602</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22437,7 +22437,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>276.595995</v>
+        <v>277.596146</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22618,7 +22618,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>168.942859</v>
+        <v>169.943009</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22799,7 +22799,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>122.723137</v>
+        <v>123.723287</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -22980,7 +22980,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>140.544306</v>
+        <v>141.544456</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23158,7 +23158,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>59.588542</v>
+        <v>60.588692</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23339,7 +23339,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>255.564664</v>
+        <v>256.564815</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23523,7 +23523,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>229.705718</v>
+        <v>230.705868</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23701,7 +23701,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>207.576157</v>
+        <v>208.576308</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23882,7 +23882,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>11.596667</v>
+        <v>12.596817</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24063,7 +24063,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>193.885278</v>
+        <v>194.885428</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24241,7 +24241,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>271.503368</v>
+        <v>272.503519</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24422,7 +24422,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>111.695752</v>
+        <v>112.695903</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24603,7 +24603,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>95.54288200000001</v>
+        <v>96.543032</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24776,7 +24776,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>266.597963</v>
+        <v>267.598113</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -24957,7 +24957,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>96.798391</v>
+        <v>97.798542</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25138,7 +25138,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>25.675081</v>
+        <v>26.675231</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25319,7 +25319,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>180.805532</v>
+        <v>181.805683</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25500,7 +25500,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>174.956944</v>
+        <v>175.957095</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25678,7 +25678,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>284.647986</v>
+        <v>285.648137</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25856,7 +25856,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>210.488345</v>
+        <v>211.488495</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26037,7 +26037,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>168.942315</v>
+        <v>169.942465</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26213,7 +26213,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>104.814815</v>
+        <v>105.814965</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26394,7 +26394,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>38.835752</v>
+        <v>39.835903</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26572,7 +26572,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>266.648657</v>
+        <v>267.648808</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26750,7 +26750,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>271.505023</v>
+        <v>272.505174</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -26889,7 +26889,7 @@
         <v>46090.5815483912</v>
       </c>
       <c r="AQ148">
-        <v>7.690405</v>
+        <v>8.690556000000001</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27070,7 +27070,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>207.685648</v>
+        <v>208.685799</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27248,7 +27248,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>241.822326</v>
+        <v>242.822477</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27426,7 +27426,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>238.566794</v>
+        <v>239.566944</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27607,7 +27607,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>201.686644</v>
+        <v>202.686794</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27788,7 +27788,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>60.604826</v>
+        <v>61.604977</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -27969,7 +27969,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>173.818819</v>
+        <v>174.81897</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28150,7 +28150,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>173.618877</v>
+        <v>174.619028</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28328,7 +28328,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>40.951863</v>
+        <v>41.952014</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28512,7 +28512,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>96.805938</v>
+        <v>97.806088</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28693,7 +28693,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>195.517014</v>
+        <v>196.517164</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -28882,7 +28882,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>185.582245</v>
+        <v>186.582396</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29050,7 +29050,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>215.652419</v>
+        <v>216.652569</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29231,7 +29231,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>168.94162</v>
+        <v>169.941771</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29412,7 +29412,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>112.515463</v>
+        <v>113.515613</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29593,7 +29593,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>53.628484</v>
+        <v>54.628634</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29774,7 +29774,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>237.874201</v>
+        <v>238.874352</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -29955,7 +29955,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>193.890891</v>
+        <v>194.891042</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30136,7 +30136,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>117.538414</v>
+        <v>118.538565</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30314,7 +30314,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>40.956308</v>
+        <v>41.956458</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30492,7 +30492,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>227.897014</v>
+        <v>228.897164</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30673,7 +30673,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>143.643461</v>
+        <v>144.643611</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30851,7 +30851,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>111.692674</v>
+        <v>112.692824</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31032,7 +31032,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>11.597697</v>
+        <v>12.597847</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31210,7 +31210,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>276.598796</v>
+        <v>277.598947</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31391,7 +31391,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>252.949097</v>
+        <v>253.949248</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31569,7 +31569,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>61.679653</v>
+        <v>62.679803</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31747,7 +31747,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>34.724954</v>
+        <v>35.725104</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -31920,7 +31920,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>192.591921</v>
+        <v>193.592072</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32101,7 +32101,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>70.936076</v>
+        <v>71.936227</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32279,7 +32279,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>20.571563</v>
+        <v>21.571713</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32457,7 +32457,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>227.901956</v>
+        <v>228.902106</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32635,7 +32635,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>280.834965</v>
+        <v>281.835116</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32813,7 +32813,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>202.603032</v>
+        <v>203.603183</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -32991,7 +32991,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>273.598345</v>
+        <v>274.598495</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33169,7 +33169,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>264.705185</v>
+        <v>265.705336</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33347,7 +33347,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>202.623785</v>
+        <v>203.623935</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33528,7 +33528,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>131.72081</v>
+        <v>132.720961</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33709,7 +33709,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>0.878947</v>
+        <v>1.879097</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -33887,7 +33887,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>273.597986</v>
+        <v>274.598137</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34068,7 +34068,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>229.701528</v>
+        <v>230.701678</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34249,7 +34249,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>174.956227</v>
+        <v>175.956377</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34430,7 +34430,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>207.515938</v>
+        <v>208.516088</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34611,7 +34611,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>118.669282</v>
+        <v>119.669433</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34789,7 +34789,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>40.954282</v>
+        <v>41.954433</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -34967,7 +34967,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>280.842535</v>
+        <v>281.842685</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35135,7 +35135,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>215.664606</v>
+        <v>216.664757</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35316,7 +35316,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>193.888403</v>
+        <v>194.888553</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35500,7 +35500,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>174.959769</v>
+        <v>175.959919</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35684,7 +35684,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>229.705347</v>
+        <v>230.705498</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35865,7 +35865,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>96.797708</v>
+        <v>97.797859</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36043,7 +36043,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>273.688993</v>
+        <v>274.689144</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36221,7 +36221,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>287.909826</v>
+        <v>288.909977</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36402,7 +36402,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>193.894248</v>
+        <v>194.894398</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36580,7 +36580,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>167.681644</v>
+        <v>168.681794</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36761,7 +36761,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>260.925532</v>
+        <v>261.925683</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -36939,7 +36939,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>271.503935</v>
+        <v>272.504086</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37117,7 +37117,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>199.607488</v>
+        <v>200.607639</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37295,7 +37295,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>24.60419</v>
+        <v>25.60434</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37476,7 +37476,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>255.561505</v>
+        <v>256.561655</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37657,7 +37657,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>203.530926</v>
+        <v>204.531076</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37835,7 +37835,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>61.685266</v>
+        <v>62.685417</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38013,7 +38013,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>276.57213</v>
+        <v>277.57228</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38191,7 +38191,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>273.688449</v>
+        <v>274.6886</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38369,7 +38369,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>7.541829</v>
+        <v>8.541979</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38547,7 +38547,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>272.610671</v>
+        <v>273.610822</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38725,7 +38725,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>284.593252</v>
+        <v>285.593403</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -38903,7 +38903,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>286.733646</v>
+        <v>287.733796</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39081,7 +39081,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>276.646829</v>
+        <v>277.646979</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39259,7 +39259,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>238.568519</v>
+        <v>239.568669</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39440,7 +39440,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>238.586493</v>
+        <v>239.586644</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39621,7 +39621,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>143.911528</v>
+        <v>144.911678</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39802,7 +39802,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>0.703947</v>
+        <v>1.704097</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -39980,7 +39980,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>285.68897</v>
+        <v>286.68912</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40158,7 +40158,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>276.587894</v>
+        <v>277.588044</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40336,7 +40336,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>285.684838</v>
+        <v>286.684988</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40517,7 +40517,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>186.639144</v>
+        <v>187.639294</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40698,7 +40698,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>118.693438</v>
+        <v>119.693588</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -40879,7 +40879,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>111.711586</v>
+        <v>112.711736</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41060,7 +41060,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>46.933079</v>
+        <v>47.933229</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41241,7 +41241,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>46.934757</v>
+        <v>47.934907</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41422,7 +41422,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>193.8936</v>
+        <v>194.89375</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41603,7 +41603,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>245.659074</v>
+        <v>246.659225</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41781,7 +41781,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>262.900382</v>
+        <v>263.900532</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -41962,7 +41962,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>202.669988</v>
+        <v>203.670139</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42146,7 +42146,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>194.910185</v>
+        <v>195.910336</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42327,7 +42327,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>174.958079</v>
+        <v>175.958229</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42505,7 +42505,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>125.886944</v>
+        <v>126.887095</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42686,7 +42686,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>11.595556</v>
+        <v>12.595706</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42867,7 +42867,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>237.874734</v>
+        <v>238.874884</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43048,7 +43048,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>193.753194</v>
+        <v>194.753345</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43229,7 +43229,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>96.798935</v>
+        <v>97.799086</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43407,7 +43407,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>61.6786</v>
+        <v>62.67875</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43588,7 +43588,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>112.515961</v>
+        <v>113.516111</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43769,7 +43769,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>227.900729</v>
+        <v>228.90088</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -43942,7 +43942,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>273.573229</v>
+        <v>274.57338</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44120,7 +44120,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>238.567303</v>
+        <v>239.567454</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44304,7 +44304,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>202.601377</v>
+        <v>203.601528</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44485,7 +44485,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>145.855961</v>
+        <v>146.856111</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44669,7 +44669,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>174.660845</v>
+        <v>175.660995</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44850,7 +44850,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>168.940741</v>
+        <v>169.940891</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45031,7 +45031,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>19.719549</v>
+        <v>20.719699</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45209,7 +45209,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>238.567708</v>
+        <v>239.567859</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45390,7 +45390,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>209.828241</v>
+        <v>210.828391</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45571,7 +45571,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>46.678426</v>
+        <v>47.678576</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45752,7 +45752,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>258.720903</v>
+        <v>259.721053</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -45933,7 +45933,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>47.724387</v>
+        <v>48.724537</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46043,7 +46043,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>0.874317</v>
+        <v>1.874468</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46153,7 +46153,7 @@
         <v>46097.39764412037</v>
       </c>
       <c r="AN256">
-        <v>0.874306</v>
+        <v>1.874456</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46334,7 +46334,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>70.93535900000001</v>
+        <v>71.935509</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46515,7 +46515,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>237.835313</v>
+        <v>238.835463</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46693,7 +46693,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>168.950486</v>
+        <v>169.950637</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46874,7 +46874,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>168.948333</v>
+        <v>169.948484</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47052,7 +47052,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>143.532882</v>
+        <v>144.533032</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47228,7 +47228,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>235.779572</v>
+        <v>236.779722</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47406,7 +47406,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>159.939051</v>
+        <v>160.939201</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47590,7 +47590,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>145.711273</v>
+        <v>146.711424</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47768,7 +47768,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>94.70796300000001</v>
+        <v>95.708113</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -47949,7 +47949,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>266.698009</v>
+        <v>267.69816</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48127,7 +48127,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>276.646088</v>
+        <v>277.646238</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48308,7 +48308,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>255.561852</v>
+        <v>256.562002</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48489,7 +48489,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>131.720706</v>
+        <v>132.720856</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48667,7 +48667,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>145.712083</v>
+        <v>146.712234</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48848,7 +48848,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>111.695475</v>
+        <v>112.695625</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49029,7 +49029,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>255.562396</v>
+        <v>256.562546</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49207,7 +49207,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>174.952477</v>
+        <v>175.952627</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49391,7 +49391,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>126.699317</v>
+        <v>127.699468</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49572,7 +49572,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>265.591204</v>
+        <v>266.591354</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49753,7 +49753,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>180.806725</v>
+        <v>181.806875</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -49934,7 +49934,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>111.712245</v>
+        <v>112.712396</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50115,7 +50115,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>132.893333</v>
+        <v>133.893484</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50296,7 +50296,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>251.783194</v>
+        <v>252.783345</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50503,7 +50503,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>131.826389</v>
+        <v>132.826539</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50681,7 +50681,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>122.622396</v>
+        <v>123.622546</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50862,7 +50862,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>105.655104</v>
+        <v>106.655255</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51046,7 +51046,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>160.942477</v>
+        <v>161.942627</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51185,7 +51185,7 @@
         <v>46090.58126142361</v>
       </c>
       <c r="AQ284">
-        <v>7.690694</v>
+        <v>8.690844999999999</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51363,7 +51363,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>252.949468</v>
+        <v>253.949618</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51541,7 +51541,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>264.706134</v>
+        <v>265.706285</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51719,7 +51719,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>227.901794</v>
+        <v>228.901944</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -51900,7 +51900,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>207.629861</v>
+        <v>208.630012</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52084,7 +52084,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>148.95728</v>
+        <v>149.957431</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52265,7 +52265,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>126.692975</v>
+        <v>127.693125</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52446,7 +52446,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>251.911863</v>
+        <v>252.912014</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52624,7 +52624,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>265.911065</v>
+        <v>266.911215</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52805,7 +52805,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>210.518958</v>
+        <v>211.519109</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -52983,7 +52983,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>271.501968</v>
+        <v>272.502118</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53164,7 +53164,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>193.894815</v>
+        <v>194.894965</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53345,7 +53345,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>0.875556</v>
+        <v>1.875706</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53526,7 +53526,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>111.563704</v>
+        <v>112.563854</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53704,7 +53704,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>238.569641</v>
+        <v>239.569792</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -53843,7 +53843,7 @@
         <v>46090.58068733796</v>
       </c>
       <c r="AQ299">
-        <v>7.691262</v>
+        <v>8.691412</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54032,7 +54032,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>262.900845</v>
+        <v>263.900995</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54213,7 +54213,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>193.887685</v>
+        <v>194.887836</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54391,7 +54391,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>168.699155</v>
+        <v>169.699306</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54572,7 +54572,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>90.84487300000001</v>
+        <v>91.845023</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54758,7 +54758,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>203.660625</v>
+        <v>204.660775</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -54936,7 +54936,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>277.940567</v>
+        <v>278.940718</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55117,7 +55117,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>167.612778</v>
+        <v>168.612928</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55298,7 +55298,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>122.722986</v>
+        <v>123.723137</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55479,7 +55479,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>96.810451</v>
+        <v>97.810602</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55660,7 +55660,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>70.93718800000001</v>
+        <v>71.937338</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -55841,7 +55841,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>167.611343</v>
+        <v>168.611493</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56022,7 +56022,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>167.613113</v>
+        <v>168.613264</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56132,7 +56132,7 @@
         <v>46097.39763636574</v>
       </c>
       <c r="AN312">
-        <v>0.874317</v>
+        <v>1.874468</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56310,7 +56310,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>271.50235</v>
+        <v>272.5025</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56488,7 +56488,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>40.958588</v>
+        <v>41.958738</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56669,7 +56669,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>224.564039</v>
+        <v>225.56419</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -56847,7 +56847,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>20.571042</v>
+        <v>21.571192</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57028,7 +57028,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>143.64441</v>
+        <v>144.64456</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57209,7 +57209,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>0.876019</v>
+        <v>1.876169</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57348,7 +57348,7 @@
         <v>46090.58107568287</v>
       </c>
       <c r="AQ319">
-        <v>7.69088</v>
+        <v>8.69103</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57529,7 +57529,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>224.566829</v>
+        <v>225.566979</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57710,7 +57710,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>237.872072</v>
+        <v>238.872222</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -57888,7 +57888,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>46.601979</v>
+        <v>47.60213</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58066,7 +58066,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>280.835417</v>
+        <v>281.835567</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58247,7 +58247,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>174.95162</v>
+        <v>175.951771</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58425,7 +58425,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>138.661701</v>
+        <v>139.661852</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58606,7 +58606,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>126.696956</v>
+        <v>127.697106</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -58787,7 +58787,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>259.609468</v>
+        <v>260.609618</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -58968,7 +58968,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>214.668484</v>
+        <v>215.668634</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59149,7 +59149,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>96.81197899999999</v>
+        <v>97.81213</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59330,7 +59330,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>55.814595</v>
+        <v>56.814745</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59508,7 +59508,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>207.575856</v>
+        <v>208.576007</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59692,7 +59692,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>153.586574</v>
+        <v>154.586725</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -59870,7 +59870,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>238.56897</v>
+        <v>239.56912</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60051,7 +60051,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>132.889549</v>
+        <v>133.889699</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60232,7 +60232,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>122.622824</v>
+        <v>123.622975</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60410,7 +60410,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>217.593449</v>
+        <v>218.5936</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60591,7 +60591,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>63.575313</v>
+        <v>64.575463</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -60772,7 +60772,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>209.824884</v>
+        <v>210.825035</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -60948,7 +60948,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>143.643924</v>
+        <v>144.644074</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61058,7 +61058,7 @@
         <v>46092.38034266204</v>
       </c>
       <c r="AN340">
-        <v>5.891609</v>
+        <v>6.891759</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61239,7 +61239,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>0.876516</v>
+        <v>1.876667</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61417,7 +61417,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>285.693796</v>
+        <v>286.693947</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61598,7 +61598,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>195.892766</v>
+        <v>196.892917</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -61779,7 +61779,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>174.958981</v>
+        <v>175.959132</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -61960,7 +61960,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>124.607002</v>
+        <v>125.607153</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62141,7 +62141,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>242.932141</v>
+        <v>243.932292</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62322,7 +62322,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>40.77287</v>
+        <v>41.773021</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62503,7 +62503,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>21.945313</v>
+        <v>22.945463</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62684,7 +62684,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>105.655718</v>
+        <v>106.655868</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -62862,7 +62862,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>199.652523</v>
+        <v>200.652674</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63043,7 +63043,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>178.591042</v>
+        <v>179.591192</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63221,7 +63221,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>143.645035</v>
+        <v>144.645185</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63402,7 +63402,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>124.608229</v>
+        <v>125.60838</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63583,7 +63583,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>251.912083</v>
+        <v>252.912234</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -63764,7 +63764,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>180.806273</v>
+        <v>181.806424</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -63945,7 +63945,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>168.939977</v>
+        <v>169.940127</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64126,7 +64126,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>175.012488</v>
+        <v>176.012639</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64307,7 +64307,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>110.727234</v>
+        <v>111.727384</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64488,7 +64488,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>60.606424</v>
+        <v>61.606574</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64669,7 +64669,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>276.596701</v>
+        <v>277.596852</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -64847,7 +64847,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>277.938877</v>
+        <v>278.939028</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65028,7 +65028,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>91.726169</v>
+        <v>92.726319</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65209,7 +65209,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>46.740486</v>
+        <v>47.740637</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65387,7 +65387,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>284.587546</v>
+        <v>285.587697</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65568,7 +65568,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>174.960197</v>
+        <v>175.960347</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -65746,7 +65746,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>94.707882</v>
+        <v>95.708032</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -65927,7 +65927,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>255.562917</v>
+        <v>256.563067</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66108,7 +66108,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>145.857465</v>
+        <v>146.857616</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66289,7 +66289,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>143.8925</v>
+        <v>144.89265</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66467,7 +66467,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>271.501701</v>
+        <v>272.501852</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66648,7 +66648,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>242.929456</v>
+        <v>243.929606</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -66826,7 +66826,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>161.529653</v>
+        <v>162.529803</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67004,7 +67004,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>245.722014</v>
+        <v>246.722164</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67185,7 +67185,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>193.889039</v>
+        <v>194.88919</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67366,7 +67366,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>0.875208</v>
+        <v>1.875359</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67544,7 +67544,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>280.727454</v>
+        <v>281.727604</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67722,7 +67722,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>276.63331</v>
+        <v>277.633461</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -67903,7 +67903,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>124.613623</v>
+        <v>125.613773</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68081,7 +68081,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>277.939676</v>
+        <v>278.939826</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68259,7 +68259,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>255.563438</v>
+        <v>256.563588</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68437,7 +68437,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>285.685197</v>
+        <v>286.685347</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -68615,7 +68615,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>133.621574</v>
+        <v>134.621725</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -68793,7 +68793,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>271.500231</v>
+        <v>272.500382</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -68971,7 +68971,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>238.566111</v>
+        <v>239.566262</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69152,7 +69152,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>229.698738</v>
+        <v>230.698889</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69333,7 +69333,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>145.856782</v>
+        <v>146.856933</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69514,7 +69514,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>90.843715</v>
+        <v>91.84386600000001</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69695,7 +69695,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>96.810903</v>
+        <v>97.811053</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -69868,7 +69868,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>192.592269</v>
+        <v>193.592419</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70041,7 +70041,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>192.591806</v>
+        <v>193.591956</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70222,7 +70222,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>96.80932900000001</v>
+        <v>97.809479</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70403,7 +70403,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>111.70985</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70584,7 +70584,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>124.607211</v>
+        <v>125.607361</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>281.834433</v>
+        <v>282.834294</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>124.950428</v>
+        <v>125.950289</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>112.708472</v>
+        <v>113.708333</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>236.780093</v>
+        <v>237.779954</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>239.566644</v>
+        <v>240.566505</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>47.93419</v>
+        <v>48.934051</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>274.604144</v>
+        <v>275.604005</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>223.64478</v>
+        <v>224.644641</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>207.728067</v>
+        <v>208.727928</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>123.624711</v>
+        <v>124.624572</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>208.63044</v>
+        <v>209.630301</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>286.688137</v>
+        <v>287.687998</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>272.503287</v>
+        <v>273.503148</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>241.631817</v>
+        <v>242.631678</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>243.92912</v>
+        <v>244.928981</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>123.578935</v>
+        <v>124.578796</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>105.815197</v>
+        <v>106.815058</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>211.515949</v>
+        <v>212.51581</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>203.604711</v>
+        <v>204.604572</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>124.950856</v>
+        <v>125.950718</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>41.952882</v>
+        <v>42.952743</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>40.698079</v>
+        <v>41.69794</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>47.931609</v>
+        <v>48.93147</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>236.77956</v>
+        <v>237.779421</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>123.723773</v>
+        <v>124.723634</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>21.577928</v>
+        <v>22.577789</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>71.934583</v>
+        <v>72.934444</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>272.508796</v>
+        <v>273.508657</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>193.59228</v>
+        <v>194.592141</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>202.685764</v>
+        <v>203.685625</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>132.82581</v>
+        <v>133.825671</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>274.599051</v>
+        <v>275.598912</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>131.607211</v>
+        <v>132.607072</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>210.827766</v>
+        <v>211.827627</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>119.725556</v>
+        <v>120.725417</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>238.873565</v>
+        <v>239.873426</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>246.659306</v>
+        <v>247.659167</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7351,7 +7351,7 @@
         <v>46076.71127025463</v>
       </c>
       <c r="J39" s="2">
-        <v>46097.58292320602</v>
+        <v>46099.50652622685</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -7424,9 +7424,19 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD39" t="inlineStr">
         <is>
           <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -7455,8 +7465,17 @@
       <c r="AO39" s="2">
         <v>46090.58235540509</v>
       </c>
+      <c r="AP39" s="2">
+        <v>46099.50652210649</v>
+      </c>
       <c r="AQ39">
-        <v>8.689745</v>
+        <v>8.924167000000001</v>
+      </c>
+      <c r="AR39" s="2">
+        <v>46099.50652269676</v>
+      </c>
+      <c r="AT39">
+        <v>0.76544</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7637,7 +7656,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>133.891204</v>
+        <v>134.891065</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7818,7 +7837,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>112.705451</v>
+        <v>113.705313</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -7999,7 +8018,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>71.695185</v>
+        <v>72.695046</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8177,7 +8196,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>41.954873</v>
+        <v>42.954734</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8358,7 +8377,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>61.618831</v>
+        <v>62.618692</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8539,7 +8558,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>20.718866</v>
+        <v>21.718727</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8720,7 +8739,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>195.910567</v>
+        <v>196.910428</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8901,7 +8920,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>210.827153</v>
+        <v>211.827014</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9035,7 +9054,7 @@
         <v>46090.58140600695</v>
       </c>
       <c r="AQ48">
-        <v>8.690694000000001</v>
+        <v>9.690556000000001</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9219,7 +9238,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>161.943924</v>
+        <v>162.943785</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9400,7 +9419,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>161.942708</v>
+        <v>162.942569</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9568,7 +9587,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>19.592963</v>
+        <v>20.592824</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9749,7 +9768,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>238.874549</v>
+        <v>239.87441</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9927,7 +9946,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>239.568056</v>
+        <v>240.567917</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10111,7 +10130,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>146.710671</v>
+        <v>147.710532</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10292,7 +10311,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>252.783542</v>
+        <v>253.783403</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10470,7 +10489,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>19.592222</v>
+        <v>20.592083</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10654,7 +10673,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>230.541076</v>
+        <v>231.540938</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10668,12 +10687,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="E58" s="2">
@@ -10688,7 +10707,7 @@
         <v>46076.60419387731</v>
       </c>
       <c r="J58" s="2">
-        <v>46097.58153351852</v>
+        <v>46099.50513487268</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -10761,14 +10780,24 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD58" t="inlineStr">
         <is>
           <t>Reprovado</t>
         </is>
       </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
+        </is>
+      </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="AI58" s="2">
@@ -10784,16 +10813,25 @@
         <v>46090.57999959491</v>
       </c>
       <c r="AM58" s="2">
-        <v>46090.58088317129</v>
+        <v>46099.5051354051</v>
       </c>
       <c r="AN58">
-        <v>0.00088</v>
+        <v>0.000903</v>
       </c>
       <c r="AO58" s="2">
         <v>46090.58088335648</v>
       </c>
+      <c r="AP58" s="2">
+        <v>46099.50510756945</v>
+      </c>
       <c r="AQ58">
-        <v>8.691215</v>
+        <v>8.924213</v>
+      </c>
+      <c r="AR58" s="2">
+        <v>46099.50513576389</v>
+      </c>
+      <c r="AT58">
+        <v>0.766829</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -10971,7 +11009,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>277.645729</v>
+        <v>278.64559</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11149,7 +11187,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>267.694549</v>
+        <v>268.69441</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11330,7 +11368,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>97.797095</v>
+        <v>98.79695599999999</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11508,7 +11546,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>62.68838</v>
+        <v>63.688241</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11686,7 +11724,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>239.567222</v>
+        <v>240.567083</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11867,7 +11905,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>133.895313</v>
+        <v>134.895174</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12048,7 +12086,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>113.514954</v>
+        <v>114.514815</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12229,7 +12267,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>175.568796</v>
+        <v>176.568657</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12407,7 +12445,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>242.822905</v>
+        <v>243.822766</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12585,7 +12623,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>203.624051</v>
+        <v>204.623912</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12769,7 +12807,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>123.623924</v>
+        <v>124.623785</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -12947,7 +12985,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>61.598472</v>
+        <v>62.598333</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13125,7 +13163,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>278.938866</v>
+        <v>279.938727</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13303,7 +13341,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>281.831759</v>
+        <v>282.83162</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13481,7 +13519,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>239.582998</v>
+        <v>240.582859</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13662,7 +13700,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>196.684525</v>
+        <v>197.684387</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13840,7 +13878,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>132.721123</v>
+        <v>133.720984</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14021,7 +14059,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>139.717083</v>
+        <v>140.716944</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14202,7 +14240,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>91.84478</v>
+        <v>92.844641</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14383,7 +14421,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>96.542326</v>
+        <v>97.542188</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14564,7 +14602,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>41.773715</v>
+        <v>42.773576</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14745,7 +14783,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>1.879572</v>
+        <v>2.879433</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -14931,7 +14969,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>253.654433</v>
+        <v>254.654294</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15109,7 +15147,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>190.680648</v>
+        <v>191.680509</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15290,7 +15328,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>125.607639</v>
+        <v>126.6075</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15471,7 +15509,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>1.875197</v>
+        <v>2.875058</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15655,7 +15693,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>194.889294</v>
+        <v>195.889155</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15836,7 +15874,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>112.695799</v>
+        <v>113.69566</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16017,7 +16055,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>267.69794</v>
+        <v>268.697801</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16198,7 +16236,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>161.943704</v>
+        <v>162.943565</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16376,7 +16414,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>146.859063</v>
+        <v>147.858924</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16557,7 +16595,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>141.553819</v>
+        <v>142.553681</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16738,7 +16776,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>131.605868</v>
+        <v>132.605729</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16916,7 +16954,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>246.723264</v>
+        <v>247.723125</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17094,7 +17132,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>277.598009</v>
+        <v>278.59787</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17283,7 +17321,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>225.567674</v>
+        <v>226.567535</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17464,7 +17502,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>194.887581</v>
+        <v>195.887442</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17645,7 +17683,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>175.561644</v>
+        <v>176.561505</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17826,7 +17864,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>97.80645800000001</v>
+        <v>98.806319</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17936,7 +17974,7 @@
         <v>46097.3976521875</v>
       </c>
       <c r="AN98">
-        <v>1.874444</v>
+        <v>2.874306</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18117,7 +18155,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>231.570185</v>
+        <v>232.570046</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18295,7 +18333,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>272.502905</v>
+        <v>273.502766</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18473,7 +18511,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>181.943333</v>
+        <v>182.943194</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18651,7 +18689,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>239.566447</v>
+        <v>240.566308</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18832,7 +18870,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>71.93820599999999</v>
+        <v>72.938067</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19010,7 +19048,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>278.939259</v>
+        <v>279.93912</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19188,7 +19226,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>190.553924</v>
+        <v>191.553785</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19369,7 +19407,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>112.709028</v>
+        <v>113.708889</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19550,7 +19588,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>208.623102</v>
+        <v>209.622963</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19731,7 +19769,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>200.698958</v>
+        <v>201.698819</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19909,7 +19947,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>40.722743</v>
+        <v>41.722604</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20087,7 +20125,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>274.688866</v>
+        <v>275.688727</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20268,7 +20306,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>230.685856</v>
+        <v>231.685718</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20452,7 +20490,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>169.944606</v>
+        <v>170.944468</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20633,7 +20671,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>111.723924</v>
+        <v>112.723785</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20814,7 +20852,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>229.122731</v>
+        <v>230.122593</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -20995,7 +21033,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>237.76625</v>
+        <v>238.766111</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21176,7 +21214,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>190.609873</v>
+        <v>191.609734</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21357,7 +21395,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>139.698565</v>
+        <v>140.698426</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21538,7 +21576,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>112.694479</v>
+        <v>113.69434</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21719,7 +21757,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>71.936829</v>
+        <v>72.93669</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21900,7 +21938,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>48.72412</v>
+        <v>49.723981</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22078,7 +22116,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>281.834722</v>
+        <v>282.834583</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22256,7 +22294,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>267.645602</v>
+        <v>268.645463</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22437,7 +22475,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>277.596146</v>
+        <v>278.596007</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22618,7 +22656,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>169.943009</v>
+        <v>170.94287</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22799,7 +22837,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>123.723287</v>
+        <v>124.723148</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -22980,7 +23018,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>141.544456</v>
+        <v>142.544317</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23158,7 +23196,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>60.588692</v>
+        <v>61.588553</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23339,7 +23377,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>256.564815</v>
+        <v>257.564676</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23523,7 +23561,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>230.705868</v>
+        <v>231.705729</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23701,7 +23739,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>208.576308</v>
+        <v>209.576169</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23882,7 +23920,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>12.596817</v>
+        <v>13.596678</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24063,7 +24101,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>194.885428</v>
+        <v>195.885289</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24241,7 +24279,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>272.503519</v>
+        <v>273.50338</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24422,7 +24460,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>112.695903</v>
+        <v>113.695764</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24603,7 +24641,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>96.543032</v>
+        <v>97.542894</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24776,7 +24814,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>267.598113</v>
+        <v>268.597975</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -24957,7 +24995,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>97.798542</v>
+        <v>98.79840299999999</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25138,7 +25176,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>26.675231</v>
+        <v>27.675093</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25319,7 +25357,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>181.805683</v>
+        <v>182.805544</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25500,7 +25538,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>175.957095</v>
+        <v>176.956956</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25678,7 +25716,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>285.648137</v>
+        <v>286.647998</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25856,7 +25894,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>211.488495</v>
+        <v>212.488356</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26037,7 +26075,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>169.942465</v>
+        <v>170.942326</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26213,7 +26251,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>105.814965</v>
+        <v>106.814826</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26394,7 +26432,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>39.835903</v>
+        <v>40.835764</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26572,7 +26610,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>267.648808</v>
+        <v>268.648669</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26750,7 +26788,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>272.505174</v>
+        <v>273.505035</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -26764,7 +26802,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -26784,7 +26822,7 @@
         <v>46076.60416021991</v>
       </c>
       <c r="J148" s="2">
-        <v>46097.58222946759</v>
+        <v>46099.50642649306</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -26857,9 +26895,19 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD148" t="inlineStr">
         <is>
           <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -26888,8 +26936,17 @@
       <c r="AO148" s="2">
         <v>46090.5815483912</v>
       </c>
+      <c r="AP148" s="2">
+        <v>46099.50642686342</v>
+      </c>
       <c r="AQ148">
-        <v>8.690556000000001</v>
+        <v>8.924873</v>
+      </c>
+      <c r="AR148" s="2">
+        <v>46099.50642746528</v>
+      </c>
+      <c r="AT148">
+        <v>0.765532</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27070,7 +27127,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>208.685799</v>
+        <v>209.68566</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27248,7 +27305,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>242.822477</v>
+        <v>243.822338</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27426,7 +27483,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>239.566944</v>
+        <v>240.566806</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27607,7 +27664,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>202.686794</v>
+        <v>203.686655</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27788,7 +27845,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>61.604977</v>
+        <v>62.604838</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -27969,7 +28026,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>174.81897</v>
+        <v>175.818831</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28150,7 +28207,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>174.619028</v>
+        <v>175.618889</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28328,7 +28385,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>41.952014</v>
+        <v>42.951875</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28512,7 +28569,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>97.806088</v>
+        <v>98.805949</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28693,7 +28750,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>196.517164</v>
+        <v>197.517025</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -28882,7 +28939,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>186.582396</v>
+        <v>187.582257</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29050,7 +29107,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>216.652569</v>
+        <v>217.652431</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29231,7 +29288,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>169.941771</v>
+        <v>170.941632</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29412,7 +29469,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>113.515613</v>
+        <v>114.515475</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29593,7 +29650,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>54.628634</v>
+        <v>55.628495</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29774,7 +29831,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>238.874352</v>
+        <v>239.874213</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -29955,7 +30012,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>194.891042</v>
+        <v>195.890903</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30136,7 +30193,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>118.538565</v>
+        <v>119.538426</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30314,7 +30371,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>41.956458</v>
+        <v>42.956319</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30492,7 +30549,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>228.897164</v>
+        <v>229.897025</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30673,7 +30730,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>144.643611</v>
+        <v>145.643472</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30851,7 +30908,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>112.692824</v>
+        <v>113.692685</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31032,7 +31089,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>12.597847</v>
+        <v>13.597708</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31210,7 +31267,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>277.598947</v>
+        <v>278.598808</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31391,7 +31448,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>253.949248</v>
+        <v>254.949109</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31569,7 +31626,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>62.679803</v>
+        <v>63.679664</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31747,7 +31804,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>35.725104</v>
+        <v>36.724965</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -31920,7 +31977,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>193.592072</v>
+        <v>194.591933</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32101,7 +32158,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>71.936227</v>
+        <v>72.936088</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32279,7 +32336,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>21.571713</v>
+        <v>22.571574</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32457,7 +32514,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>228.902106</v>
+        <v>229.901968</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32635,7 +32692,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>281.835116</v>
+        <v>282.834977</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32813,7 +32870,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>203.603183</v>
+        <v>204.603044</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -32991,7 +33048,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>274.598495</v>
+        <v>275.598356</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33169,7 +33226,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>265.705336</v>
+        <v>266.705197</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33347,7 +33404,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>203.623935</v>
+        <v>204.623796</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33528,7 +33585,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>132.720961</v>
+        <v>133.720822</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33709,7 +33766,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>1.879097</v>
+        <v>2.878958</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -33887,7 +33944,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>274.598137</v>
+        <v>275.597998</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34068,7 +34125,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>230.701678</v>
+        <v>231.701539</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34249,7 +34306,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>175.956377</v>
+        <v>176.956238</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34430,7 +34487,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>208.516088</v>
+        <v>209.515949</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34611,7 +34668,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>119.669433</v>
+        <v>120.669294</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34789,7 +34846,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>41.954433</v>
+        <v>42.954294</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -34967,7 +35024,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>281.842685</v>
+        <v>282.842546</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35135,7 +35192,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>216.664757</v>
+        <v>217.664618</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35316,7 +35373,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>194.888553</v>
+        <v>195.888414</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35500,7 +35557,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>175.959919</v>
+        <v>176.95978</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35684,7 +35741,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>230.705498</v>
+        <v>231.705359</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35865,7 +35922,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>97.797859</v>
+        <v>98.79772</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36043,7 +36100,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>274.689144</v>
+        <v>275.689005</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36221,7 +36278,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>288.909977</v>
+        <v>289.909838</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36402,7 +36459,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>194.894398</v>
+        <v>195.894259</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36580,7 +36637,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>168.681794</v>
+        <v>169.681655</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36761,7 +36818,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>261.925683</v>
+        <v>262.925544</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -36939,7 +36996,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>272.504086</v>
+        <v>273.503947</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37117,7 +37174,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>200.607639</v>
+        <v>201.6075</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37295,7 +37352,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>25.60434</v>
+        <v>26.604201</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37476,7 +37533,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>256.561655</v>
+        <v>257.561516</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37657,7 +37714,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>204.531076</v>
+        <v>205.530938</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37835,7 +37892,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>62.685417</v>
+        <v>63.685278</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38013,7 +38070,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>277.57228</v>
+        <v>278.572141</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38191,7 +38248,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>274.6886</v>
+        <v>275.688461</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38369,7 +38426,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>8.541979</v>
+        <v>9.541840000000001</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38547,7 +38604,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>273.610822</v>
+        <v>274.610683</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38725,7 +38782,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>285.593403</v>
+        <v>286.593264</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -38903,7 +38960,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>287.733796</v>
+        <v>288.733657</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39081,7 +39138,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>277.646979</v>
+        <v>278.64684</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39259,7 +39316,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>239.568669</v>
+        <v>240.56853</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39440,7 +39497,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>239.586644</v>
+        <v>240.586505</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39621,7 +39678,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>144.911678</v>
+        <v>145.911539</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39802,7 +39859,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>1.704097</v>
+        <v>2.703958</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -39980,7 +40037,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>286.68912</v>
+        <v>287.688981</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40158,7 +40215,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>277.588044</v>
+        <v>278.587905</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40336,7 +40393,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>286.684988</v>
+        <v>287.68485</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40517,7 +40574,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>187.639294</v>
+        <v>188.639155</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40698,7 +40755,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>119.693588</v>
+        <v>120.693449</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -40879,7 +40936,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>112.711736</v>
+        <v>113.711597</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41060,7 +41117,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>47.933229</v>
+        <v>48.93309</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41241,7 +41298,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>47.934907</v>
+        <v>48.934769</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41422,7 +41479,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>194.89375</v>
+        <v>195.893611</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41603,7 +41660,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>246.659225</v>
+        <v>247.659086</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41781,7 +41838,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>263.900532</v>
+        <v>264.900394</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -41962,7 +42019,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>203.670139</v>
+        <v>204.67</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42146,7 +42203,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>195.910336</v>
+        <v>196.910197</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42327,7 +42384,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>175.958229</v>
+        <v>176.95809</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42505,7 +42562,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>126.887095</v>
+        <v>127.886956</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42686,7 +42743,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>12.595706</v>
+        <v>13.595567</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42867,7 +42924,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>238.874884</v>
+        <v>239.874745</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43048,7 +43105,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>194.753345</v>
+        <v>195.753206</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43229,7 +43286,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>97.799086</v>
+        <v>98.798947</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43407,7 +43464,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>62.67875</v>
+        <v>63.678611</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43588,7 +43645,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>113.516111</v>
+        <v>114.515972</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43769,7 +43826,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>228.90088</v>
+        <v>229.900741</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -43942,7 +43999,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>274.57338</v>
+        <v>275.573241</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44120,7 +44177,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>239.567454</v>
+        <v>240.567315</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44304,7 +44361,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>203.601528</v>
+        <v>204.601389</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44485,7 +44542,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>146.856111</v>
+        <v>147.855972</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44669,7 +44726,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>175.660995</v>
+        <v>176.660856</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44850,7 +44907,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>169.940891</v>
+        <v>170.940752</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45031,7 +45088,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>20.719699</v>
+        <v>21.71956</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45209,7 +45266,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>239.567859</v>
+        <v>240.56772</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45390,7 +45447,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>210.828391</v>
+        <v>211.828252</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45571,7 +45628,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>47.678576</v>
+        <v>48.678438</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45752,7 +45809,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>259.721053</v>
+        <v>260.720914</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -45933,7 +45990,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>48.724537</v>
+        <v>49.724398</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46043,7 +46100,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>1.874468</v>
+        <v>2.874329</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46153,7 +46210,7 @@
         <v>46097.39764412037</v>
       </c>
       <c r="AN256">
-        <v>1.874456</v>
+        <v>2.874317</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46334,7 +46391,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>71.935509</v>
+        <v>72.93537000000001</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46515,7 +46572,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>238.835463</v>
+        <v>239.835324</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46693,7 +46750,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>169.950637</v>
+        <v>170.950498</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46874,7 +46931,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>169.948484</v>
+        <v>170.948345</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47052,7 +47109,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>144.533032</v>
+        <v>145.532894</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47228,7 +47285,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>236.779722</v>
+        <v>237.779583</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47406,7 +47463,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>160.939201</v>
+        <v>161.939063</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47590,7 +47647,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>146.711424</v>
+        <v>147.711285</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47768,7 +47825,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>95.708113</v>
+        <v>96.707975</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -47949,7 +48006,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>267.69816</v>
+        <v>268.698021</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48127,7 +48184,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>277.646238</v>
+        <v>278.6461</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48308,7 +48365,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>256.562002</v>
+        <v>257.561863</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48489,7 +48546,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>132.720856</v>
+        <v>133.720718</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48667,7 +48724,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>146.712234</v>
+        <v>147.712095</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48848,7 +48905,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>112.695625</v>
+        <v>113.695486</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49029,7 +49086,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>256.562546</v>
+        <v>257.562407</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49207,7 +49264,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>175.952627</v>
+        <v>176.952488</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49391,7 +49448,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>127.699468</v>
+        <v>128.699329</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49572,7 +49629,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>266.591354</v>
+        <v>267.591215</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49753,7 +49810,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>181.806875</v>
+        <v>182.806736</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -49934,7 +49991,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>112.712396</v>
+        <v>113.712257</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50115,7 +50172,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>133.893484</v>
+        <v>134.893345</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50296,7 +50353,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>252.783345</v>
+        <v>253.783206</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50503,7 +50560,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>132.826539</v>
+        <v>133.8264</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50681,7 +50738,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>123.622546</v>
+        <v>124.622407</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50862,7 +50919,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>106.655255</v>
+        <v>107.655116</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51046,7 +51103,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>161.942627</v>
+        <v>162.942488</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51060,7 +51117,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -51080,7 +51137,7 @@
         <v>46076.6041722338</v>
       </c>
       <c r="J284" s="2">
-        <v>46097.58153459491</v>
+        <v>46099.50631019676</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -51153,9 +51210,19 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD284" t="inlineStr">
         <is>
           <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -51184,8 +51251,17 @@
       <c r="AO284" s="2">
         <v>46090.58126142361</v>
       </c>
+      <c r="AP284" s="2">
+        <v>46099.506310625</v>
+      </c>
       <c r="AQ284">
-        <v>8.690844999999999</v>
+        <v>8.925046</v>
+      </c>
+      <c r="AR284" s="2">
+        <v>46099.50631127315</v>
+      </c>
+      <c r="AT284">
+        <v>0.765648</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51363,7 +51439,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>253.949618</v>
+        <v>254.949479</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51541,7 +51617,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>265.706285</v>
+        <v>266.706146</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51719,7 +51795,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>228.901944</v>
+        <v>229.901806</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -51900,7 +51976,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>208.630012</v>
+        <v>209.629873</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52084,7 +52160,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>149.957431</v>
+        <v>150.957292</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52265,7 +52341,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>127.693125</v>
+        <v>128.692986</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52446,7 +52522,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>252.912014</v>
+        <v>253.911875</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52624,7 +52700,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>266.911215</v>
+        <v>267.911076</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52805,7 +52881,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>211.519109</v>
+        <v>212.51897</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -52983,7 +53059,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>272.502118</v>
+        <v>273.501979</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53164,7 +53240,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>194.894965</v>
+        <v>195.894826</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53345,7 +53421,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>1.875706</v>
+        <v>2.875567</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53526,7 +53602,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>112.563854</v>
+        <v>113.563715</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53704,7 +53780,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>239.569792</v>
+        <v>240.569653</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -53718,12 +53794,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="E299" s="2">
@@ -53738,7 +53814,7 @@
         <v>46076.60418768518</v>
       </c>
       <c r="J299" s="2">
-        <v>46097.58083784723</v>
+        <v>46099.50462641203</v>
       </c>
       <c r="N299" t="b">
         <v>0</v>
@@ -53811,14 +53887,24 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD299" t="inlineStr">
         <is>
           <t>Aprovado</t>
         </is>
       </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
+        </is>
+      </c>
       <c r="AF299" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="AI299" s="2">
@@ -53834,16 +53920,25 @@
         <v>46090.58000841436</v>
       </c>
       <c r="AM299" s="2">
-        <v>46090.58068712963</v>
+        <v>46099.50462729167</v>
       </c>
       <c r="AN299">
-        <v>0.000671</v>
+        <v>0.000775</v>
       </c>
       <c r="AO299" s="2">
         <v>46090.58068733796</v>
       </c>
+      <c r="AP299" s="2">
+        <v>46099.50452881945</v>
+      </c>
       <c r="AQ299">
-        <v>8.691412</v>
+        <v>8.923831</v>
+      </c>
+      <c r="AR299" s="2">
+        <v>46099.50462768519</v>
+      </c>
+      <c r="AT299">
+        <v>0.767338</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54032,7 +54127,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>263.900995</v>
+        <v>264.900856</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54213,7 +54308,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>194.887836</v>
+        <v>195.887697</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54391,7 +54486,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>169.699306</v>
+        <v>170.699167</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54572,7 +54667,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>91.845023</v>
+        <v>92.84488399999999</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54758,7 +54853,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>204.660775</v>
+        <v>205.660637</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -54936,7 +55031,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>278.940718</v>
+        <v>279.940579</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55117,7 +55212,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>168.612928</v>
+        <v>169.612789</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55298,7 +55393,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>123.723137</v>
+        <v>124.722998</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55479,7 +55574,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>97.810602</v>
+        <v>98.810463</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55660,7 +55755,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>71.937338</v>
+        <v>72.93719900000001</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -55841,7 +55936,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>168.611493</v>
+        <v>169.611354</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56022,7 +56117,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>168.613264</v>
+        <v>169.613125</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56132,7 +56227,7 @@
         <v>46097.39763636574</v>
       </c>
       <c r="AN312">
-        <v>1.874468</v>
+        <v>2.874329</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56310,7 +56405,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>272.5025</v>
+        <v>273.502361</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56488,7 +56583,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>41.958738</v>
+        <v>42.9586</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56669,7 +56764,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>225.56419</v>
+        <v>226.564051</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -56847,7 +56942,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>21.571192</v>
+        <v>22.571053</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57028,7 +57123,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>144.64456</v>
+        <v>145.644421</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57209,7 +57304,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>1.876169</v>
+        <v>2.87603</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57223,7 +57318,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -57243,7 +57338,7 @@
         <v>46076.6041787037</v>
       </c>
       <c r="J319" s="2">
-        <v>46097.58153369214</v>
+        <v>46099.50602307871</v>
       </c>
       <c r="N319" t="b">
         <v>0</v>
@@ -57316,9 +57411,19 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD319" t="inlineStr">
         <is>
           <t>Reprovado</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -57347,8 +57452,17 @@
       <c r="AO319" s="2">
         <v>46090.58107568287</v>
       </c>
+      <c r="AP319" s="2">
+        <v>46099.50602331018</v>
+      </c>
       <c r="AQ319">
-        <v>8.69103</v>
+        <v>8.924942</v>
+      </c>
+      <c r="AR319" s="2">
+        <v>46099.50602414352</v>
+      </c>
+      <c r="AT319">
+        <v>0.765938</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57529,7 +57643,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>225.566979</v>
+        <v>226.56684</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57710,7 +57824,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>238.872222</v>
+        <v>239.872083</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -57888,7 +58002,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>47.60213</v>
+        <v>48.601991</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58066,7 +58180,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>281.835567</v>
+        <v>282.835428</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58247,7 +58361,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>175.951771</v>
+        <v>176.951632</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58425,7 +58539,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>139.661852</v>
+        <v>140.661713</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58606,7 +58720,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>127.697106</v>
+        <v>128.696968</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -58787,7 +58901,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>260.609618</v>
+        <v>261.609479</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -58968,7 +59082,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>215.668634</v>
+        <v>216.668495</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59149,7 +59263,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>97.81213</v>
+        <v>98.81199100000001</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59330,7 +59444,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>56.814745</v>
+        <v>57.814606</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59508,7 +59622,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>208.576007</v>
+        <v>209.575868</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59692,7 +59806,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>154.586725</v>
+        <v>155.586586</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -59870,7 +59984,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>239.56912</v>
+        <v>240.568981</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60051,7 +60165,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>133.889699</v>
+        <v>134.88956</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60232,7 +60346,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>123.622975</v>
+        <v>124.622836</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60410,7 +60524,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>218.5936</v>
+        <v>219.593461</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60591,7 +60705,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>64.575463</v>
+        <v>65.57532399999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -60772,7 +60886,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>210.825035</v>
+        <v>211.824896</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -60948,7 +61062,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>144.644074</v>
+        <v>145.643935</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61058,7 +61172,7 @@
         <v>46092.38034266204</v>
       </c>
       <c r="AN340">
-        <v>6.891759</v>
+        <v>7.89162</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61239,7 +61353,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>1.876667</v>
+        <v>2.876528</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61417,7 +61531,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>286.693947</v>
+        <v>287.693808</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61598,7 +61712,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>196.892917</v>
+        <v>197.892778</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -61779,7 +61893,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>175.959132</v>
+        <v>176.958993</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -61960,7 +62074,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>125.607153</v>
+        <v>126.607014</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62141,7 +62255,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>243.932292</v>
+        <v>244.932153</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62322,7 +62436,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>41.773021</v>
+        <v>42.772882</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62503,7 +62617,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>22.945463</v>
+        <v>23.945324</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62684,7 +62798,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>106.655868</v>
+        <v>107.655729</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -62862,7 +62976,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>200.652674</v>
+        <v>201.652535</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63043,7 +63157,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>179.591192</v>
+        <v>180.591053</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63221,7 +63335,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>144.645185</v>
+        <v>145.645046</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63402,7 +63516,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>125.60838</v>
+        <v>126.608241</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63583,7 +63697,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>252.912234</v>
+        <v>253.912095</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -63764,7 +63878,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>181.806424</v>
+        <v>182.806285</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -63945,7 +64059,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>169.940127</v>
+        <v>170.939988</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64126,7 +64240,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>176.012639</v>
+        <v>177.0125</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64307,7 +64421,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>111.727384</v>
+        <v>112.727245</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64488,7 +64602,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>61.606574</v>
+        <v>62.606435</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64669,7 +64783,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>277.596852</v>
+        <v>278.596713</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -64847,7 +64961,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>278.939028</v>
+        <v>279.938889</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65028,7 +65142,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>92.726319</v>
+        <v>93.726181</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65209,7 +65323,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>47.740637</v>
+        <v>48.740498</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65387,7 +65501,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>285.587697</v>
+        <v>286.587558</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65568,7 +65682,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>175.960347</v>
+        <v>176.960208</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -65746,7 +65860,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>95.708032</v>
+        <v>96.707894</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -65927,7 +66041,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>256.563067</v>
+        <v>257.562928</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66108,7 +66222,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>146.857616</v>
+        <v>147.857477</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66289,7 +66403,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>144.89265</v>
+        <v>145.892512</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66467,7 +66581,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>272.501852</v>
+        <v>273.501713</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66648,7 +66762,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>243.929606</v>
+        <v>244.929468</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -66826,7 +66940,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>162.529803</v>
+        <v>163.529664</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67004,7 +67118,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>246.722164</v>
+        <v>247.722025</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67185,7 +67299,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>194.88919</v>
+        <v>195.889051</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67366,7 +67480,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>1.875359</v>
+        <v>2.87522</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67544,7 +67658,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>281.727604</v>
+        <v>282.727465</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67722,7 +67836,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>277.633461</v>
+        <v>278.633322</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -67903,7 +68017,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>125.613773</v>
+        <v>126.613634</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68081,7 +68195,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>278.939826</v>
+        <v>279.939688</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68259,7 +68373,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>256.563588</v>
+        <v>257.563449</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68437,7 +68551,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>286.685347</v>
+        <v>287.685208</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -68615,7 +68729,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>134.621725</v>
+        <v>135.621586</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -68793,7 +68907,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>272.500382</v>
+        <v>273.500243</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -68971,7 +69085,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>239.566262</v>
+        <v>240.566123</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69152,7 +69266,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>230.698889</v>
+        <v>231.69875</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69333,7 +69447,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>146.856933</v>
+        <v>147.856794</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69514,7 +69628,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>91.84386600000001</v>
+        <v>92.843727</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69695,7 +69809,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>97.811053</v>
+        <v>98.810914</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -69868,7 +69982,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>193.592419</v>
+        <v>194.59228</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70041,7 +70155,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>193.591956</v>
+        <v>194.591817</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70222,7 +70336,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>97.809479</v>
+        <v>98.80934000000001</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70403,7 +70517,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>112.71</v>
+        <v>113.709861</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70584,7 +70698,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>125.607361</v>
+        <v>126.607222</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>282.834294</v>
+        <v>283.834282</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>125.950289</v>
+        <v>126.950278</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>113.708333</v>
+        <v>114.708322</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>237.779954</v>
+        <v>238.779942</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>240.566505</v>
+        <v>241.566493</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>48.934051</v>
+        <v>49.934039</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>275.604005</v>
+        <v>276.603993</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>224.644641</v>
+        <v>225.64463</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>208.727928</v>
+        <v>209.727917</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>124.624572</v>
+        <v>125.62456</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>209.630301</v>
+        <v>210.630289</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>287.687998</v>
+        <v>288.687986</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>273.503148</v>
+        <v>274.503137</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>242.631678</v>
+        <v>243.631667</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>244.928981</v>
+        <v>245.92897</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>124.578796</v>
+        <v>125.578785</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>106.815058</v>
+        <v>107.815046</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>212.51581</v>
+        <v>213.515799</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>204.604572</v>
+        <v>205.60456</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>125.950718</v>
+        <v>126.950706</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>42.952743</v>
+        <v>43.952731</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>41.69794</v>
+        <v>42.697928</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>48.93147</v>
+        <v>49.931458</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>237.779421</v>
+        <v>238.77941</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>124.723634</v>
+        <v>125.723623</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>22.577789</v>
+        <v>23.577778</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>72.934444</v>
+        <v>73.934433</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>273.508657</v>
+        <v>274.508646</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>194.592141</v>
+        <v>195.59213</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>203.685625</v>
+        <v>204.685613</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>133.825671</v>
+        <v>134.82566</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>275.598912</v>
+        <v>276.5989</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>132.607072</v>
+        <v>133.60706</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>211.827627</v>
+        <v>212.827616</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>120.725417</v>
+        <v>121.725405</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>239.873426</v>
+        <v>240.873414</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>247.659167</v>
+        <v>248.659155</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7347,11 +7347,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H39" s="2">
+        <v>46100.38240085648</v>
+      </c>
       <c r="I39" s="2">
         <v>46076.71127025463</v>
       </c>
       <c r="J39" s="2">
-        <v>46099.50652622685</v>
+        <v>46100.38240104166</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -7444,6 +7447,14 @@
           <t>Gestão</t>
         </is>
       </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>00:51:00</t>
+        </is>
+      </c>
+      <c r="AH39">
+        <v>6</v>
+      </c>
       <c r="AI39" s="2">
         <v>46076.71127598379</v>
       </c>
@@ -7474,8 +7485,17 @@
       <c r="AR39" s="2">
         <v>46099.50652269676</v>
       </c>
+      <c r="AS39" s="2">
+        <v>46100.3824021875</v>
+      </c>
       <c r="AT39">
-        <v>0.76544</v>
+        <v>0.875868</v>
+      </c>
+      <c r="AU39" s="2">
+        <v>46100.38240289352</v>
+      </c>
+      <c r="AW39">
+        <v>0.889549</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7656,7 +7676,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>134.891065</v>
+        <v>135.891053</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7837,7 +7857,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>113.705313</v>
+        <v>114.705301</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8018,7 +8038,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>72.695046</v>
+        <v>73.695035</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8196,7 +8216,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>42.954734</v>
+        <v>43.954722</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8377,7 +8397,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>62.618692</v>
+        <v>63.618681</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8558,7 +8578,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>21.718727</v>
+        <v>22.718715</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8739,7 +8759,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>196.910428</v>
+        <v>197.910417</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8920,7 +8940,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>211.827014</v>
+        <v>212.827002</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -8939,7 +8959,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="E48" s="2">
@@ -8954,7 +8974,7 @@
         <v>46076.60416619213</v>
       </c>
       <c r="J48" s="2">
-        <v>46097.58153456019</v>
+        <v>46100.38120965278</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -9029,7 +9049,7 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="AI48" s="2">
@@ -9045,16 +9065,16 @@
         <v>46090.58026958333</v>
       </c>
       <c r="AM48" s="2">
-        <v>46090.58140582176</v>
+        <v>46100.38120206018</v>
       </c>
       <c r="AN48">
-        <v>0.001134</v>
+        <v>0.001192</v>
       </c>
       <c r="AO48" s="2">
         <v>46090.58140600695</v>
       </c>
       <c r="AQ48">
-        <v>9.690556000000001</v>
+        <v>10.690486</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9238,7 +9258,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>162.943785</v>
+        <v>163.943773</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9419,7 +9439,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>162.942569</v>
+        <v>163.942558</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9587,7 +9607,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>20.592824</v>
+        <v>21.592813</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9768,7 +9788,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>239.87441</v>
+        <v>240.874398</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9946,7 +9966,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>240.567917</v>
+        <v>241.567905</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10130,7 +10150,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>147.710532</v>
+        <v>148.710521</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10311,7 +10331,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>253.783403</v>
+        <v>254.783391</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10489,7 +10509,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>20.592083</v>
+        <v>21.592072</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10673,7 +10693,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>231.540938</v>
+        <v>232.540926</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10687,7 +10707,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10703,11 +10723,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H58" s="2">
+        <v>46100.38269596065</v>
+      </c>
       <c r="I58" s="2">
         <v>46076.60419387731</v>
       </c>
       <c r="J58" s="2">
-        <v>46099.50513487268</v>
+        <v>46100.38269601853</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -10800,6 +10823,14 @@
           <t>Reprovado na Validação</t>
         </is>
       </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>00:55:00</t>
+        </is>
+      </c>
+      <c r="AH58">
+        <v>7</v>
+      </c>
       <c r="AI58" s="2">
         <v>46076.60419797454</v>
       </c>
@@ -10830,8 +10861,17 @@
       <c r="AR58" s="2">
         <v>46099.50513576389</v>
       </c>
+      <c r="AS58" s="2">
+        <v>46100.38269644676</v>
+      </c>
       <c r="AT58">
-        <v>0.766829</v>
+        <v>0.8775579999999999</v>
+      </c>
+      <c r="AU58" s="2">
+        <v>46100.38269733796</v>
+      </c>
+      <c r="AW58">
+        <v>0.889248</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11009,7 +11049,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>278.64559</v>
+        <v>279.645579</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11187,7 +11227,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>268.69441</v>
+        <v>269.694398</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11368,7 +11408,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>98.79695599999999</v>
+        <v>99.796944</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11546,7 +11586,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>63.688241</v>
+        <v>64.68822900000001</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11724,7 +11764,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>240.567083</v>
+        <v>241.567072</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11905,7 +11945,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>134.895174</v>
+        <v>135.895162</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12086,7 +12126,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>114.514815</v>
+        <v>115.514803</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12267,7 +12307,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>176.568657</v>
+        <v>177.568646</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12445,7 +12485,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>243.822766</v>
+        <v>244.822755</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12623,7 +12663,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>204.623912</v>
+        <v>205.6239</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12807,7 +12847,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>124.623785</v>
+        <v>125.623773</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -12985,7 +13025,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>62.598333</v>
+        <v>63.598322</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13163,7 +13203,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>279.938727</v>
+        <v>280.938715</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13341,7 +13381,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>282.83162</v>
+        <v>283.831609</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13519,7 +13559,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>240.582859</v>
+        <v>241.582847</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13700,7 +13740,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>197.684387</v>
+        <v>198.684375</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13878,7 +13918,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>133.720984</v>
+        <v>134.720972</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14059,7 +14099,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>140.716944</v>
+        <v>141.716933</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14240,7 +14280,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>92.844641</v>
+        <v>93.84463</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14421,7 +14461,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>97.542188</v>
+        <v>98.542176</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14602,7 +14642,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>42.773576</v>
+        <v>43.773565</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14783,7 +14823,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>2.879433</v>
+        <v>3.879421</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -14969,7 +15009,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>254.654294</v>
+        <v>255.654282</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15147,7 +15187,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>191.680509</v>
+        <v>192.680498</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15328,7 +15368,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>126.6075</v>
+        <v>127.607488</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15509,7 +15549,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>2.875058</v>
+        <v>3.875046</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15693,7 +15733,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>195.889155</v>
+        <v>196.889144</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15874,7 +15914,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>113.69566</v>
+        <v>114.695648</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16055,7 +16095,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>268.697801</v>
+        <v>269.697789</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16236,7 +16276,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>162.943565</v>
+        <v>163.943553</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16414,7 +16454,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>147.858924</v>
+        <v>148.858912</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16595,7 +16635,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>142.553681</v>
+        <v>143.553669</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16776,7 +16816,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>132.605729</v>
+        <v>133.605718</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16954,7 +16994,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>247.723125</v>
+        <v>248.723113</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17132,7 +17172,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>278.59787</v>
+        <v>279.597859</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17321,7 +17361,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>226.567535</v>
+        <v>227.567523</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17502,7 +17542,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>195.887442</v>
+        <v>196.887431</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17683,7 +17723,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>176.561505</v>
+        <v>177.561493</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17864,7 +17904,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>98.806319</v>
+        <v>99.806308</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17974,7 +18014,7 @@
         <v>46097.3976521875</v>
       </c>
       <c r="AN98">
-        <v>2.874306</v>
+        <v>3.874294</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18155,7 +18195,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>232.570046</v>
+        <v>233.570035</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18333,7 +18373,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>273.502766</v>
+        <v>274.502755</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18511,7 +18551,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>182.943194</v>
+        <v>183.943183</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18689,7 +18729,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>240.566308</v>
+        <v>241.566296</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18870,7 +18910,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>72.938067</v>
+        <v>73.938056</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19048,7 +19088,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>279.93912</v>
+        <v>280.939109</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19226,7 +19266,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>191.553785</v>
+        <v>192.553773</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19407,7 +19447,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>113.708889</v>
+        <v>114.708877</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19588,7 +19628,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>209.622963</v>
+        <v>210.622951</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19769,7 +19809,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>201.698819</v>
+        <v>202.698808</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19947,7 +19987,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>41.722604</v>
+        <v>42.722593</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20125,7 +20165,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>275.688727</v>
+        <v>276.688715</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20306,7 +20346,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>231.685718</v>
+        <v>232.685706</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20490,7 +20530,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>170.944468</v>
+        <v>171.944456</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20671,7 +20711,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>112.723785</v>
+        <v>113.723773</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20852,7 +20892,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>230.122593</v>
+        <v>231.122581</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21033,7 +21073,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>238.766111</v>
+        <v>239.7661</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21214,7 +21254,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>191.609734</v>
+        <v>192.609722</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21395,7 +21435,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>140.698426</v>
+        <v>141.698414</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21576,7 +21616,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>113.69434</v>
+        <v>114.694329</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21757,7 +21797,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>72.93669</v>
+        <v>73.936678</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21938,7 +21978,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>49.723981</v>
+        <v>50.72397</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22116,7 +22156,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>282.834583</v>
+        <v>283.834572</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22294,7 +22334,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>268.645463</v>
+        <v>269.645451</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22475,7 +22515,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>278.596007</v>
+        <v>279.595995</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22656,7 +22696,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>170.94287</v>
+        <v>171.942859</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22837,7 +22877,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>124.723148</v>
+        <v>125.723137</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23018,7 +23058,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>142.544317</v>
+        <v>143.544306</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23196,7 +23236,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>61.588553</v>
+        <v>62.588542</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23377,7 +23417,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>257.564676</v>
+        <v>258.564664</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23561,7 +23601,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>231.705729</v>
+        <v>232.705718</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23739,7 +23779,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>209.576169</v>
+        <v>210.576157</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23920,7 +23960,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>13.596678</v>
+        <v>14.596667</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24101,7 +24141,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>195.885289</v>
+        <v>196.885278</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24279,7 +24319,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>273.50338</v>
+        <v>274.503368</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24460,7 +24500,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>113.695764</v>
+        <v>114.695752</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24641,7 +24681,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>97.542894</v>
+        <v>98.54288200000001</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24814,7 +24854,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>268.597975</v>
+        <v>269.597963</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -24995,7 +25035,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>98.79840299999999</v>
+        <v>99.798391</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25176,7 +25216,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>27.675093</v>
+        <v>28.675081</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25357,7 +25397,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>182.805544</v>
+        <v>183.805532</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25538,7 +25578,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>176.956956</v>
+        <v>177.956944</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25716,7 +25756,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>286.647998</v>
+        <v>287.647986</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25894,7 +25934,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>212.488356</v>
+        <v>213.488345</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26075,7 +26115,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>170.942326</v>
+        <v>171.942315</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26251,7 +26291,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>106.814826</v>
+        <v>107.814815</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26432,7 +26472,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>40.835764</v>
+        <v>41.835752</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26610,7 +26650,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>268.648669</v>
+        <v>269.648657</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26788,7 +26828,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>273.505035</v>
+        <v>274.505023</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -26802,7 +26842,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -26818,11 +26858,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H148" s="2">
+        <v>46100.38703587963</v>
+      </c>
       <c r="I148" s="2">
         <v>46076.60416021991</v>
       </c>
       <c r="J148" s="2">
-        <v>46099.50642649306</v>
+        <v>46100.38703594907</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -26915,6 +26958,14 @@
           <t>Gestão</t>
         </is>
       </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>00:35:00</t>
+        </is>
+      </c>
+      <c r="AH148">
+        <v>4</v>
+      </c>
       <c r="AI148" s="2">
         <v>46076.60416425926</v>
       </c>
@@ -26945,8 +26996,17 @@
       <c r="AR148" s="2">
         <v>46099.50642746528</v>
       </c>
+      <c r="AS148" s="2">
+        <v>46100.38703622685</v>
+      </c>
       <c r="AT148">
-        <v>0.765532</v>
+        <v>0.880602</v>
+      </c>
+      <c r="AU148" s="2">
+        <v>46100.38703670139</v>
+      </c>
+      <c r="AW148">
+        <v>0.884919</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27127,7 +27187,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>209.68566</v>
+        <v>210.685648</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27305,7 +27365,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>243.822338</v>
+        <v>244.822326</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27483,7 +27543,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>240.566806</v>
+        <v>241.566794</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27664,7 +27724,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>203.686655</v>
+        <v>204.686644</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27845,7 +27905,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>62.604838</v>
+        <v>63.604826</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28026,7 +28086,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>175.818831</v>
+        <v>176.818819</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28207,7 +28267,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>175.618889</v>
+        <v>176.618877</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28385,7 +28445,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>42.951875</v>
+        <v>43.951863</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28569,7 +28629,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>98.805949</v>
+        <v>99.805938</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28750,7 +28810,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>197.517025</v>
+        <v>198.517014</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -28939,7 +28999,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>187.582257</v>
+        <v>188.582245</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29107,7 +29167,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>217.652431</v>
+        <v>218.652419</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29288,7 +29348,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>170.941632</v>
+        <v>171.94162</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29469,7 +29529,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>114.515475</v>
+        <v>115.515463</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29650,7 +29710,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>55.628495</v>
+        <v>56.628484</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29831,7 +29891,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>239.874213</v>
+        <v>240.874201</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30012,7 +30072,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>195.890903</v>
+        <v>196.890891</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30193,7 +30253,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>119.538426</v>
+        <v>120.538414</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30371,7 +30431,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>42.956319</v>
+        <v>43.956308</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30549,7 +30609,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>229.897025</v>
+        <v>230.897014</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30730,7 +30790,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>145.643472</v>
+        <v>146.643461</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30908,7 +30968,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>113.692685</v>
+        <v>114.692674</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31089,7 +31149,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>13.597708</v>
+        <v>14.597697</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31267,7 +31327,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>278.598808</v>
+        <v>279.598796</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31448,7 +31508,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>254.949109</v>
+        <v>255.949097</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31626,7 +31686,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>63.679664</v>
+        <v>64.679653</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31804,7 +31864,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>36.724965</v>
+        <v>37.724954</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -31977,7 +32037,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>194.591933</v>
+        <v>195.591921</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32158,7 +32218,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>72.936088</v>
+        <v>73.936076</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32336,7 +32396,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>22.571574</v>
+        <v>23.571563</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32514,7 +32574,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>229.901968</v>
+        <v>230.901956</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32692,7 +32752,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>282.834977</v>
+        <v>283.834965</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32870,7 +32930,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>204.603044</v>
+        <v>205.603032</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33048,7 +33108,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>275.598356</v>
+        <v>276.598345</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33226,7 +33286,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>266.705197</v>
+        <v>267.705185</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33404,7 +33464,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>204.623796</v>
+        <v>205.623785</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33585,7 +33645,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>133.720822</v>
+        <v>134.72081</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33766,7 +33826,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>2.878958</v>
+        <v>3.878947</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -33944,7 +34004,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>275.597998</v>
+        <v>276.597986</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34125,7 +34185,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>231.701539</v>
+        <v>232.701528</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34306,7 +34366,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>176.956238</v>
+        <v>177.956227</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34487,7 +34547,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>209.515949</v>
+        <v>210.515938</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34668,7 +34728,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>120.669294</v>
+        <v>121.669282</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34846,7 +34906,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>42.954294</v>
+        <v>43.954282</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35024,7 +35084,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>282.842546</v>
+        <v>283.842535</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35192,7 +35252,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>217.664618</v>
+        <v>218.664606</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35373,7 +35433,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>195.888414</v>
+        <v>196.888403</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35557,7 +35617,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>176.95978</v>
+        <v>177.959769</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35741,7 +35801,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>231.705359</v>
+        <v>232.705347</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35922,7 +35982,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>98.79772</v>
+        <v>99.797708</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36100,7 +36160,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>275.689005</v>
+        <v>276.688993</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36278,7 +36338,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>289.909838</v>
+        <v>290.909826</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36459,7 +36519,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>195.894259</v>
+        <v>196.894248</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36637,7 +36697,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>169.681655</v>
+        <v>170.681644</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36818,7 +36878,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>262.925544</v>
+        <v>263.925532</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -36996,7 +37056,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>273.503947</v>
+        <v>274.503935</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37174,7 +37234,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>201.6075</v>
+        <v>202.607488</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37352,7 +37412,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>26.604201</v>
+        <v>27.60419</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37533,7 +37593,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>257.561516</v>
+        <v>258.561505</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37714,7 +37774,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>205.530938</v>
+        <v>206.530926</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37892,7 +37952,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>63.685278</v>
+        <v>64.685266</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38070,7 +38130,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>278.572141</v>
+        <v>279.57213</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38248,7 +38308,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>275.688461</v>
+        <v>276.688449</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38426,7 +38486,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>9.541840000000001</v>
+        <v>10.541829</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38604,7 +38664,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>274.610683</v>
+        <v>275.610671</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38782,7 +38842,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>286.593264</v>
+        <v>287.593252</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -38960,7 +39020,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>288.733657</v>
+        <v>289.733646</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39138,7 +39198,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>278.64684</v>
+        <v>279.646829</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39316,7 +39376,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>240.56853</v>
+        <v>241.568519</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39497,7 +39557,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>240.586505</v>
+        <v>241.586493</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39678,7 +39738,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>145.911539</v>
+        <v>146.911528</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39859,7 +39919,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>2.703958</v>
+        <v>3.703947</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40037,7 +40097,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>287.688981</v>
+        <v>288.68897</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40215,7 +40275,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>278.587905</v>
+        <v>279.587894</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40393,7 +40453,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>287.68485</v>
+        <v>288.684838</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40574,7 +40634,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>188.639155</v>
+        <v>189.639144</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40755,7 +40815,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>120.693449</v>
+        <v>121.693438</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -40936,7 +40996,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>113.711597</v>
+        <v>114.711586</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41117,7 +41177,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>48.93309</v>
+        <v>49.933079</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41298,7 +41358,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>48.934769</v>
+        <v>49.934757</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41479,7 +41539,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>195.893611</v>
+        <v>196.8936</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41660,7 +41720,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>247.659086</v>
+        <v>248.659074</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41838,7 +41898,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>264.900394</v>
+        <v>265.900382</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42019,7 +42079,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>204.67</v>
+        <v>205.669988</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42203,7 +42263,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>196.910197</v>
+        <v>197.910185</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42384,7 +42444,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>176.95809</v>
+        <v>177.958079</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42562,7 +42622,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>127.886956</v>
+        <v>128.886944</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42743,7 +42803,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>13.595567</v>
+        <v>14.595556</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42924,7 +42984,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>239.874745</v>
+        <v>240.874734</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43105,7 +43165,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>195.753206</v>
+        <v>196.753194</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43286,7 +43346,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>98.798947</v>
+        <v>99.798935</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43464,7 +43524,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>63.678611</v>
+        <v>64.6786</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43645,7 +43705,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>114.515972</v>
+        <v>115.515961</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43826,7 +43886,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>229.900741</v>
+        <v>230.900729</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -43999,7 +44059,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>275.573241</v>
+        <v>276.573229</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44177,7 +44237,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>240.567315</v>
+        <v>241.567303</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44361,7 +44421,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>204.601389</v>
+        <v>205.601377</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44542,7 +44602,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>147.855972</v>
+        <v>148.855961</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44726,7 +44786,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>176.660856</v>
+        <v>177.660845</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44907,7 +44967,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>170.940752</v>
+        <v>171.940741</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45088,7 +45148,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>21.71956</v>
+        <v>22.719549</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45266,7 +45326,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>240.56772</v>
+        <v>241.567708</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45447,7 +45507,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>211.828252</v>
+        <v>212.828241</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45628,7 +45688,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>48.678438</v>
+        <v>49.678426</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45809,7 +45869,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>260.720914</v>
+        <v>261.720903</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -45990,7 +46050,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>49.724398</v>
+        <v>50.724387</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46100,7 +46160,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>2.874329</v>
+        <v>3.874317</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46210,7 +46270,7 @@
         <v>46097.39764412037</v>
       </c>
       <c r="AN256">
-        <v>2.874317</v>
+        <v>3.874306</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46391,7 +46451,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>72.93537000000001</v>
+        <v>73.93535900000001</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46572,7 +46632,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>239.835324</v>
+        <v>240.835313</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46750,7 +46810,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>170.950498</v>
+        <v>171.950486</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46931,7 +46991,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>170.948345</v>
+        <v>171.948333</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47109,7 +47169,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>145.532894</v>
+        <v>146.532882</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47285,7 +47345,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>237.779583</v>
+        <v>238.779572</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47463,7 +47523,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>161.939063</v>
+        <v>162.939051</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47647,7 +47707,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>147.711285</v>
+        <v>148.711273</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47825,7 +47885,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>96.707975</v>
+        <v>97.70796300000001</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48006,7 +48066,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>268.698021</v>
+        <v>269.698009</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48184,7 +48244,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>278.6461</v>
+        <v>279.646088</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48365,7 +48425,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>257.561863</v>
+        <v>258.561852</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48546,7 +48606,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>133.720718</v>
+        <v>134.720706</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48724,7 +48784,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>147.712095</v>
+        <v>148.712083</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48905,7 +48965,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>113.695486</v>
+        <v>114.695475</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49086,7 +49146,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>257.562407</v>
+        <v>258.562396</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49264,7 +49324,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>176.952488</v>
+        <v>177.952477</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49448,7 +49508,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>128.699329</v>
+        <v>129.699317</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49629,7 +49689,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>267.591215</v>
+        <v>268.591204</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49810,7 +49870,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>182.806736</v>
+        <v>183.806725</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -49991,7 +50051,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>113.712257</v>
+        <v>114.712245</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50172,7 +50232,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>134.893345</v>
+        <v>135.893333</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50353,7 +50413,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>253.783206</v>
+        <v>254.783194</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50560,7 +50620,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>133.8264</v>
+        <v>134.826389</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50738,7 +50798,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>124.622407</v>
+        <v>125.622396</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50919,7 +50979,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>107.655116</v>
+        <v>108.655104</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51103,7 +51163,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>162.942488</v>
+        <v>163.942477</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51117,7 +51177,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -51133,11 +51193,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H284" s="2">
+        <v>46100.38526637731</v>
+      </c>
       <c r="I284" s="2">
         <v>46076.6041722338</v>
       </c>
       <c r="J284" s="2">
-        <v>46099.50631019676</v>
+        <v>46100.38526644676</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -51230,6 +51293,14 @@
           <t>Gestão</t>
         </is>
       </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>01:13:00</t>
+        </is>
+      </c>
+      <c r="AH284">
+        <v>7</v>
+      </c>
       <c r="AI284" s="2">
         <v>46076.6041765625</v>
       </c>
@@ -51260,8 +51331,17 @@
       <c r="AR284" s="2">
         <v>46099.50631127315</v>
       </c>
+      <c r="AS284" s="2">
+        <v>46100.38526677083</v>
+      </c>
       <c r="AT284">
-        <v>0.765648</v>
+        <v>0.878947</v>
+      </c>
+      <c r="AU284" s="2">
+        <v>46100.38526741898</v>
+      </c>
+      <c r="AW284">
+        <v>0.886678</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51439,7 +51519,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>254.949479</v>
+        <v>255.949468</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51617,7 +51697,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>266.706146</v>
+        <v>267.706134</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51795,7 +51875,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>229.901806</v>
+        <v>230.901794</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -51976,7 +52056,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>209.629873</v>
+        <v>210.629861</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52160,7 +52240,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>150.957292</v>
+        <v>151.95728</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52341,7 +52421,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>128.692986</v>
+        <v>129.692975</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52522,7 +52602,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>253.911875</v>
+        <v>254.911863</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52700,7 +52780,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>267.911076</v>
+        <v>268.911065</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52881,7 +52961,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>212.51897</v>
+        <v>213.518958</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53059,7 +53139,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>273.501979</v>
+        <v>274.501968</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53240,7 +53320,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>195.894826</v>
+        <v>196.894815</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53421,7 +53501,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>2.875567</v>
+        <v>3.875556</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53602,7 +53682,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>113.563715</v>
+        <v>114.563704</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53780,7 +53860,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>240.569653</v>
+        <v>241.569641</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -53794,7 +53874,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -53810,11 +53890,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H299" s="2">
+        <v>46100.38306050926</v>
+      </c>
       <c r="I299" s="2">
         <v>46076.60418768518</v>
       </c>
       <c r="J299" s="2">
-        <v>46099.50462641203</v>
+        <v>46100.3830605787</v>
       </c>
       <c r="N299" t="b">
         <v>0</v>
@@ -53907,6 +53990,14 @@
           <t>Reprovado na Validação</t>
         </is>
       </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="AH299">
+        <v>9</v>
+      </c>
       <c r="AI299" s="2">
         <v>46076.60419196759</v>
       </c>
@@ -53937,8 +54028,17 @@
       <c r="AR299" s="2">
         <v>46099.50462768519</v>
       </c>
+      <c r="AS299" s="2">
+        <v>46100.38306098379</v>
+      </c>
       <c r="AT299">
-        <v>0.767338</v>
+        <v>0.878426</v>
+      </c>
+      <c r="AU299" s="2">
+        <v>46100.38306148148</v>
+      </c>
+      <c r="AW299">
+        <v>0.888889</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54127,7 +54227,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>264.900856</v>
+        <v>265.900845</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54308,7 +54408,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>195.887697</v>
+        <v>196.887685</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54486,7 +54586,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>170.699167</v>
+        <v>171.699155</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54667,7 +54767,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>92.84488399999999</v>
+        <v>93.84487300000001</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54853,7 +54953,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>205.660637</v>
+        <v>206.660625</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55031,7 +55131,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>279.940579</v>
+        <v>280.940567</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55212,7 +55312,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>169.612789</v>
+        <v>170.612778</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55393,7 +55493,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>124.722998</v>
+        <v>125.722986</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55574,7 +55674,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>98.810463</v>
+        <v>99.810451</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55755,7 +55855,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>72.93719900000001</v>
+        <v>73.93718800000001</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -55936,7 +56036,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>169.611354</v>
+        <v>170.611343</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56117,7 +56217,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>169.613125</v>
+        <v>170.613113</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56227,7 +56327,7 @@
         <v>46097.39763636574</v>
       </c>
       <c r="AN312">
-        <v>2.874329</v>
+        <v>3.874317</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56405,7 +56505,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>273.502361</v>
+        <v>274.50235</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56583,7 +56683,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>42.9586</v>
+        <v>43.958588</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56764,7 +56864,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>226.564051</v>
+        <v>227.564039</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -56942,7 +57042,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>22.571053</v>
+        <v>23.571042</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57123,7 +57223,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>145.644421</v>
+        <v>146.64441</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57304,7 +57404,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>2.87603</v>
+        <v>3.876019</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57318,7 +57418,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -57334,11 +57434,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H319" s="2">
+        <v>46100.38381832176</v>
+      </c>
       <c r="I319" s="2">
         <v>46076.6041787037</v>
       </c>
       <c r="J319" s="2">
-        <v>46099.50602307871</v>
+        <v>46100.38381842592</v>
       </c>
       <c r="N319" t="b">
         <v>0</v>
@@ -57431,6 +57534,14 @@
           <t>Gestão</t>
         </is>
       </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>00:03:00</t>
+        </is>
+      </c>
+      <c r="AH319">
+        <v>1</v>
+      </c>
       <c r="AI319" s="2">
         <v>46076.60418275463</v>
       </c>
@@ -57461,8 +57572,17 @@
       <c r="AR319" s="2">
         <v>46099.50602414352</v>
       </c>
+      <c r="AS319" s="2">
+        <v>46100.38381898149</v>
+      </c>
       <c r="AT319">
-        <v>0.765938</v>
+        <v>0.877789</v>
+      </c>
+      <c r="AU319" s="2">
+        <v>46100.38381973379</v>
+      </c>
+      <c r="AW319">
+        <v>0.8881250000000001</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57643,7 +57763,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>226.56684</v>
+        <v>227.566829</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57824,7 +57944,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>239.872083</v>
+        <v>240.872072</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58002,7 +58122,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>48.601991</v>
+        <v>49.601979</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58180,7 +58300,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>282.835428</v>
+        <v>283.835417</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58361,7 +58481,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>176.951632</v>
+        <v>177.95162</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58539,7 +58659,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>140.661713</v>
+        <v>141.661701</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58720,7 +58840,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>128.696968</v>
+        <v>129.696956</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -58901,7 +59021,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>261.609479</v>
+        <v>262.609468</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59082,7 +59202,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>216.668495</v>
+        <v>217.668484</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59263,7 +59383,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>98.81199100000001</v>
+        <v>99.81197899999999</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59444,7 +59564,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>57.814606</v>
+        <v>58.814595</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59622,7 +59742,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>209.575868</v>
+        <v>210.575856</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59806,7 +59926,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>155.586586</v>
+        <v>156.586574</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -59984,7 +60104,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>240.568981</v>
+        <v>241.56897</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60165,7 +60285,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>134.88956</v>
+        <v>135.889549</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60346,7 +60466,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>124.622836</v>
+        <v>125.622824</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60524,7 +60644,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>219.593461</v>
+        <v>220.593449</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60705,7 +60825,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>65.57532399999999</v>
+        <v>66.57531299999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -60886,7 +61006,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>211.824896</v>
+        <v>212.824884</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61062,7 +61182,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>145.643935</v>
+        <v>146.643924</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61076,7 +61196,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Construção no Canvas</t>
+          <t>Validação</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -61096,7 +61216,7 @@
         <v>46076.60421634259</v>
       </c>
       <c r="J340" s="2">
-        <v>46092.38034170138</v>
+        <v>46100.40009980324</v>
       </c>
       <c r="N340" t="b">
         <v>0</v>
@@ -61159,6 +61279,21 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rehagro.instructure.com/courses/2910 </t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://app.pipefy.com/open-cards/1301624491 </t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>Gestão</t>
+        </is>
+      </c>
       <c r="AI340" s="2">
         <v>46076.60422097222</v>
       </c>
@@ -61171,8 +61306,17 @@
       <c r="AL340" s="2">
         <v>46092.38034266204</v>
       </c>
+      <c r="AM340" s="2">
+        <v>46100.40009168981</v>
+      </c>
       <c r="AN340">
-        <v>7.89162</v>
+        <v>8.019745</v>
+      </c>
+      <c r="AO340" s="2">
+        <v>46100.40009251158</v>
+      </c>
+      <c r="AQ340">
+        <v>0.8718630000000001</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61353,7 +61497,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>2.876528</v>
+        <v>3.876516</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61531,7 +61675,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>287.693808</v>
+        <v>288.693796</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61712,7 +61856,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>197.892778</v>
+        <v>198.892766</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -61893,7 +62037,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>176.958993</v>
+        <v>177.958981</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62074,7 +62218,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>126.607014</v>
+        <v>127.607002</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62255,7 +62399,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>244.932153</v>
+        <v>245.932141</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62436,7 +62580,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>42.772882</v>
+        <v>43.77287</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62617,7 +62761,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>23.945324</v>
+        <v>24.945313</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62798,7 +62942,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>107.655729</v>
+        <v>108.655718</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -62976,7 +63120,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>201.652535</v>
+        <v>202.652523</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63157,7 +63301,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>180.591053</v>
+        <v>181.591042</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63335,7 +63479,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>145.645046</v>
+        <v>146.645035</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63516,7 +63660,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>126.608241</v>
+        <v>127.608229</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63697,7 +63841,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>253.912095</v>
+        <v>254.912083</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -63878,7 +64022,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>182.806285</v>
+        <v>183.806273</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64059,7 +64203,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>170.939988</v>
+        <v>171.939977</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64240,7 +64384,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>177.0125</v>
+        <v>178.012488</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64421,7 +64565,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>112.727245</v>
+        <v>113.727234</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64602,7 +64746,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>62.606435</v>
+        <v>63.606424</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64783,7 +64927,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>278.596713</v>
+        <v>279.596701</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -64961,7 +65105,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>279.938889</v>
+        <v>280.938877</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65142,7 +65286,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>93.726181</v>
+        <v>94.726169</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65323,7 +65467,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>48.740498</v>
+        <v>49.740486</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65501,7 +65645,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>286.587558</v>
+        <v>287.587546</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65682,7 +65826,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>176.960208</v>
+        <v>177.960197</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -65860,7 +66004,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>96.707894</v>
+        <v>97.707882</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66041,7 +66185,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>257.562928</v>
+        <v>258.562917</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66222,7 +66366,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>147.857477</v>
+        <v>148.857465</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66403,7 +66547,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>145.892512</v>
+        <v>146.8925</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66581,7 +66725,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>273.501713</v>
+        <v>274.501701</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66762,7 +66906,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>244.929468</v>
+        <v>245.929456</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -66940,7 +67084,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>163.529664</v>
+        <v>164.529653</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67118,7 +67262,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>247.722025</v>
+        <v>248.722014</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67299,7 +67443,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>195.889051</v>
+        <v>196.889039</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67480,7 +67624,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>2.87522</v>
+        <v>3.875208</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67658,7 +67802,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>282.727465</v>
+        <v>283.727454</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67836,7 +67980,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>278.633322</v>
+        <v>279.63331</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68017,7 +68161,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>126.613634</v>
+        <v>127.613623</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68195,7 +68339,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>279.939688</v>
+        <v>280.939676</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68373,7 +68517,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>257.563449</v>
+        <v>258.563438</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68551,7 +68695,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>287.685208</v>
+        <v>288.685197</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -68729,7 +68873,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>135.621586</v>
+        <v>136.621574</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -68907,7 +69051,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>273.500243</v>
+        <v>274.500231</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69085,7 +69229,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>240.566123</v>
+        <v>241.566111</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69266,7 +69410,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>231.69875</v>
+        <v>232.698738</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69447,7 +69591,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>147.856794</v>
+        <v>148.856782</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69628,7 +69772,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>92.843727</v>
+        <v>93.843715</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69809,7 +69953,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>98.810914</v>
+        <v>99.810903</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -69982,7 +70126,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>194.59228</v>
+        <v>195.592269</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70155,7 +70299,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>194.591817</v>
+        <v>195.591806</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70336,7 +70480,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>98.80934000000001</v>
+        <v>99.80932900000001</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70517,7 +70661,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>113.709861</v>
+        <v>114.70985</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70698,7 +70842,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>126.607222</v>
+        <v>127.607211</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>283.834282</v>
+        <v>286.834317</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>126.950278</v>
+        <v>129.950313</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>114.708322</v>
+        <v>117.708356</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>238.779942</v>
+        <v>241.779977</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>241.566493</v>
+        <v>244.566528</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>49.934039</v>
+        <v>52.934074</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>276.603993</v>
+        <v>279.604028</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>225.64463</v>
+        <v>228.644664</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>209.727917</v>
+        <v>212.727951</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>125.62456</v>
+        <v>128.624595</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>210.630289</v>
+        <v>213.630324</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>288.687986</v>
+        <v>291.688021</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>274.503137</v>
+        <v>277.503171</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>243.631667</v>
+        <v>246.631701</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>245.92897</v>
+        <v>248.929005</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>125.578785</v>
+        <v>128.578819</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>107.815046</v>
+        <v>110.815081</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>213.515799</v>
+        <v>216.515833</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>205.60456</v>
+        <v>208.604595</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>126.950706</v>
+        <v>129.950741</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>43.952731</v>
+        <v>46.952766</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>42.697928</v>
+        <v>45.697963</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>49.931458</v>
+        <v>52.931493</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>238.77941</v>
+        <v>241.779444</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>125.723623</v>
+        <v>128.723657</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>23.577778</v>
+        <v>26.577813</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>73.934433</v>
+        <v>76.934468</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>274.508646</v>
+        <v>277.508681</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>195.59213</v>
+        <v>198.592164</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>204.685613</v>
+        <v>207.685648</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>134.82566</v>
+        <v>137.825694</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>276.5989</v>
+        <v>279.598935</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>133.60706</v>
+        <v>136.607095</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>212.827616</v>
+        <v>215.82765</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>121.725405</v>
+        <v>124.72544</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>240.873414</v>
+        <v>243.873449</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>248.659155</v>
+        <v>251.65919</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7495,7 +7495,7 @@
         <v>46100.38240289352</v>
       </c>
       <c r="AW39">
-        <v>0.889549</v>
+        <v>3.889583</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7676,7 +7676,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>135.891053</v>
+        <v>138.891088</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7857,7 +7857,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>114.705301</v>
+        <v>117.705336</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8038,7 +8038,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>73.695035</v>
+        <v>76.695069</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8216,7 +8216,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>43.954722</v>
+        <v>46.954757</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8397,7 +8397,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>63.618681</v>
+        <v>66.61871499999999</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8578,7 +8578,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>22.718715</v>
+        <v>25.71875</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8759,7 +8759,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>197.910417</v>
+        <v>200.910451</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8940,7 +8940,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>212.827002</v>
+        <v>215.827037</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9074,7 +9074,7 @@
         <v>46090.58140600695</v>
       </c>
       <c r="AQ48">
-        <v>10.690486</v>
+        <v>13.690521</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9258,7 +9258,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>163.943773</v>
+        <v>166.943808</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9439,7 +9439,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>163.942558</v>
+        <v>166.942593</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9607,7 +9607,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>21.592813</v>
+        <v>24.592847</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9788,7 +9788,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>240.874398</v>
+        <v>243.874433</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9966,7 +9966,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>241.567905</v>
+        <v>244.56794</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10150,7 +10150,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>148.710521</v>
+        <v>151.710556</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10331,7 +10331,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>254.783391</v>
+        <v>257.783426</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10509,7 +10509,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>21.592072</v>
+        <v>24.592106</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10693,7 +10693,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>232.540926</v>
+        <v>235.540961</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10871,7 +10871,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>0.889248</v>
+        <v>3.889282</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11049,7 +11049,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>279.645579</v>
+        <v>282.645613</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11227,7 +11227,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>269.694398</v>
+        <v>272.694433</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11408,7 +11408,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>99.796944</v>
+        <v>102.796979</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11586,7 +11586,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>64.68822900000001</v>
+        <v>67.688264</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11764,7 +11764,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>241.567072</v>
+        <v>244.567106</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11945,7 +11945,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>135.895162</v>
+        <v>138.895197</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12126,7 +12126,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>115.514803</v>
+        <v>118.514838</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12307,7 +12307,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>177.568646</v>
+        <v>180.568681</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12485,7 +12485,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>244.822755</v>
+        <v>247.822789</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12663,7 +12663,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>205.6239</v>
+        <v>208.623935</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12847,7 +12847,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>125.623773</v>
+        <v>128.623808</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13025,7 +13025,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>63.598322</v>
+        <v>66.598356</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13203,7 +13203,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>280.938715</v>
+        <v>283.93875</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13381,7 +13381,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>283.831609</v>
+        <v>286.831644</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13559,7 +13559,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>241.582847</v>
+        <v>244.582882</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13740,7 +13740,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>198.684375</v>
+        <v>201.68441</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13918,7 +13918,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>134.720972</v>
+        <v>137.721007</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14099,7 +14099,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>141.716933</v>
+        <v>144.716968</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14280,7 +14280,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>93.84463</v>
+        <v>96.84466399999999</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14461,7 +14461,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>98.542176</v>
+        <v>101.542211</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14642,7 +14642,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>43.773565</v>
+        <v>46.7736</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14823,7 +14823,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>3.879421</v>
+        <v>6.879456</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15009,7 +15009,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>255.654282</v>
+        <v>258.654317</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15187,7 +15187,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>192.680498</v>
+        <v>195.680532</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15368,7 +15368,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>127.607488</v>
+        <v>130.607523</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15549,7 +15549,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>3.875046</v>
+        <v>6.875081</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15733,7 +15733,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>196.889144</v>
+        <v>199.889178</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15914,7 +15914,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>114.695648</v>
+        <v>117.695683</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16095,7 +16095,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>269.697789</v>
+        <v>272.697824</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16276,7 +16276,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>163.943553</v>
+        <v>166.943588</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16454,7 +16454,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>148.858912</v>
+        <v>151.858947</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16635,7 +16635,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>143.553669</v>
+        <v>146.553704</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16816,7 +16816,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>133.605718</v>
+        <v>136.605752</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16994,7 +16994,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>248.723113</v>
+        <v>251.723148</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17172,7 +17172,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>279.597859</v>
+        <v>282.597894</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17361,7 +17361,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>227.567523</v>
+        <v>230.567558</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17542,7 +17542,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>196.887431</v>
+        <v>199.887465</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17723,7 +17723,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>177.561493</v>
+        <v>180.561528</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17904,7 +17904,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>99.806308</v>
+        <v>102.806343</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -18014,7 +18014,7 @@
         <v>46097.3976521875</v>
       </c>
       <c r="AN98">
-        <v>3.874294</v>
+        <v>6.874329</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18195,7 +18195,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>233.570035</v>
+        <v>236.570069</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18373,7 +18373,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>274.502755</v>
+        <v>277.502789</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18551,7 +18551,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>183.943183</v>
+        <v>186.943218</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18729,7 +18729,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>241.566296</v>
+        <v>244.566331</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18910,7 +18910,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>73.938056</v>
+        <v>76.93809</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19088,7 +19088,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>280.939109</v>
+        <v>283.939144</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19266,7 +19266,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>192.553773</v>
+        <v>195.553808</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19447,7 +19447,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>114.708877</v>
+        <v>117.708912</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19628,7 +19628,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>210.622951</v>
+        <v>213.622986</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19809,7 +19809,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>202.698808</v>
+        <v>205.698843</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19987,7 +19987,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>42.722593</v>
+        <v>45.722627</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20165,7 +20165,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>276.688715</v>
+        <v>279.68875</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20346,7 +20346,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>232.685706</v>
+        <v>235.685741</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20530,7 +20530,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>171.944456</v>
+        <v>174.944491</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20711,7 +20711,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>113.723773</v>
+        <v>116.723808</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20892,7 +20892,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>231.122581</v>
+        <v>234.122616</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21073,7 +21073,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>239.7661</v>
+        <v>242.766134</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21254,7 +21254,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>192.609722</v>
+        <v>195.609757</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21435,7 +21435,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>141.698414</v>
+        <v>144.698449</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21616,7 +21616,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>114.694329</v>
+        <v>117.694363</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21797,7 +21797,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>73.936678</v>
+        <v>76.936713</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21978,7 +21978,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>50.72397</v>
+        <v>53.724005</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22156,7 +22156,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>283.834572</v>
+        <v>286.834606</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22334,7 +22334,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>269.645451</v>
+        <v>272.645486</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22515,7 +22515,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>279.595995</v>
+        <v>282.59603</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22696,7 +22696,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>171.942859</v>
+        <v>174.942894</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22877,7 +22877,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>125.723137</v>
+        <v>128.723171</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23058,7 +23058,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>143.544306</v>
+        <v>146.54434</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23236,7 +23236,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>62.588542</v>
+        <v>65.588576</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23417,7 +23417,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>258.564664</v>
+        <v>261.564699</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23601,7 +23601,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>232.705718</v>
+        <v>235.705752</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23779,7 +23779,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>210.576157</v>
+        <v>213.576192</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23960,7 +23960,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>14.596667</v>
+        <v>17.596701</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24141,7 +24141,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>196.885278</v>
+        <v>199.885313</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24319,7 +24319,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>274.503368</v>
+        <v>277.503403</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24500,7 +24500,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>114.695752</v>
+        <v>117.695787</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24681,7 +24681,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>98.54288200000001</v>
+        <v>101.542917</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24854,7 +24854,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>269.597963</v>
+        <v>272.597998</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25035,7 +25035,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>99.798391</v>
+        <v>102.798426</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25216,7 +25216,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>28.675081</v>
+        <v>31.675116</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25397,7 +25397,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>183.805532</v>
+        <v>186.805567</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25578,7 +25578,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>177.956944</v>
+        <v>180.956979</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25756,7 +25756,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>287.647986</v>
+        <v>290.648021</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25934,7 +25934,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>213.488345</v>
+        <v>216.48838</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26115,7 +26115,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>171.942315</v>
+        <v>174.94235</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26291,7 +26291,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>107.814815</v>
+        <v>110.81485</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26472,7 +26472,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>41.835752</v>
+        <v>44.835787</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26650,7 +26650,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>269.648657</v>
+        <v>272.648692</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26828,7 +26828,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>274.505023</v>
+        <v>277.505058</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27006,7 +27006,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>0.884919</v>
+        <v>3.884954</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27187,7 +27187,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>210.685648</v>
+        <v>213.685683</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27365,7 +27365,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>244.822326</v>
+        <v>247.822361</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27543,7 +27543,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>241.566794</v>
+        <v>244.566829</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27724,7 +27724,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>204.686644</v>
+        <v>207.686678</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27905,7 +27905,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>63.604826</v>
+        <v>66.604861</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28086,7 +28086,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>176.818819</v>
+        <v>179.818854</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28267,7 +28267,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>176.618877</v>
+        <v>179.618912</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28445,7 +28445,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>43.951863</v>
+        <v>46.951898</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28629,7 +28629,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>99.805938</v>
+        <v>102.805972</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28810,7 +28810,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>198.517014</v>
+        <v>201.517049</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -28999,7 +28999,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>188.582245</v>
+        <v>191.58228</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29167,7 +29167,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>218.652419</v>
+        <v>221.652454</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29348,7 +29348,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>171.94162</v>
+        <v>174.941655</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29529,7 +29529,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>115.515463</v>
+        <v>118.515498</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29710,7 +29710,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>56.628484</v>
+        <v>59.628519</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29891,7 +29891,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>240.874201</v>
+        <v>243.874236</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30072,7 +30072,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>196.890891</v>
+        <v>199.890926</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30253,7 +30253,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>120.538414</v>
+        <v>123.538449</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30431,7 +30431,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>43.956308</v>
+        <v>46.956343</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30609,7 +30609,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>230.897014</v>
+        <v>233.897049</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30790,7 +30790,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>146.643461</v>
+        <v>149.643495</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30968,7 +30968,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>114.692674</v>
+        <v>117.692708</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31149,7 +31149,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>14.597697</v>
+        <v>17.597731</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31327,7 +31327,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>279.598796</v>
+        <v>282.598831</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31508,7 +31508,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>255.949097</v>
+        <v>258.949132</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31686,7 +31686,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>64.679653</v>
+        <v>67.679688</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31864,7 +31864,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>37.724954</v>
+        <v>40.724988</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32037,7 +32037,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>195.591921</v>
+        <v>198.591956</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32218,7 +32218,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>73.936076</v>
+        <v>76.936111</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32396,7 +32396,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>23.571563</v>
+        <v>26.571597</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32574,7 +32574,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>230.901956</v>
+        <v>233.901991</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32752,7 +32752,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>283.834965</v>
+        <v>286.835</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32930,7 +32930,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>205.603032</v>
+        <v>208.603067</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33108,7 +33108,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>276.598345</v>
+        <v>279.59838</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33286,7 +33286,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>267.705185</v>
+        <v>270.70522</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33464,7 +33464,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>205.623785</v>
+        <v>208.623819</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33645,7 +33645,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>134.72081</v>
+        <v>137.720845</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33826,7 +33826,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>3.878947</v>
+        <v>6.878981</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34004,7 +34004,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>276.597986</v>
+        <v>279.598021</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34185,7 +34185,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>232.701528</v>
+        <v>235.701563</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34366,7 +34366,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>177.956227</v>
+        <v>180.956262</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34547,7 +34547,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>210.515938</v>
+        <v>213.515972</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34728,7 +34728,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>121.669282</v>
+        <v>124.669317</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34906,7 +34906,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>43.954282</v>
+        <v>46.954317</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35084,7 +35084,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>283.842535</v>
+        <v>286.842569</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35252,7 +35252,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>218.664606</v>
+        <v>221.664641</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35433,7 +35433,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>196.888403</v>
+        <v>199.888438</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35617,7 +35617,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>177.959769</v>
+        <v>180.959803</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35801,7 +35801,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>232.705347</v>
+        <v>235.705382</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35982,7 +35982,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>99.797708</v>
+        <v>102.797743</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36160,7 +36160,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>276.688993</v>
+        <v>279.689028</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36338,7 +36338,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>290.909826</v>
+        <v>293.909861</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36519,7 +36519,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>196.894248</v>
+        <v>199.894282</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36697,7 +36697,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>170.681644</v>
+        <v>173.681678</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36878,7 +36878,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>263.925532</v>
+        <v>266.925567</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37056,7 +37056,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>274.503935</v>
+        <v>277.50397</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37234,7 +37234,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>202.607488</v>
+        <v>205.607523</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37412,7 +37412,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>27.60419</v>
+        <v>30.604225</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37593,7 +37593,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>258.561505</v>
+        <v>261.561539</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37774,7 +37774,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>206.530926</v>
+        <v>209.530961</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37952,7 +37952,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>64.685266</v>
+        <v>67.685301</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38130,7 +38130,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>279.57213</v>
+        <v>282.572164</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38308,7 +38308,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>276.688449</v>
+        <v>279.688484</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38486,7 +38486,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>10.541829</v>
+        <v>13.541863</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38664,7 +38664,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>275.610671</v>
+        <v>278.610706</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38842,7 +38842,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>287.593252</v>
+        <v>290.593287</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39020,7 +39020,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>289.733646</v>
+        <v>292.733681</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39198,7 +39198,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>279.646829</v>
+        <v>282.646863</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39376,7 +39376,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>241.568519</v>
+        <v>244.568553</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39557,7 +39557,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>241.586493</v>
+        <v>244.586528</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39738,7 +39738,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>146.911528</v>
+        <v>149.911563</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39919,7 +39919,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>3.703947</v>
+        <v>6.703981</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40097,7 +40097,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>288.68897</v>
+        <v>291.689005</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40275,7 +40275,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>279.587894</v>
+        <v>282.587928</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40453,7 +40453,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>288.684838</v>
+        <v>291.684873</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40634,7 +40634,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>189.639144</v>
+        <v>192.639178</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40815,7 +40815,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>121.693438</v>
+        <v>124.693472</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -40996,7 +40996,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>114.711586</v>
+        <v>117.71162</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41177,7 +41177,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>49.933079</v>
+        <v>52.933113</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41358,7 +41358,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>49.934757</v>
+        <v>52.934792</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41539,7 +41539,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>196.8936</v>
+        <v>199.893634</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41720,7 +41720,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>248.659074</v>
+        <v>251.659109</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41898,7 +41898,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>265.900382</v>
+        <v>268.900417</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42079,7 +42079,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>205.669988</v>
+        <v>208.670023</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42263,7 +42263,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>197.910185</v>
+        <v>200.91022</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42444,7 +42444,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>177.958079</v>
+        <v>180.958113</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42622,7 +42622,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>128.886944</v>
+        <v>131.886979</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42803,7 +42803,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>14.595556</v>
+        <v>17.59559</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42984,7 +42984,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>240.874734</v>
+        <v>243.874769</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43165,7 +43165,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>196.753194</v>
+        <v>199.753229</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43346,7 +43346,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>99.798935</v>
+        <v>102.79897</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43524,7 +43524,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>64.6786</v>
+        <v>67.678634</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43705,7 +43705,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>115.515961</v>
+        <v>118.515995</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43886,7 +43886,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>230.900729</v>
+        <v>233.900764</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44059,7 +44059,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>276.573229</v>
+        <v>279.573264</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44237,7 +44237,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>241.567303</v>
+        <v>244.567338</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44421,7 +44421,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>205.601377</v>
+        <v>208.601412</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44602,7 +44602,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>148.855961</v>
+        <v>151.855995</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44786,7 +44786,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>177.660845</v>
+        <v>180.66088</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44967,7 +44967,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>171.940741</v>
+        <v>174.940775</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45148,7 +45148,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>22.719549</v>
+        <v>25.719583</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45326,7 +45326,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>241.567708</v>
+        <v>244.567743</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45507,7 +45507,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>212.828241</v>
+        <v>215.828275</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45688,7 +45688,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>49.678426</v>
+        <v>52.678461</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45869,7 +45869,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>261.720903</v>
+        <v>264.720938</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46050,7 +46050,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>50.724387</v>
+        <v>53.724421</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46160,7 +46160,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>3.874317</v>
+        <v>6.874352</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46270,7 +46270,7 @@
         <v>46097.39764412037</v>
       </c>
       <c r="AN256">
-        <v>3.874306</v>
+        <v>6.87434</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46451,7 +46451,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>73.93535900000001</v>
+        <v>76.935394</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46632,7 +46632,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>240.835313</v>
+        <v>243.835347</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46810,7 +46810,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>171.950486</v>
+        <v>174.950521</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46991,7 +46991,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>171.948333</v>
+        <v>174.948368</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47169,7 +47169,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>146.532882</v>
+        <v>149.532917</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47345,7 +47345,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>238.779572</v>
+        <v>241.779606</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47523,7 +47523,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>162.939051</v>
+        <v>165.939086</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47707,7 +47707,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>148.711273</v>
+        <v>151.711308</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47885,7 +47885,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>97.70796300000001</v>
+        <v>100.707998</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48066,7 +48066,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>269.698009</v>
+        <v>272.698044</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48244,7 +48244,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>279.646088</v>
+        <v>282.646123</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48425,7 +48425,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>258.561852</v>
+        <v>261.561887</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48606,7 +48606,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>134.720706</v>
+        <v>137.720741</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48784,7 +48784,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>148.712083</v>
+        <v>151.712118</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48965,7 +48965,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>114.695475</v>
+        <v>117.695509</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49146,7 +49146,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>258.562396</v>
+        <v>261.562431</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49324,7 +49324,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>177.952477</v>
+        <v>180.952512</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49508,7 +49508,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>129.699317</v>
+        <v>132.699352</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49689,7 +49689,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>268.591204</v>
+        <v>271.591238</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49870,7 +49870,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>183.806725</v>
+        <v>186.806759</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50051,7 +50051,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>114.712245</v>
+        <v>117.71228</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50232,7 +50232,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>135.893333</v>
+        <v>138.893368</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50413,7 +50413,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>254.783194</v>
+        <v>257.783229</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50620,7 +50620,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>134.826389</v>
+        <v>137.826424</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50798,7 +50798,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>125.622396</v>
+        <v>128.622431</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50979,7 +50979,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>108.655104</v>
+        <v>111.655139</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51163,7 +51163,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>163.942477</v>
+        <v>166.942512</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51341,7 +51341,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>0.886678</v>
+        <v>3.886713</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51519,7 +51519,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>255.949468</v>
+        <v>258.949502</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51697,7 +51697,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>267.706134</v>
+        <v>270.706169</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51875,7 +51875,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>230.901794</v>
+        <v>233.901829</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52056,7 +52056,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>210.629861</v>
+        <v>213.629896</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52240,7 +52240,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>151.95728</v>
+        <v>154.957315</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52421,7 +52421,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>129.692975</v>
+        <v>132.693009</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52602,7 +52602,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>254.911863</v>
+        <v>257.911898</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52780,7 +52780,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>268.911065</v>
+        <v>271.9111</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52961,7 +52961,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>213.518958</v>
+        <v>216.518993</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53139,7 +53139,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>274.501968</v>
+        <v>277.502002</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53320,7 +53320,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>196.894815</v>
+        <v>199.89485</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53501,7 +53501,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>3.875556</v>
+        <v>6.87559</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53682,7 +53682,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>114.563704</v>
+        <v>117.563738</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53860,7 +53860,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>241.569641</v>
+        <v>244.569676</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54038,7 +54038,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>0.888889</v>
+        <v>3.888924</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54227,7 +54227,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>265.900845</v>
+        <v>268.90088</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54408,7 +54408,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>196.887685</v>
+        <v>199.88772</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54586,7 +54586,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>171.699155</v>
+        <v>174.69919</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54767,7 +54767,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>93.84487300000001</v>
+        <v>96.84490700000001</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54953,7 +54953,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>206.660625</v>
+        <v>209.66066</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55131,7 +55131,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>280.940567</v>
+        <v>283.940602</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55312,7 +55312,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>170.612778</v>
+        <v>173.612813</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55493,7 +55493,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>125.722986</v>
+        <v>128.723021</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55674,7 +55674,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>99.810451</v>
+        <v>102.810486</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55855,7 +55855,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>73.93718800000001</v>
+        <v>76.93722200000001</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56036,7 +56036,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>170.611343</v>
+        <v>173.611377</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56217,7 +56217,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>170.613113</v>
+        <v>173.613148</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56327,7 +56327,7 @@
         <v>46097.39763636574</v>
       </c>
       <c r="AN312">
-        <v>3.874317</v>
+        <v>6.874352</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56505,7 +56505,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>274.50235</v>
+        <v>277.502384</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56683,7 +56683,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>43.958588</v>
+        <v>46.958623</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56864,7 +56864,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>227.564039</v>
+        <v>230.564074</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57042,7 +57042,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>23.571042</v>
+        <v>26.571076</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57223,7 +57223,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>146.64441</v>
+        <v>149.644444</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57404,7 +57404,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>3.876019</v>
+        <v>6.876053</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57582,7 +57582,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW319">
-        <v>0.8881250000000001</v>
+        <v>3.88816</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57763,7 +57763,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>227.566829</v>
+        <v>230.566863</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57944,7 +57944,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>240.872072</v>
+        <v>243.872106</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58122,7 +58122,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>49.601979</v>
+        <v>52.602014</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58300,7 +58300,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>283.835417</v>
+        <v>286.835451</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58481,7 +58481,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>177.95162</v>
+        <v>180.951655</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58659,7 +58659,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>141.661701</v>
+        <v>144.661736</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58840,7 +58840,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>129.696956</v>
+        <v>132.696991</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59021,7 +59021,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>262.609468</v>
+        <v>265.609502</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59202,7 +59202,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>217.668484</v>
+        <v>220.668519</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59383,7 +59383,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>99.81197899999999</v>
+        <v>102.812014</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59564,7 +59564,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>58.814595</v>
+        <v>61.81463</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59742,7 +59742,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>210.575856</v>
+        <v>213.575891</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59926,7 +59926,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>156.586574</v>
+        <v>159.586609</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60104,7 +60104,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>241.56897</v>
+        <v>244.569005</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60285,7 +60285,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>135.889549</v>
+        <v>138.889583</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60466,7 +60466,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>125.622824</v>
+        <v>128.622859</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60644,7 +60644,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>220.593449</v>
+        <v>223.593484</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60825,7 +60825,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>66.57531299999999</v>
+        <v>69.57534699999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61006,7 +61006,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>212.824884</v>
+        <v>215.824919</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61182,7 +61182,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>146.643924</v>
+        <v>149.643958</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61316,7 +61316,7 @@
         <v>46100.40009251158</v>
       </c>
       <c r="AQ340">
-        <v>0.8718630000000001</v>
+        <v>3.871898</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61497,7 +61497,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>3.876516</v>
+        <v>6.876551</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61675,7 +61675,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>288.693796</v>
+        <v>291.693831</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61856,7 +61856,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>198.892766</v>
+        <v>201.892801</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62037,7 +62037,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>177.958981</v>
+        <v>180.959016</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62218,7 +62218,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>127.607002</v>
+        <v>130.607037</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62399,7 +62399,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>245.932141</v>
+        <v>248.932176</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62580,7 +62580,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>43.77287</v>
+        <v>46.772905</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62761,7 +62761,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>24.945313</v>
+        <v>27.945347</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62942,7 +62942,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>108.655718</v>
+        <v>111.655752</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63120,7 +63120,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>202.652523</v>
+        <v>205.652558</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63301,7 +63301,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>181.591042</v>
+        <v>184.591076</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63479,7 +63479,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>146.645035</v>
+        <v>149.645069</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63660,7 +63660,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>127.608229</v>
+        <v>130.608264</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63841,7 +63841,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>254.912083</v>
+        <v>257.912118</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64022,7 +64022,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>183.806273</v>
+        <v>186.806308</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64203,7 +64203,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>171.939977</v>
+        <v>174.940012</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64384,7 +64384,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>178.012488</v>
+        <v>181.012523</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64565,7 +64565,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>113.727234</v>
+        <v>116.727269</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64746,7 +64746,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>63.606424</v>
+        <v>66.606458</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64927,7 +64927,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>279.596701</v>
+        <v>282.596736</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65105,7 +65105,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>280.938877</v>
+        <v>283.938912</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65286,7 +65286,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>94.726169</v>
+        <v>97.726204</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65467,7 +65467,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>49.740486</v>
+        <v>52.740521</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65645,7 +65645,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>287.587546</v>
+        <v>290.587581</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65826,7 +65826,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>177.960197</v>
+        <v>180.960231</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66004,7 +66004,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>97.707882</v>
+        <v>100.707917</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66185,7 +66185,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>258.562917</v>
+        <v>261.562951</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66366,7 +66366,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>148.857465</v>
+        <v>151.8575</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66547,7 +66547,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>146.8925</v>
+        <v>149.892535</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66725,7 +66725,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>274.501701</v>
+        <v>277.501736</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66906,7 +66906,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>245.929456</v>
+        <v>248.929491</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67084,7 +67084,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>164.529653</v>
+        <v>167.529688</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67262,7 +67262,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>248.722014</v>
+        <v>251.722049</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67443,7 +67443,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>196.889039</v>
+        <v>199.889074</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67624,7 +67624,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>3.875208</v>
+        <v>6.875243</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67802,7 +67802,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>283.727454</v>
+        <v>286.727488</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67980,7 +67980,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>279.63331</v>
+        <v>282.633345</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68161,7 +68161,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>127.613623</v>
+        <v>130.613657</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68339,7 +68339,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>280.939676</v>
+        <v>283.939711</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68517,7 +68517,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>258.563438</v>
+        <v>261.563472</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68695,7 +68695,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>288.685197</v>
+        <v>291.685231</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -68873,7 +68873,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>136.621574</v>
+        <v>139.621609</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69051,7 +69051,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>274.500231</v>
+        <v>277.500266</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69229,7 +69229,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>241.566111</v>
+        <v>244.566146</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69410,7 +69410,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>232.698738</v>
+        <v>235.698773</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69591,7 +69591,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>148.856782</v>
+        <v>151.856817</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69772,7 +69772,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>93.843715</v>
+        <v>96.84375</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69953,7 +69953,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>99.810903</v>
+        <v>102.810938</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70126,7 +70126,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>195.592269</v>
+        <v>198.592303</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70299,7 +70299,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>195.591806</v>
+        <v>198.59184</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70480,7 +70480,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>99.80932900000001</v>
+        <v>102.809363</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70661,7 +70661,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>114.70985</v>
+        <v>117.709884</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70842,7 +70842,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>127.607211</v>
+        <v>130.607245</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>286.834317</v>
+        <v>287.834294</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>129.950313</v>
+        <v>130.950289</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>117.708356</v>
+        <v>118.708333</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>241.779977</v>
+        <v>242.779954</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>244.566528</v>
+        <v>245.566505</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>52.934074</v>
+        <v>53.934051</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>279.604028</v>
+        <v>280.604005</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>228.644664</v>
+        <v>229.644641</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>212.727951</v>
+        <v>213.727928</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>128.624595</v>
+        <v>129.624572</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>213.630324</v>
+        <v>214.630301</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>291.688021</v>
+        <v>292.687998</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>277.503171</v>
+        <v>278.503148</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>246.631701</v>
+        <v>247.631678</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>248.929005</v>
+        <v>249.928981</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>128.578819</v>
+        <v>129.578796</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>110.815081</v>
+        <v>111.815058</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>216.515833</v>
+        <v>217.51581</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>208.604595</v>
+        <v>209.604572</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>129.950741</v>
+        <v>130.950718</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>46.952766</v>
+        <v>47.952743</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>45.697963</v>
+        <v>46.69794</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>52.931493</v>
+        <v>53.93147</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>241.779444</v>
+        <v>242.779421</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>128.723657</v>
+        <v>129.723634</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>26.577813</v>
+        <v>27.577789</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>76.934468</v>
+        <v>77.934444</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>277.508681</v>
+        <v>278.508657</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>198.592164</v>
+        <v>199.592141</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>207.685648</v>
+        <v>208.685625</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>137.825694</v>
+        <v>138.825671</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>279.598935</v>
+        <v>280.598912</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>136.607095</v>
+        <v>137.607072</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>215.82765</v>
+        <v>216.827627</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>124.72544</v>
+        <v>125.725417</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>243.873449</v>
+        <v>244.873426</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>251.65919</v>
+        <v>252.659167</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7347,14 +7347,11 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
-      <c r="H39" s="2">
-        <v>46100.38240085648</v>
-      </c>
       <c r="I39" s="2">
         <v>46076.71127025463</v>
       </c>
       <c r="J39" s="2">
-        <v>46100.38240104166</v>
+        <v>46104.65056451389</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -7477,10 +7474,10 @@
         <v>46090.58235540509</v>
       </c>
       <c r="AP39" s="2">
-        <v>46099.50652210649</v>
+        <v>46104.52614081019</v>
       </c>
       <c r="AQ39">
-        <v>8.924167000000001</v>
+        <v>8.924352000000001</v>
       </c>
       <c r="AR39" s="2">
         <v>46099.50652269676</v>
@@ -7489,13 +7486,16 @@
         <v>46100.3824021875</v>
       </c>
       <c r="AT39">
-        <v>0.875868</v>
+        <v>1.621701</v>
       </c>
       <c r="AU39" s="2">
         <v>46100.38240289352</v>
       </c>
+      <c r="AV39" s="2">
+        <v>46104.52594388889</v>
+      </c>
       <c r="AW39">
-        <v>3.889583</v>
+        <v>4.14353</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7676,7 +7676,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>138.891088</v>
+        <v>139.891065</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7857,7 +7857,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>117.705336</v>
+        <v>118.705313</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8038,7 +8038,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>76.695069</v>
+        <v>77.695046</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8216,7 +8216,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>46.954757</v>
+        <v>47.954734</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8397,7 +8397,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>66.61871499999999</v>
+        <v>67.618692</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8578,7 +8578,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>25.71875</v>
+        <v>26.718727</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8759,7 +8759,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>200.910451</v>
+        <v>201.910428</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8940,7 +8940,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>215.827037</v>
+        <v>216.827014</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -8974,7 +8974,7 @@
         <v>46076.60416619213</v>
       </c>
       <c r="J48" s="2">
-        <v>46100.38120965278</v>
+        <v>46104.68505300926</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -9047,6 +9047,11 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AF48" t="inlineStr">
         <is>
           <t>Reprovado na Validação</t>
@@ -9074,7 +9079,7 @@
         <v>46090.58140600695</v>
       </c>
       <c r="AQ48">
-        <v>13.690521</v>
+        <v>14.690498</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9258,7 +9263,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>166.943808</v>
+        <v>167.943785</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9439,7 +9444,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>166.942593</v>
+        <v>167.942569</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9607,7 +9612,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>24.592847</v>
+        <v>25.592824</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9788,7 +9793,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>243.874433</v>
+        <v>244.87441</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9966,7 +9971,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>244.56794</v>
+        <v>245.567917</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10150,7 +10155,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>151.710556</v>
+        <v>152.710532</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10331,7 +10336,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>257.783426</v>
+        <v>258.783403</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10509,7 +10514,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>24.592106</v>
+        <v>25.592083</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10693,7 +10698,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>235.540961</v>
+        <v>236.540938</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10871,7 +10876,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>3.889282</v>
+        <v>4.889259</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11049,7 +11054,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>282.645613</v>
+        <v>283.64559</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11227,7 +11232,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>272.694433</v>
+        <v>273.69441</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11408,7 +11413,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>102.796979</v>
+        <v>103.796956</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11586,7 +11591,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>67.688264</v>
+        <v>68.688241</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11764,7 +11769,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>244.567106</v>
+        <v>245.567083</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11945,7 +11950,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>138.895197</v>
+        <v>139.895174</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12126,7 +12131,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>118.514838</v>
+        <v>119.514815</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12307,7 +12312,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>180.568681</v>
+        <v>181.568657</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12485,7 +12490,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>247.822789</v>
+        <v>248.822766</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12663,7 +12668,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>208.623935</v>
+        <v>209.623912</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12847,7 +12852,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>128.623808</v>
+        <v>129.623785</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13025,7 +13030,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>66.598356</v>
+        <v>67.598333</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13203,7 +13208,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>283.93875</v>
+        <v>284.938727</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13381,7 +13386,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>286.831644</v>
+        <v>287.83162</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13559,7 +13564,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>244.582882</v>
+        <v>245.582859</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13740,7 +13745,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>201.68441</v>
+        <v>202.684387</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13918,7 +13923,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>137.721007</v>
+        <v>138.720984</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14099,7 +14104,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>144.716968</v>
+        <v>145.716944</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14280,7 +14285,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>96.84466399999999</v>
+        <v>97.844641</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14461,7 +14466,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>101.542211</v>
+        <v>102.542188</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14642,7 +14647,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>46.7736</v>
+        <v>47.773576</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14823,7 +14828,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>6.879456</v>
+        <v>7.879433</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15009,7 +15014,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>258.654317</v>
+        <v>259.654294</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15187,7 +15192,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>195.680532</v>
+        <v>196.680509</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15368,7 +15373,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>130.607523</v>
+        <v>131.6075</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15549,7 +15554,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>6.875081</v>
+        <v>7.875058</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15733,7 +15738,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>199.889178</v>
+        <v>200.889155</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15914,7 +15919,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>117.695683</v>
+        <v>118.69566</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16095,7 +16100,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>272.697824</v>
+        <v>273.697801</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16276,7 +16281,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>166.943588</v>
+        <v>167.943565</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16454,7 +16459,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>151.858947</v>
+        <v>152.858924</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16635,7 +16640,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>146.553704</v>
+        <v>147.553681</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16816,7 +16821,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>136.605752</v>
+        <v>137.605729</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16994,7 +16999,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>251.723148</v>
+        <v>252.723125</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17172,7 +17177,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>282.597894</v>
+        <v>283.59787</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17361,7 +17366,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>230.567558</v>
+        <v>231.567535</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17542,7 +17547,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>199.887465</v>
+        <v>200.887442</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17723,7 +17728,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>180.561528</v>
+        <v>181.561505</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17904,7 +17909,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>102.806343</v>
+        <v>103.806319</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -18014,7 +18019,7 @@
         <v>46097.3976521875</v>
       </c>
       <c r="AN98">
-        <v>6.874329</v>
+        <v>7.874306</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18195,7 +18200,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>236.570069</v>
+        <v>237.570046</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18373,7 +18378,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>277.502789</v>
+        <v>278.502766</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18551,7 +18556,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>186.943218</v>
+        <v>187.943194</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18729,7 +18734,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>244.566331</v>
+        <v>245.566308</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18910,7 +18915,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>76.93809</v>
+        <v>77.938067</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19088,7 +19093,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>283.939144</v>
+        <v>284.93912</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19266,7 +19271,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>195.553808</v>
+        <v>196.553785</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19447,7 +19452,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>117.708912</v>
+        <v>118.708889</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19628,7 +19633,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>213.622986</v>
+        <v>214.622963</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19809,7 +19814,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>205.698843</v>
+        <v>206.698819</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19987,7 +19992,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>45.722627</v>
+        <v>46.722604</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20165,7 +20170,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>279.68875</v>
+        <v>280.688727</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20346,7 +20351,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>235.685741</v>
+        <v>236.685718</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20530,7 +20535,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>174.944491</v>
+        <v>175.944468</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20711,7 +20716,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>116.723808</v>
+        <v>117.723785</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20892,7 +20897,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>234.122616</v>
+        <v>235.122593</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21073,7 +21078,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>242.766134</v>
+        <v>243.766111</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21254,7 +21259,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>195.609757</v>
+        <v>196.609734</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21435,7 +21440,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>144.698449</v>
+        <v>145.698426</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21616,7 +21621,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>117.694363</v>
+        <v>118.69434</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21797,7 +21802,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>76.936713</v>
+        <v>77.93669</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21978,7 +21983,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>53.724005</v>
+        <v>54.723981</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22156,7 +22161,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>286.834606</v>
+        <v>287.834583</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22334,7 +22339,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>272.645486</v>
+        <v>273.645463</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22515,7 +22520,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>282.59603</v>
+        <v>283.596007</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22696,7 +22701,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>174.942894</v>
+        <v>175.94287</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22877,7 +22882,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>128.723171</v>
+        <v>129.723148</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23058,7 +23063,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>146.54434</v>
+        <v>147.544317</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23236,7 +23241,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>65.588576</v>
+        <v>66.588553</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23417,7 +23422,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>261.564699</v>
+        <v>262.564676</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23601,7 +23606,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>235.705752</v>
+        <v>236.705729</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23779,7 +23784,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>213.576192</v>
+        <v>214.576169</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23960,7 +23965,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>17.596701</v>
+        <v>18.596678</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24141,7 +24146,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>199.885313</v>
+        <v>200.885289</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24319,7 +24324,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>277.503403</v>
+        <v>278.50338</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24500,7 +24505,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>117.695787</v>
+        <v>118.695764</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24681,7 +24686,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>101.542917</v>
+        <v>102.542894</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24854,7 +24859,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>272.597998</v>
+        <v>273.597975</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25035,7 +25040,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>102.798426</v>
+        <v>103.798403</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25216,7 +25221,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>31.675116</v>
+        <v>32.675093</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25397,7 +25402,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>186.805567</v>
+        <v>187.805544</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25578,7 +25583,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>180.956979</v>
+        <v>181.956956</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25756,7 +25761,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>290.648021</v>
+        <v>291.647998</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25934,7 +25939,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>216.48838</v>
+        <v>217.488356</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26115,7 +26120,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>174.94235</v>
+        <v>175.942326</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26291,7 +26296,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>110.81485</v>
+        <v>111.814826</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26472,7 +26477,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>44.835787</v>
+        <v>45.835764</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26650,7 +26655,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>272.648692</v>
+        <v>273.648669</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26828,7 +26833,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>277.505058</v>
+        <v>278.505035</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27006,7 +27011,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>3.884954</v>
+        <v>4.884931</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27187,7 +27192,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>213.685683</v>
+        <v>214.68566</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27365,7 +27370,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>247.822361</v>
+        <v>248.822338</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27543,7 +27548,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>244.566829</v>
+        <v>245.566806</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27724,7 +27729,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>207.686678</v>
+        <v>208.686655</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27905,7 +27910,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>66.604861</v>
+        <v>67.604838</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28086,7 +28091,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>179.818854</v>
+        <v>180.818831</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28267,7 +28272,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>179.618912</v>
+        <v>180.618889</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28445,7 +28450,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>46.951898</v>
+        <v>47.951875</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28629,7 +28634,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>102.805972</v>
+        <v>103.805949</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28810,7 +28815,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>201.517049</v>
+        <v>202.517025</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -28999,7 +29004,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>191.58228</v>
+        <v>192.582257</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29167,7 +29172,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>221.652454</v>
+        <v>222.652431</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29348,7 +29353,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>174.941655</v>
+        <v>175.941632</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29529,7 +29534,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>118.515498</v>
+        <v>119.515475</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29710,7 +29715,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>59.628519</v>
+        <v>60.628495</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29891,7 +29896,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>243.874236</v>
+        <v>244.874213</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30072,7 +30077,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>199.890926</v>
+        <v>200.890903</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30253,7 +30258,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>123.538449</v>
+        <v>124.538426</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30431,7 +30436,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>46.956343</v>
+        <v>47.956319</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30609,7 +30614,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>233.897049</v>
+        <v>234.897025</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30790,7 +30795,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>149.643495</v>
+        <v>150.643472</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30968,7 +30973,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>117.692708</v>
+        <v>118.692685</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31149,7 +31154,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>17.597731</v>
+        <v>18.597708</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31327,7 +31332,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>282.598831</v>
+        <v>283.598808</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31508,7 +31513,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>258.949132</v>
+        <v>259.949109</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31686,7 +31691,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>67.679688</v>
+        <v>68.679664</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31864,7 +31869,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>40.724988</v>
+        <v>41.724965</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32037,7 +32042,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>198.591956</v>
+        <v>199.591933</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32218,7 +32223,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>76.936111</v>
+        <v>77.936088</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32396,7 +32401,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>26.571597</v>
+        <v>27.571574</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32574,7 +32579,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>233.901991</v>
+        <v>234.901968</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32752,7 +32757,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>286.835</v>
+        <v>287.834977</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32930,7 +32935,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>208.603067</v>
+        <v>209.603044</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33108,7 +33113,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>279.59838</v>
+        <v>280.598356</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33286,7 +33291,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>270.70522</v>
+        <v>271.705197</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33464,7 +33469,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>208.623819</v>
+        <v>209.623796</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33645,7 +33650,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>137.720845</v>
+        <v>138.720822</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33826,7 +33831,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>6.878981</v>
+        <v>7.878958</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34004,7 +34009,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>279.598021</v>
+        <v>280.597998</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34185,7 +34190,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>235.701563</v>
+        <v>236.701539</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34366,7 +34371,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>180.956262</v>
+        <v>181.956238</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34547,7 +34552,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>213.515972</v>
+        <v>214.515949</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34728,7 +34733,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>124.669317</v>
+        <v>125.669294</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34906,7 +34911,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>46.954317</v>
+        <v>47.954294</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35084,7 +35089,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>286.842569</v>
+        <v>287.842546</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35252,7 +35257,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>221.664641</v>
+        <v>222.664618</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35433,7 +35438,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>199.888438</v>
+        <v>200.888414</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35617,7 +35622,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>180.959803</v>
+        <v>181.95978</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35801,7 +35806,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>235.705382</v>
+        <v>236.705359</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35982,7 +35987,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>102.797743</v>
+        <v>103.79772</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36160,7 +36165,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>279.689028</v>
+        <v>280.689005</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36338,7 +36343,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>293.909861</v>
+        <v>294.909838</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36519,7 +36524,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>199.894282</v>
+        <v>200.894259</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36697,7 +36702,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>173.681678</v>
+        <v>174.681655</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36878,7 +36883,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>266.925567</v>
+        <v>267.925544</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37056,7 +37061,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>277.50397</v>
+        <v>278.503947</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37234,7 +37239,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>205.607523</v>
+        <v>206.6075</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37412,7 +37417,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>30.604225</v>
+        <v>31.604201</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37593,7 +37598,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>261.561539</v>
+        <v>262.561516</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37774,7 +37779,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>209.530961</v>
+        <v>210.530938</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37952,7 +37957,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>67.685301</v>
+        <v>68.685278</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38130,7 +38135,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>282.572164</v>
+        <v>283.572141</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38308,7 +38313,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>279.688484</v>
+        <v>280.688461</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38486,7 +38491,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>13.541863</v>
+        <v>14.54184</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38664,7 +38669,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>278.610706</v>
+        <v>279.610683</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38842,7 +38847,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>290.593287</v>
+        <v>291.593264</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39020,7 +39025,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>292.733681</v>
+        <v>293.733657</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39198,7 +39203,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>282.646863</v>
+        <v>283.64684</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39376,7 +39381,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>244.568553</v>
+        <v>245.56853</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39557,7 +39562,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>244.586528</v>
+        <v>245.586505</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39738,7 +39743,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>149.911563</v>
+        <v>150.911539</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39919,7 +39924,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>6.703981</v>
+        <v>7.703958</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40097,7 +40102,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>291.689005</v>
+        <v>292.688981</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40275,7 +40280,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>282.587928</v>
+        <v>283.587905</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40453,7 +40458,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>291.684873</v>
+        <v>292.68485</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40634,7 +40639,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>192.639178</v>
+        <v>193.639155</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40815,7 +40820,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>124.693472</v>
+        <v>125.693449</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -40996,7 +41001,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>117.71162</v>
+        <v>118.711597</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41177,7 +41182,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>52.933113</v>
+        <v>53.93309</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41358,7 +41363,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>52.934792</v>
+        <v>53.934769</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41539,7 +41544,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>199.893634</v>
+        <v>200.893611</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41720,7 +41725,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>251.659109</v>
+        <v>252.659086</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41898,7 +41903,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>268.900417</v>
+        <v>269.900394</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42079,7 +42084,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>208.670023</v>
+        <v>209.67</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42263,7 +42268,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>200.91022</v>
+        <v>201.910197</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42444,7 +42449,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>180.958113</v>
+        <v>181.95809</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42622,7 +42627,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>131.886979</v>
+        <v>132.886956</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42803,7 +42808,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>17.59559</v>
+        <v>18.595567</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42984,7 +42989,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>243.874769</v>
+        <v>244.874745</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43165,7 +43170,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>199.753229</v>
+        <v>200.753206</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43346,7 +43351,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>102.79897</v>
+        <v>103.798947</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43524,7 +43529,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>67.678634</v>
+        <v>68.678611</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43705,7 +43710,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>118.515995</v>
+        <v>119.515972</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43886,7 +43891,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>233.900764</v>
+        <v>234.900741</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44059,7 +44064,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>279.573264</v>
+        <v>280.573241</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44237,7 +44242,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>244.567338</v>
+        <v>245.567315</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44421,7 +44426,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>208.601412</v>
+        <v>209.601389</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44602,7 +44607,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>151.855995</v>
+        <v>152.855972</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44786,7 +44791,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>180.66088</v>
+        <v>181.660856</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44967,7 +44972,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>174.940775</v>
+        <v>175.940752</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45148,7 +45153,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>25.719583</v>
+        <v>26.71956</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45326,7 +45331,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>244.567743</v>
+        <v>245.56772</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45507,7 +45512,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>215.828275</v>
+        <v>216.828252</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45688,7 +45693,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>52.678461</v>
+        <v>53.678438</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45869,7 +45874,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>264.720938</v>
+        <v>265.720914</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46050,7 +46055,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>53.724421</v>
+        <v>54.724398</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46160,7 +46165,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>6.874352</v>
+        <v>7.874329</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46270,7 +46275,7 @@
         <v>46097.39764412037</v>
       </c>
       <c r="AN256">
-        <v>6.87434</v>
+        <v>7.874317</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46451,7 +46456,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>76.935394</v>
+        <v>77.93537000000001</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46632,7 +46637,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>243.835347</v>
+        <v>244.835324</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46810,7 +46815,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>174.950521</v>
+        <v>175.950498</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46991,7 +46996,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>174.948368</v>
+        <v>175.948345</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47169,7 +47174,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>149.532917</v>
+        <v>150.532894</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47345,7 +47350,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>241.779606</v>
+        <v>242.779583</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47523,7 +47528,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>165.939086</v>
+        <v>166.939063</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47707,7 +47712,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>151.711308</v>
+        <v>152.711285</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47885,7 +47890,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>100.707998</v>
+        <v>101.707975</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48066,7 +48071,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>272.698044</v>
+        <v>273.698021</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48244,7 +48249,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>282.646123</v>
+        <v>283.6461</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48425,7 +48430,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>261.561887</v>
+        <v>262.561863</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48606,7 +48611,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>137.720741</v>
+        <v>138.720718</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48784,7 +48789,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>151.712118</v>
+        <v>152.712095</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48965,7 +48970,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>117.695509</v>
+        <v>118.695486</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49146,7 +49151,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>261.562431</v>
+        <v>262.562407</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49324,7 +49329,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>180.952512</v>
+        <v>181.952488</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49508,7 +49513,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>132.699352</v>
+        <v>133.699329</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49689,7 +49694,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>271.591238</v>
+        <v>272.591215</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49870,7 +49875,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>186.806759</v>
+        <v>187.806736</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50051,7 +50056,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>117.71228</v>
+        <v>118.712257</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50232,7 +50237,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>138.893368</v>
+        <v>139.893345</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50413,7 +50418,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>257.783229</v>
+        <v>258.783206</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50620,7 +50625,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>137.826424</v>
+        <v>138.8264</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50798,7 +50803,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>128.622431</v>
+        <v>129.622407</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50979,7 +50984,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>111.655139</v>
+        <v>112.655116</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51163,7 +51168,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>166.942512</v>
+        <v>167.942488</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51341,7 +51346,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>3.886713</v>
+        <v>4.88669</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51519,7 +51524,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>258.949502</v>
+        <v>259.949479</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51697,7 +51702,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>270.706169</v>
+        <v>271.706146</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51875,7 +51880,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>233.901829</v>
+        <v>234.901806</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52056,7 +52061,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>213.629896</v>
+        <v>214.629873</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52240,7 +52245,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>154.957315</v>
+        <v>155.957292</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52421,7 +52426,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>132.693009</v>
+        <v>133.692986</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52602,7 +52607,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>257.911898</v>
+        <v>258.911875</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52780,7 +52785,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>271.9111</v>
+        <v>272.911076</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52961,7 +52966,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>216.518993</v>
+        <v>217.51897</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53139,7 +53144,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>277.502002</v>
+        <v>278.501979</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53320,7 +53325,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>199.89485</v>
+        <v>200.894826</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53501,7 +53506,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>6.87559</v>
+        <v>7.875567</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53682,7 +53687,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>117.563738</v>
+        <v>118.563715</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53860,7 +53865,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>244.569676</v>
+        <v>245.569653</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54038,7 +54043,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>3.888924</v>
+        <v>4.8889</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54227,7 +54232,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>268.90088</v>
+        <v>269.900856</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54408,7 +54413,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>199.88772</v>
+        <v>200.887697</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54586,7 +54591,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>174.69919</v>
+        <v>175.699167</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54767,7 +54772,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>96.84490700000001</v>
+        <v>97.84488399999999</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54953,7 +54958,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>209.66066</v>
+        <v>210.660637</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55131,7 +55136,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>283.940602</v>
+        <v>284.940579</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55312,7 +55317,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>173.612813</v>
+        <v>174.612789</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55493,7 +55498,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>128.723021</v>
+        <v>129.722998</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55674,7 +55679,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>102.810486</v>
+        <v>103.810463</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55855,7 +55860,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>76.93722200000001</v>
+        <v>77.93719900000001</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56036,7 +56041,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>173.611377</v>
+        <v>174.611354</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56217,7 +56222,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>173.613148</v>
+        <v>174.613125</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56327,7 +56332,7 @@
         <v>46097.39763636574</v>
       </c>
       <c r="AN312">
-        <v>6.874352</v>
+        <v>7.874329</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56505,7 +56510,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>277.502384</v>
+        <v>278.502361</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56683,7 +56688,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>46.958623</v>
+        <v>47.9586</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56864,7 +56869,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>230.564074</v>
+        <v>231.564051</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57042,7 +57047,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>26.571076</v>
+        <v>27.571053</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57223,7 +57228,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>149.644444</v>
+        <v>150.644421</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57404,7 +57409,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>6.876053</v>
+        <v>7.87603</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57582,7 +57587,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW319">
-        <v>3.88816</v>
+        <v>4.888137</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57763,7 +57768,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>230.566863</v>
+        <v>231.56684</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57944,7 +57949,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>243.872106</v>
+        <v>244.872083</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58122,7 +58127,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>52.602014</v>
+        <v>53.601991</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58300,7 +58305,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>286.835451</v>
+        <v>287.835428</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58481,7 +58486,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>180.951655</v>
+        <v>181.951632</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58659,7 +58664,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>144.661736</v>
+        <v>145.661713</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58840,7 +58845,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>132.696991</v>
+        <v>133.696968</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59021,7 +59026,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>265.609502</v>
+        <v>266.609479</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59202,7 +59207,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>220.668519</v>
+        <v>221.668495</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59383,7 +59388,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>102.812014</v>
+        <v>103.811991</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59564,7 +59569,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>61.81463</v>
+        <v>62.814606</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59742,7 +59747,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>213.575891</v>
+        <v>214.575868</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59926,7 +59931,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>159.586609</v>
+        <v>160.586586</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60104,7 +60109,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>244.569005</v>
+        <v>245.568981</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60285,7 +60290,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>138.889583</v>
+        <v>139.88956</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60466,7 +60471,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>128.622859</v>
+        <v>129.622836</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60644,7 +60649,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>223.593484</v>
+        <v>224.593461</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60825,7 +60830,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>69.57534699999999</v>
+        <v>70.57532399999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61006,7 +61011,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>215.824919</v>
+        <v>216.824896</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61182,7 +61187,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>149.643958</v>
+        <v>150.643935</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61201,7 +61206,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="E340" s="2">
@@ -61216,10 +61221,10 @@
         <v>46076.60421634259</v>
       </c>
       <c r="J340" s="2">
-        <v>46100.40009980324</v>
+        <v>46104.71070659722</v>
       </c>
       <c r="N340" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O340" t="inlineStr">
         <is>
@@ -61291,7 +61296,7 @@
       </c>
       <c r="AF340" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="AI340" s="2">
@@ -61307,16 +61312,19 @@
         <v>46092.38034266204</v>
       </c>
       <c r="AM340" s="2">
-        <v>46100.40009168981</v>
+        <v>46104.71069792824</v>
       </c>
       <c r="AN340">
-        <v>8.019745</v>
+        <v>8.075637</v>
       </c>
       <c r="AO340" s="2">
         <v>46100.40009251158</v>
       </c>
+      <c r="AP340" s="2">
+        <v>46104.65479837963</v>
+      </c>
       <c r="AQ340">
-        <v>3.871898</v>
+        <v>4.815972</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61497,7 +61505,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>6.876551</v>
+        <v>7.876528</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61675,7 +61683,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>291.693831</v>
+        <v>292.693808</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61856,7 +61864,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>201.892801</v>
+        <v>202.892778</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62037,7 +62045,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>180.959016</v>
+        <v>181.958993</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62218,7 +62226,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>130.607037</v>
+        <v>131.607014</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62399,7 +62407,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>248.932176</v>
+        <v>249.932153</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62580,7 +62588,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>46.772905</v>
+        <v>47.772882</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62761,7 +62769,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>27.945347</v>
+        <v>28.945324</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62942,7 +62950,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>111.655752</v>
+        <v>112.655729</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63120,7 +63128,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>205.652558</v>
+        <v>206.652535</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63301,7 +63309,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>184.591076</v>
+        <v>185.591053</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63479,7 +63487,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>149.645069</v>
+        <v>150.645046</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63660,7 +63668,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>130.608264</v>
+        <v>131.608241</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63841,7 +63849,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>257.912118</v>
+        <v>258.912095</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64022,7 +64030,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>186.806308</v>
+        <v>187.806285</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64203,7 +64211,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>174.940012</v>
+        <v>175.939988</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64384,7 +64392,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>181.012523</v>
+        <v>182.0125</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64565,7 +64573,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>116.727269</v>
+        <v>117.727245</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64746,7 +64754,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>66.606458</v>
+        <v>67.606435</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64927,7 +64935,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>282.596736</v>
+        <v>283.596713</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65105,7 +65113,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>283.938912</v>
+        <v>284.938889</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65286,7 +65294,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>97.726204</v>
+        <v>98.726181</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65467,7 +65475,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>52.740521</v>
+        <v>53.740498</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65645,7 +65653,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>290.587581</v>
+        <v>291.587558</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65826,7 +65834,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>180.960231</v>
+        <v>181.960208</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66004,7 +66012,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>100.707917</v>
+        <v>101.707894</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66185,7 +66193,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>261.562951</v>
+        <v>262.562928</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66366,7 +66374,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>151.8575</v>
+        <v>152.857477</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66547,7 +66555,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>149.892535</v>
+        <v>150.892512</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66725,7 +66733,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>277.501736</v>
+        <v>278.501713</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66906,7 +66914,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>248.929491</v>
+        <v>249.929468</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67084,7 +67092,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>167.529688</v>
+        <v>168.529664</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67262,7 +67270,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>251.722049</v>
+        <v>252.722025</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67443,7 +67451,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>199.889074</v>
+        <v>200.889051</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67624,7 +67632,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>6.875243</v>
+        <v>7.87522</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67802,7 +67810,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>286.727488</v>
+        <v>287.727465</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67980,7 +67988,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>282.633345</v>
+        <v>283.633322</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68161,7 +68169,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>130.613657</v>
+        <v>131.613634</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68339,7 +68347,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>283.939711</v>
+        <v>284.939688</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68517,7 +68525,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>261.563472</v>
+        <v>262.563449</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68695,7 +68703,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>291.685231</v>
+        <v>292.685208</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -68873,7 +68881,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>139.621609</v>
+        <v>140.621586</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69051,7 +69059,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>277.500266</v>
+        <v>278.500243</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69229,7 +69237,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>244.566146</v>
+        <v>245.566123</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69410,7 +69418,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>235.698773</v>
+        <v>236.69875</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69591,7 +69599,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>151.856817</v>
+        <v>152.856794</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69772,7 +69780,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>96.84375</v>
+        <v>97.843727</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69953,7 +69961,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>102.810938</v>
+        <v>103.810914</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70126,7 +70134,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>198.592303</v>
+        <v>199.59228</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70299,7 +70307,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>198.59184</v>
+        <v>199.591817</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70480,7 +70488,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>102.809363</v>
+        <v>103.80934</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70661,7 +70669,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>117.709884</v>
+        <v>118.709861</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70842,7 +70850,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>130.607245</v>
+        <v>131.607222</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>287.834294</v>
+        <v>288.834329</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>130.950289</v>
+        <v>131.950324</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>118.708333</v>
+        <v>119.708368</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>242.779954</v>
+        <v>243.779988</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>245.566505</v>
+        <v>246.566539</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>53.934051</v>
+        <v>54.934086</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>280.604005</v>
+        <v>281.604039</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>229.644641</v>
+        <v>230.644676</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>213.727928</v>
+        <v>214.727963</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>129.624572</v>
+        <v>130.624606</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>214.630301</v>
+        <v>215.630336</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>292.687998</v>
+        <v>293.688032</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>278.503148</v>
+        <v>279.503183</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>247.631678</v>
+        <v>248.631713</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>249.928981</v>
+        <v>250.929016</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>129.578796</v>
+        <v>130.578831</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>111.815058</v>
+        <v>112.815093</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>217.51581</v>
+        <v>218.515845</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>209.604572</v>
+        <v>210.604606</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>130.950718</v>
+        <v>131.950752</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>47.952743</v>
+        <v>48.952778</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>46.69794</v>
+        <v>47.697975</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>53.93147</v>
+        <v>54.931505</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>242.779421</v>
+        <v>243.779456</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>129.723634</v>
+        <v>130.723669</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>27.577789</v>
+        <v>28.577824</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>77.934444</v>
+        <v>78.934479</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>278.508657</v>
+        <v>279.508692</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>199.592141</v>
+        <v>200.592176</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>208.685625</v>
+        <v>209.68566</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>138.825671</v>
+        <v>139.825706</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>280.598912</v>
+        <v>281.598947</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>137.607072</v>
+        <v>138.607106</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>216.827627</v>
+        <v>217.827662</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>125.725417</v>
+        <v>126.725451</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>244.873426</v>
+        <v>245.873461</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>252.659167</v>
+        <v>253.659201</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7354,7 +7354,7 @@
         <v>46104.65056451389</v>
       </c>
       <c r="N39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>46100.3824021875</v>
       </c>
       <c r="AT39">
-        <v>1.621701</v>
+        <v>2.621736</v>
       </c>
       <c r="AU39" s="2">
         <v>46100.38240289352</v>
@@ -7676,7 +7676,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>139.891065</v>
+        <v>140.8911</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7857,7 +7857,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>118.705313</v>
+        <v>119.705347</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8038,7 +8038,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>77.695046</v>
+        <v>78.695081</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8216,7 +8216,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>47.954734</v>
+        <v>48.954769</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8397,7 +8397,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>67.618692</v>
+        <v>68.61872700000001</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8578,7 +8578,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>26.718727</v>
+        <v>27.718762</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8759,7 +8759,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>201.910428</v>
+        <v>202.910463</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8940,7 +8940,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>216.827014</v>
+        <v>217.827049</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8974,10 +8974,10 @@
         <v>46076.60416619213</v>
       </c>
       <c r="J48" s="2">
-        <v>46104.68505300926</v>
+        <v>46105.34261104166</v>
       </c>
       <c r="N48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -9047,9 +9047,19 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.u432ivoyjq30</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AD48" t="inlineStr">
         <is>
           <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -9078,8 +9088,17 @@
       <c r="AO48" s="2">
         <v>46090.58140600695</v>
       </c>
+      <c r="AP48" s="2">
+        <v>46105.34261200231</v>
+      </c>
       <c r="AQ48">
-        <v>14.690498</v>
+        <v>14.761146</v>
+      </c>
+      <c r="AR48" s="2">
+        <v>46105.34261277778</v>
+      </c>
+      <c r="AT48">
+        <v>0.929387</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9263,7 +9282,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>167.943785</v>
+        <v>168.943819</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9444,7 +9463,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>167.942569</v>
+        <v>168.942604</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9612,7 +9631,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>25.592824</v>
+        <v>26.592859</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9793,7 +9812,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>244.87441</v>
+        <v>245.874444</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -9971,7 +9990,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>245.567917</v>
+        <v>246.567951</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10155,7 +10174,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>152.710532</v>
+        <v>153.710567</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10336,7 +10355,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>258.783403</v>
+        <v>259.783438</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10514,7 +10533,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>25.592083</v>
+        <v>26.592118</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10698,7 +10717,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>236.540938</v>
+        <v>237.540972</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10876,7 +10895,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>4.889259</v>
+        <v>5.889294</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11054,7 +11073,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>283.64559</v>
+        <v>284.645625</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11232,7 +11251,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>273.69441</v>
+        <v>274.694444</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11413,7 +11432,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>103.796956</v>
+        <v>104.796991</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11591,7 +11610,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>68.688241</v>
+        <v>69.688275</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11769,7 +11788,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>245.567083</v>
+        <v>246.567118</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11950,7 +11969,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>139.895174</v>
+        <v>140.895208</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12131,7 +12150,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>119.514815</v>
+        <v>120.51485</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12312,7 +12331,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>181.568657</v>
+        <v>182.568692</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12490,7 +12509,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>248.822766</v>
+        <v>249.822801</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12668,7 +12687,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>209.623912</v>
+        <v>210.623947</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12852,7 +12871,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>129.623785</v>
+        <v>130.623819</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13030,7 +13049,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>67.598333</v>
+        <v>68.59836799999999</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13208,7 +13227,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>284.938727</v>
+        <v>285.938762</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13386,7 +13405,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>287.83162</v>
+        <v>288.831655</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13564,7 +13583,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>245.582859</v>
+        <v>246.582894</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13745,7 +13764,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>202.684387</v>
+        <v>203.684421</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13923,7 +13942,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>138.720984</v>
+        <v>139.721019</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14104,7 +14123,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>145.716944</v>
+        <v>146.716979</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14285,7 +14304,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>97.844641</v>
+        <v>98.84467600000001</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14466,7 +14485,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>102.542188</v>
+        <v>103.542222</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14647,7 +14666,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>47.773576</v>
+        <v>48.773611</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14828,7 +14847,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>7.879433</v>
+        <v>8.879467999999999</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15014,7 +15033,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>259.654294</v>
+        <v>260.654329</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15192,7 +15211,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>196.680509</v>
+        <v>197.680544</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15373,7 +15392,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>131.6075</v>
+        <v>132.607535</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15554,7 +15573,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>7.875058</v>
+        <v>8.875093</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15738,7 +15757,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>200.889155</v>
+        <v>201.88919</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15919,7 +15938,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>118.69566</v>
+        <v>119.695694</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16100,7 +16119,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>273.697801</v>
+        <v>274.697836</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16281,7 +16300,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>167.943565</v>
+        <v>168.9436</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16459,7 +16478,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>152.858924</v>
+        <v>153.858958</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16640,7 +16659,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>147.553681</v>
+        <v>148.553715</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16821,7 +16840,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>137.605729</v>
+        <v>138.605764</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -16999,7 +17018,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>252.723125</v>
+        <v>253.72316</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17177,7 +17196,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>283.59787</v>
+        <v>284.597905</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17366,7 +17385,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>231.567535</v>
+        <v>232.567569</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17547,7 +17566,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>200.887442</v>
+        <v>201.887477</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17728,7 +17747,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>181.561505</v>
+        <v>182.561539</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17909,7 +17928,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>103.806319</v>
+        <v>104.806354</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17946,7 +17965,7 @@
         <v>46097.3976515625</v>
       </c>
       <c r="N98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -18019,7 +18038,7 @@
         <v>46097.3976521875</v>
       </c>
       <c r="AN98">
-        <v>7.874306</v>
+        <v>8.87434</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18200,7 +18219,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>237.570046</v>
+        <v>238.570081</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18378,7 +18397,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>278.502766</v>
+        <v>279.502801</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18556,7 +18575,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>187.943194</v>
+        <v>188.943229</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18734,7 +18753,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>245.566308</v>
+        <v>246.566343</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18915,7 +18934,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>77.938067</v>
+        <v>78.938102</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19093,7 +19112,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>284.93912</v>
+        <v>285.939155</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19271,7 +19290,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>196.553785</v>
+        <v>197.553819</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19452,7 +19471,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>118.708889</v>
+        <v>119.708924</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19633,7 +19652,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>214.622963</v>
+        <v>215.622998</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19814,7 +19833,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>206.698819</v>
+        <v>207.698854</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -19992,7 +20011,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>46.722604</v>
+        <v>47.722639</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20170,7 +20189,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>280.688727</v>
+        <v>281.688762</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20351,7 +20370,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>236.685718</v>
+        <v>237.685752</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20535,7 +20554,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>175.944468</v>
+        <v>176.944502</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20716,7 +20735,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>117.723785</v>
+        <v>118.723819</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20897,7 +20916,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>235.122593</v>
+        <v>236.122627</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21078,7 +21097,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>243.766111</v>
+        <v>244.766146</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21259,7 +21278,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>196.609734</v>
+        <v>197.609769</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21440,7 +21459,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>145.698426</v>
+        <v>146.698461</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21621,7 +21640,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>118.69434</v>
+        <v>119.694375</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21802,7 +21821,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>77.93669</v>
+        <v>78.936725</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -21983,7 +22002,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>54.723981</v>
+        <v>55.724016</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22161,7 +22180,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>287.834583</v>
+        <v>288.834618</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22339,7 +22358,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>273.645463</v>
+        <v>274.645498</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22520,7 +22539,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>283.596007</v>
+        <v>284.596042</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22701,7 +22720,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>175.94287</v>
+        <v>176.942905</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22882,7 +22901,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>129.723148</v>
+        <v>130.723183</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23063,7 +23082,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>147.544317</v>
+        <v>148.544352</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23241,7 +23260,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>66.588553</v>
+        <v>67.588588</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23422,7 +23441,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>262.564676</v>
+        <v>263.564711</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23606,7 +23625,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>236.705729</v>
+        <v>237.705764</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23784,7 +23803,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>214.576169</v>
+        <v>215.576204</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -23965,7 +23984,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>18.596678</v>
+        <v>19.596713</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24146,7 +24165,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>200.885289</v>
+        <v>201.885324</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24324,7 +24343,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>278.50338</v>
+        <v>279.503414</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24505,7 +24524,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>118.695764</v>
+        <v>119.695799</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24686,7 +24705,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>102.542894</v>
+        <v>103.542928</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24859,7 +24878,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>273.597975</v>
+        <v>274.598009</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25040,7 +25059,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>103.798403</v>
+        <v>104.798438</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25221,7 +25240,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>32.675093</v>
+        <v>33.675127</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25402,7 +25421,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>187.805544</v>
+        <v>188.805579</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25583,7 +25602,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>181.956956</v>
+        <v>182.956991</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25761,7 +25780,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>291.647998</v>
+        <v>292.648032</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25939,7 +25958,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>217.488356</v>
+        <v>218.488391</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26120,7 +26139,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>175.942326</v>
+        <v>176.942361</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26296,7 +26315,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>111.814826</v>
+        <v>112.814861</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26477,7 +26496,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>45.835764</v>
+        <v>46.835799</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26655,7 +26674,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>273.648669</v>
+        <v>274.648704</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26833,7 +26852,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>278.505035</v>
+        <v>279.505069</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27011,7 +27030,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>4.884931</v>
+        <v>5.884965</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27192,7 +27211,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>214.68566</v>
+        <v>215.685694</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27370,7 +27389,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>248.822338</v>
+        <v>249.822373</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27548,7 +27567,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>245.566806</v>
+        <v>246.56684</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27729,7 +27748,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>208.686655</v>
+        <v>209.68669</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27910,7 +27929,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>67.604838</v>
+        <v>68.604873</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28091,7 +28110,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>180.818831</v>
+        <v>181.818866</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28272,7 +28291,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>180.618889</v>
+        <v>181.618924</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28450,7 +28469,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>47.951875</v>
+        <v>48.95191</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28634,7 +28653,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>103.805949</v>
+        <v>104.805984</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28815,7 +28834,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>202.517025</v>
+        <v>203.51706</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -29004,7 +29023,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>192.582257</v>
+        <v>193.582292</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29172,7 +29191,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>222.652431</v>
+        <v>223.652465</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29353,7 +29372,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>175.941632</v>
+        <v>176.941667</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29534,7 +29553,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>119.515475</v>
+        <v>120.515509</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29715,7 +29734,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>60.628495</v>
+        <v>61.62853</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29896,7 +29915,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>244.874213</v>
+        <v>245.874248</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30077,7 +30096,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>200.890903</v>
+        <v>201.890938</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30258,7 +30277,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>124.538426</v>
+        <v>125.538461</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30436,7 +30455,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>47.956319</v>
+        <v>48.956354</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30614,7 +30633,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>234.897025</v>
+        <v>235.89706</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30795,7 +30814,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>150.643472</v>
+        <v>151.643507</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -30973,7 +30992,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>118.692685</v>
+        <v>119.69272</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31154,7 +31173,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>18.597708</v>
+        <v>19.597743</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31332,7 +31351,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>283.598808</v>
+        <v>284.598843</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31513,7 +31532,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>259.949109</v>
+        <v>260.949144</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31691,7 +31710,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>68.679664</v>
+        <v>69.679699</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31869,7 +31888,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>41.724965</v>
+        <v>42.725</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32042,7 +32061,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>199.591933</v>
+        <v>200.591968</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32223,7 +32242,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>77.936088</v>
+        <v>78.93612299999999</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32401,7 +32420,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>27.571574</v>
+        <v>28.571609</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32579,7 +32598,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>234.901968</v>
+        <v>235.902002</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32757,7 +32776,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>287.834977</v>
+        <v>288.835012</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32935,7 +32954,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>209.603044</v>
+        <v>210.603079</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33113,7 +33132,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>280.598356</v>
+        <v>281.598391</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33291,7 +33310,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>271.705197</v>
+        <v>272.705231</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33469,7 +33488,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>209.623796</v>
+        <v>210.623831</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33650,7 +33669,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>138.720822</v>
+        <v>139.720856</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33831,7 +33850,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>7.878958</v>
+        <v>8.878992999999999</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34009,7 +34028,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>280.597998</v>
+        <v>281.598032</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34190,7 +34209,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>236.701539</v>
+        <v>237.701574</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34371,7 +34390,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>181.956238</v>
+        <v>182.956273</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34552,7 +34571,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>214.515949</v>
+        <v>215.515984</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34733,7 +34752,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>125.669294</v>
+        <v>126.669329</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34911,7 +34930,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>47.954294</v>
+        <v>48.954329</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35089,7 +35108,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>287.842546</v>
+        <v>288.842581</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35257,7 +35276,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>222.664618</v>
+        <v>223.664653</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35438,7 +35457,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>200.888414</v>
+        <v>201.888449</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35622,7 +35641,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>181.95978</v>
+        <v>182.959815</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35806,7 +35825,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>236.705359</v>
+        <v>237.705394</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -35987,7 +36006,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>103.79772</v>
+        <v>104.797755</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36165,7 +36184,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>280.689005</v>
+        <v>281.689039</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36343,7 +36362,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>294.909838</v>
+        <v>295.909873</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36524,7 +36543,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>200.894259</v>
+        <v>201.894294</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36702,7 +36721,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>174.681655</v>
+        <v>175.68169</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36883,7 +36902,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>267.925544</v>
+        <v>268.925579</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37061,7 +37080,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>278.503947</v>
+        <v>279.503981</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37239,7 +37258,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>206.6075</v>
+        <v>207.607535</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37417,7 +37436,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>31.604201</v>
+        <v>32.604236</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37598,7 +37617,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>262.561516</v>
+        <v>263.561551</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37779,7 +37798,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>210.530938</v>
+        <v>211.530972</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -37957,7 +37976,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>68.685278</v>
+        <v>69.68531299999999</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38135,7 +38154,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>283.572141</v>
+        <v>284.572176</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38313,7 +38332,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>280.688461</v>
+        <v>281.688495</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38491,7 +38510,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>14.54184</v>
+        <v>15.541875</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38669,7 +38688,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>279.610683</v>
+        <v>280.610718</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38847,7 +38866,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>291.593264</v>
+        <v>292.593299</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39025,7 +39044,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>293.733657</v>
+        <v>294.733692</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39203,7 +39222,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>283.64684</v>
+        <v>284.646875</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39381,7 +39400,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>245.56853</v>
+        <v>246.568565</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39562,7 +39581,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>245.586505</v>
+        <v>246.586539</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39743,7 +39762,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>150.911539</v>
+        <v>151.911574</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39924,7 +39943,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>7.703958</v>
+        <v>8.703993000000001</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40102,7 +40121,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>292.688981</v>
+        <v>293.689016</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40280,7 +40299,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>283.587905</v>
+        <v>284.58794</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40458,7 +40477,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>292.68485</v>
+        <v>293.684884</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40639,7 +40658,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>193.639155</v>
+        <v>194.63919</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40820,7 +40839,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>125.693449</v>
+        <v>126.693484</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -41001,7 +41020,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>118.711597</v>
+        <v>119.711632</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41182,7 +41201,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>53.93309</v>
+        <v>54.933125</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41363,7 +41382,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>53.934769</v>
+        <v>54.934803</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41544,7 +41563,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>200.893611</v>
+        <v>201.893646</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41725,7 +41744,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>252.659086</v>
+        <v>253.65912</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41903,7 +41922,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>269.900394</v>
+        <v>270.900428</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42084,7 +42103,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>209.67</v>
+        <v>210.670035</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42268,7 +42287,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>201.910197</v>
+        <v>202.910231</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42449,7 +42468,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>181.95809</v>
+        <v>182.958125</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42627,7 +42646,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>132.886956</v>
+        <v>133.886991</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42808,7 +42827,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>18.595567</v>
+        <v>19.595602</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -42989,7 +43008,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>244.874745</v>
+        <v>245.87478</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43170,7 +43189,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>200.753206</v>
+        <v>201.753241</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43351,7 +43370,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>103.798947</v>
+        <v>104.798981</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43529,7 +43548,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>68.678611</v>
+        <v>69.678646</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43710,7 +43729,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>119.515972</v>
+        <v>120.516007</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43891,7 +43910,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>234.900741</v>
+        <v>235.900775</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44064,7 +44083,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>280.573241</v>
+        <v>281.573275</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44242,7 +44261,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>245.567315</v>
+        <v>246.56735</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44426,7 +44445,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>209.601389</v>
+        <v>210.601424</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44607,7 +44626,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>152.855972</v>
+        <v>153.856007</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44791,7 +44810,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>181.660856</v>
+        <v>182.660891</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -44972,7 +44991,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>175.940752</v>
+        <v>176.940787</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45153,7 +45172,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>26.71956</v>
+        <v>27.719595</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45331,7 +45350,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>245.56772</v>
+        <v>246.567755</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45512,7 +45531,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>216.828252</v>
+        <v>217.828287</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45693,7 +45712,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>53.678438</v>
+        <v>54.678472</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45874,7 +45893,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>265.720914</v>
+        <v>266.720949</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46055,7 +46074,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>54.724398</v>
+        <v>55.724433</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46092,7 +46111,7 @@
         <v>46097.3976275</v>
       </c>
       <c r="N255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -46165,7 +46184,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>7.874329</v>
+        <v>8.874363000000001</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46202,7 +46221,7 @@
         <v>46097.39764336806</v>
       </c>
       <c r="N256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -46275,7 +46294,7 @@
         <v>46097.39764412037</v>
       </c>
       <c r="AN256">
-        <v>7.874317</v>
+        <v>8.874352</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46456,7 +46475,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>77.93537000000001</v>
+        <v>78.935405</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46637,7 +46656,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>244.835324</v>
+        <v>245.835359</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46815,7 +46834,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>175.950498</v>
+        <v>176.950532</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -46996,7 +47015,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>175.948345</v>
+        <v>176.94838</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47174,7 +47193,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>150.532894</v>
+        <v>151.532928</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47350,7 +47369,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>242.779583</v>
+        <v>243.779618</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47528,7 +47547,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>166.939063</v>
+        <v>167.939097</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47712,7 +47731,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>152.711285</v>
+        <v>153.711319</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47890,7 +47909,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>101.707975</v>
+        <v>102.708009</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48071,7 +48090,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>273.698021</v>
+        <v>274.698056</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48249,7 +48268,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>283.6461</v>
+        <v>284.646134</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48430,7 +48449,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>262.561863</v>
+        <v>263.561898</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48611,7 +48630,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>138.720718</v>
+        <v>139.720752</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48789,7 +48808,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>152.712095</v>
+        <v>153.71213</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -48970,7 +48989,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>118.695486</v>
+        <v>119.695521</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49151,7 +49170,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>262.562407</v>
+        <v>263.562442</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49329,7 +49348,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>181.952488</v>
+        <v>182.952523</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49513,7 +49532,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>133.699329</v>
+        <v>134.699363</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49694,7 +49713,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>272.591215</v>
+        <v>273.59125</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49875,7 +49894,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>187.806736</v>
+        <v>188.806771</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50056,7 +50075,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>118.712257</v>
+        <v>119.712292</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50237,7 +50256,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>139.893345</v>
+        <v>140.89338</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50418,7 +50437,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>258.783206</v>
+        <v>259.783241</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50625,7 +50644,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>138.8264</v>
+        <v>139.826435</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50803,7 +50822,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>129.622407</v>
+        <v>130.622442</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -50984,7 +51003,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>112.655116</v>
+        <v>113.65515</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51168,7 +51187,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>167.942488</v>
+        <v>168.942523</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51346,7 +51365,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>4.88669</v>
+        <v>5.886725</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51524,7 +51543,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>259.949479</v>
+        <v>260.949514</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51702,7 +51721,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>271.706146</v>
+        <v>272.706181</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51880,7 +51899,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>234.901806</v>
+        <v>235.90184</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52061,7 +52080,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>214.629873</v>
+        <v>215.629907</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52245,7 +52264,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>155.957292</v>
+        <v>156.957326</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52426,7 +52445,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>133.692986</v>
+        <v>134.693021</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52607,7 +52626,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>258.911875</v>
+        <v>259.91191</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52785,7 +52804,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>272.911076</v>
+        <v>273.911111</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -52966,7 +52985,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>217.51897</v>
+        <v>218.519005</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53144,7 +53163,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>278.501979</v>
+        <v>279.502014</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53325,7 +53344,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>200.894826</v>
+        <v>201.894861</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53506,7 +53525,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>7.875567</v>
+        <v>8.875602000000001</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53687,7 +53706,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>118.563715</v>
+        <v>119.56375</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53865,7 +53884,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>245.569653</v>
+        <v>246.569688</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54043,7 +54062,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>4.8889</v>
+        <v>5.888935</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54232,7 +54251,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>269.900856</v>
+        <v>270.900891</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54413,7 +54432,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>200.887697</v>
+        <v>201.887731</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54591,7 +54610,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>175.699167</v>
+        <v>176.699201</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54772,7 +54791,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>97.84488399999999</v>
+        <v>98.844919</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -54958,7 +54977,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>210.660637</v>
+        <v>211.660671</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55136,7 +55155,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>284.940579</v>
+        <v>285.940613</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55317,7 +55336,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>174.612789</v>
+        <v>175.612824</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55498,7 +55517,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>129.722998</v>
+        <v>130.723032</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55679,7 +55698,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>103.810463</v>
+        <v>104.810498</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55860,7 +55879,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>77.93719900000001</v>
+        <v>78.937234</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56041,7 +56060,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>174.611354</v>
+        <v>175.611389</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56222,7 +56241,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>174.613125</v>
+        <v>175.61316</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56259,7 +56278,7 @@
         <v>46097.39763533564</v>
       </c>
       <c r="N312" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -56332,7 +56351,7 @@
         <v>46097.39763636574</v>
       </c>
       <c r="AN312">
-        <v>7.874329</v>
+        <v>8.874363000000001</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56510,7 +56529,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>278.502361</v>
+        <v>279.502396</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56688,7 +56707,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>47.9586</v>
+        <v>48.958634</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56869,7 +56888,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>231.564051</v>
+        <v>232.564086</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57047,7 +57066,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>27.571053</v>
+        <v>28.571088</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57228,7 +57247,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>150.644421</v>
+        <v>151.644456</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57409,7 +57428,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>7.87603</v>
+        <v>8.876065000000001</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57587,7 +57606,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW319">
-        <v>4.888137</v>
+        <v>5.888171</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57768,7 +57787,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>231.56684</v>
+        <v>232.566875</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -57949,7 +57968,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>244.872083</v>
+        <v>245.872118</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58127,7 +58146,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>53.601991</v>
+        <v>54.602025</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58305,7 +58324,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>287.835428</v>
+        <v>288.835463</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58486,7 +58505,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>181.951632</v>
+        <v>182.951667</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58664,7 +58683,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>145.661713</v>
+        <v>146.661748</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58845,7 +58864,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>133.696968</v>
+        <v>134.697002</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59026,7 +59045,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>266.609479</v>
+        <v>267.609514</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59207,7 +59226,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>221.668495</v>
+        <v>222.66853</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59388,7 +59407,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>103.811991</v>
+        <v>104.812025</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59569,7 +59588,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>62.814606</v>
+        <v>63.814641</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59747,7 +59766,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>214.575868</v>
+        <v>215.575903</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -59931,7 +59950,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>160.586586</v>
+        <v>161.58662</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60109,7 +60128,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>245.568981</v>
+        <v>246.569016</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60290,7 +60309,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>139.88956</v>
+        <v>140.889595</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60471,7 +60490,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>129.622836</v>
+        <v>130.62287</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60649,7 +60668,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>224.593461</v>
+        <v>225.593495</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60830,7 +60849,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>70.57532399999999</v>
+        <v>71.57535900000001</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61011,7 +61030,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>216.824896</v>
+        <v>217.824931</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61187,7 +61206,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>150.643935</v>
+        <v>151.64397</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61221,7 +61240,7 @@
         <v>46076.60421634259</v>
       </c>
       <c r="J340" s="2">
-        <v>46104.71070659722</v>
+        <v>46105.34751850694</v>
       </c>
       <c r="N340" t="b">
         <v>1</v>
@@ -61294,6 +61313,11 @@
           <t xml:space="preserve">https://app.pipefy.com/open-cards/1301624491 </t>
         </is>
       </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="AF340" t="inlineStr">
         <is>
           <t>Reprovado na Validação</t>
@@ -61324,7 +61348,7 @@
         <v>46104.65479837963</v>
       </c>
       <c r="AQ340">
-        <v>4.815972</v>
+        <v>5.816007</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61505,7 +61529,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>7.876528</v>
+        <v>8.876563000000001</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61683,7 +61707,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>292.693808</v>
+        <v>293.693843</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61864,7 +61888,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>202.892778</v>
+        <v>203.892813</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62045,7 +62069,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>181.958993</v>
+        <v>182.959028</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62226,7 +62250,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>131.607014</v>
+        <v>132.607049</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62407,7 +62431,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>249.932153</v>
+        <v>250.932188</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62588,7 +62612,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>47.772882</v>
+        <v>48.772917</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62769,7 +62793,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>28.945324</v>
+        <v>29.945359</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -62950,7 +62974,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>112.655729</v>
+        <v>113.655764</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63128,7 +63152,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>206.652535</v>
+        <v>207.652569</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63309,7 +63333,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>185.591053</v>
+        <v>186.591088</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63487,7 +63511,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>150.645046</v>
+        <v>151.645081</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63668,7 +63692,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>131.608241</v>
+        <v>132.608275</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63849,7 +63873,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>258.912095</v>
+        <v>259.91213</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64030,7 +64054,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>187.806285</v>
+        <v>188.806319</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64211,7 +64235,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>175.939988</v>
+        <v>176.940023</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64392,7 +64416,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>182.0125</v>
+        <v>183.012535</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64573,7 +64597,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>117.727245</v>
+        <v>118.72728</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64754,7 +64778,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>67.606435</v>
+        <v>68.60647</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -64935,7 +64959,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>283.596713</v>
+        <v>284.596748</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65113,7 +65137,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>284.938889</v>
+        <v>285.938924</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65294,7 +65318,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>98.726181</v>
+        <v>99.726215</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65475,7 +65499,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>53.740498</v>
+        <v>54.740532</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65653,7 +65677,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>291.587558</v>
+        <v>292.587593</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65834,7 +65858,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>181.960208</v>
+        <v>182.960243</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66012,7 +66036,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>101.707894</v>
+        <v>102.707928</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66193,7 +66217,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>262.562928</v>
+        <v>263.562963</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66374,7 +66398,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>152.857477</v>
+        <v>153.857512</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66555,7 +66579,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>150.892512</v>
+        <v>151.892546</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66733,7 +66757,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>278.501713</v>
+        <v>279.501748</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -66914,7 +66938,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>249.929468</v>
+        <v>250.929502</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67092,7 +67116,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>168.529664</v>
+        <v>169.529699</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67270,7 +67294,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>252.722025</v>
+        <v>253.72206</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67451,7 +67475,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>200.889051</v>
+        <v>201.889086</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67632,7 +67656,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>7.87522</v>
+        <v>8.875254999999999</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67810,7 +67834,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>287.727465</v>
+        <v>288.7275</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -67988,7 +68012,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>283.633322</v>
+        <v>284.633356</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68169,7 +68193,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>131.613634</v>
+        <v>132.613669</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68347,7 +68371,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>284.939688</v>
+        <v>285.939722</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68525,7 +68549,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>262.563449</v>
+        <v>263.563484</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68703,7 +68727,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>292.685208</v>
+        <v>293.685243</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -68881,7 +68905,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>140.621586</v>
+        <v>141.62162</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69059,7 +69083,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>278.500243</v>
+        <v>279.500278</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69237,7 +69261,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>245.566123</v>
+        <v>246.566157</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69418,7 +69442,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>236.69875</v>
+        <v>237.698785</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69599,7 +69623,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>152.856794</v>
+        <v>153.856829</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69780,7 +69804,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>97.843727</v>
+        <v>98.843762</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -69961,7 +69985,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>103.810914</v>
+        <v>104.810949</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70134,7 +70158,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>199.59228</v>
+        <v>200.592315</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70307,7 +70331,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>199.591817</v>
+        <v>200.591852</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70488,7 +70512,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>103.80934</v>
+        <v>104.809375</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70669,7 +70693,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>118.709861</v>
+        <v>119.709896</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70850,7 +70874,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>131.607222</v>
+        <v>132.607257</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>289.83434</v>
+        <v>290.834294</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1025,7 +1025,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW3">
-        <v>120.70838</v>
+        <v>121.708333</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW4">
-        <v>132.950336</v>
+        <v>133.950289</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>244.78</v>
+        <v>245.779954</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>247.566551</v>
+        <v>248.566505</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>55.934097</v>
+        <v>56.934051</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>282.604051</v>
+        <v>283.604005</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>231.644688</v>
+        <v>232.644641</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>215.727975</v>
+        <v>216.727928</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>131.624618</v>
+        <v>132.624572</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>216.630347</v>
+        <v>217.630301</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>294.688044</v>
+        <v>295.687998</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>280.503194</v>
+        <v>281.503148</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>249.631725</v>
+        <v>250.631678</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>251.929028</v>
+        <v>252.928981</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>131.578843</v>
+        <v>132.578796</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>113.815104</v>
+        <v>114.815058</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>219.515856</v>
+        <v>220.51581</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>211.604618</v>
+        <v>212.604572</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>132.950764</v>
+        <v>133.950718</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>49.952789</v>
+        <v>50.952743</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>48.697986</v>
+        <v>49.69794</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>55.931516</v>
+        <v>56.93147</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>244.779468</v>
+        <v>245.779421</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>131.723681</v>
+        <v>132.723634</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>29.577836</v>
+        <v>30.577789</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>79.93449099999999</v>
+        <v>80.934444</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>280.508704</v>
+        <v>281.508657</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5878,7 +5878,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW30">
-        <v>210.685671</v>
+        <v>211.685625</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW31">
-        <v>201.592188</v>
+        <v>202.592141</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>140.825718</v>
+        <v>141.825671</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>282.598958</v>
+        <v>283.598912</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW34">
-        <v>218.827674</v>
+        <v>219.827627</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW35">
-        <v>139.607118</v>
+        <v>140.607072</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>127.725463</v>
+        <v>128.725417</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>246.873472</v>
+        <v>247.873426</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>254.659213</v>
+        <v>255.659167</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7498,7 +7498,7 @@
         <v>46104.52594388889</v>
       </c>
       <c r="AW39">
-        <v>5.040255</v>
+        <v>6.040208</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7679,7 +7679,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>141.891111</v>
+        <v>142.891065</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7860,7 +7860,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>120.705359</v>
+        <v>121.705313</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8041,7 +8041,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>79.695093</v>
+        <v>80.695046</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8222,7 +8222,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW43">
-        <v>69.61873799999999</v>
+        <v>70.618692</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8400,7 +8400,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW44">
-        <v>49.95478</v>
+        <v>50.954734</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8581,7 +8581,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>28.718773</v>
+        <v>29.718727</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8762,7 +8762,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>203.910475</v>
+        <v>204.910428</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8943,7 +8943,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>218.82706</v>
+        <v>219.827014</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9121,7 +9121,7 @@
         <v>46106.37582024305</v>
       </c>
       <c r="AW48">
-        <v>0.896192</v>
+        <v>1.896146</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9305,7 +9305,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>169.943831</v>
+        <v>170.943785</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9486,7 +9486,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>169.942616</v>
+        <v>170.942569</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9654,7 +9654,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>27.59287</v>
+        <v>28.592824</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9835,7 +9835,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>246.874456</v>
+        <v>247.87441</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -10013,7 +10013,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>247.567963</v>
+        <v>248.567917</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10197,7 +10197,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>154.710579</v>
+        <v>155.710532</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10378,7 +10378,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>260.783449</v>
+        <v>261.783403</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10556,7 +10556,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>27.59213</v>
+        <v>28.592083</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10740,7 +10740,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>238.540984</v>
+        <v>239.540938</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10918,7 +10918,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>6.889306</v>
+        <v>7.889259</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11096,7 +11096,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>285.645637</v>
+        <v>286.64559</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11274,7 +11274,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>275.694456</v>
+        <v>276.69441</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11455,7 +11455,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>105.797002</v>
+        <v>106.796956</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11633,7 +11633,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>70.688287</v>
+        <v>71.688241</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11811,7 +11811,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>247.56713</v>
+        <v>248.567083</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11992,7 +11992,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>141.89522</v>
+        <v>142.895174</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12173,7 +12173,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>121.514861</v>
+        <v>122.514815</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12351,7 +12351,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW66">
-        <v>250.822813</v>
+        <v>251.822766</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12535,7 +12535,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW67">
-        <v>131.623831</v>
+        <v>132.623785</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12713,7 +12713,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>211.623958</v>
+        <v>212.623912</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12894,7 +12894,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW69">
-        <v>183.568704</v>
+        <v>184.568657</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13072,7 +13072,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>69.59838000000001</v>
+        <v>70.598333</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13250,7 +13250,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>286.938773</v>
+        <v>287.938727</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13428,7 +13428,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>289.831667</v>
+        <v>290.83162</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13606,7 +13606,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>247.582905</v>
+        <v>248.582859</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13787,7 +13787,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>204.684433</v>
+        <v>205.684387</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13968,7 +13968,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW75">
-        <v>99.844688</v>
+        <v>100.844641</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14149,7 +14149,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>147.716991</v>
+        <v>148.716944</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14327,7 +14327,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW77">
-        <v>140.72103</v>
+        <v>141.720984</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14508,7 +14508,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>104.542234</v>
+        <v>105.542188</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14689,7 +14689,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>49.773623</v>
+        <v>50.773576</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14870,7 +14870,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>9.879479</v>
+        <v>10.879433</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15056,7 +15056,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>261.65434</v>
+        <v>262.654294</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15234,7 +15234,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>198.680556</v>
+        <v>199.680509</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15415,7 +15415,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>133.607546</v>
+        <v>134.6075</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15596,7 +15596,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>9.875104</v>
+        <v>10.875058</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15780,7 +15780,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>202.889201</v>
+        <v>203.889155</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15961,7 +15961,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>120.695706</v>
+        <v>121.69566</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16142,7 +16142,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>275.697847</v>
+        <v>276.697801</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16320,7 +16320,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW88">
-        <v>154.85897</v>
+        <v>155.858924</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16501,7 +16501,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW89">
-        <v>169.943611</v>
+        <v>170.943565</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16682,7 +16682,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>149.553727</v>
+        <v>150.553681</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16863,7 +16863,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>139.605775</v>
+        <v>140.605729</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -17041,7 +17041,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>254.723171</v>
+        <v>255.723125</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17219,7 +17219,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>285.597917</v>
+        <v>286.59787</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17408,7 +17408,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>233.567581</v>
+        <v>234.567535</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17589,7 +17589,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>202.887488</v>
+        <v>203.887442</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17770,7 +17770,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>183.561551</v>
+        <v>184.561505</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17951,7 +17951,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>105.806366</v>
+        <v>106.806319</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17965,12 +17965,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Construção no Canvas</t>
+          <t>Publicar na plataforma</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Reprovado na Validação</t>
         </is>
       </c>
       <c r="E98" s="2">
@@ -17985,7 +17985,7 @@
         <v>46076.60414072916</v>
       </c>
       <c r="J98" s="2">
-        <v>46106.60479704861</v>
+        <v>46107.65867810186</v>
       </c>
       <c r="M98" s="2">
         <v>46106.60414072916</v>
@@ -18051,6 +18051,36 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>https://rehagro.instructure.com/courses/2981/modules</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.tqzjurqxgryn</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>Reprovado na Validação</t>
+        </is>
+      </c>
       <c r="AI98" s="2">
         <v>46076.60414643519</v>
       </c>
@@ -18063,8 +18093,26 @@
       <c r="AL98" s="2">
         <v>46097.3976521875</v>
       </c>
+      <c r="AM98" s="2">
+        <v>46107.65861842592</v>
+      </c>
       <c r="AN98">
-        <v>9.874352</v>
+        <v>10.260903</v>
+      </c>
+      <c r="AO98" s="2">
+        <v>46107.65675528935</v>
+      </c>
+      <c r="AP98" s="2">
+        <v>46107.65867834491</v>
+      </c>
+      <c r="AQ98">
+        <v>0.000116</v>
+      </c>
+      <c r="AR98" s="2">
+        <v>46107.65867851852</v>
+      </c>
+      <c r="AT98">
+        <v>0.613287</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18245,7 +18293,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>239.570093</v>
+        <v>240.570046</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18423,7 +18471,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>280.502813</v>
+        <v>281.502766</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18601,7 +18649,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>189.943241</v>
+        <v>190.943194</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18779,7 +18827,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>247.566354</v>
+        <v>248.566308</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -18960,7 +19008,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>79.938113</v>
+        <v>80.938067</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19138,7 +19186,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>286.939167</v>
+        <v>287.93912</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19316,7 +19364,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>198.553831</v>
+        <v>199.553785</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19497,7 +19545,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>120.708935</v>
+        <v>121.708889</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19678,7 +19726,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>216.623009</v>
+        <v>217.622963</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19859,7 +19907,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>208.698866</v>
+        <v>209.698819</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -20037,7 +20085,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>48.72265</v>
+        <v>49.722604</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20215,7 +20263,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>282.688773</v>
+        <v>283.688727</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20396,7 +20444,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>238.685764</v>
+        <v>239.685718</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20577,7 +20625,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW112">
-        <v>119.723831</v>
+        <v>120.723785</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20761,7 +20809,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW113">
-        <v>177.944514</v>
+        <v>178.944468</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20942,7 +20990,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW114">
-        <v>198.60978</v>
+        <v>199.609734</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21123,7 +21171,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW115">
-        <v>237.122639</v>
+        <v>238.122593</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21304,7 +21352,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW116">
-        <v>245.766157</v>
+        <v>246.766111</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21485,7 +21533,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>147.698472</v>
+        <v>148.698426</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21666,7 +21714,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>120.694387</v>
+        <v>121.69434</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21847,7 +21895,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>79.936736</v>
+        <v>80.93669</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -22028,7 +22076,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>56.724028</v>
+        <v>57.723981</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22206,7 +22254,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>289.83463</v>
+        <v>290.834583</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22387,7 +22435,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW122">
-        <v>285.596053</v>
+        <v>286.596007</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22565,7 +22613,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW123">
-        <v>275.645509</v>
+        <v>276.645463</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22746,7 +22794,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>177.942917</v>
+        <v>178.94287</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22927,7 +22975,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>131.723194</v>
+        <v>132.723148</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23108,7 +23156,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>149.544363</v>
+        <v>150.544317</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23286,7 +23334,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>68.5886</v>
+        <v>69.588553</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23464,7 +23512,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW128">
-        <v>216.576215</v>
+        <v>217.576169</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23645,7 +23693,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW129">
-        <v>264.564722</v>
+        <v>265.564676</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23829,7 +23877,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW130">
-        <v>238.705775</v>
+        <v>239.705729</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -24010,7 +24058,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>20.596725</v>
+        <v>21.596678</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24191,7 +24239,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>202.885336</v>
+        <v>203.885289</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24369,7 +24417,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>280.503426</v>
+        <v>281.50338</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24550,7 +24598,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW134">
-        <v>104.54294</v>
+        <v>105.542894</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24731,7 +24779,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW135">
-        <v>120.69581</v>
+        <v>121.695764</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24904,7 +24952,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>275.598021</v>
+        <v>276.597975</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25085,7 +25133,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>105.798449</v>
+        <v>106.798403</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25266,7 +25314,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>34.675139</v>
+        <v>35.675093</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25447,7 +25495,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>189.80559</v>
+        <v>190.805544</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25628,7 +25676,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>183.957002</v>
+        <v>184.956956</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25806,7 +25854,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>293.648044</v>
+        <v>294.647998</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -25984,7 +26032,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>219.488403</v>
+        <v>220.488356</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26165,7 +26213,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>177.942373</v>
+        <v>178.942326</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26341,7 +26389,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>113.814873</v>
+        <v>114.814826</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26522,7 +26570,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>47.83581</v>
+        <v>48.835764</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26700,7 +26748,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>275.648715</v>
+        <v>276.648669</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26878,7 +26926,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>280.505081</v>
+        <v>281.505035</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27056,7 +27104,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>6.884977</v>
+        <v>7.884931</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27237,7 +27285,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>216.685706</v>
+        <v>217.68566</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27415,7 +27463,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>250.822384</v>
+        <v>251.822338</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27593,7 +27641,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>247.566852</v>
+        <v>248.566806</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27774,7 +27822,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>210.686701</v>
+        <v>211.686655</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -27955,7 +28003,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>69.604884</v>
+        <v>70.604838</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28136,7 +28184,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW154">
-        <v>182.618935</v>
+        <v>183.618889</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28317,7 +28365,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW155">
-        <v>182.818877</v>
+        <v>183.818831</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28495,7 +28543,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>49.951921</v>
+        <v>50.951875</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28679,7 +28727,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>105.805995</v>
+        <v>106.805949</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28860,7 +28908,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>204.517072</v>
+        <v>205.517025</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -29049,7 +29097,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>194.582303</v>
+        <v>195.582257</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29217,7 +29265,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>224.652477</v>
+        <v>225.652431</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29398,7 +29446,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>177.941678</v>
+        <v>178.941632</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29579,7 +29627,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>121.515521</v>
+        <v>122.515475</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29760,7 +29808,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>62.628542</v>
+        <v>63.628495</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29941,7 +29989,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>246.874259</v>
+        <v>247.874213</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30122,7 +30170,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>202.890949</v>
+        <v>203.890903</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30303,7 +30351,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>126.538472</v>
+        <v>127.538426</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30481,7 +30529,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>49.956366</v>
+        <v>50.956319</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30659,7 +30707,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>236.897072</v>
+        <v>237.897025</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30840,7 +30888,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>152.643519</v>
+        <v>153.643472</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -31018,7 +31066,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>120.692731</v>
+        <v>121.692685</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31199,7 +31247,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>20.597755</v>
+        <v>21.597708</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31377,7 +31425,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>285.598854</v>
+        <v>286.598808</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31558,7 +31606,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>261.949155</v>
+        <v>262.949109</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31736,7 +31784,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>70.679711</v>
+        <v>71.679664</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31914,7 +31962,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>43.725012</v>
+        <v>44.724965</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32087,7 +32135,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>201.591979</v>
+        <v>202.591933</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32268,7 +32316,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>79.936134</v>
+        <v>80.936088</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32446,7 +32494,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>29.57162</v>
+        <v>30.571574</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32624,7 +32672,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>236.902014</v>
+        <v>237.901968</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32802,7 +32850,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>289.835023</v>
+        <v>290.834977</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -32980,7 +33028,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>211.60309</v>
+        <v>212.603044</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33158,7 +33206,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>282.598403</v>
+        <v>283.598356</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33336,7 +33384,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>273.705243</v>
+        <v>274.705197</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33514,7 +33562,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>211.623843</v>
+        <v>212.623796</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33695,7 +33743,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>140.720868</v>
+        <v>141.720822</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33876,7 +33924,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>9.879004999999999</v>
+        <v>10.878958</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34054,7 +34102,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>282.598044</v>
+        <v>283.597998</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34235,7 +34283,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>238.701586</v>
+        <v>239.701539</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34416,7 +34464,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>183.956285</v>
+        <v>184.956238</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34597,7 +34645,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>216.515995</v>
+        <v>217.515949</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34778,7 +34826,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>127.66934</v>
+        <v>128.669294</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -34956,7 +35004,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>49.95434</v>
+        <v>50.954294</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35134,7 +35182,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>289.842593</v>
+        <v>290.842546</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35302,7 +35350,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>224.664664</v>
+        <v>225.664618</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35483,7 +35531,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>202.888461</v>
+        <v>203.888414</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35667,7 +35715,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>183.959826</v>
+        <v>184.95978</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35851,7 +35899,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>238.705405</v>
+        <v>239.705359</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -36032,7 +36080,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>105.797766</v>
+        <v>106.79772</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36210,7 +36258,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW199">
-        <v>296.909884</v>
+        <v>297.909838</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36388,7 +36436,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW200">
-        <v>282.689051</v>
+        <v>283.689005</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36569,7 +36617,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>202.894306</v>
+        <v>203.894259</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36747,7 +36795,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>176.681701</v>
+        <v>177.681655</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36928,7 +36976,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>269.92559</v>
+        <v>270.925544</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37106,7 +37154,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>280.503993</v>
+        <v>281.503947</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37284,7 +37332,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>208.607546</v>
+        <v>209.6075</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37462,7 +37510,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>33.604248</v>
+        <v>34.604201</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37643,7 +37691,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>264.561563</v>
+        <v>265.561516</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37824,7 +37872,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>212.530984</v>
+        <v>213.530938</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -38002,7 +38050,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>70.68532399999999</v>
+        <v>71.685278</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38180,7 +38228,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>285.572188</v>
+        <v>286.572141</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38358,7 +38406,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>282.688507</v>
+        <v>283.688461</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38536,7 +38584,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>16.541887</v>
+        <v>17.54184</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38714,7 +38762,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW213">
-        <v>295.733704</v>
+        <v>296.733657</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38892,7 +38940,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW214">
-        <v>281.610729</v>
+        <v>282.610683</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39070,7 +39118,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW215">
-        <v>293.59331</v>
+        <v>294.593264</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39248,7 +39296,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>285.646887</v>
+        <v>286.64684</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39429,7 +39477,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW217">
-        <v>152.911586</v>
+        <v>153.911539</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39607,7 +39655,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW218">
-        <v>247.568576</v>
+        <v>248.56853</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39788,7 +39836,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW219">
-        <v>247.586551</v>
+        <v>248.586505</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -39969,7 +40017,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>9.704005</v>
+        <v>10.703958</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40147,7 +40195,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>294.689028</v>
+        <v>295.688981</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40325,7 +40373,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>285.587951</v>
+        <v>286.587905</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40503,7 +40551,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>294.684896</v>
+        <v>295.68485</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40684,7 +40732,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>195.639201</v>
+        <v>196.639155</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40865,7 +40913,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>127.693495</v>
+        <v>128.693449</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -41046,7 +41094,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>120.711644</v>
+        <v>121.711597</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41227,7 +41275,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW227">
-        <v>55.934815</v>
+        <v>56.934769</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41408,7 +41456,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW228">
-        <v>55.933137</v>
+        <v>56.93309</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41589,7 +41637,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>202.893657</v>
+        <v>203.893611</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41770,7 +41818,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>254.659132</v>
+        <v>255.659086</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41948,7 +41996,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>271.90044</v>
+        <v>272.900394</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42129,7 +42177,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>211.670046</v>
+        <v>212.67</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42313,7 +42361,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>203.910243</v>
+        <v>204.910197</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42494,7 +42542,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>183.958137</v>
+        <v>184.95809</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42672,7 +42720,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>134.887002</v>
+        <v>135.886956</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42853,7 +42901,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>20.595613</v>
+        <v>21.595567</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -43034,7 +43082,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>246.874792</v>
+        <v>247.874745</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43215,7 +43263,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>202.753252</v>
+        <v>203.753206</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43396,7 +43444,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>105.798993</v>
+        <v>106.798947</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43574,7 +43622,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>70.678657</v>
+        <v>71.678611</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43755,7 +43803,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>121.516019</v>
+        <v>122.515972</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43936,7 +43984,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>236.900787</v>
+        <v>237.900741</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44109,7 +44157,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>282.573287</v>
+        <v>283.573241</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44287,7 +44335,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>247.567361</v>
+        <v>248.567315</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44471,7 +44519,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>211.601435</v>
+        <v>212.601389</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44652,7 +44700,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>154.856019</v>
+        <v>155.855972</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44836,7 +44884,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>183.660903</v>
+        <v>184.660856</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -45017,7 +45065,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>177.940799</v>
+        <v>178.940752</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45198,7 +45246,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>28.719606</v>
+        <v>29.71956</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45376,7 +45424,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>247.567766</v>
+        <v>248.56772</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45557,7 +45605,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>218.828299</v>
+        <v>219.828252</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45738,7 +45786,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>55.678484</v>
+        <v>56.678438</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45919,7 +45967,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>267.720961</v>
+        <v>268.720914</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46100,7 +46148,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>56.724444</v>
+        <v>57.724398</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46213,7 +46261,7 @@
         <v>46097.39764412037</v>
       </c>
       <c r="AN255">
-        <v>9.874363000000001</v>
+        <v>10.874317</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46326,7 +46374,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN256">
-        <v>9.874375000000001</v>
+        <v>10.874329</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46507,7 +46555,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>79.935417</v>
+        <v>80.93537000000001</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46688,7 +46736,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>246.83537</v>
+        <v>247.835324</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46869,7 +46917,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW259">
-        <v>177.948391</v>
+        <v>178.948345</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -47047,7 +47095,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW260">
-        <v>177.950544</v>
+        <v>178.950498</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47225,7 +47273,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>152.53294</v>
+        <v>153.532894</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47401,7 +47449,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>244.77963</v>
+        <v>245.779583</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47579,7 +47627,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>168.939109</v>
+        <v>169.939063</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47763,7 +47811,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>154.711331</v>
+        <v>155.711285</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47941,7 +47989,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>103.708021</v>
+        <v>104.707975</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48122,7 +48170,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>275.698067</v>
+        <v>276.698021</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48300,7 +48348,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>285.646146</v>
+        <v>286.6461</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48481,7 +48529,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>264.56191</v>
+        <v>265.561863</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48659,7 +48707,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW269">
-        <v>154.712141</v>
+        <v>155.712095</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48840,7 +48888,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW270">
-        <v>140.720764</v>
+        <v>141.720718</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -49021,7 +49069,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>120.695532</v>
+        <v>121.695486</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49202,7 +49250,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>264.562454</v>
+        <v>265.562407</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49380,7 +49428,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>183.952535</v>
+        <v>184.952488</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49564,7 +49612,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>135.699375</v>
+        <v>136.699329</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49745,7 +49793,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>274.591262</v>
+        <v>275.591215</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49926,7 +49974,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>189.806782</v>
+        <v>190.806736</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50107,7 +50155,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW277">
-        <v>141.893391</v>
+        <v>142.893345</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50288,7 +50336,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW278">
-        <v>260.783252</v>
+        <v>261.783206</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50495,7 +50543,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW279">
-        <v>140.826447</v>
+        <v>141.8264</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50676,7 +50724,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW280">
-        <v>120.712303</v>
+        <v>121.712257</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50854,7 +50902,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>131.622454</v>
+        <v>132.622407</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -51038,7 +51086,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW282">
-        <v>169.942535</v>
+        <v>170.942488</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51219,7 +51267,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW283">
-        <v>114.655162</v>
+        <v>115.655116</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51397,7 +51445,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>6.886736</v>
+        <v>7.88669</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51575,7 +51623,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>261.949525</v>
+        <v>262.949479</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51753,7 +51801,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>273.706192</v>
+        <v>274.706146</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51934,7 +51982,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW287">
-        <v>216.629919</v>
+        <v>217.629873</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52112,7 +52160,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW288">
-        <v>236.901852</v>
+        <v>237.901806</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52296,7 +52344,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>157.957338</v>
+        <v>158.957292</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52477,7 +52525,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW290">
-        <v>260.911921</v>
+        <v>261.911875</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52658,7 +52706,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW291">
-        <v>135.693032</v>
+        <v>136.692986</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52836,7 +52884,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>274.911123</v>
+        <v>275.911076</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -53017,7 +53065,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>219.519016</v>
+        <v>220.51897</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53195,7 +53243,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>280.502025</v>
+        <v>281.501979</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53376,7 +53424,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>202.894873</v>
+        <v>203.894826</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53557,7 +53605,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>9.875613</v>
+        <v>10.875567</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53738,7 +53786,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>120.563762</v>
+        <v>121.563715</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53916,7 +53964,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>247.569699</v>
+        <v>248.569653</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54094,7 +54142,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>6.888947</v>
+        <v>7.8889</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54283,7 +54331,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>271.900903</v>
+        <v>272.900856</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54464,7 +54512,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>202.887743</v>
+        <v>203.887697</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54642,7 +54690,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>177.699213</v>
+        <v>178.699167</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54823,7 +54871,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>99.844931</v>
+        <v>100.844884</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -55001,7 +55049,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW304">
-        <v>286.940625</v>
+        <v>287.940579</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55182,7 +55230,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW305">
-        <v>131.723044</v>
+        <v>132.722998</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55368,7 +55416,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW306">
-        <v>212.660683</v>
+        <v>213.660637</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55549,7 +55597,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW307">
-        <v>176.612836</v>
+        <v>177.612789</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55730,7 +55778,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>105.810509</v>
+        <v>106.810463</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55911,7 +55959,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>79.937245</v>
+        <v>80.93719900000001</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56092,7 +56140,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW310">
-        <v>176.613171</v>
+        <v>177.613125</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56273,7 +56321,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW311">
-        <v>176.6114</v>
+        <v>177.611354</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56307,7 +56355,7 @@
         <v>46076.70817686342</v>
       </c>
       <c r="J312" s="2">
-        <v>46106.70819864584</v>
+        <v>46107.65272324074</v>
       </c>
       <c r="M312" s="2">
         <v>46106.70817686342</v>
@@ -56434,7 +56482,7 @@
         <v>46106.65167777778</v>
       </c>
       <c r="AT312">
-        <v>0.620336</v>
+        <v>1.620289</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56612,7 +56660,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>280.502407</v>
+        <v>281.502361</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56790,7 +56838,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>49.958646</v>
+        <v>50.9586</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -56971,7 +57019,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>233.564097</v>
+        <v>234.564051</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57152,7 +57200,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW316">
-        <v>152.644468</v>
+        <v>153.644421</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57330,7 +57378,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW317">
-        <v>29.5711</v>
+        <v>30.571053</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57511,7 +57559,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>9.876075999999999</v>
+        <v>10.87603</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57689,7 +57737,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW319">
-        <v>6.888183</v>
+        <v>7.888137</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57870,7 +57918,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>233.566887</v>
+        <v>234.56684</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -58051,7 +58099,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>246.87213</v>
+        <v>247.872083</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58229,7 +58277,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>55.602037</v>
+        <v>56.601991</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58407,7 +58455,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>289.835475</v>
+        <v>290.835428</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58588,7 +58636,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>183.951678</v>
+        <v>184.951632</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58766,7 +58814,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>147.661759</v>
+        <v>148.661713</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58947,7 +58995,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>135.697014</v>
+        <v>136.696968</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59128,7 +59176,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>268.609525</v>
+        <v>269.609479</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59309,7 +59357,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>223.668542</v>
+        <v>224.668495</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59490,7 +59538,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>105.812037</v>
+        <v>106.811991</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59671,7 +59719,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>64.81465300000001</v>
+        <v>65.814606</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59849,7 +59897,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>216.575914</v>
+        <v>217.575868</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -60033,7 +60081,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>162.586632</v>
+        <v>163.586586</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60214,7 +60262,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW333">
-        <v>141.889606</v>
+        <v>142.88956</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60395,7 +60443,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW334">
-        <v>131.622882</v>
+        <v>132.622836</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60573,7 +60621,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW335">
-        <v>247.569028</v>
+        <v>248.568981</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60751,7 +60799,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>226.593507</v>
+        <v>227.593461</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60932,7 +60980,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>72.57537000000001</v>
+        <v>73.57532399999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61108,7 +61156,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW338">
-        <v>152.643981</v>
+        <v>153.643935</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61289,7 +61337,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW339">
-        <v>218.824942</v>
+        <v>219.824896</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61323,7 +61371,7 @@
         <v>46076.60421634259</v>
       </c>
       <c r="J340" s="2">
-        <v>46106.60479703704</v>
+        <v>46107.43268002315</v>
       </c>
       <c r="M340" s="2">
         <v>46106.60421634259</v>
@@ -61450,7 +61498,7 @@
         <v>46106.43213740741</v>
       </c>
       <c r="AT340">
-        <v>0.839873</v>
+        <v>1.839826</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61631,7 +61679,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>9.876574</v>
+        <v>10.876528</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61809,7 +61857,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>294.693854</v>
+        <v>295.693808</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -61990,7 +62038,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>204.892824</v>
+        <v>205.892778</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62171,7 +62219,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>183.959039</v>
+        <v>184.958993</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62352,7 +62400,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>133.60706</v>
+        <v>134.607014</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62533,7 +62581,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>251.932199</v>
+        <v>252.932153</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62714,7 +62762,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>49.772928</v>
+        <v>50.772882</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62895,7 +62943,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>30.94537</v>
+        <v>31.945324</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -63076,7 +63124,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>114.655775</v>
+        <v>115.655729</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63254,7 +63302,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>208.652581</v>
+        <v>209.652535</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63435,7 +63483,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>187.5911</v>
+        <v>188.591053</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63613,7 +63661,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>152.645093</v>
+        <v>153.645046</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63794,7 +63842,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>133.608287</v>
+        <v>134.608241</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -63975,7 +64023,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>260.912141</v>
+        <v>261.912095</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64156,7 +64204,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>189.806331</v>
+        <v>190.806285</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64337,7 +64385,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>177.940035</v>
+        <v>178.939988</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64518,7 +64566,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>184.012546</v>
+        <v>185.0125</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64699,7 +64747,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>119.727292</v>
+        <v>120.727245</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64880,7 +64928,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>69.606481</v>
+        <v>70.606435</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -65061,7 +65109,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>285.596759</v>
+        <v>286.596713</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65239,7 +65287,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>286.938935</v>
+        <v>287.938889</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65420,7 +65468,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>100.726227</v>
+        <v>101.726181</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65601,7 +65649,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>55.740544</v>
+        <v>56.740498</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65779,7 +65827,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>293.587604</v>
+        <v>294.587558</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -65960,7 +66008,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>183.960255</v>
+        <v>184.960208</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66138,7 +66186,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>103.70794</v>
+        <v>104.707894</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66319,7 +66367,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>264.562975</v>
+        <v>265.562928</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66500,7 +66548,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>154.857523</v>
+        <v>155.857477</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66681,7 +66729,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>152.892558</v>
+        <v>153.892512</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66859,7 +66907,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>280.501759</v>
+        <v>281.501713</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -67040,7 +67088,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>251.929514</v>
+        <v>252.929468</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67218,7 +67266,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>170.529711</v>
+        <v>171.529664</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67396,7 +67444,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>254.722072</v>
+        <v>255.722025</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67577,7 +67625,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>202.889097</v>
+        <v>203.889051</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67758,7 +67806,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>9.875266</v>
+        <v>10.87522</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67936,7 +67984,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>289.727512</v>
+        <v>290.727465</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -68114,7 +68162,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>285.633368</v>
+        <v>286.633322</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68295,7 +68343,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>133.613681</v>
+        <v>134.613634</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68473,7 +68521,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>286.939734</v>
+        <v>287.939688</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68651,7 +68699,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>264.563495</v>
+        <v>265.563449</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68829,7 +68877,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>294.685255</v>
+        <v>295.685208</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -69007,7 +69055,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>142.621632</v>
+        <v>143.621586</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69185,7 +69233,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>280.500289</v>
+        <v>281.500243</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69363,7 +69411,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>247.566169</v>
+        <v>248.566123</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69544,7 +69592,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>238.698796</v>
+        <v>239.69875</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69725,7 +69773,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>154.85684</v>
+        <v>155.856794</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69906,7 +69954,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW387">
-        <v>105.810961</v>
+        <v>106.810914</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -70087,7 +70135,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW388">
-        <v>99.843773</v>
+        <v>100.843727</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70260,7 +70308,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>201.592326</v>
+        <v>202.59228</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70433,7 +70481,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>201.591863</v>
+        <v>202.591817</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70614,7 +70662,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>105.809387</v>
+        <v>106.80934</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70795,7 +70843,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW392">
-        <v>133.607269</v>
+        <v>134.607222</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -70976,7 +71024,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW393">
-        <v>120.709907</v>
+        <v>121.709861</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>293.834282</v>
+        <v>294.834317</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>136.950278</v>
+        <v>137.950313</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>124.708322</v>
+        <v>125.708356</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>248.779942</v>
+        <v>249.779977</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>251.566493</v>
+        <v>252.566528</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>59.934039</v>
+        <v>60.934074</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>286.603993</v>
+        <v>287.604028</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>235.64463</v>
+        <v>236.644664</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>219.727917</v>
+        <v>220.727951</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>135.62456</v>
+        <v>136.624595</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>220.630289</v>
+        <v>221.630324</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>298.687986</v>
+        <v>299.688021</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>284.503137</v>
+        <v>285.503171</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>253.631667</v>
+        <v>254.631701</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>255.92897</v>
+        <v>256.929005</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>135.578785</v>
+        <v>136.578819</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>117.815046</v>
+        <v>118.815081</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>223.515799</v>
+        <v>224.515833</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>215.60456</v>
+        <v>216.604595</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>136.950706</v>
+        <v>137.950741</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>53.952731</v>
+        <v>54.952766</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>52.697928</v>
+        <v>53.697963</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>59.931458</v>
+        <v>60.931493</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>248.77941</v>
+        <v>249.779444</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>135.723623</v>
+        <v>136.723657</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>33.577778</v>
+        <v>34.577813</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>83.934433</v>
+        <v>84.934468</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>284.508646</v>
+        <v>285.508681</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>205.59213</v>
+        <v>206.592164</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>214.685613</v>
+        <v>215.685648</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>144.82566</v>
+        <v>145.825694</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>286.5989</v>
+        <v>287.598935</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>143.60706</v>
+        <v>144.607095</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>222.827616</v>
+        <v>223.82765</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>131.725405</v>
+        <v>132.72544</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>250.873414</v>
+        <v>251.873449</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>258.659155</v>
+        <v>259.65919</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7498,7 +7498,7 @@
         <v>46104.52594388889</v>
       </c>
       <c r="AW39">
-        <v>9.040196999999999</v>
+        <v>10.040231</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7679,7 +7679,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>145.891053</v>
+        <v>146.891088</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7860,7 +7860,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>124.705301</v>
+        <v>125.705336</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8041,7 +8041,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>83.695035</v>
+        <v>84.695069</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8219,7 +8219,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>53.954722</v>
+        <v>54.954757</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8400,7 +8400,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>73.618681</v>
+        <v>74.61871499999999</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8581,7 +8581,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>32.718715</v>
+        <v>33.71875</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8762,7 +8762,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>207.910417</v>
+        <v>208.910451</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8943,7 +8943,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>222.827002</v>
+        <v>223.827037</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9121,7 +9121,7 @@
         <v>46106.37582024305</v>
       </c>
       <c r="AW48">
-        <v>4.896134</v>
+        <v>5.896169</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9305,7 +9305,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>173.943773</v>
+        <v>174.943808</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9486,7 +9486,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>173.942558</v>
+        <v>174.942593</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9654,7 +9654,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>31.592813</v>
+        <v>32.592847</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9835,7 +9835,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>250.874398</v>
+        <v>251.874433</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -10013,7 +10013,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>251.567905</v>
+        <v>252.56794</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10197,7 +10197,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>158.710521</v>
+        <v>159.710556</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10378,7 +10378,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>264.783391</v>
+        <v>265.783426</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10556,7 +10556,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>31.592072</v>
+        <v>32.592106</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10740,7 +10740,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>242.540926</v>
+        <v>243.540961</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10918,7 +10918,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>10.889248</v>
+        <v>11.889282</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11096,7 +11096,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>289.645579</v>
+        <v>290.645613</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11274,7 +11274,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>279.694398</v>
+        <v>280.694433</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11455,7 +11455,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>109.796944</v>
+        <v>110.796979</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11633,7 +11633,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>74.68822900000001</v>
+        <v>75.688264</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11811,7 +11811,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>251.567072</v>
+        <v>252.567106</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11992,7 +11992,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>145.895162</v>
+        <v>146.895197</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12173,7 +12173,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>125.514803</v>
+        <v>126.514838</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12354,7 +12354,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>187.568646</v>
+        <v>188.568681</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12532,7 +12532,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>254.822755</v>
+        <v>255.822789</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12710,7 +12710,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>215.6239</v>
+        <v>216.623935</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12894,7 +12894,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>135.623773</v>
+        <v>136.623808</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13072,7 +13072,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>73.598322</v>
+        <v>74.598356</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13250,7 +13250,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>290.938715</v>
+        <v>291.93875</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13428,7 +13428,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>293.831609</v>
+        <v>294.831644</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13606,7 +13606,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>251.582847</v>
+        <v>252.582882</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13787,7 +13787,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>208.684375</v>
+        <v>209.68441</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13965,7 +13965,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>144.720972</v>
+        <v>145.721007</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14146,7 +14146,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>151.716933</v>
+        <v>152.716968</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14327,7 +14327,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>103.84463</v>
+        <v>104.844664</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14508,7 +14508,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>108.542176</v>
+        <v>109.542211</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14689,7 +14689,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>53.773565</v>
+        <v>54.7736</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14870,7 +14870,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>13.879421</v>
+        <v>14.879456</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15056,7 +15056,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>265.654282</v>
+        <v>266.654317</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15234,7 +15234,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>202.680498</v>
+        <v>203.680532</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15415,7 +15415,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>137.607488</v>
+        <v>138.607523</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15596,7 +15596,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>13.875046</v>
+        <v>14.875081</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15780,7 +15780,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>206.889144</v>
+        <v>207.889178</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15961,7 +15961,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>124.695648</v>
+        <v>125.695683</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16142,7 +16142,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>279.697789</v>
+        <v>280.697824</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16323,7 +16323,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>173.943553</v>
+        <v>174.943588</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16501,7 +16501,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>158.858912</v>
+        <v>159.858947</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16682,7 +16682,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>153.553669</v>
+        <v>154.553704</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16863,7 +16863,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>143.605718</v>
+        <v>144.605752</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -17041,7 +17041,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>258.723113</v>
+        <v>259.723148</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17219,7 +17219,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>289.597859</v>
+        <v>290.597894</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17408,7 +17408,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>237.567523</v>
+        <v>238.567558</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17589,7 +17589,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>206.887431</v>
+        <v>207.887465</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17770,7 +17770,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>187.561493</v>
+        <v>188.561528</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17951,7 +17951,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>109.806308</v>
+        <v>110.806343</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -17981,11 +17981,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H98" s="2">
+        <v>46111.63374707176</v>
+      </c>
       <c r="I98" s="2">
         <v>46076.60414072916</v>
       </c>
       <c r="J98" s="2">
-        <v>46108.65875611111</v>
+        <v>46111.63374712963</v>
       </c>
       <c r="M98" s="2">
         <v>46106.60414072916</v>
@@ -18081,6 +18084,14 @@
           <t>Reprovado na Validação</t>
         </is>
       </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>00:08:00</t>
+        </is>
+      </c>
+      <c r="AH98">
+        <v>2</v>
+      </c>
       <c r="AI98" s="2">
         <v>46076.60414643519</v>
       </c>
@@ -18111,8 +18122,17 @@
       <c r="AR98" s="2">
         <v>46107.65867851852</v>
       </c>
+      <c r="AS98" s="2">
+        <v>46111.63374756945</v>
+      </c>
       <c r="AT98">
-        <v>3.613275</v>
+        <v>3.975058</v>
+      </c>
+      <c r="AU98" s="2">
+        <v>46111.63374820602</v>
+      </c>
+      <c r="AW98">
+        <v>0.6382409999999999</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18293,7 +18313,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>243.570035</v>
+        <v>244.570069</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18471,7 +18491,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>284.502755</v>
+        <v>285.502789</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18649,7 +18669,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>193.943183</v>
+        <v>194.943218</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18827,7 +18847,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>251.566296</v>
+        <v>252.566331</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -19008,7 +19028,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>83.938056</v>
+        <v>84.93809</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19186,7 +19206,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>290.939109</v>
+        <v>291.939144</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19364,7 +19384,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>202.553773</v>
+        <v>203.553808</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19545,7 +19565,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>124.708877</v>
+        <v>125.708912</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19726,7 +19746,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>220.622951</v>
+        <v>221.622986</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19907,7 +19927,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>212.698808</v>
+        <v>213.698843</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -20085,7 +20105,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>52.722593</v>
+        <v>53.722627</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20263,7 +20283,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>286.688715</v>
+        <v>287.68875</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20444,7 +20464,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>242.685706</v>
+        <v>243.685741</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20628,7 +20648,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>181.944456</v>
+        <v>182.944491</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20809,7 +20829,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>123.723773</v>
+        <v>124.723808</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20990,7 +21010,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>241.122581</v>
+        <v>242.122616</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21171,7 +21191,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>249.7661</v>
+        <v>250.766134</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21352,7 +21372,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>202.609722</v>
+        <v>203.609757</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21533,7 +21553,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>151.698414</v>
+        <v>152.698449</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21714,7 +21734,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>124.694329</v>
+        <v>125.694363</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21895,7 +21915,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>83.936678</v>
+        <v>84.936713</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -22076,7 +22096,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>60.72397</v>
+        <v>61.724005</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22254,7 +22274,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>293.834572</v>
+        <v>294.834606</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22432,7 +22452,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>279.645451</v>
+        <v>280.645486</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22613,7 +22633,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>289.595995</v>
+        <v>290.59603</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22794,7 +22814,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>181.942859</v>
+        <v>182.942894</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22975,7 +22995,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>135.723137</v>
+        <v>136.723171</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23156,7 +23176,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>153.544306</v>
+        <v>154.54434</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23334,7 +23354,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>72.588542</v>
+        <v>73.588576</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23515,7 +23535,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>268.564664</v>
+        <v>269.564699</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23699,7 +23719,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>242.705718</v>
+        <v>243.705752</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23877,7 +23897,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>220.576157</v>
+        <v>221.576192</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -24058,7 +24078,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>24.596667</v>
+        <v>25.596701</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24239,7 +24259,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>206.885278</v>
+        <v>207.885313</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24417,7 +24437,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>284.503368</v>
+        <v>285.503403</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24598,7 +24618,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>124.695752</v>
+        <v>125.695787</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24779,7 +24799,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>108.542882</v>
+        <v>109.542917</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24952,7 +24972,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>279.597963</v>
+        <v>280.597998</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25133,7 +25153,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>109.798391</v>
+        <v>110.798426</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25314,7 +25334,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>38.675081</v>
+        <v>39.675116</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25495,7 +25515,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>193.805532</v>
+        <v>194.805567</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25676,7 +25696,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>187.956944</v>
+        <v>188.956979</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25854,7 +25874,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>297.647986</v>
+        <v>298.648021</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -26032,7 +26052,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>223.488345</v>
+        <v>224.48838</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26213,7 +26233,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>181.942315</v>
+        <v>182.94235</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26389,7 +26409,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>117.814815</v>
+        <v>118.81485</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26570,7 +26590,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>51.835752</v>
+        <v>52.835787</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26748,7 +26768,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>279.648657</v>
+        <v>280.648692</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26926,7 +26946,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>284.505023</v>
+        <v>285.505058</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27104,7 +27124,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>10.884919</v>
+        <v>11.884954</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27285,7 +27305,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>220.685648</v>
+        <v>221.685683</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27463,7 +27483,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>254.822326</v>
+        <v>255.822361</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27641,7 +27661,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>251.566794</v>
+        <v>252.566829</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27822,7 +27842,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>214.686644</v>
+        <v>215.686678</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -28003,7 +28023,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>73.604826</v>
+        <v>74.604861</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28184,7 +28204,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>186.818819</v>
+        <v>187.818854</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28365,7 +28385,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>186.618877</v>
+        <v>187.618912</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28543,7 +28563,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>53.951863</v>
+        <v>54.951898</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28727,7 +28747,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>109.805938</v>
+        <v>110.805972</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28908,7 +28928,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>208.517014</v>
+        <v>209.517049</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -29097,7 +29117,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>198.582245</v>
+        <v>199.58228</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29265,7 +29285,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>228.652419</v>
+        <v>229.652454</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29446,7 +29466,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>181.94162</v>
+        <v>182.941655</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29627,7 +29647,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>125.515463</v>
+        <v>126.515498</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29808,7 +29828,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>66.628484</v>
+        <v>67.628519</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29989,7 +30009,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>250.874201</v>
+        <v>251.874236</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30170,7 +30190,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>206.890891</v>
+        <v>207.890926</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30351,7 +30371,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>130.538414</v>
+        <v>131.538449</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30529,7 +30549,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>53.956308</v>
+        <v>54.956343</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30707,7 +30727,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>240.897014</v>
+        <v>241.897049</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30888,7 +30908,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>156.643461</v>
+        <v>157.643495</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -31066,7 +31086,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>124.692674</v>
+        <v>125.692708</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31247,7 +31267,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>24.597697</v>
+        <v>25.597731</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31425,7 +31445,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>289.598796</v>
+        <v>290.598831</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31606,7 +31626,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>265.949097</v>
+        <v>266.949132</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31784,7 +31804,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>74.679653</v>
+        <v>75.679688</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31962,7 +31982,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>47.724954</v>
+        <v>48.724988</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32135,7 +32155,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>205.591921</v>
+        <v>206.591956</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32316,7 +32336,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>83.936076</v>
+        <v>84.936111</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32494,7 +32514,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>33.571563</v>
+        <v>34.571597</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32672,7 +32692,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>240.901956</v>
+        <v>241.901991</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32850,7 +32870,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>293.834965</v>
+        <v>294.835</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -33028,7 +33048,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>215.603032</v>
+        <v>216.603067</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33206,7 +33226,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>286.598345</v>
+        <v>287.59838</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33384,7 +33404,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>277.705185</v>
+        <v>278.70522</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33562,7 +33582,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>215.623785</v>
+        <v>216.623819</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33743,7 +33763,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>144.72081</v>
+        <v>145.720845</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33924,7 +33944,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>13.878947</v>
+        <v>14.878981</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34102,7 +34122,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>286.597986</v>
+        <v>287.598021</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34283,7 +34303,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>242.701528</v>
+        <v>243.701563</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34464,7 +34484,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>187.956227</v>
+        <v>188.956262</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34645,7 +34665,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>220.515938</v>
+        <v>221.515972</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34826,7 +34846,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>131.669282</v>
+        <v>132.669317</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -35004,7 +35024,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>53.954282</v>
+        <v>54.954317</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35182,7 +35202,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>293.842535</v>
+        <v>294.842569</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35350,7 +35370,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>228.664606</v>
+        <v>229.664641</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35531,7 +35551,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>206.888403</v>
+        <v>207.888438</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35715,7 +35735,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>187.959769</v>
+        <v>188.959803</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35899,7 +35919,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>242.705347</v>
+        <v>243.705382</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -36080,7 +36100,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>109.797708</v>
+        <v>110.797743</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36258,7 +36278,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>286.688993</v>
+        <v>287.689028</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36436,7 +36456,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>300.909826</v>
+        <v>301.909861</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36617,7 +36637,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>206.894248</v>
+        <v>207.894282</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36795,7 +36815,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>180.681644</v>
+        <v>181.681678</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36976,7 +36996,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>273.925532</v>
+        <v>274.925567</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37154,7 +37174,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>284.503935</v>
+        <v>285.50397</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37332,7 +37352,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>212.607488</v>
+        <v>213.607523</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37510,7 +37530,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>37.60419</v>
+        <v>38.604225</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37691,7 +37711,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>268.561505</v>
+        <v>269.561539</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37872,7 +37892,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>216.530926</v>
+        <v>217.530961</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -38050,7 +38070,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>74.685266</v>
+        <v>75.685301</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38228,7 +38248,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>289.57213</v>
+        <v>290.572164</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38406,7 +38426,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>286.688449</v>
+        <v>287.688484</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38584,7 +38604,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>20.541829</v>
+        <v>21.541863</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38762,7 +38782,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>285.610671</v>
+        <v>286.610706</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38940,7 +38960,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>297.593252</v>
+        <v>298.593287</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39118,7 +39138,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>299.733646</v>
+        <v>300.733681</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39296,7 +39316,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>289.646829</v>
+        <v>290.646863</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39474,7 +39494,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>251.568519</v>
+        <v>252.568553</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39655,7 +39675,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>251.586493</v>
+        <v>252.586528</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39836,7 +39856,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>156.911528</v>
+        <v>157.911563</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -40017,7 +40037,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>13.703947</v>
+        <v>14.703981</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40195,7 +40215,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>298.68897</v>
+        <v>299.689005</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40373,7 +40393,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>289.587894</v>
+        <v>290.587928</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40551,7 +40571,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>298.684838</v>
+        <v>299.684873</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40732,7 +40752,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>199.639144</v>
+        <v>200.639178</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40913,7 +40933,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>131.693438</v>
+        <v>132.693472</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -41094,7 +41114,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>124.711586</v>
+        <v>125.71162</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41275,7 +41295,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>59.933079</v>
+        <v>60.933113</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41456,7 +41476,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>59.934757</v>
+        <v>60.934792</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41637,7 +41657,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>206.8936</v>
+        <v>207.893634</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41818,7 +41838,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>258.659074</v>
+        <v>259.659109</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41996,7 +42016,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>275.900382</v>
+        <v>276.900417</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42177,7 +42197,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>215.669988</v>
+        <v>216.670023</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42361,7 +42381,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>207.910185</v>
+        <v>208.91022</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42542,7 +42562,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>187.958079</v>
+        <v>188.958113</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42720,7 +42740,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>138.886944</v>
+        <v>139.886979</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42901,7 +42921,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>24.595556</v>
+        <v>25.59559</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -43082,7 +43102,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>250.874734</v>
+        <v>251.874769</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43263,7 +43283,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>206.753194</v>
+        <v>207.753229</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43444,7 +43464,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>109.798935</v>
+        <v>110.79897</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43622,7 +43642,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>74.6786</v>
+        <v>75.678634</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43803,7 +43823,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>125.515961</v>
+        <v>126.515995</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43984,7 +44004,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>240.900729</v>
+        <v>241.900764</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44157,7 +44177,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>286.573229</v>
+        <v>287.573264</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44335,7 +44355,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>251.567303</v>
+        <v>252.567338</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44519,7 +44539,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>215.601377</v>
+        <v>216.601412</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44700,7 +44720,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>158.855961</v>
+        <v>159.855995</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44884,7 +44904,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>187.660845</v>
+        <v>188.66088</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -45065,7 +45085,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>181.940741</v>
+        <v>182.940775</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45246,7 +45266,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>32.719549</v>
+        <v>33.719583</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45424,7 +45444,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>251.567708</v>
+        <v>252.567743</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45605,7 +45625,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>222.828241</v>
+        <v>223.828275</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45786,7 +45806,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>59.678426</v>
+        <v>60.678461</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45967,7 +45987,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>271.720903</v>
+        <v>272.720938</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46148,7 +46168,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>60.724387</v>
+        <v>61.724421</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46182,7 +46202,7 @@
         <v>46076.7099121875</v>
       </c>
       <c r="J255" s="2">
-        <v>46106.71027606481</v>
+        <v>46111.39818359954</v>
       </c>
       <c r="M255" s="2">
         <v>46106.70991219908</v>
@@ -46261,7 +46281,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>13.874317</v>
+        <v>14.874352</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46275,7 +46295,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Construção no Canvas</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -46291,11 +46311,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H256" s="2">
+        <v>46111.70316394676</v>
+      </c>
       <c r="I256" s="2">
         <v>46076.60415420139</v>
       </c>
       <c r="J256" s="2">
-        <v>46106.60479694445</v>
+        <v>46111.70316409722</v>
       </c>
       <c r="M256" s="2">
         <v>46106.60415420139</v>
@@ -46361,6 +46384,44 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>https://rehagro.instructure.com/courses/2981/modules</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.tqzjurqxgryn</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>Gestão</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>01:17:00</t>
+        </is>
+      </c>
+      <c r="AH256">
+        <v>10</v>
+      </c>
       <c r="AI256" s="2">
         <v>46076.60415833333</v>
       </c>
@@ -46373,8 +46434,35 @@
       <c r="AL256" s="2">
         <v>46097.39764412037</v>
       </c>
+      <c r="AM256" s="2">
+        <v>46111.34199363425</v>
+      </c>
       <c r="AN256">
-        <v>13.874306</v>
+        <v>13.94434</v>
+      </c>
+      <c r="AO256" s="2">
+        <v>46111.34199420139</v>
+      </c>
+      <c r="AP256" s="2">
+        <v>46111.70264722222</v>
+      </c>
+      <c r="AQ256">
+        <v>0.360648</v>
+      </c>
+      <c r="AR256" s="2">
+        <v>46111.70264784723</v>
+      </c>
+      <c r="AS256" s="2">
+        <v>46111.70316510416</v>
+      </c>
+      <c r="AT256">
+        <v>0.000509</v>
+      </c>
+      <c r="AU256" s="2">
+        <v>46111.70316528935</v>
+      </c>
+      <c r="AW256">
+        <v>0.568819</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46555,7 +46643,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>83.93535900000001</v>
+        <v>84.935394</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46736,7 +46824,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>250.835313</v>
+        <v>251.835347</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46914,7 +47002,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>181.950486</v>
+        <v>182.950521</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -47095,7 +47183,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>181.948333</v>
+        <v>182.948368</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47273,7 +47361,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>156.532882</v>
+        <v>157.532917</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47449,7 +47537,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>248.779572</v>
+        <v>249.779606</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47627,7 +47715,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>172.939051</v>
+        <v>173.939086</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47811,7 +47899,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>158.711273</v>
+        <v>159.711308</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -47989,7 +48077,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>107.707963</v>
+        <v>108.707998</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48170,7 +48258,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>279.698009</v>
+        <v>280.698044</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48348,7 +48436,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>289.646088</v>
+        <v>290.646123</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48529,7 +48617,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>268.561852</v>
+        <v>269.561887</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48710,7 +48798,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>144.720706</v>
+        <v>145.720741</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48888,7 +48976,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>158.712083</v>
+        <v>159.712118</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -49069,7 +49157,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>124.695475</v>
+        <v>125.695509</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49250,7 +49338,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>268.562396</v>
+        <v>269.562431</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49428,7 +49516,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>187.952477</v>
+        <v>188.952512</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49612,7 +49700,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>139.699317</v>
+        <v>140.699352</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49793,7 +49881,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>278.591204</v>
+        <v>279.591238</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -49974,7 +50062,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>193.806725</v>
+        <v>194.806759</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50155,7 +50243,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>124.712245</v>
+        <v>125.71228</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50336,7 +50424,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>145.893333</v>
+        <v>146.893368</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50517,7 +50605,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>264.783194</v>
+        <v>265.783229</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50724,7 +50812,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>144.826389</v>
+        <v>145.826424</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50902,7 +50990,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>135.622396</v>
+        <v>136.622431</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -51083,7 +51171,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>118.655104</v>
+        <v>119.655139</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51267,7 +51355,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>173.942477</v>
+        <v>174.942512</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51445,7 +51533,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>10.886678</v>
+        <v>11.886713</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51623,7 +51711,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>265.949468</v>
+        <v>266.949502</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51801,7 +51889,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>277.706134</v>
+        <v>278.706169</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -51979,7 +52067,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>240.901794</v>
+        <v>241.901829</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52160,7 +52248,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>220.629861</v>
+        <v>221.629896</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52344,7 +52432,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>161.95728</v>
+        <v>162.957315</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52525,7 +52613,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>139.692975</v>
+        <v>140.693009</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52706,7 +52794,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>264.911863</v>
+        <v>265.911898</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52884,7 +52972,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>278.911065</v>
+        <v>279.9111</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -53065,7 +53153,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>223.518958</v>
+        <v>224.518993</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53243,7 +53331,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>284.501968</v>
+        <v>285.502002</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53424,7 +53512,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>206.894815</v>
+        <v>207.89485</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53605,7 +53693,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>13.875556</v>
+        <v>14.87559</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53786,7 +53874,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>124.563704</v>
+        <v>125.563738</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -53964,7 +54052,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>251.569641</v>
+        <v>252.569676</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54142,7 +54230,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>10.888889</v>
+        <v>11.888924</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54331,7 +54419,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>275.900845</v>
+        <v>276.90088</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54512,7 +54600,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>206.887685</v>
+        <v>207.88772</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54690,7 +54778,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>181.699155</v>
+        <v>182.69919</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54871,7 +54959,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>103.844873</v>
+        <v>104.844907</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -55057,7 +55145,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>216.660625</v>
+        <v>217.66066</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55235,7 +55323,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>290.940567</v>
+        <v>291.940602</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55416,7 +55504,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>180.612778</v>
+        <v>181.612813</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55597,7 +55685,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>135.722986</v>
+        <v>136.723021</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55778,7 +55866,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>109.810451</v>
+        <v>110.810486</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -55959,7 +56047,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>83.93718800000001</v>
+        <v>84.93722200000001</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56140,7 +56228,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>180.611343</v>
+        <v>181.611377</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56321,7 +56409,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>180.613113</v>
+        <v>181.613148</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56335,7 +56423,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -56351,11 +56439,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H312" s="2">
+        <v>46111.63328078703</v>
+      </c>
       <c r="I312" s="2">
         <v>46076.70817686342</v>
       </c>
       <c r="J312" s="2">
-        <v>46107.65272324074</v>
+        <v>46111.63328091435</v>
       </c>
       <c r="M312" s="2">
         <v>46106.70817686342</v>
@@ -56451,6 +56542,14 @@
           <t>Gestão</t>
         </is>
       </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>01:38:00</t>
+        </is>
+      </c>
+      <c r="AH312">
+        <v>6</v>
+      </c>
       <c r="AI312" s="2">
         <v>46076.70818526621</v>
       </c>
@@ -56481,8 +56580,17 @@
       <c r="AR312" s="2">
         <v>46106.65167777778</v>
       </c>
+      <c r="AS312" s="2">
+        <v>46111.63328203704</v>
+      </c>
       <c r="AT312">
-        <v>4.620278</v>
+        <v>4.981597</v>
+      </c>
+      <c r="AU312" s="2">
+        <v>46111.63328278935</v>
+      </c>
+      <c r="AW312">
+        <v>0.638704</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56660,7 +56768,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>284.50235</v>
+        <v>285.502384</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56838,7 +56946,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>53.958588</v>
+        <v>54.958623</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -57019,7 +57127,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>237.564039</v>
+        <v>238.564074</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57197,7 +57305,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>33.571042</v>
+        <v>34.571076</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57378,7 +57486,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>156.64441</v>
+        <v>157.644444</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57559,7 +57667,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>13.876019</v>
+        <v>14.876053</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57737,7 +57845,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW319">
-        <v>10.888125</v>
+        <v>11.88816</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -57918,7 +58026,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>237.566829</v>
+        <v>238.566863</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -58099,7 +58207,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>250.872072</v>
+        <v>251.872106</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58277,7 +58385,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>59.601979</v>
+        <v>60.602014</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58455,7 +58563,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>293.835417</v>
+        <v>294.835451</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58636,7 +58744,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>187.95162</v>
+        <v>188.951655</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58814,7 +58922,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>151.661701</v>
+        <v>152.661736</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -58995,7 +59103,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>139.696956</v>
+        <v>140.696991</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59176,7 +59284,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>272.609468</v>
+        <v>273.609502</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59357,7 +59465,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>227.668484</v>
+        <v>228.668519</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59538,7 +59646,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>109.811979</v>
+        <v>110.812014</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59719,7 +59827,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>68.814595</v>
+        <v>69.81462999999999</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59897,7 +60005,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>220.575856</v>
+        <v>221.575891</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -60081,7 +60189,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>166.586574</v>
+        <v>167.586609</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60259,7 +60367,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>251.56897</v>
+        <v>252.569005</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60440,7 +60548,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>145.889549</v>
+        <v>146.889583</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60621,7 +60729,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>135.622824</v>
+        <v>136.622859</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60799,7 +60907,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>230.593449</v>
+        <v>231.593484</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -60980,7 +61088,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>76.57531299999999</v>
+        <v>77.57534699999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61161,7 +61269,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>222.824884</v>
+        <v>223.824919</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61337,7 +61445,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>156.643924</v>
+        <v>157.643958</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61351,7 +61459,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Publicar na plataforma</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -61367,11 +61475,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H340" s="2">
+        <v>46111.63441890046</v>
+      </c>
       <c r="I340" s="2">
         <v>46076.60421634259</v>
       </c>
       <c r="J340" s="2">
-        <v>46107.43268002315</v>
+        <v>46111.63441898148</v>
       </c>
       <c r="M340" s="2">
         <v>46106.60421634259</v>
@@ -61467,6 +61578,14 @@
           <t>Reprovado na Validação</t>
         </is>
       </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>01:50:00</t>
+        </is>
+      </c>
+      <c r="AH340">
+        <v>12</v>
+      </c>
       <c r="AI340" s="2">
         <v>46076.60422097222</v>
       </c>
@@ -61497,8 +61616,17 @@
       <c r="AR340" s="2">
         <v>46106.43213740741</v>
       </c>
+      <c r="AS340" s="2">
+        <v>46111.63441952546</v>
+      </c>
       <c r="AT340">
-        <v>4.839815</v>
+        <v>5.20228</v>
+      </c>
+      <c r="AU340" s="2">
+        <v>46111.63441997685</v>
+      </c>
+      <c r="AW340">
+        <v>0.6375690000000001</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61679,7 +61807,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>13.876516</v>
+        <v>14.876551</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61857,7 +61985,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>298.693796</v>
+        <v>299.693831</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -62038,7 +62166,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>208.892766</v>
+        <v>209.892801</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62219,7 +62347,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>187.958981</v>
+        <v>188.959016</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62400,7 +62528,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>137.607002</v>
+        <v>138.607037</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62581,7 +62709,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>255.932141</v>
+        <v>256.932176</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62762,7 +62890,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>53.77287</v>
+        <v>54.772905</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -62943,7 +63071,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>34.945313</v>
+        <v>35.945347</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -63124,7 +63252,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>118.655718</v>
+        <v>119.655752</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63302,7 +63430,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>212.652523</v>
+        <v>213.652558</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63483,7 +63611,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>191.591042</v>
+        <v>192.591076</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63661,7 +63789,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>156.645035</v>
+        <v>157.645069</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63842,7 +63970,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>137.608229</v>
+        <v>138.608264</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -64023,7 +64151,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>264.912083</v>
+        <v>265.912118</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64204,7 +64332,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>193.806273</v>
+        <v>194.806308</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64385,7 +64513,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>181.939977</v>
+        <v>182.940012</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64566,7 +64694,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>188.012488</v>
+        <v>189.012523</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64747,7 +64875,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>123.727234</v>
+        <v>124.727269</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -64928,7 +65056,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>73.606424</v>
+        <v>74.606458</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -65109,7 +65237,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>289.596701</v>
+        <v>290.596736</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65287,7 +65415,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>290.938877</v>
+        <v>291.938912</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65468,7 +65596,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>104.726169</v>
+        <v>105.726204</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65649,7 +65777,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>59.740486</v>
+        <v>60.740521</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65827,7 +65955,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>297.587546</v>
+        <v>298.587581</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -66008,7 +66136,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>187.960197</v>
+        <v>188.960231</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66186,7 +66314,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>107.707882</v>
+        <v>108.707917</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66367,7 +66495,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>268.562917</v>
+        <v>269.562951</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66548,7 +66676,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>158.857465</v>
+        <v>159.8575</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66729,7 +66857,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>156.8925</v>
+        <v>157.892535</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -66907,7 +67035,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>284.501701</v>
+        <v>285.501736</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -67088,7 +67216,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>255.929456</v>
+        <v>256.929491</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67266,7 +67394,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>174.529653</v>
+        <v>175.529688</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67444,7 +67572,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>258.722014</v>
+        <v>259.722049</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67625,7 +67753,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>206.889039</v>
+        <v>207.889074</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67806,7 +67934,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>13.875208</v>
+        <v>14.875243</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -67984,7 +68112,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>293.727454</v>
+        <v>294.727488</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -68162,7 +68290,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>289.63331</v>
+        <v>290.633345</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68343,7 +68471,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>137.613623</v>
+        <v>138.613657</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68521,7 +68649,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>290.939676</v>
+        <v>291.939711</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68699,7 +68827,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>268.563438</v>
+        <v>269.563472</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68877,7 +69005,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>298.685197</v>
+        <v>299.685231</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -69055,7 +69183,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>146.621574</v>
+        <v>147.621609</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69233,7 +69361,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>284.500231</v>
+        <v>285.500266</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69411,7 +69539,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>251.566111</v>
+        <v>252.566146</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69592,7 +69720,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>242.698738</v>
+        <v>243.698773</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69773,7 +69901,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>158.856782</v>
+        <v>159.856817</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -69954,7 +70082,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>103.843715</v>
+        <v>104.84375</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -70135,7 +70263,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>109.810903</v>
+        <v>110.810938</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70308,7 +70436,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>205.592269</v>
+        <v>206.592303</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70481,7 +70609,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>205.591806</v>
+        <v>206.59184</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70662,7 +70790,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>109.809329</v>
+        <v>110.809363</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70843,7 +70971,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>124.70985</v>
+        <v>125.709884</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -71024,7 +71152,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>137.607211</v>
+        <v>138.607245</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>294.834317</v>
+        <v>295.834282</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>137.950313</v>
+        <v>138.950278</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>125.708356</v>
+        <v>126.708322</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>249.779977</v>
+        <v>250.779942</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1557,7 +1557,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW6">
-        <v>252.566528</v>
+        <v>253.566493</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW7">
-        <v>60.934074</v>
+        <v>61.934039</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1916,7 +1916,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW8">
-        <v>287.604028</v>
+        <v>288.603993</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2100,7 +2100,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW9">
-        <v>236.644664</v>
+        <v>237.64463</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2278,7 +2278,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW10">
-        <v>220.727951</v>
+        <v>221.727917</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW11">
-        <v>136.624595</v>
+        <v>137.62456</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW12">
-        <v>221.630324</v>
+        <v>222.630289</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2818,7 +2818,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW13">
-        <v>299.688021</v>
+        <v>300.687986</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2996,7 +2996,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW14">
-        <v>285.503171</v>
+        <v>286.503137</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3174,7 +3174,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW15">
-        <v>254.631701</v>
+        <v>255.631667</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3355,7 +3355,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW16">
-        <v>256.929005</v>
+        <v>257.92897</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3536,7 +3536,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>136.578819</v>
+        <v>137.578785</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW18">
-        <v>118.815081</v>
+        <v>119.815046</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW19">
-        <v>224.515833</v>
+        <v>225.515799</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW20">
-        <v>216.604595</v>
+        <v>217.60456</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>137.950741</v>
+        <v>138.950706</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>54.952766</v>
+        <v>55.952731</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>53.697963</v>
+        <v>54.697928</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>60.931493</v>
+        <v>61.931458</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>249.779444</v>
+        <v>250.77941</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>136.723657</v>
+        <v>137.723623</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>34.577813</v>
+        <v>35.577778</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>84.934468</v>
+        <v>85.934433</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5697,7 +5697,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW29">
-        <v>285.508681</v>
+        <v>286.508646</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW30">
-        <v>206.592164</v>
+        <v>207.59213</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>215.685648</v>
+        <v>216.685613</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>145.825694</v>
+        <v>146.82566</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>287.598935</v>
+        <v>288.5989</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW34">
-        <v>144.607095</v>
+        <v>145.60706</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW35">
-        <v>223.82765</v>
+        <v>224.827616</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>132.72544</v>
+        <v>133.725405</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7136,7 +7136,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW37">
-        <v>251.873449</v>
+        <v>252.873414</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW38">
-        <v>259.65919</v>
+        <v>260.659155</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7498,7 +7498,7 @@
         <v>46104.52594388889</v>
       </c>
       <c r="AW39">
-        <v>10.040231</v>
+        <v>11.040197</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7679,7 +7679,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>146.891088</v>
+        <v>147.891053</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7860,7 +7860,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>125.705336</v>
+        <v>126.705301</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8041,7 +8041,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>84.695069</v>
+        <v>85.695035</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8219,7 +8219,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW43">
-        <v>54.954757</v>
+        <v>55.954722</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8400,7 +8400,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>74.61871499999999</v>
+        <v>75.618681</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8581,7 +8581,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW45">
-        <v>33.71875</v>
+        <v>34.718715</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8762,7 +8762,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>208.910451</v>
+        <v>209.910417</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8943,7 +8943,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>223.827037</v>
+        <v>224.827002</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9121,7 +9121,7 @@
         <v>46106.37582024305</v>
       </c>
       <c r="AW48">
-        <v>5.896169</v>
+        <v>6.896134</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9305,7 +9305,7 @@
         <v>45924.33465340278</v>
       </c>
       <c r="AW49">
-        <v>174.943808</v>
+        <v>175.943773</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9486,7 +9486,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW50">
-        <v>174.942593</v>
+        <v>175.942558</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9654,7 +9654,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>32.592847</v>
+        <v>33.592813</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9835,7 +9835,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW52">
-        <v>251.874433</v>
+        <v>252.874398</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -10013,7 +10013,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW53">
-        <v>252.56794</v>
+        <v>253.567905</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10197,7 +10197,7 @@
         <v>45946.6547500926</v>
       </c>
       <c r="AW54">
-        <v>159.710556</v>
+        <v>160.710521</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10378,7 +10378,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW55">
-        <v>265.783426</v>
+        <v>266.783391</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10556,7 +10556,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>32.592106</v>
+        <v>33.592072</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10740,7 +10740,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>243.540961</v>
+        <v>244.540926</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10918,7 +10918,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>11.889282</v>
+        <v>12.889248</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11096,7 +11096,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>290.645613</v>
+        <v>291.645579</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11274,7 +11274,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>280.694433</v>
+        <v>281.694398</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11455,7 +11455,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>110.796979</v>
+        <v>111.796944</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11633,7 +11633,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>75.688264</v>
+        <v>76.68822900000001</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11811,7 +11811,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>252.567106</v>
+        <v>253.567072</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11992,7 +11992,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW64">
-        <v>146.895197</v>
+        <v>147.895162</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12173,7 +12173,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW65">
-        <v>126.514838</v>
+        <v>127.514803</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12354,7 +12354,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>188.568681</v>
+        <v>189.568646</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12532,7 +12532,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>255.822789</v>
+        <v>256.822755</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12710,7 +12710,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>216.623935</v>
+        <v>217.6239</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12894,7 +12894,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>136.623808</v>
+        <v>137.623773</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13072,7 +13072,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>74.598356</v>
+        <v>75.598322</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13250,7 +13250,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>291.93875</v>
+        <v>292.938715</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13428,7 +13428,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>294.831644</v>
+        <v>295.831609</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13606,7 +13606,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW73">
-        <v>252.582882</v>
+        <v>253.582847</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13787,7 +13787,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW74">
-        <v>209.68441</v>
+        <v>210.684375</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13965,7 +13965,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW75">
-        <v>145.721007</v>
+        <v>146.720972</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14146,7 +14146,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW76">
-        <v>152.716968</v>
+        <v>153.716933</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14327,7 +14327,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW77">
-        <v>104.844664</v>
+        <v>105.84463</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14508,7 +14508,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW78">
-        <v>109.542211</v>
+        <v>110.542176</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14689,7 +14689,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW79">
-        <v>54.7736</v>
+        <v>55.773565</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14870,7 +14870,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW80">
-        <v>14.879456</v>
+        <v>15.879421</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15056,7 +15056,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW81">
-        <v>266.654317</v>
+        <v>267.654282</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15234,7 +15234,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>203.680532</v>
+        <v>204.680498</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15415,7 +15415,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW83">
-        <v>138.607523</v>
+        <v>139.607488</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15596,7 +15596,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>14.875081</v>
+        <v>15.875046</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15780,7 +15780,7 @@
         <v>45894.4102940162</v>
       </c>
       <c r="AW85">
-        <v>207.889178</v>
+        <v>208.889144</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15961,7 +15961,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>125.695683</v>
+        <v>126.695648</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16142,7 +16142,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>280.697824</v>
+        <v>281.697789</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16323,7 +16323,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW88">
-        <v>174.943588</v>
+        <v>175.943553</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16501,7 +16501,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW89">
-        <v>159.858947</v>
+        <v>160.858912</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16682,7 +16682,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>154.553704</v>
+        <v>155.553669</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16863,7 +16863,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW91">
-        <v>144.605752</v>
+        <v>145.605718</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -17041,7 +17041,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW92">
-        <v>259.723148</v>
+        <v>260.723113</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17219,7 +17219,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW93">
-        <v>290.597894</v>
+        <v>291.597859</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17408,7 +17408,7 @@
         <v>45873.70541589121</v>
       </c>
       <c r="AW94">
-        <v>238.567558</v>
+        <v>239.567523</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17589,7 +17589,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW95">
-        <v>207.887465</v>
+        <v>208.887431</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17770,7 +17770,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW96">
-        <v>188.561528</v>
+        <v>189.561493</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17951,7 +17951,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>110.806343</v>
+        <v>111.806308</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -18132,7 +18132,7 @@
         <v>46111.63374820602</v>
       </c>
       <c r="AW98">
-        <v>0.6382409999999999</v>
+        <v>1.638206</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18313,7 +18313,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>244.570069</v>
+        <v>245.570035</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18491,7 +18491,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>285.502789</v>
+        <v>286.502755</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18669,7 +18669,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>194.943218</v>
+        <v>195.943183</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18847,7 +18847,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>252.566331</v>
+        <v>253.566296</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -19028,7 +19028,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>84.93809</v>
+        <v>85.938056</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19206,7 +19206,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>291.939144</v>
+        <v>292.939109</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19384,7 +19384,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>203.553808</v>
+        <v>204.553773</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19565,7 +19565,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>125.708912</v>
+        <v>126.708877</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19746,7 +19746,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>221.622986</v>
+        <v>222.622951</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19927,7 +19927,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>213.698843</v>
+        <v>214.698808</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -20105,7 +20105,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>53.722627</v>
+        <v>54.722593</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20283,7 +20283,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW110">
-        <v>287.68875</v>
+        <v>288.688715</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20464,7 +20464,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW111">
-        <v>243.685741</v>
+        <v>244.685706</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20648,7 +20648,7 @@
         <v>45875.68373804398</v>
       </c>
       <c r="AW112">
-        <v>182.944491</v>
+        <v>183.944456</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20829,7 +20829,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW113">
-        <v>124.723808</v>
+        <v>125.723773</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -21010,7 +21010,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>242.122616</v>
+        <v>243.122581</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21191,7 +21191,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW115">
-        <v>250.766134</v>
+        <v>251.7661</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21372,7 +21372,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW116">
-        <v>203.609757</v>
+        <v>204.609722</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21553,7 +21553,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW117">
-        <v>152.698449</v>
+        <v>153.698414</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21734,7 +21734,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW118">
-        <v>125.694363</v>
+        <v>126.694329</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21915,7 +21915,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW119">
-        <v>84.936713</v>
+        <v>85.936678</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -22096,7 +22096,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW120">
-        <v>61.724005</v>
+        <v>62.72397</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22274,7 +22274,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>294.834606</v>
+        <v>295.834572</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22452,7 +22452,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW122">
-        <v>280.645486</v>
+        <v>281.645451</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22633,7 +22633,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW123">
-        <v>290.59603</v>
+        <v>291.595995</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22814,7 +22814,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW124">
-        <v>182.942894</v>
+        <v>183.942859</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22995,7 +22995,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW125">
-        <v>136.723171</v>
+        <v>137.723137</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23176,7 +23176,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW126">
-        <v>154.54434</v>
+        <v>155.544306</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23354,7 +23354,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW127">
-        <v>73.588576</v>
+        <v>74.588542</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23535,7 +23535,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW128">
-        <v>269.564699</v>
+        <v>270.564664</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23719,7 +23719,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW129">
-        <v>243.705752</v>
+        <v>244.705718</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23897,7 +23897,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW130">
-        <v>221.576192</v>
+        <v>222.576157</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -24078,7 +24078,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>25.596701</v>
+        <v>26.596667</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24259,7 +24259,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>207.885313</v>
+        <v>208.885278</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24437,7 +24437,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>285.503403</v>
+        <v>286.503368</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24618,7 +24618,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>125.695787</v>
+        <v>126.695752</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24799,7 +24799,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>109.542917</v>
+        <v>110.542882</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24972,7 +24972,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>280.597998</v>
+        <v>281.597963</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25153,7 +25153,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>110.798426</v>
+        <v>111.798391</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25334,7 +25334,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>39.675116</v>
+        <v>40.675081</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25515,7 +25515,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW139">
-        <v>194.805567</v>
+        <v>195.805532</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25696,7 +25696,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW140">
-        <v>188.956979</v>
+        <v>189.956944</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25874,7 +25874,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>298.648021</v>
+        <v>299.647986</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -26052,7 +26052,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>224.48838</v>
+        <v>225.488345</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26233,7 +26233,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>182.94235</v>
+        <v>183.942315</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26409,7 +26409,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW144">
-        <v>118.81485</v>
+        <v>119.814815</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26590,7 +26590,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW145">
-        <v>52.835787</v>
+        <v>53.835752</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26768,7 +26768,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>280.648692</v>
+        <v>281.648657</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26946,7 +26946,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>285.505058</v>
+        <v>286.505023</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27124,7 +27124,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>11.884954</v>
+        <v>12.884919</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27305,7 +27305,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>221.685683</v>
+        <v>222.685648</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27483,7 +27483,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>255.822361</v>
+        <v>256.822326</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27661,7 +27661,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW151">
-        <v>252.566829</v>
+        <v>253.566794</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27842,7 +27842,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW152">
-        <v>215.686678</v>
+        <v>216.686644</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -28023,7 +28023,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>74.604861</v>
+        <v>75.604826</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28204,7 +28204,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW154">
-        <v>187.818854</v>
+        <v>188.818819</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28385,7 +28385,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW155">
-        <v>187.618912</v>
+        <v>188.618877</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28563,7 +28563,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW156">
-        <v>54.951898</v>
+        <v>55.951863</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28747,7 +28747,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>110.805972</v>
+        <v>111.805938</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28928,7 +28928,7 @@
         <v>45905.60530078704</v>
       </c>
       <c r="AW158">
-        <v>209.517049</v>
+        <v>210.517014</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -29117,7 +29117,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW159">
-        <v>199.58228</v>
+        <v>200.582245</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29285,7 +29285,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW160">
-        <v>229.652454</v>
+        <v>230.652419</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29466,7 +29466,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW161">
-        <v>182.941655</v>
+        <v>183.94162</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29647,7 +29647,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW162">
-        <v>126.515498</v>
+        <v>127.515463</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29828,7 +29828,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW163">
-        <v>67.628519</v>
+        <v>68.628484</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -30009,7 +30009,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW164">
-        <v>251.874236</v>
+        <v>252.874201</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30190,7 +30190,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW165">
-        <v>207.890926</v>
+        <v>208.890891</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30371,7 +30371,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW166">
-        <v>131.538449</v>
+        <v>132.538414</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30549,7 +30549,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>54.956343</v>
+        <v>55.956308</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30727,7 +30727,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>241.897049</v>
+        <v>242.897014</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30908,7 +30908,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>157.643495</v>
+        <v>158.643461</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -31086,7 +31086,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>125.692708</v>
+        <v>126.692674</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31267,7 +31267,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>25.597731</v>
+        <v>26.597697</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31445,7 +31445,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>290.598831</v>
+        <v>291.598796</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31626,7 +31626,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>266.949132</v>
+        <v>267.949097</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31804,7 +31804,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>75.679688</v>
+        <v>76.679653</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31982,7 +31982,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>48.724988</v>
+        <v>49.724954</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32155,7 +32155,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>206.591956</v>
+        <v>207.591921</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32336,7 +32336,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>84.936111</v>
+        <v>85.936076</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32514,7 +32514,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>34.571597</v>
+        <v>35.571563</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32692,7 +32692,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW179">
-        <v>241.901991</v>
+        <v>242.901956</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32870,7 +32870,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW180">
-        <v>294.835</v>
+        <v>295.834965</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -33048,7 +33048,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>216.603067</v>
+        <v>217.603032</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33226,7 +33226,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW182">
-        <v>287.59838</v>
+        <v>288.598345</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33404,7 +33404,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW183">
-        <v>278.70522</v>
+        <v>279.705185</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33582,7 +33582,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW184">
-        <v>216.623819</v>
+        <v>217.623785</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33763,7 +33763,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>145.720845</v>
+        <v>146.72081</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33944,7 +33944,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW186">
-        <v>14.878981</v>
+        <v>15.878947</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34122,7 +34122,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>287.598021</v>
+        <v>288.597986</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34303,7 +34303,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>243.701563</v>
+        <v>244.701528</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34484,7 +34484,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW189">
-        <v>188.956262</v>
+        <v>189.956227</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34665,7 +34665,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW190">
-        <v>221.515972</v>
+        <v>222.515938</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34846,7 +34846,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>132.669317</v>
+        <v>133.669282</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -35024,7 +35024,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>54.954317</v>
+        <v>55.954282</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35202,7 +35202,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>294.842569</v>
+        <v>295.842535</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35370,7 +35370,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW194">
-        <v>229.664641</v>
+        <v>230.664606</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35551,7 +35551,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW195">
-        <v>207.888438</v>
+        <v>208.888403</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35735,7 +35735,7 @@
         <v>45905.68527717593</v>
       </c>
       <c r="AW196">
-        <v>188.959803</v>
+        <v>189.959769</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35919,7 +35919,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW197">
-        <v>243.705382</v>
+        <v>244.705347</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -36100,7 +36100,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW198">
-        <v>110.797743</v>
+        <v>111.797708</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36278,7 +36278,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW199">
-        <v>287.689028</v>
+        <v>288.688993</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36456,7 +36456,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW200">
-        <v>301.909861</v>
+        <v>302.909826</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36637,7 +36637,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW201">
-        <v>207.894282</v>
+        <v>208.894248</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36815,7 +36815,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW202">
-        <v>181.681678</v>
+        <v>182.681644</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36996,7 +36996,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW203">
-        <v>274.925567</v>
+        <v>275.925532</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37174,7 +37174,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW204">
-        <v>285.50397</v>
+        <v>286.503935</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37352,7 +37352,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW205">
-        <v>213.607523</v>
+        <v>214.607488</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37530,7 +37530,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>38.604225</v>
+        <v>39.60419</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37711,7 +37711,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW207">
-        <v>269.561539</v>
+        <v>270.561505</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37892,7 +37892,7 @@
         <v>45880.49447488426</v>
       </c>
       <c r="AW208">
-        <v>217.530961</v>
+        <v>218.530926</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -38070,7 +38070,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>75.685301</v>
+        <v>76.685266</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38248,7 +38248,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>290.572164</v>
+        <v>291.57213</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38426,7 +38426,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>287.688484</v>
+        <v>288.688449</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38604,7 +38604,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>21.541863</v>
+        <v>22.541829</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38782,7 +38782,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>286.610706</v>
+        <v>287.610671</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38960,7 +38960,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW214">
-        <v>298.593287</v>
+        <v>299.593252</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39138,7 +39138,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW215">
-        <v>300.733681</v>
+        <v>301.733646</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39316,7 +39316,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>290.646863</v>
+        <v>291.646829</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39494,7 +39494,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>252.568553</v>
+        <v>253.568519</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39675,7 +39675,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>252.586528</v>
+        <v>253.586493</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39856,7 +39856,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>157.911563</v>
+        <v>158.911528</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -40037,7 +40037,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>14.703981</v>
+        <v>15.703947</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40215,7 +40215,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW221">
-        <v>299.689005</v>
+        <v>300.68897</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40393,7 +40393,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW222">
-        <v>290.587928</v>
+        <v>291.587894</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40571,7 +40571,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW223">
-        <v>299.684873</v>
+        <v>300.684838</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40752,7 +40752,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW224">
-        <v>200.639178</v>
+        <v>201.639144</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40933,7 +40933,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW225">
-        <v>132.693472</v>
+        <v>133.693438</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -41114,7 +41114,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW226">
-        <v>125.71162</v>
+        <v>126.711586</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41295,7 +41295,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW227">
-        <v>60.933113</v>
+        <v>61.933079</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41476,7 +41476,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW228">
-        <v>60.934792</v>
+        <v>61.934757</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41657,7 +41657,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW229">
-        <v>207.893634</v>
+        <v>208.8936</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41838,7 +41838,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW230">
-        <v>259.659109</v>
+        <v>260.659074</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -42016,7 +42016,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW231">
-        <v>276.900417</v>
+        <v>277.900382</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42197,7 +42197,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW232">
-        <v>216.670023</v>
+        <v>217.669988</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42381,7 +42381,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW233">
-        <v>208.91022</v>
+        <v>209.910185</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42562,7 +42562,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW234">
-        <v>188.958113</v>
+        <v>189.958079</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42740,7 +42740,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>139.886979</v>
+        <v>140.886944</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42921,7 +42921,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>25.59559</v>
+        <v>26.595556</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -43102,7 +43102,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW237">
-        <v>251.874769</v>
+        <v>252.874734</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43283,7 +43283,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW238">
-        <v>207.753229</v>
+        <v>208.753194</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43464,7 +43464,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW239">
-        <v>110.79897</v>
+        <v>111.798935</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43642,7 +43642,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>75.678634</v>
+        <v>76.6786</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43823,7 +43823,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>126.515995</v>
+        <v>127.515961</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -44004,7 +44004,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>241.900764</v>
+        <v>242.900729</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44177,7 +44177,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW243">
-        <v>287.573264</v>
+        <v>288.573229</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44355,7 +44355,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>252.567338</v>
+        <v>253.567303</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44539,7 +44539,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW245">
-        <v>216.601412</v>
+        <v>217.601377</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44720,7 +44720,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>159.855995</v>
+        <v>160.855961</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44904,7 +44904,7 @@
         <v>45923.57573010417</v>
       </c>
       <c r="AW247">
-        <v>188.66088</v>
+        <v>189.660845</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -45085,7 +45085,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>182.940775</v>
+        <v>183.940741</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45266,7 +45266,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>33.719583</v>
+        <v>34.719549</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45444,7 +45444,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>252.567743</v>
+        <v>253.567708</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45625,7 +45625,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>223.828275</v>
+        <v>224.828241</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45806,7 +45806,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>60.678461</v>
+        <v>61.678426</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45987,7 +45987,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>272.720938</v>
+        <v>273.720903</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46168,7 +46168,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>61.724421</v>
+        <v>62.724387</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46281,7 +46281,7 @@
         <v>46097.39762828704</v>
       </c>
       <c r="AN255">
-        <v>14.874352</v>
+        <v>15.874317</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46462,7 +46462,7 @@
         <v>46111.70316528935</v>
       </c>
       <c r="AW256">
-        <v>0.568819</v>
+        <v>1.568785</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46643,7 +46643,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>84.935394</v>
+        <v>85.93535900000001</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46824,7 +46824,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW258">
-        <v>251.835347</v>
+        <v>252.835313</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -47002,7 +47002,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW259">
-        <v>182.950521</v>
+        <v>183.950486</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -47183,7 +47183,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW260">
-        <v>182.948368</v>
+        <v>183.948333</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47361,7 +47361,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>157.532917</v>
+        <v>158.532882</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47537,7 +47537,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>249.779606</v>
+        <v>250.779572</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47715,7 +47715,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW263">
-        <v>173.939086</v>
+        <v>174.939051</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47899,7 +47899,7 @@
         <v>45946.65466756944</v>
       </c>
       <c r="AW264">
-        <v>159.711308</v>
+        <v>160.711273</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -48077,7 +48077,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW265">
-        <v>108.707998</v>
+        <v>109.707963</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48258,7 +48258,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW266">
-        <v>280.698044</v>
+        <v>281.698009</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48436,7 +48436,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW267">
-        <v>290.646123</v>
+        <v>291.646088</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48617,7 +48617,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>269.561887</v>
+        <v>270.561852</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48798,7 +48798,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW269">
-        <v>145.720741</v>
+        <v>146.720706</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48976,7 +48976,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW270">
-        <v>159.712118</v>
+        <v>160.712083</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -49157,7 +49157,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>125.695509</v>
+        <v>126.695475</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49338,7 +49338,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>269.562431</v>
+        <v>270.562396</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49516,7 +49516,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW273">
-        <v>188.952512</v>
+        <v>189.952477</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49700,7 +49700,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW274">
-        <v>140.699352</v>
+        <v>141.699317</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49881,7 +49881,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW275">
-        <v>279.591238</v>
+        <v>280.591204</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -50062,7 +50062,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW276">
-        <v>194.806759</v>
+        <v>195.806725</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50243,7 +50243,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW277">
-        <v>125.71228</v>
+        <v>126.712245</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50424,7 +50424,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>146.893368</v>
+        <v>147.893333</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50605,7 +50605,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW279">
-        <v>265.783229</v>
+        <v>266.783194</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50812,7 +50812,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW280">
-        <v>145.826424</v>
+        <v>146.826389</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50990,7 +50990,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW281">
-        <v>136.622431</v>
+        <v>137.622396</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -51171,7 +51171,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW282">
-        <v>119.655139</v>
+        <v>120.655104</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51355,7 +51355,7 @@
         <v>45924.33433900463</v>
       </c>
       <c r="AW283">
-        <v>174.942512</v>
+        <v>175.942477</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51533,7 +51533,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>11.886713</v>
+        <v>12.886678</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51711,7 +51711,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>266.949502</v>
+        <v>267.949468</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51889,7 +51889,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>278.706169</v>
+        <v>279.706134</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -52067,7 +52067,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW287">
-        <v>241.901829</v>
+        <v>242.901794</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52248,7 +52248,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>221.629896</v>
+        <v>222.629861</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52432,7 +52432,7 @@
         <v>45944.44625667824</v>
       </c>
       <c r="AW289">
-        <v>162.957315</v>
+        <v>163.95728</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52613,7 +52613,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>140.693009</v>
+        <v>141.692975</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52794,7 +52794,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW291">
-        <v>265.911898</v>
+        <v>266.911863</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52972,7 +52972,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW292">
-        <v>279.9111</v>
+        <v>280.911065</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -53153,7 +53153,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW293">
-        <v>224.518993</v>
+        <v>225.518958</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53331,7 +53331,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>285.502002</v>
+        <v>286.501968</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53512,7 +53512,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>207.89485</v>
+        <v>208.894815</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53693,7 +53693,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>14.87559</v>
+        <v>15.875556</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53874,7 +53874,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW297">
-        <v>125.563738</v>
+        <v>126.563704</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -54052,7 +54052,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW298">
-        <v>252.569676</v>
+        <v>253.569641</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54230,7 +54230,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>11.888924</v>
+        <v>12.888889</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54419,7 +54419,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>276.90088</v>
+        <v>277.900845</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54600,7 +54600,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW301">
-        <v>207.88772</v>
+        <v>208.887685</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54778,7 +54778,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW302">
-        <v>182.69919</v>
+        <v>183.699155</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54959,7 +54959,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>104.844907</v>
+        <v>105.844873</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -55145,7 +55145,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW304">
-        <v>217.66066</v>
+        <v>218.660625</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55323,7 +55323,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>291.940602</v>
+        <v>292.940567</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55504,7 +55504,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW306">
-        <v>181.612813</v>
+        <v>182.612778</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55685,7 +55685,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>136.723021</v>
+        <v>137.722986</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55866,7 +55866,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW308">
-        <v>110.810486</v>
+        <v>111.810451</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -56047,7 +56047,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW309">
-        <v>84.93722200000001</v>
+        <v>85.93718800000001</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56228,7 +56228,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW310">
-        <v>181.611377</v>
+        <v>182.611343</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56409,7 +56409,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW311">
-        <v>181.613148</v>
+        <v>182.613113</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56590,7 +56590,7 @@
         <v>46111.63328278935</v>
       </c>
       <c r="AW312">
-        <v>0.638704</v>
+        <v>1.638669</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56768,7 +56768,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>285.502384</v>
+        <v>286.50235</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56946,7 +56946,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>54.958623</v>
+        <v>55.958588</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -57127,7 +57127,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW315">
-        <v>238.564074</v>
+        <v>239.564039</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57305,7 +57305,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW316">
-        <v>34.571076</v>
+        <v>35.571042</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57486,7 +57486,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW317">
-        <v>157.644444</v>
+        <v>158.64441</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57667,7 +57667,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW318">
-        <v>14.876053</v>
+        <v>15.876019</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57845,7 +57845,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW319">
-        <v>11.88816</v>
+        <v>12.888125</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -58026,7 +58026,7 @@
         <v>45873.70610516204</v>
       </c>
       <c r="AW320">
-        <v>238.566863</v>
+        <v>239.566829</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -58207,7 +58207,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>251.872106</v>
+        <v>252.872072</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58385,7 +58385,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>60.602014</v>
+        <v>61.601979</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58563,7 +58563,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW323">
-        <v>294.835451</v>
+        <v>295.835417</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58744,7 +58744,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW324">
-        <v>188.951655</v>
+        <v>189.95162</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58922,7 +58922,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW325">
-        <v>152.661736</v>
+        <v>153.661701</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -59103,7 +59103,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>140.696991</v>
+        <v>141.696956</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59284,7 +59284,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>273.609502</v>
+        <v>274.609468</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59465,7 +59465,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW328">
-        <v>228.668519</v>
+        <v>229.668484</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59646,7 +59646,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW329">
-        <v>110.812014</v>
+        <v>111.811979</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59827,7 +59827,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW330">
-        <v>69.81462999999999</v>
+        <v>70.814595</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -60005,7 +60005,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>221.575891</v>
+        <v>222.575856</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -60189,7 +60189,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>167.586609</v>
+        <v>168.586574</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60367,7 +60367,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW333">
-        <v>252.569005</v>
+        <v>253.56897</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60548,7 +60548,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW334">
-        <v>146.889583</v>
+        <v>147.889549</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60729,7 +60729,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>136.622859</v>
+        <v>137.622824</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60907,7 +60907,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>231.593484</v>
+        <v>232.593449</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -61088,7 +61088,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>77.57534699999999</v>
+        <v>78.57531299999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61269,7 +61269,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>223.824919</v>
+        <v>224.824884</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61445,7 +61445,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>157.643958</v>
+        <v>158.643924</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61626,7 +61626,7 @@
         <v>46111.63441997685</v>
       </c>
       <c r="AW340">
-        <v>0.6375690000000001</v>
+        <v>1.637535</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61807,7 +61807,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>14.876551</v>
+        <v>15.876516</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61985,7 +61985,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>299.693831</v>
+        <v>300.693796</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -62166,7 +62166,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW343">
-        <v>209.892801</v>
+        <v>210.892766</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62347,7 +62347,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW344">
-        <v>188.959016</v>
+        <v>189.958981</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62528,7 +62528,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>138.607037</v>
+        <v>139.607002</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62709,7 +62709,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>256.932176</v>
+        <v>257.932141</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62890,7 +62890,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>54.772905</v>
+        <v>55.77287</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -63071,7 +63071,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>35.945347</v>
+        <v>36.945313</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -63252,7 +63252,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>119.655752</v>
+        <v>120.655718</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63430,7 +63430,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW350">
-        <v>213.652558</v>
+        <v>214.652523</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63611,7 +63611,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW351">
-        <v>192.591076</v>
+        <v>193.591042</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63789,7 +63789,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW352">
-        <v>157.645069</v>
+        <v>158.645035</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63970,7 +63970,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW353">
-        <v>138.608264</v>
+        <v>139.608229</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -64151,7 +64151,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>265.912118</v>
+        <v>266.912083</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64332,7 +64332,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>194.806308</v>
+        <v>195.806273</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64513,7 +64513,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>182.940012</v>
+        <v>183.939977</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64694,7 +64694,7 @@
         <v>45915.4691385301</v>
       </c>
       <c r="AW357">
-        <v>189.012523</v>
+        <v>190.012488</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64875,7 +64875,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW358">
-        <v>124.727269</v>
+        <v>125.727234</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -65056,7 +65056,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW359">
-        <v>74.606458</v>
+        <v>75.606424</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -65237,7 +65237,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW360">
-        <v>290.596736</v>
+        <v>291.596701</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65415,7 +65415,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW361">
-        <v>291.938912</v>
+        <v>292.938877</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65596,7 +65596,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW362">
-        <v>105.726204</v>
+        <v>106.726169</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65777,7 +65777,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW363">
-        <v>60.740521</v>
+        <v>61.740486</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65955,7 +65955,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>298.587581</v>
+        <v>299.587546</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -66136,7 +66136,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>188.960231</v>
+        <v>189.960197</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66314,7 +66314,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>108.707917</v>
+        <v>109.707882</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66495,7 +66495,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>269.562951</v>
+        <v>270.562917</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66676,7 +66676,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW368">
-        <v>159.8575</v>
+        <v>160.857465</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66857,7 +66857,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW369">
-        <v>157.892535</v>
+        <v>158.8925</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -67035,7 +67035,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW370">
-        <v>285.501736</v>
+        <v>286.501701</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -67216,7 +67216,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW371">
-        <v>256.929491</v>
+        <v>257.929456</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67394,7 +67394,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>175.529688</v>
+        <v>176.529653</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67572,7 +67572,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>259.722049</v>
+        <v>260.722014</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67753,7 +67753,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>207.889074</v>
+        <v>208.889039</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67934,7 +67934,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>14.875243</v>
+        <v>15.875208</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -68112,7 +68112,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW376">
-        <v>294.727488</v>
+        <v>295.727454</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -68290,7 +68290,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW377">
-        <v>290.633345</v>
+        <v>291.63331</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68471,7 +68471,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>138.613657</v>
+        <v>139.613623</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68649,7 +68649,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>291.939711</v>
+        <v>292.939676</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68827,7 +68827,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW380">
-        <v>269.563472</v>
+        <v>270.563438</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -69005,7 +69005,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW381">
-        <v>299.685231</v>
+        <v>300.685197</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -69183,7 +69183,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>147.621609</v>
+        <v>148.621574</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69361,7 +69361,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>285.500266</v>
+        <v>286.500231</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69539,7 +69539,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW384">
-        <v>252.566146</v>
+        <v>253.566111</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69720,7 +69720,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW385">
-        <v>243.698773</v>
+        <v>244.698738</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69901,7 +69901,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW386">
-        <v>159.856817</v>
+        <v>160.856782</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -70082,7 +70082,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW387">
-        <v>104.84375</v>
+        <v>105.843715</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -70263,7 +70263,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW388">
-        <v>110.810938</v>
+        <v>111.810903</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70436,7 +70436,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>206.592303</v>
+        <v>207.592269</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70609,7 +70609,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>206.59184</v>
+        <v>207.591806</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70790,7 +70790,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>110.809363</v>
+        <v>111.809329</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70971,7 +70971,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW392">
-        <v>125.709884</v>
+        <v>126.70985</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -71152,7 +71152,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW393">
-        <v>138.607245</v>
+        <v>139.607211</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>296.834306</v>
+        <v>297.834282</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>139.950301</v>
+        <v>140.950278</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>127.708345</v>
+        <v>128.708322</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>251.779965</v>
+        <v>252.779942</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1560,7 +1560,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW6">
-        <v>62.934063</v>
+        <v>63.934039</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW7">
-        <v>254.566516</v>
+        <v>255.566493</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1919,7 +1919,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW8">
-        <v>138.624583</v>
+        <v>139.62456</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2097,7 +2097,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW9">
-        <v>289.604016</v>
+        <v>290.603993</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2281,7 +2281,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW10">
-        <v>238.644653</v>
+        <v>239.64463</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2462,7 +2462,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW11">
-        <v>223.630313</v>
+        <v>224.630289</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW12">
-        <v>222.72794</v>
+        <v>223.727917</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2821,7 +2821,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW13">
-        <v>258.928993</v>
+        <v>259.92897</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2999,7 +2999,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW14">
-        <v>301.688009</v>
+        <v>302.687986</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3177,7 +3177,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW15">
-        <v>287.50316</v>
+        <v>288.503137</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3353,7 +3353,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW16">
-        <v>120.815069</v>
+        <v>121.815046</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3534,7 +3534,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>138.578808</v>
+        <v>139.578785</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW18">
-        <v>256.63169</v>
+        <v>257.631667</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW19">
-        <v>218.604583</v>
+        <v>219.60456</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW20">
-        <v>226.515822</v>
+        <v>227.515799</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>139.950729</v>
+        <v>140.950706</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>56.952755</v>
+        <v>57.952731</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>55.697951</v>
+        <v>56.697928</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>62.931481</v>
+        <v>63.931458</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>251.779433</v>
+        <v>252.77941</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>138.723646</v>
+        <v>139.723623</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>36.577801</v>
+        <v>37.577778</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>86.934456</v>
+        <v>87.934433</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5689,7 +5689,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW29">
-        <v>208.592153</v>
+        <v>209.59213</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW30">
-        <v>287.508669</v>
+        <v>288.508646</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>217.685637</v>
+        <v>218.685613</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>147.825683</v>
+        <v>148.82566</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>289.598924</v>
+        <v>290.5989</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW34">
-        <v>225.827639</v>
+        <v>226.827616</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW35">
-        <v>146.607083</v>
+        <v>147.60706</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>134.725428</v>
+        <v>135.725405</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7139,7 +7139,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW37">
-        <v>261.659178</v>
+        <v>262.659155</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW38">
-        <v>253.873438</v>
+        <v>254.873414</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7495,7 +7495,7 @@
         <v>46100.38240289352</v>
       </c>
       <c r="AW39">
-        <v>12.04022</v>
+        <v>13.040197</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7676,7 +7676,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>148.891076</v>
+        <v>149.891053</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7857,7 +7857,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>127.705324</v>
+        <v>128.705301</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8038,7 +8038,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>86.695058</v>
+        <v>87.695035</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8219,7 +8219,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW43">
-        <v>35.718738</v>
+        <v>36.718715</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8400,7 +8400,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>76.61870399999999</v>
+        <v>77.618681</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8578,7 +8578,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW45">
-        <v>56.954745</v>
+        <v>57.954722</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8759,7 +8759,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>210.91044</v>
+        <v>211.910417</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8940,7 +8940,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>225.827025</v>
+        <v>226.827002</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9118,7 +9118,7 @@
         <v>46106.37582024305</v>
       </c>
       <c r="AW48">
-        <v>7.896157</v>
+        <v>8.896134</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9299,7 +9299,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW49">
-        <v>176.942581</v>
+        <v>177.942558</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9480,7 +9480,7 @@
         <v>45924.33459813657</v>
       </c>
       <c r="AW50">
-        <v>176.943796</v>
+        <v>177.943773</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9648,7 +9648,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>34.592836</v>
+        <v>35.592813</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9829,7 +9829,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW52">
-        <v>267.783414</v>
+        <v>268.783391</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -10010,7 +10010,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW53">
-        <v>253.874421</v>
+        <v>254.874398</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10188,7 +10188,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW54">
-        <v>254.567928</v>
+        <v>255.567905</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10369,7 +10369,7 @@
         <v>45946.65447922454</v>
       </c>
       <c r="AW55">
-        <v>161.710544</v>
+        <v>162.710521</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10547,7 +10547,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>34.592095</v>
+        <v>35.592072</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10731,7 +10731,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>245.540949</v>
+        <v>246.540926</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10909,7 +10909,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>13.889271</v>
+        <v>14.889248</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11087,7 +11087,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>292.645602</v>
+        <v>293.645579</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11265,7 +11265,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>282.694421</v>
+        <v>283.694398</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11446,7 +11446,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>112.796968</v>
+        <v>113.796944</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11624,7 +11624,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>77.68825200000001</v>
+        <v>78.68822900000001</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11802,7 +11802,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>254.567095</v>
+        <v>255.567072</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11983,7 +11983,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW64">
-        <v>128.514826</v>
+        <v>129.514803</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12164,7 +12164,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW65">
-        <v>148.895185</v>
+        <v>149.895162</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12345,7 +12345,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>190.568669</v>
+        <v>191.568646</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12523,7 +12523,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>257.822778</v>
+        <v>258.822755</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12701,7 +12701,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>218.623924</v>
+        <v>219.6239</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12885,7 +12885,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>138.623796</v>
+        <v>139.623773</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13063,7 +13063,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>76.59834499999999</v>
+        <v>77.598322</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13241,7 +13241,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>293.938738</v>
+        <v>294.938715</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13419,7 +13419,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>296.831632</v>
+        <v>297.831609</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13600,7 +13600,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW73">
-        <v>16.879444</v>
+        <v>17.879421</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13781,7 +13781,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW74">
-        <v>154.716956</v>
+        <v>155.716933</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13962,7 +13962,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW75">
-        <v>211.684398</v>
+        <v>212.684375</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14140,7 +14140,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW76">
-        <v>254.58287</v>
+        <v>255.582847</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14321,7 +14321,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW77">
-        <v>111.542199</v>
+        <v>112.542176</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14502,7 +14502,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW78">
-        <v>56.773588</v>
+        <v>57.773565</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14683,7 +14683,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW79">
-        <v>106.844653</v>
+        <v>107.84463</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14861,7 +14861,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW80">
-        <v>147.720995</v>
+        <v>148.720972</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15042,7 +15042,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW81">
-        <v>140.607512</v>
+        <v>141.607488</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15220,7 +15220,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>205.680521</v>
+        <v>206.680498</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15406,7 +15406,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW83">
-        <v>268.654306</v>
+        <v>269.654282</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15587,7 +15587,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>16.875069</v>
+        <v>17.875046</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15768,7 +15768,7 @@
         <v>45890.42079241898</v>
       </c>
       <c r="AW85">
-        <v>209.889167</v>
+        <v>210.889144</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15949,7 +15949,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>127.695671</v>
+        <v>128.695648</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16130,7 +16130,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>282.697813</v>
+        <v>283.697789</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16308,7 +16308,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW88">
-        <v>161.858935</v>
+        <v>162.858912</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16489,7 +16489,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW89">
-        <v>146.605741</v>
+        <v>147.605718</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16670,7 +16670,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>156.553692</v>
+        <v>157.553669</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16851,7 +16851,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW91">
-        <v>176.943576</v>
+        <v>177.943553</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -17032,7 +17032,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW92">
-        <v>190.561516</v>
+        <v>191.561493</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17213,7 +17213,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW93">
-        <v>209.887454</v>
+        <v>210.887431</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17399,7 +17399,7 @@
         <v>45873.70399680555</v>
       </c>
       <c r="AW94">
-        <v>240.567546</v>
+        <v>241.567523</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17577,7 +17577,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW95">
-        <v>261.723137</v>
+        <v>262.723113</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17755,7 +17755,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW96">
-        <v>292.597882</v>
+        <v>293.597859</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17936,7 +17936,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>112.806331</v>
+        <v>113.806308</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -18117,7 +18117,7 @@
         <v>46111.63374820602</v>
       </c>
       <c r="AW98">
-        <v>2.638229</v>
+        <v>3.638206</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18298,7 +18298,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>246.570058</v>
+        <v>247.570035</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18476,7 +18476,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>287.502778</v>
+        <v>288.502755</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18654,7 +18654,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>196.943206</v>
+        <v>197.943183</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18832,7 +18832,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>254.566319</v>
+        <v>255.566296</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -19013,7 +19013,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>86.938079</v>
+        <v>87.938056</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19191,7 +19191,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>293.939132</v>
+        <v>294.939109</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19369,7 +19369,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>205.553796</v>
+        <v>206.553773</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19550,7 +19550,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>127.7089</v>
+        <v>128.708877</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19731,7 +19731,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>223.622975</v>
+        <v>224.622951</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19912,7 +19912,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>215.698831</v>
+        <v>216.698808</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -20090,7 +20090,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>55.722616</v>
+        <v>56.722593</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20271,7 +20271,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW110">
-        <v>245.685729</v>
+        <v>246.685706</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20449,7 +20449,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW111">
-        <v>289.688738</v>
+        <v>290.688715</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20630,7 +20630,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW112">
-        <v>126.723796</v>
+        <v>127.723773</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20811,7 +20811,7 @@
         <v>45875.68270515047</v>
       </c>
       <c r="AW113">
-        <v>184.944479</v>
+        <v>185.944456</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20992,7 +20992,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>244.122604</v>
+        <v>245.122581</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21173,7 +21173,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW115">
-        <v>127.694352</v>
+        <v>128.694329</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21354,7 +21354,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW116">
-        <v>154.698438</v>
+        <v>155.698414</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21535,7 +21535,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW117">
-        <v>205.609745</v>
+        <v>206.609722</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21716,7 +21716,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW118">
-        <v>252.766123</v>
+        <v>253.7661</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21897,7 +21897,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW119">
-        <v>63.723993</v>
+        <v>64.72396999999999</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -22078,7 +22078,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW120">
-        <v>86.936701</v>
+        <v>87.936678</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22256,7 +22256,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>296.834595</v>
+        <v>297.834572</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22437,7 +22437,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW122">
-        <v>156.544329</v>
+        <v>157.544306</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22618,7 +22618,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW123">
-        <v>138.72316</v>
+        <v>139.723137</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22796,7 +22796,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW124">
-        <v>75.588565</v>
+        <v>76.588542</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22977,7 +22977,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW125">
-        <v>292.596019</v>
+        <v>293.595995</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23155,7 +23155,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW126">
-        <v>282.645475</v>
+        <v>283.645451</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23336,7 +23336,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW127">
-        <v>184.942882</v>
+        <v>185.942859</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23520,7 +23520,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW128">
-        <v>245.705741</v>
+        <v>246.705718</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23698,7 +23698,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW129">
-        <v>223.576181</v>
+        <v>224.576157</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23879,7 +23879,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW130">
-        <v>271.564688</v>
+        <v>272.564664</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -24060,7 +24060,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>27.59669</v>
+        <v>28.596667</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24241,7 +24241,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>209.885301</v>
+        <v>210.885278</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24419,7 +24419,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>287.503391</v>
+        <v>288.503368</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24600,7 +24600,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>127.695775</v>
+        <v>128.695752</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24781,7 +24781,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>111.542905</v>
+        <v>112.542882</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24954,7 +24954,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>282.597986</v>
+        <v>283.597963</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25135,7 +25135,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>112.798414</v>
+        <v>113.798391</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25316,7 +25316,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>41.675104</v>
+        <v>42.675081</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25497,7 +25497,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW139">
-        <v>190.956968</v>
+        <v>191.956944</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25678,7 +25678,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW140">
-        <v>196.805556</v>
+        <v>197.805532</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25856,7 +25856,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>300.648009</v>
+        <v>301.647986</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -26034,7 +26034,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>226.488368</v>
+        <v>227.488345</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26215,7 +26215,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>184.942338</v>
+        <v>185.942315</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26396,7 +26396,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW144">
-        <v>54.835775</v>
+        <v>55.835752</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26572,7 +26572,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW145">
-        <v>120.814838</v>
+        <v>121.814815</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26750,7 +26750,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>282.648681</v>
+        <v>283.648657</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26928,7 +26928,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>287.505046</v>
+        <v>288.505023</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27106,7 +27106,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>13.884942</v>
+        <v>14.884919</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27287,7 +27287,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>223.685671</v>
+        <v>224.685648</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27465,7 +27465,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>257.82235</v>
+        <v>258.822326</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27646,7 +27646,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW151">
-        <v>217.686667</v>
+        <v>218.686644</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27824,7 +27824,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW152">
-        <v>254.566817</v>
+        <v>255.566794</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -28005,7 +28005,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>76.60485</v>
+        <v>77.604826</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28183,7 +28183,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW154">
-        <v>56.951887</v>
+        <v>57.951863</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28364,7 +28364,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW155">
-        <v>189.818843</v>
+        <v>190.818819</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28545,7 +28545,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW156">
-        <v>189.6189</v>
+        <v>190.618877</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28729,7 +28729,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>112.805961</v>
+        <v>113.805938</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28918,7 +28918,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW158">
-        <v>201.582269</v>
+        <v>202.582245</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -29096,7 +29096,7 @@
         <v>45898.61987270833</v>
       </c>
       <c r="AW159">
-        <v>211.517037</v>
+        <v>212.517014</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29277,7 +29277,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW160">
-        <v>128.515486</v>
+        <v>129.515463</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29458,7 +29458,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW161">
-        <v>69.628507</v>
+        <v>70.628484</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29626,7 +29626,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW162">
-        <v>231.652442</v>
+        <v>232.652419</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29807,7 +29807,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW163">
-        <v>184.941644</v>
+        <v>185.94162</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29988,7 +29988,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW164">
-        <v>209.890914</v>
+        <v>210.890891</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30169,7 +30169,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW165">
-        <v>133.538438</v>
+        <v>134.538414</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30350,7 +30350,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW166">
-        <v>253.874225</v>
+        <v>254.874201</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30528,7 +30528,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>56.956331</v>
+        <v>57.956308</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30706,7 +30706,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>243.897037</v>
+        <v>244.897014</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30887,7 +30887,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>159.643484</v>
+        <v>160.643461</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -31065,7 +31065,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>127.692697</v>
+        <v>128.692674</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31246,7 +31246,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>27.59772</v>
+        <v>28.597697</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31424,7 +31424,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>292.598819</v>
+        <v>293.598796</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31605,7 +31605,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>268.94912</v>
+        <v>269.949097</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31783,7 +31783,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>77.679676</v>
+        <v>78.679653</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31961,7 +31961,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>50.724977</v>
+        <v>51.724954</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32134,7 +32134,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>208.591944</v>
+        <v>209.591921</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32315,7 +32315,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>86.9361</v>
+        <v>87.936076</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32493,7 +32493,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>36.571586</v>
+        <v>37.571563</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32671,7 +32671,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW179">
-        <v>296.834988</v>
+        <v>297.834965</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32849,7 +32849,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW180">
-        <v>243.901979</v>
+        <v>244.901956</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -33027,7 +33027,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>218.603056</v>
+        <v>219.603032</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33208,7 +33208,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW182">
-        <v>16.87897</v>
+        <v>17.878947</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33386,7 +33386,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW183">
-        <v>289.598368</v>
+        <v>290.598345</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33564,7 +33564,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW184">
-        <v>280.705208</v>
+        <v>281.705185</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33745,7 +33745,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>147.720833</v>
+        <v>148.72081</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33923,7 +33923,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW186">
-        <v>218.623808</v>
+        <v>219.623785</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34101,7 +34101,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>289.598009</v>
+        <v>290.597986</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34282,7 +34282,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>245.701551</v>
+        <v>246.701528</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34463,7 +34463,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW189">
-        <v>223.515961</v>
+        <v>224.515938</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34644,7 +34644,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW190">
-        <v>190.95625</v>
+        <v>191.956227</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34825,7 +34825,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>134.669306</v>
+        <v>135.669282</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -35003,7 +35003,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>56.954306</v>
+        <v>57.954282</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35181,7 +35181,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>296.842558</v>
+        <v>297.842535</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35362,7 +35362,7 @@
         <v>45905.68518516204</v>
       </c>
       <c r="AW194">
-        <v>190.959792</v>
+        <v>191.959769</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35546,7 +35546,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW195">
-        <v>245.70537</v>
+        <v>246.705347</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35727,7 +35727,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW196">
-        <v>112.797731</v>
+        <v>113.797708</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35908,7 +35908,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW197">
-        <v>209.888426</v>
+        <v>210.888403</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -36076,7 +36076,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW198">
-        <v>231.66463</v>
+        <v>232.664606</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36254,7 +36254,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW199">
-        <v>183.681667</v>
+        <v>184.681644</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36435,7 +36435,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW200">
-        <v>209.894271</v>
+        <v>210.894248</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36613,7 +36613,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW201">
-        <v>289.689016</v>
+        <v>290.688993</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36791,7 +36791,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW202">
-        <v>303.90985</v>
+        <v>304.909826</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36969,7 +36969,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW203">
-        <v>215.607512</v>
+        <v>216.607488</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37150,7 +37150,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW204">
-        <v>276.925556</v>
+        <v>277.925532</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37328,7 +37328,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW205">
-        <v>287.503958</v>
+        <v>288.503935</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37506,7 +37506,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>40.604213</v>
+        <v>41.60419</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37684,7 +37684,7 @@
         <v>45880.4943486574</v>
       </c>
       <c r="AW207">
-        <v>219.530949</v>
+        <v>220.530926</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37865,7 +37865,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW208">
-        <v>271.561528</v>
+        <v>272.561505</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -38043,7 +38043,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>77.685289</v>
+        <v>78.685266</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38221,7 +38221,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>292.572153</v>
+        <v>293.57213</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38399,7 +38399,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>289.688472</v>
+        <v>290.688449</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38577,7 +38577,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>23.541852</v>
+        <v>24.541829</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38755,7 +38755,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>288.610694</v>
+        <v>289.610671</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38933,7 +38933,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW214">
-        <v>302.733669</v>
+        <v>303.733646</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39111,7 +39111,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW215">
-        <v>300.593275</v>
+        <v>301.593252</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39289,7 +39289,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>292.646852</v>
+        <v>293.646829</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39467,7 +39467,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>254.568542</v>
+        <v>255.568519</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39648,7 +39648,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>254.586516</v>
+        <v>255.586493</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39829,7 +39829,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>159.911551</v>
+        <v>160.911528</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -40010,7 +40010,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>16.70397</v>
+        <v>17.703947</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40191,7 +40191,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW221">
-        <v>62.93478</v>
+        <v>63.934757</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40372,7 +40372,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW222">
-        <v>62.933102</v>
+        <v>63.933079</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40553,7 +40553,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW223">
-        <v>134.693461</v>
+        <v>135.693438</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40734,7 +40734,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW224">
-        <v>127.711609</v>
+        <v>128.711586</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40912,7 +40912,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW225">
-        <v>292.587917</v>
+        <v>293.587894</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -41090,7 +41090,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW226">
-        <v>301.688993</v>
+        <v>302.68897</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41268,7 +41268,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW227">
-        <v>301.684861</v>
+        <v>302.684838</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41449,7 +41449,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW228">
-        <v>202.639167</v>
+        <v>203.639144</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41630,7 +41630,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW229">
-        <v>261.659097</v>
+        <v>262.659074</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41811,7 +41811,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW230">
-        <v>209.893623</v>
+        <v>210.8936</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41992,7 +41992,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW231">
-        <v>218.670012</v>
+        <v>219.669988</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42170,7 +42170,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW232">
-        <v>278.900405</v>
+        <v>279.900382</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42351,7 +42351,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW233">
-        <v>190.958102</v>
+        <v>191.958079</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42535,7 +42535,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW234">
-        <v>210.910208</v>
+        <v>211.910185</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42713,7 +42713,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>141.886968</v>
+        <v>142.886944</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42894,7 +42894,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>27.595579</v>
+        <v>28.595556</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -43075,7 +43075,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW237">
-        <v>112.798958</v>
+        <v>113.798935</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43256,7 +43256,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW238">
-        <v>253.874757</v>
+        <v>254.874734</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43437,7 +43437,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW239">
-        <v>209.753218</v>
+        <v>210.753194</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43615,7 +43615,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>77.678623</v>
+        <v>78.6786</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43796,7 +43796,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>128.515984</v>
+        <v>129.515961</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43977,7 +43977,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>243.900752</v>
+        <v>244.900729</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44161,7 +44161,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW243">
-        <v>218.6014</v>
+        <v>219.601377</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44339,7 +44339,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>254.567326</v>
+        <v>255.567303</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44512,7 +44512,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW245">
-        <v>289.573252</v>
+        <v>290.573229</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44693,7 +44693,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>161.855984</v>
+        <v>162.855961</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44874,7 +44874,7 @@
         <v>45923.56720940972</v>
       </c>
       <c r="AW247">
-        <v>190.660868</v>
+        <v>191.660845</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -45055,7 +45055,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>184.940764</v>
+        <v>185.940741</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45236,7 +45236,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>35.719572</v>
+        <v>36.719549</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45414,7 +45414,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>254.567731</v>
+        <v>255.567708</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45595,7 +45595,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>225.828264</v>
+        <v>226.828241</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45776,7 +45776,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>62.678449</v>
+        <v>63.678426</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45957,7 +45957,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>274.720926</v>
+        <v>275.720903</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46138,7 +46138,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>63.72441</v>
+        <v>64.72438699999999</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46319,7 +46319,7 @@
         <v>46111.70316528935</v>
       </c>
       <c r="AW255">
-        <v>2.568808</v>
+        <v>3.568785</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46456,7 +46456,7 @@
         <v>46113.36897872685</v>
       </c>
       <c r="AQ256">
-        <v>0.902998</v>
+        <v>1.902975</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46637,7 +46637,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>86.935382</v>
+        <v>87.93535900000001</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46818,7 +46818,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW258">
-        <v>184.948356</v>
+        <v>185.948333</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46999,7 +46999,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW259">
-        <v>253.835336</v>
+        <v>254.835313</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -47177,7 +47177,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW260">
-        <v>184.950509</v>
+        <v>185.950486</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47355,7 +47355,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>159.532905</v>
+        <v>160.532882</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47531,7 +47531,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>251.779595</v>
+        <v>252.779572</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47709,7 +47709,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW263">
-        <v>110.707986</v>
+        <v>111.707963</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47887,7 +47887,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW264">
-        <v>175.939074</v>
+        <v>176.939051</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -48068,7 +48068,7 @@
         <v>45946.65440010416</v>
       </c>
       <c r="AW265">
-        <v>161.711296</v>
+        <v>162.711273</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48246,7 +48246,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW266">
-        <v>292.646111</v>
+        <v>293.646088</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48427,7 +48427,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW267">
-        <v>282.698032</v>
+        <v>283.698009</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48608,7 +48608,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>271.561875</v>
+        <v>272.561852</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48786,7 +48786,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW269">
-        <v>161.712106</v>
+        <v>162.712083</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48967,7 +48967,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW270">
-        <v>147.720729</v>
+        <v>148.720706</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -49148,7 +49148,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>127.695498</v>
+        <v>128.695475</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49329,7 +49329,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>271.562419</v>
+        <v>272.562396</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49513,7 +49513,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW273">
-        <v>142.69934</v>
+        <v>143.699317</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49691,7 +49691,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW274">
-        <v>190.9525</v>
+        <v>191.952477</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49872,7 +49872,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW275">
-        <v>267.783218</v>
+        <v>268.783194</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -50053,7 +50053,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW276">
-        <v>281.591227</v>
+        <v>282.591204</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50234,7 +50234,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW277">
-        <v>196.806748</v>
+        <v>197.806725</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50415,7 +50415,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>148.893356</v>
+        <v>149.893333</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50622,7 +50622,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW279">
-        <v>147.826412</v>
+        <v>148.826389</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50800,7 +50800,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW280">
-        <v>138.622419</v>
+        <v>139.622396</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50981,7 +50981,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW281">
-        <v>127.712269</v>
+        <v>128.712245</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -51162,7 +51162,7 @@
         <v>45924.33429111111</v>
       </c>
       <c r="AW282">
-        <v>176.9425</v>
+        <v>177.942477</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51343,7 +51343,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW283">
-        <v>121.655127</v>
+        <v>122.655104</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51521,7 +51521,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>13.886701</v>
+        <v>14.886678</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51699,7 +51699,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>268.949491</v>
+        <v>269.949468</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51877,7 +51877,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>280.706157</v>
+        <v>281.706134</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -52058,7 +52058,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW287">
-        <v>267.911887</v>
+        <v>268.911863</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52239,7 +52239,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>223.629884</v>
+        <v>224.629861</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52417,7 +52417,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW289">
-        <v>243.901817</v>
+        <v>244.901794</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52598,7 +52598,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>142.692998</v>
+        <v>143.692975</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52779,7 +52779,7 @@
         <v>45939.31507973379</v>
       </c>
       <c r="AW291">
-        <v>164.957303</v>
+        <v>165.95728</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52960,7 +52960,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW292">
-        <v>226.518981</v>
+        <v>227.518958</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -53138,7 +53138,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW293">
-        <v>281.911088</v>
+        <v>282.911065</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53316,7 +53316,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>287.501991</v>
+        <v>288.501968</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53497,7 +53497,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>209.894838</v>
+        <v>210.894815</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53678,7 +53678,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>16.875579</v>
+        <v>17.875556</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53856,7 +53856,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW297">
-        <v>254.569664</v>
+        <v>255.569641</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -54037,7 +54037,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW298">
-        <v>127.563727</v>
+        <v>128.563704</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54215,7 +54215,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>13.888912</v>
+        <v>14.888889</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54404,7 +54404,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>278.900868</v>
+        <v>279.900845</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54582,7 +54582,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW301">
-        <v>184.699178</v>
+        <v>185.699155</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54763,7 +54763,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW302">
-        <v>209.887708</v>
+        <v>210.887685</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54944,7 +54944,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>106.844896</v>
+        <v>107.844873</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -55125,7 +55125,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW304">
-        <v>183.612801</v>
+        <v>184.612778</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55303,7 +55303,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>293.94059</v>
+        <v>294.940567</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55489,7 +55489,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW306">
-        <v>219.660648</v>
+        <v>220.660625</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55670,7 +55670,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>138.723009</v>
+        <v>139.722986</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55851,7 +55851,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW308">
-        <v>86.937211</v>
+        <v>87.93718800000001</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -56032,7 +56032,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW309">
-        <v>112.810475</v>
+        <v>113.810451</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56213,7 +56213,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW310">
-        <v>183.613137</v>
+        <v>184.613113</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56394,7 +56394,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW311">
-        <v>183.611366</v>
+        <v>184.611343</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56575,7 +56575,7 @@
         <v>46111.63328278935</v>
       </c>
       <c r="AW312">
-        <v>2.638692</v>
+        <v>3.638669</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56753,7 +56753,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>287.502373</v>
+        <v>288.50235</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56931,7 +56931,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>56.958611</v>
+        <v>57.958588</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -57112,7 +57112,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW315">
-        <v>159.644433</v>
+        <v>160.64441</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57293,7 +57293,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW316">
-        <v>240.564063</v>
+        <v>241.564039</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57471,7 +57471,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW317">
-        <v>36.571065</v>
+        <v>37.571042</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57649,7 +57649,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW318">
-        <v>13.888148</v>
+        <v>14.888125</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57830,7 +57830,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW319">
-        <v>16.876042</v>
+        <v>17.876019</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -58008,7 +58008,7 @@
         <v>45873.70497479167</v>
       </c>
       <c r="AW320">
-        <v>240.566852</v>
+        <v>241.566829</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -58189,7 +58189,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>253.872095</v>
+        <v>254.872072</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58367,7 +58367,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>62.602002</v>
+        <v>63.601979</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58545,7 +58545,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW323">
-        <v>154.661725</v>
+        <v>155.661701</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58723,7 +58723,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW324">
-        <v>296.83544</v>
+        <v>297.835417</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58904,7 +58904,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW325">
-        <v>190.951644</v>
+        <v>191.95162</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -59085,7 +59085,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>142.696979</v>
+        <v>143.696956</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59266,7 +59266,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>275.609491</v>
+        <v>276.609468</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59447,7 +59447,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW328">
-        <v>112.812002</v>
+        <v>113.811979</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59628,7 +59628,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW329">
-        <v>71.814618</v>
+        <v>72.814595</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59809,7 +59809,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW330">
-        <v>230.668507</v>
+        <v>231.668484</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59987,7 +59987,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>223.57588</v>
+        <v>224.575856</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -60171,7 +60171,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>169.586597</v>
+        <v>170.586574</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60352,7 +60352,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW333">
-        <v>148.889572</v>
+        <v>149.889549</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60530,7 +60530,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW334">
-        <v>254.568993</v>
+        <v>255.56897</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60711,7 +60711,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>138.622847</v>
+        <v>139.622824</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60889,7 +60889,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>233.593472</v>
+        <v>234.593449</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -61070,7 +61070,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>79.57533599999999</v>
+        <v>80.57531299999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61251,7 +61251,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>225.824907</v>
+        <v>226.824884</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61427,7 +61427,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>159.643947</v>
+        <v>160.643924</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61608,7 +61608,7 @@
         <v>46111.63441997685</v>
       </c>
       <c r="AW340">
-        <v>2.637558</v>
+        <v>3.637535</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61789,7 +61789,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>16.876539</v>
+        <v>17.876516</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61967,7 +61967,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>301.693819</v>
+        <v>302.693796</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -62148,7 +62148,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW343">
-        <v>190.959005</v>
+        <v>191.958981</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62329,7 +62329,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW344">
-        <v>211.892789</v>
+        <v>212.892766</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62510,7 +62510,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>140.607025</v>
+        <v>141.607002</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62691,7 +62691,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>258.932164</v>
+        <v>259.932141</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62872,7 +62872,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>56.772894</v>
+        <v>57.77287</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -63053,7 +63053,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>37.945336</v>
+        <v>38.945313</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -63234,7 +63234,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>121.655741</v>
+        <v>122.655718</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63415,7 +63415,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW350">
-        <v>194.591065</v>
+        <v>195.591042</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63593,7 +63593,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW351">
-        <v>215.652546</v>
+        <v>216.652523</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63774,7 +63774,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW352">
-        <v>140.608252</v>
+        <v>141.608229</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63952,7 +63952,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW353">
-        <v>159.645058</v>
+        <v>160.645035</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -64133,7 +64133,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>267.912106</v>
+        <v>268.912083</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64314,7 +64314,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>196.806296</v>
+        <v>197.806273</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64495,7 +64495,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>184.94</v>
+        <v>185.939977</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64673,7 +64673,7 @@
         <v>45915.32586412037</v>
       </c>
       <c r="AW357">
-        <v>191.012512</v>
+        <v>192.012488</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64854,7 +64854,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW358">
-        <v>76.606447</v>
+        <v>77.606424</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -65035,7 +65035,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW359">
-        <v>126.727257</v>
+        <v>127.727234</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -65216,7 +65216,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW360">
-        <v>107.726192</v>
+        <v>108.726169</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65397,7 +65397,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW361">
-        <v>62.740509</v>
+        <v>63.740486</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65575,7 +65575,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW362">
-        <v>293.9389</v>
+        <v>294.938877</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65756,7 +65756,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW363">
-        <v>292.596725</v>
+        <v>293.596701</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65934,7 +65934,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>300.587569</v>
+        <v>301.587546</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -66115,7 +66115,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>190.96022</v>
+        <v>191.960197</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66293,7 +66293,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>110.707905</v>
+        <v>111.707882</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66474,7 +66474,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>271.56294</v>
+        <v>272.562917</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66655,7 +66655,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW368">
-        <v>159.892523</v>
+        <v>160.8925</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66836,7 +66836,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW369">
-        <v>161.857488</v>
+        <v>162.857465</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -67017,7 +67017,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW370">
-        <v>258.929479</v>
+        <v>259.929456</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -67195,7 +67195,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW371">
-        <v>287.501725</v>
+        <v>288.501701</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67373,7 +67373,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>177.529676</v>
+        <v>178.529653</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67551,7 +67551,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>261.722037</v>
+        <v>262.722014</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67732,7 +67732,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>209.889063</v>
+        <v>210.889039</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67913,7 +67913,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>16.875231</v>
+        <v>17.875208</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -68091,7 +68091,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW376">
-        <v>292.633333</v>
+        <v>293.63331</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -68269,7 +68269,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW377">
-        <v>296.727477</v>
+        <v>297.727454</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68450,7 +68450,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>140.613646</v>
+        <v>141.613623</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68628,7 +68628,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>293.939699</v>
+        <v>294.939676</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68806,7 +68806,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW380">
-        <v>301.68522</v>
+        <v>302.685197</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68984,7 +68984,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW381">
-        <v>271.563461</v>
+        <v>272.563438</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -69162,7 +69162,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>149.621597</v>
+        <v>150.621574</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69340,7 +69340,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>287.500255</v>
+        <v>288.500231</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69521,7 +69521,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW384">
-        <v>245.698762</v>
+        <v>246.698738</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69699,7 +69699,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW385">
-        <v>254.566134</v>
+        <v>255.566111</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69880,7 +69880,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW386">
-        <v>112.810926</v>
+        <v>113.810903</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -70061,7 +70061,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW387">
-        <v>161.856806</v>
+        <v>162.856782</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -70242,7 +70242,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW388">
-        <v>106.843738</v>
+        <v>107.843715</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70415,7 +70415,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>208.592292</v>
+        <v>209.592269</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70588,7 +70588,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>208.591829</v>
+        <v>209.591806</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70769,7 +70769,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>112.809352</v>
+        <v>113.809329</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70950,7 +70950,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW392">
-        <v>140.607234</v>
+        <v>141.607211</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -71131,7 +71131,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW393">
-        <v>127.709873</v>
+        <v>128.70985</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>297.834282</v>
+        <v>300.834282</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>140.950278</v>
+        <v>143.950278</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>128.708322</v>
+        <v>131.708322</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>252.779942</v>
+        <v>255.779942</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1560,7 +1560,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW6">
-        <v>63.934039</v>
+        <v>66.934039</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW7">
-        <v>255.566493</v>
+        <v>258.566493</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1919,7 +1919,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW8">
-        <v>139.62456</v>
+        <v>142.62456</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2097,7 +2097,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW9">
-        <v>290.603993</v>
+        <v>293.603993</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2281,7 +2281,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW10">
-        <v>239.64463</v>
+        <v>242.64463</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2462,7 +2462,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW11">
-        <v>224.630289</v>
+        <v>227.630289</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW12">
-        <v>223.727917</v>
+        <v>226.727917</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2821,7 +2821,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW13">
-        <v>259.92897</v>
+        <v>262.92897</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2999,7 +2999,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW14">
-        <v>302.687986</v>
+        <v>305.687986</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3177,7 +3177,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW15">
-        <v>288.503137</v>
+        <v>291.503137</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3353,7 +3353,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW16">
-        <v>121.815046</v>
+        <v>124.815046</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3534,7 +3534,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>139.578785</v>
+        <v>142.578785</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW18">
-        <v>257.631667</v>
+        <v>260.631667</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW19">
-        <v>219.60456</v>
+        <v>222.60456</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW20">
-        <v>227.515799</v>
+        <v>230.515799</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>140.950706</v>
+        <v>143.950706</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>57.952731</v>
+        <v>60.952731</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>56.697928</v>
+        <v>59.697928</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>63.931458</v>
+        <v>66.93145800000001</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>252.77941</v>
+        <v>255.77941</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>139.723623</v>
+        <v>142.723623</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>37.577778</v>
+        <v>40.577778</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>87.934433</v>
+        <v>90.934433</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5689,7 +5689,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW29">
-        <v>209.59213</v>
+        <v>212.59213</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW30">
-        <v>288.508646</v>
+        <v>291.508646</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>218.685613</v>
+        <v>221.685613</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>148.82566</v>
+        <v>151.82566</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>290.5989</v>
+        <v>293.5989</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW34">
-        <v>226.827616</v>
+        <v>229.827616</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW35">
-        <v>147.60706</v>
+        <v>150.60706</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>135.725405</v>
+        <v>138.725405</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7139,7 +7139,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW37">
-        <v>262.659155</v>
+        <v>265.659155</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW38">
-        <v>254.873414</v>
+        <v>257.873414</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7495,7 +7495,7 @@
         <v>46100.38240289352</v>
       </c>
       <c r="AW39">
-        <v>13.040197</v>
+        <v>16.040197</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7676,7 +7676,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>149.891053</v>
+        <v>152.891053</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7857,7 +7857,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>128.705301</v>
+        <v>131.705301</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8038,7 +8038,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>87.695035</v>
+        <v>90.695035</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8219,7 +8219,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW43">
-        <v>36.718715</v>
+        <v>39.718715</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8400,7 +8400,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>77.618681</v>
+        <v>80.618681</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8578,7 +8578,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW45">
-        <v>57.954722</v>
+        <v>60.954722</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8759,7 +8759,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>211.910417</v>
+        <v>214.910417</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8940,7 +8940,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>226.827002</v>
+        <v>229.827002</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9118,7 +9118,7 @@
         <v>46106.37582024305</v>
       </c>
       <c r="AW48">
-        <v>8.896134</v>
+        <v>11.896134</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9299,7 +9299,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW49">
-        <v>177.942558</v>
+        <v>180.942558</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9480,7 +9480,7 @@
         <v>45924.33459813657</v>
       </c>
       <c r="AW50">
-        <v>177.943773</v>
+        <v>180.943773</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9648,7 +9648,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>35.592813</v>
+        <v>38.592813</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9829,7 +9829,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW52">
-        <v>268.783391</v>
+        <v>271.783391</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -10010,7 +10010,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW53">
-        <v>254.874398</v>
+        <v>257.874398</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10188,7 +10188,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW54">
-        <v>255.567905</v>
+        <v>258.567905</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10369,7 +10369,7 @@
         <v>45946.65447922454</v>
       </c>
       <c r="AW55">
-        <v>162.710521</v>
+        <v>165.710521</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10547,7 +10547,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>35.592072</v>
+        <v>38.592072</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10731,7 +10731,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>246.540926</v>
+        <v>249.540926</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10909,7 +10909,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>14.889248</v>
+        <v>17.889248</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11087,7 +11087,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>293.645579</v>
+        <v>296.645579</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11265,7 +11265,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>283.694398</v>
+        <v>286.694398</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11446,7 +11446,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>113.796944</v>
+        <v>116.796944</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11624,7 +11624,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>78.68822900000001</v>
+        <v>81.68822900000001</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11802,7 +11802,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>255.567072</v>
+        <v>258.567072</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11983,7 +11983,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW64">
-        <v>129.514803</v>
+        <v>132.514803</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12164,7 +12164,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW65">
-        <v>149.895162</v>
+        <v>152.895162</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12345,7 +12345,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>191.568646</v>
+        <v>194.568646</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12523,7 +12523,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>258.822755</v>
+        <v>261.822755</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12701,7 +12701,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>219.6239</v>
+        <v>222.6239</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12885,7 +12885,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>139.623773</v>
+        <v>142.623773</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13063,7 +13063,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>77.598322</v>
+        <v>80.598322</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13241,7 +13241,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>294.938715</v>
+        <v>297.938715</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13419,7 +13419,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>297.831609</v>
+        <v>300.831609</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13600,7 +13600,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW73">
-        <v>17.879421</v>
+        <v>20.879421</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13781,7 +13781,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW74">
-        <v>155.716933</v>
+        <v>158.716933</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13962,7 +13962,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW75">
-        <v>212.684375</v>
+        <v>215.684375</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14140,7 +14140,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW76">
-        <v>255.582847</v>
+        <v>258.582847</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14321,7 +14321,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW77">
-        <v>112.542176</v>
+        <v>115.542176</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14502,7 +14502,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW78">
-        <v>57.773565</v>
+        <v>60.773565</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14683,7 +14683,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW79">
-        <v>107.84463</v>
+        <v>110.84463</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14861,7 +14861,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW80">
-        <v>148.720972</v>
+        <v>151.720972</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15042,7 +15042,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW81">
-        <v>141.607488</v>
+        <v>144.607488</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15220,7 +15220,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>206.680498</v>
+        <v>209.680498</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15406,7 +15406,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW83">
-        <v>269.654282</v>
+        <v>272.654282</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15587,7 +15587,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>17.875046</v>
+        <v>20.875046</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15768,7 +15768,7 @@
         <v>45890.42079241898</v>
       </c>
       <c r="AW85">
-        <v>210.889144</v>
+        <v>213.889144</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15949,7 +15949,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>128.695648</v>
+        <v>131.695648</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16130,7 +16130,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>283.697789</v>
+        <v>286.697789</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16308,7 +16308,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW88">
-        <v>162.858912</v>
+        <v>165.858912</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16489,7 +16489,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW89">
-        <v>147.605718</v>
+        <v>150.605718</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16670,7 +16670,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>157.553669</v>
+        <v>160.553669</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16851,7 +16851,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW91">
-        <v>177.943553</v>
+        <v>180.943553</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -17032,7 +17032,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW92">
-        <v>191.561493</v>
+        <v>194.561493</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17213,7 +17213,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW93">
-        <v>210.887431</v>
+        <v>213.887431</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17399,7 +17399,7 @@
         <v>45873.70399680555</v>
       </c>
       <c r="AW94">
-        <v>241.567523</v>
+        <v>244.567523</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17577,7 +17577,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW95">
-        <v>262.723113</v>
+        <v>265.723113</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17755,7 +17755,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW96">
-        <v>293.597859</v>
+        <v>296.597859</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17936,7 +17936,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>113.806308</v>
+        <v>116.806308</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -18117,7 +18117,7 @@
         <v>46111.63374820602</v>
       </c>
       <c r="AW98">
-        <v>3.638206</v>
+        <v>6.638206</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18298,7 +18298,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>247.570035</v>
+        <v>250.570035</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18476,7 +18476,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>288.502755</v>
+        <v>291.502755</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18654,7 +18654,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>197.943183</v>
+        <v>200.943183</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18832,7 +18832,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>255.566296</v>
+        <v>258.566296</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -19013,7 +19013,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>87.938056</v>
+        <v>90.938056</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19191,7 +19191,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>294.939109</v>
+        <v>297.939109</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19369,7 +19369,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>206.553773</v>
+        <v>209.553773</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19550,7 +19550,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>128.708877</v>
+        <v>131.708877</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19731,7 +19731,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>224.622951</v>
+        <v>227.622951</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19912,7 +19912,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>216.698808</v>
+        <v>219.698808</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -20090,7 +20090,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>56.722593</v>
+        <v>59.722593</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20271,7 +20271,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW110">
-        <v>246.685706</v>
+        <v>249.685706</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20449,7 +20449,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW111">
-        <v>290.688715</v>
+        <v>293.688715</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20630,7 +20630,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW112">
-        <v>127.723773</v>
+        <v>130.723773</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20811,7 +20811,7 @@
         <v>45875.68270515047</v>
       </c>
       <c r="AW113">
-        <v>185.944456</v>
+        <v>188.944456</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20992,7 +20992,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>245.122581</v>
+        <v>248.122581</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21173,7 +21173,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW115">
-        <v>128.694329</v>
+        <v>131.694329</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21354,7 +21354,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW116">
-        <v>155.698414</v>
+        <v>158.698414</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21535,7 +21535,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW117">
-        <v>206.609722</v>
+        <v>209.609722</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21716,7 +21716,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW118">
-        <v>253.7661</v>
+        <v>256.7661</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21897,7 +21897,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW119">
-        <v>64.72396999999999</v>
+        <v>67.72396999999999</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -22078,7 +22078,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW120">
-        <v>87.936678</v>
+        <v>90.936678</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22256,7 +22256,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>297.834572</v>
+        <v>300.834572</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22437,7 +22437,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW122">
-        <v>157.544306</v>
+        <v>160.544306</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22618,7 +22618,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW123">
-        <v>139.723137</v>
+        <v>142.723137</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22796,7 +22796,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW124">
-        <v>76.588542</v>
+        <v>79.588542</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22977,7 +22977,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW125">
-        <v>293.595995</v>
+        <v>296.595995</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23155,7 +23155,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW126">
-        <v>283.645451</v>
+        <v>286.645451</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23336,7 +23336,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW127">
-        <v>185.942859</v>
+        <v>188.942859</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23520,7 +23520,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW128">
-        <v>246.705718</v>
+        <v>249.705718</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23698,7 +23698,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW129">
-        <v>224.576157</v>
+        <v>227.576157</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23879,7 +23879,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW130">
-        <v>272.564664</v>
+        <v>275.564664</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -24060,7 +24060,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>28.596667</v>
+        <v>31.596667</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24241,7 +24241,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>210.885278</v>
+        <v>213.885278</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24419,7 +24419,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>288.503368</v>
+        <v>291.503368</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24600,7 +24600,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>128.695752</v>
+        <v>131.695752</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24781,7 +24781,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>112.542882</v>
+        <v>115.542882</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24954,7 +24954,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>283.597963</v>
+        <v>286.597963</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25135,7 +25135,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>113.798391</v>
+        <v>116.798391</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25316,7 +25316,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>42.675081</v>
+        <v>45.675081</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25497,7 +25497,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW139">
-        <v>191.956944</v>
+        <v>194.956944</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25678,7 +25678,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW140">
-        <v>197.805532</v>
+        <v>200.805532</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25856,7 +25856,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>301.647986</v>
+        <v>304.647986</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -26034,7 +26034,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>227.488345</v>
+        <v>230.488345</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26215,7 +26215,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>185.942315</v>
+        <v>188.942315</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26396,7 +26396,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW144">
-        <v>55.835752</v>
+        <v>58.835752</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26572,7 +26572,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW145">
-        <v>121.814815</v>
+        <v>124.814815</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26750,7 +26750,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>283.648657</v>
+        <v>286.648657</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26928,7 +26928,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>288.505023</v>
+        <v>291.505023</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27106,7 +27106,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>14.884919</v>
+        <v>17.884919</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27287,7 +27287,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>224.685648</v>
+        <v>227.685648</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27465,7 +27465,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>258.822326</v>
+        <v>261.822326</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27646,7 +27646,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW151">
-        <v>218.686644</v>
+        <v>221.686644</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27824,7 +27824,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW152">
-        <v>255.566794</v>
+        <v>258.566794</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -28005,7 +28005,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>77.604826</v>
+        <v>80.604826</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28183,7 +28183,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW154">
-        <v>57.951863</v>
+        <v>60.951863</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28364,7 +28364,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW155">
-        <v>190.818819</v>
+        <v>193.818819</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28545,7 +28545,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW156">
-        <v>190.618877</v>
+        <v>193.618877</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28729,7 +28729,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>113.805938</v>
+        <v>116.805938</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28918,7 +28918,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW158">
-        <v>202.582245</v>
+        <v>205.582245</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -29096,7 +29096,7 @@
         <v>45898.61987270833</v>
       </c>
       <c r="AW159">
-        <v>212.517014</v>
+        <v>215.517014</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29277,7 +29277,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW160">
-        <v>129.515463</v>
+        <v>132.515463</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29458,7 +29458,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW161">
-        <v>70.628484</v>
+        <v>73.628484</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29626,7 +29626,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW162">
-        <v>232.652419</v>
+        <v>235.652419</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29807,7 +29807,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW163">
-        <v>185.94162</v>
+        <v>188.94162</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29988,7 +29988,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW164">
-        <v>210.890891</v>
+        <v>213.890891</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30169,7 +30169,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW165">
-        <v>134.538414</v>
+        <v>137.538414</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30350,7 +30350,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW166">
-        <v>254.874201</v>
+        <v>257.874201</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30528,7 +30528,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>57.956308</v>
+        <v>60.956308</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30706,7 +30706,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>244.897014</v>
+        <v>247.897014</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30887,7 +30887,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>160.643461</v>
+        <v>163.643461</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -31065,7 +31065,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>128.692674</v>
+        <v>131.692674</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31246,7 +31246,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>28.597697</v>
+        <v>31.597697</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31424,7 +31424,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>293.598796</v>
+        <v>296.598796</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31605,7 +31605,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>269.949097</v>
+        <v>272.949097</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31783,7 +31783,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>78.679653</v>
+        <v>81.679653</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31961,7 +31961,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>51.724954</v>
+        <v>54.724954</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32134,7 +32134,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>209.591921</v>
+        <v>212.591921</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32315,7 +32315,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>87.936076</v>
+        <v>90.936076</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32493,7 +32493,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>37.571563</v>
+        <v>40.571563</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32671,7 +32671,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW179">
-        <v>297.834965</v>
+        <v>300.834965</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32849,7 +32849,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW180">
-        <v>244.901956</v>
+        <v>247.901956</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -33027,7 +33027,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>219.603032</v>
+        <v>222.603032</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33208,7 +33208,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW182">
-        <v>17.878947</v>
+        <v>20.878947</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33386,7 +33386,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW183">
-        <v>290.598345</v>
+        <v>293.598345</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33564,7 +33564,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW184">
-        <v>281.705185</v>
+        <v>284.705185</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33745,7 +33745,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>148.72081</v>
+        <v>151.72081</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33923,7 +33923,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW186">
-        <v>219.623785</v>
+        <v>222.623785</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34101,7 +34101,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>290.597986</v>
+        <v>293.597986</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34282,7 +34282,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>246.701528</v>
+        <v>249.701528</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34463,7 +34463,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW189">
-        <v>224.515938</v>
+        <v>227.515938</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34644,7 +34644,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW190">
-        <v>191.956227</v>
+        <v>194.956227</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34825,7 +34825,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>135.669282</v>
+        <v>138.669282</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -35003,7 +35003,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>57.954282</v>
+        <v>60.954282</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35181,7 +35181,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>297.842535</v>
+        <v>300.842535</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35362,7 +35362,7 @@
         <v>45905.68518516204</v>
       </c>
       <c r="AW194">
-        <v>191.959769</v>
+        <v>194.959769</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35546,7 +35546,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW195">
-        <v>246.705347</v>
+        <v>249.705347</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35727,7 +35727,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW196">
-        <v>113.797708</v>
+        <v>116.797708</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35908,7 +35908,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW197">
-        <v>210.888403</v>
+        <v>213.888403</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -36076,7 +36076,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW198">
-        <v>232.664606</v>
+        <v>235.664606</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36254,7 +36254,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW199">
-        <v>184.681644</v>
+        <v>187.681644</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36435,7 +36435,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW200">
-        <v>210.894248</v>
+        <v>213.894248</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36613,7 +36613,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW201">
-        <v>290.688993</v>
+        <v>293.688993</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36791,7 +36791,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW202">
-        <v>304.909826</v>
+        <v>307.909826</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36969,7 +36969,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW203">
-        <v>216.607488</v>
+        <v>219.607488</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37150,7 +37150,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW204">
-        <v>277.925532</v>
+        <v>280.925532</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37328,7 +37328,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW205">
-        <v>288.503935</v>
+        <v>291.503935</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37506,7 +37506,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>41.60419</v>
+        <v>44.60419</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37684,7 +37684,7 @@
         <v>45880.4943486574</v>
       </c>
       <c r="AW207">
-        <v>220.530926</v>
+        <v>223.530926</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37865,7 +37865,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW208">
-        <v>272.561505</v>
+        <v>275.561505</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -38043,7 +38043,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>78.685266</v>
+        <v>81.685266</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38221,7 +38221,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>293.57213</v>
+        <v>296.57213</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38399,7 +38399,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>290.688449</v>
+        <v>293.688449</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38577,7 +38577,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>24.541829</v>
+        <v>27.541829</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38755,7 +38755,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>289.610671</v>
+        <v>292.610671</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38933,7 +38933,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW214">
-        <v>303.733646</v>
+        <v>306.733646</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39111,7 +39111,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW215">
-        <v>301.593252</v>
+        <v>304.593252</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39289,7 +39289,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>293.646829</v>
+        <v>296.646829</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39467,7 +39467,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>255.568519</v>
+        <v>258.568519</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39648,7 +39648,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>255.586493</v>
+        <v>258.586493</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39829,7 +39829,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>160.911528</v>
+        <v>163.911528</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -40010,7 +40010,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>17.703947</v>
+        <v>20.703947</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40191,7 +40191,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW221">
-        <v>63.934757</v>
+        <v>66.934757</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40372,7 +40372,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW222">
-        <v>63.933079</v>
+        <v>66.93307900000001</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40553,7 +40553,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW223">
-        <v>135.693438</v>
+        <v>138.693438</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40734,7 +40734,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW224">
-        <v>128.711586</v>
+        <v>131.711586</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40912,7 +40912,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW225">
-        <v>293.587894</v>
+        <v>296.587894</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -41090,7 +41090,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW226">
-        <v>302.68897</v>
+        <v>305.68897</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41268,7 +41268,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW227">
-        <v>302.684838</v>
+        <v>305.684838</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41449,7 +41449,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW228">
-        <v>203.639144</v>
+        <v>206.639144</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41630,7 +41630,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW229">
-        <v>262.659074</v>
+        <v>265.659074</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41811,7 +41811,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW230">
-        <v>210.8936</v>
+        <v>213.8936</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41992,7 +41992,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW231">
-        <v>219.669988</v>
+        <v>222.669988</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42170,7 +42170,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW232">
-        <v>279.900382</v>
+        <v>282.900382</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42351,7 +42351,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW233">
-        <v>191.958079</v>
+        <v>194.958079</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42535,7 +42535,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW234">
-        <v>211.910185</v>
+        <v>214.910185</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42713,7 +42713,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>142.886944</v>
+        <v>145.886944</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42894,7 +42894,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>28.595556</v>
+        <v>31.595556</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -43075,7 +43075,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW237">
-        <v>113.798935</v>
+        <v>116.798935</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43256,7 +43256,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW238">
-        <v>254.874734</v>
+        <v>257.874734</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43437,7 +43437,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW239">
-        <v>210.753194</v>
+        <v>213.753194</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43615,7 +43615,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>78.6786</v>
+        <v>81.6786</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43796,7 +43796,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>129.515961</v>
+        <v>132.515961</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43977,7 +43977,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>244.900729</v>
+        <v>247.900729</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44161,7 +44161,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW243">
-        <v>219.601377</v>
+        <v>222.601377</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44339,7 +44339,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>255.567303</v>
+        <v>258.567303</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44512,7 +44512,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW245">
-        <v>290.573229</v>
+        <v>293.573229</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44693,7 +44693,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>162.855961</v>
+        <v>165.855961</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44874,7 +44874,7 @@
         <v>45923.56720940972</v>
       </c>
       <c r="AW247">
-        <v>191.660845</v>
+        <v>194.660845</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -45055,7 +45055,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>185.940741</v>
+        <v>188.940741</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45236,7 +45236,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>36.719549</v>
+        <v>39.719549</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45414,7 +45414,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>255.567708</v>
+        <v>258.567708</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45595,7 +45595,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>226.828241</v>
+        <v>229.828241</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45776,7 +45776,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>63.678426</v>
+        <v>66.678426</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45957,7 +45957,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>275.720903</v>
+        <v>278.720903</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46138,7 +46138,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>64.72438699999999</v>
+        <v>67.72438699999999</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46319,7 +46319,7 @@
         <v>46111.70316528935</v>
       </c>
       <c r="AW255">
-        <v>3.568785</v>
+        <v>6.568785</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46456,7 +46456,7 @@
         <v>46113.36897872685</v>
       </c>
       <c r="AQ256">
-        <v>1.902975</v>
+        <v>4.902975</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46637,7 +46637,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>87.93535900000001</v>
+        <v>90.93535900000001</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46818,7 +46818,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW258">
-        <v>185.948333</v>
+        <v>188.948333</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46999,7 +46999,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW259">
-        <v>254.835313</v>
+        <v>257.835313</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -47177,7 +47177,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW260">
-        <v>185.950486</v>
+        <v>188.950486</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47355,7 +47355,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>160.532882</v>
+        <v>163.532882</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47531,7 +47531,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>252.779572</v>
+        <v>255.779572</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47709,7 +47709,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW263">
-        <v>111.707963</v>
+        <v>114.707963</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47887,7 +47887,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW264">
-        <v>176.939051</v>
+        <v>179.939051</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -48068,7 +48068,7 @@
         <v>45946.65440010416</v>
       </c>
       <c r="AW265">
-        <v>162.711273</v>
+        <v>165.711273</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48246,7 +48246,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW266">
-        <v>293.646088</v>
+        <v>296.646088</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48427,7 +48427,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW267">
-        <v>283.698009</v>
+        <v>286.698009</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48608,7 +48608,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>272.561852</v>
+        <v>275.561852</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48786,7 +48786,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW269">
-        <v>162.712083</v>
+        <v>165.712083</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48967,7 +48967,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW270">
-        <v>148.720706</v>
+        <v>151.720706</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -49148,7 +49148,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>128.695475</v>
+        <v>131.695475</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49329,7 +49329,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>272.562396</v>
+        <v>275.562396</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49513,7 +49513,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW273">
-        <v>143.699317</v>
+        <v>146.699317</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49691,7 +49691,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW274">
-        <v>191.952477</v>
+        <v>194.952477</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49872,7 +49872,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW275">
-        <v>268.783194</v>
+        <v>271.783194</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -50053,7 +50053,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW276">
-        <v>282.591204</v>
+        <v>285.591204</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50234,7 +50234,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW277">
-        <v>197.806725</v>
+        <v>200.806725</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50415,7 +50415,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>149.893333</v>
+        <v>152.893333</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50622,7 +50622,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW279">
-        <v>148.826389</v>
+        <v>151.826389</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50800,7 +50800,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW280">
-        <v>139.622396</v>
+        <v>142.622396</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50981,7 +50981,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW281">
-        <v>128.712245</v>
+        <v>131.712245</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -51162,7 +51162,7 @@
         <v>45924.33429111111</v>
       </c>
       <c r="AW282">
-        <v>177.942477</v>
+        <v>180.942477</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51343,7 +51343,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW283">
-        <v>122.655104</v>
+        <v>125.655104</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51521,7 +51521,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>14.886678</v>
+        <v>17.886678</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51699,7 +51699,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>269.949468</v>
+        <v>272.949468</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51877,7 +51877,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>281.706134</v>
+        <v>284.706134</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -52058,7 +52058,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW287">
-        <v>268.911863</v>
+        <v>271.911863</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52239,7 +52239,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>224.629861</v>
+        <v>227.629861</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52417,7 +52417,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW289">
-        <v>244.901794</v>
+        <v>247.901794</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52598,7 +52598,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>143.692975</v>
+        <v>146.692975</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52779,7 +52779,7 @@
         <v>45939.31507973379</v>
       </c>
       <c r="AW291">
-        <v>165.95728</v>
+        <v>168.95728</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52960,7 +52960,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW292">
-        <v>227.518958</v>
+        <v>230.518958</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -53138,7 +53138,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW293">
-        <v>282.911065</v>
+        <v>285.911065</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53316,7 +53316,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>288.501968</v>
+        <v>291.501968</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53497,7 +53497,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>210.894815</v>
+        <v>213.894815</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53678,7 +53678,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>17.875556</v>
+        <v>20.875556</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53856,7 +53856,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW297">
-        <v>255.569641</v>
+        <v>258.569641</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -54037,7 +54037,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW298">
-        <v>128.563704</v>
+        <v>131.563704</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54215,7 +54215,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>14.888889</v>
+        <v>17.888889</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54404,7 +54404,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>279.900845</v>
+        <v>282.900845</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54582,7 +54582,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW301">
-        <v>185.699155</v>
+        <v>188.699155</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54763,7 +54763,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW302">
-        <v>210.887685</v>
+        <v>213.887685</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54944,7 +54944,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>107.844873</v>
+        <v>110.844873</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -55125,7 +55125,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW304">
-        <v>184.612778</v>
+        <v>187.612778</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55303,7 +55303,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>294.940567</v>
+        <v>297.940567</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55489,7 +55489,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW306">
-        <v>220.660625</v>
+        <v>223.660625</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55670,7 +55670,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>139.722986</v>
+        <v>142.722986</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55851,7 +55851,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW308">
-        <v>87.93718800000001</v>
+        <v>90.93718800000001</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -56032,7 +56032,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW309">
-        <v>113.810451</v>
+        <v>116.810451</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56213,7 +56213,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW310">
-        <v>184.613113</v>
+        <v>187.613113</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56394,7 +56394,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW311">
-        <v>184.611343</v>
+        <v>187.611343</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56575,7 +56575,7 @@
         <v>46111.63328278935</v>
       </c>
       <c r="AW312">
-        <v>3.638669</v>
+        <v>6.638669</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56753,7 +56753,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>288.50235</v>
+        <v>291.50235</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56931,7 +56931,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>57.958588</v>
+        <v>60.958588</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -57112,7 +57112,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW315">
-        <v>160.64441</v>
+        <v>163.64441</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57293,7 +57293,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW316">
-        <v>241.564039</v>
+        <v>244.564039</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57471,7 +57471,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW317">
-        <v>37.571042</v>
+        <v>40.571042</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57649,7 +57649,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW318">
-        <v>14.888125</v>
+        <v>17.888125</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57830,7 +57830,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW319">
-        <v>17.876019</v>
+        <v>20.876019</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -58008,7 +58008,7 @@
         <v>45873.70497479167</v>
       </c>
       <c r="AW320">
-        <v>241.566829</v>
+        <v>244.566829</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -58189,7 +58189,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>254.872072</v>
+        <v>257.872072</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58367,7 +58367,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>63.601979</v>
+        <v>66.601979</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58545,7 +58545,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW323">
-        <v>155.661701</v>
+        <v>158.661701</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58723,7 +58723,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW324">
-        <v>297.835417</v>
+        <v>300.835417</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58904,7 +58904,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW325">
-        <v>191.95162</v>
+        <v>194.95162</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -59085,7 +59085,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>143.696956</v>
+        <v>146.696956</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59266,7 +59266,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>276.609468</v>
+        <v>279.609468</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59447,7 +59447,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW328">
-        <v>113.811979</v>
+        <v>116.811979</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59628,7 +59628,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW329">
-        <v>72.814595</v>
+        <v>75.814595</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59809,7 +59809,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW330">
-        <v>231.668484</v>
+        <v>234.668484</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59987,7 +59987,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>224.575856</v>
+        <v>227.575856</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -60171,7 +60171,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>170.586574</v>
+        <v>173.586574</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60352,7 +60352,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW333">
-        <v>149.889549</v>
+        <v>152.889549</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60530,7 +60530,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW334">
-        <v>255.56897</v>
+        <v>258.56897</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60711,7 +60711,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>139.622824</v>
+        <v>142.622824</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60889,7 +60889,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>234.593449</v>
+        <v>237.593449</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -61070,7 +61070,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>80.57531299999999</v>
+        <v>83.57531299999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61251,7 +61251,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>226.824884</v>
+        <v>229.824884</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61427,7 +61427,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>160.643924</v>
+        <v>163.643924</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61608,7 +61608,7 @@
         <v>46111.63441997685</v>
       </c>
       <c r="AW340">
-        <v>3.637535</v>
+        <v>6.637535</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61789,7 +61789,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>17.876516</v>
+        <v>20.876516</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61967,7 +61967,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>302.693796</v>
+        <v>305.693796</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -62148,7 +62148,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW343">
-        <v>191.958981</v>
+        <v>194.958981</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62329,7 +62329,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW344">
-        <v>212.892766</v>
+        <v>215.892766</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62510,7 +62510,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>141.607002</v>
+        <v>144.607002</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62691,7 +62691,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>259.932141</v>
+        <v>262.932141</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62872,7 +62872,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>57.77287</v>
+        <v>60.77287</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -63053,7 +63053,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>38.945313</v>
+        <v>41.945313</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -63234,7 +63234,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>122.655718</v>
+        <v>125.655718</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63415,7 +63415,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW350">
-        <v>195.591042</v>
+        <v>198.591042</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63593,7 +63593,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW351">
-        <v>216.652523</v>
+        <v>219.652523</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63774,7 +63774,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW352">
-        <v>141.608229</v>
+        <v>144.608229</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63952,7 +63952,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW353">
-        <v>160.645035</v>
+        <v>163.645035</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -64133,7 +64133,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>268.912083</v>
+        <v>271.912083</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64314,7 +64314,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>197.806273</v>
+        <v>200.806273</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64495,7 +64495,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>185.939977</v>
+        <v>188.939977</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64673,7 +64673,7 @@
         <v>45915.32586412037</v>
       </c>
       <c r="AW357">
-        <v>192.012488</v>
+        <v>195.012488</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64854,7 +64854,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW358">
-        <v>77.606424</v>
+        <v>80.606424</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -65035,7 +65035,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW359">
-        <v>127.727234</v>
+        <v>130.727234</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -65216,7 +65216,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW360">
-        <v>108.726169</v>
+        <v>111.726169</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65397,7 +65397,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW361">
-        <v>63.740486</v>
+        <v>66.740486</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65575,7 +65575,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW362">
-        <v>294.938877</v>
+        <v>297.938877</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65756,7 +65756,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW363">
-        <v>293.596701</v>
+        <v>296.596701</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65934,7 +65934,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>301.587546</v>
+        <v>304.587546</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -66115,7 +66115,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>191.960197</v>
+        <v>194.960197</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66293,7 +66293,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>111.707882</v>
+        <v>114.707882</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66474,7 +66474,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>272.562917</v>
+        <v>275.562917</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66655,7 +66655,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW368">
-        <v>160.8925</v>
+        <v>163.8925</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66836,7 +66836,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW369">
-        <v>162.857465</v>
+        <v>165.857465</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -67017,7 +67017,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW370">
-        <v>259.929456</v>
+        <v>262.929456</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -67195,7 +67195,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW371">
-        <v>288.501701</v>
+        <v>291.501701</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67373,7 +67373,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>178.529653</v>
+        <v>181.529653</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67551,7 +67551,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>262.722014</v>
+        <v>265.722014</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67732,7 +67732,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>210.889039</v>
+        <v>213.889039</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67913,7 +67913,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>17.875208</v>
+        <v>20.875208</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -68091,7 +68091,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW376">
-        <v>293.63331</v>
+        <v>296.63331</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -68269,7 +68269,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW377">
-        <v>297.727454</v>
+        <v>300.727454</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68450,7 +68450,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>141.613623</v>
+        <v>144.613623</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68628,7 +68628,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>294.939676</v>
+        <v>297.939676</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68806,7 +68806,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW380">
-        <v>302.685197</v>
+        <v>305.685197</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68984,7 +68984,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW381">
-        <v>272.563438</v>
+        <v>275.563438</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -69162,7 +69162,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>150.621574</v>
+        <v>153.621574</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69340,7 +69340,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>288.500231</v>
+        <v>291.500231</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69521,7 +69521,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW384">
-        <v>246.698738</v>
+        <v>249.698738</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69699,7 +69699,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW385">
-        <v>255.566111</v>
+        <v>258.566111</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69880,7 +69880,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW386">
-        <v>113.810903</v>
+        <v>116.810903</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -70061,7 +70061,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW387">
-        <v>162.856782</v>
+        <v>165.856782</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -70242,7 +70242,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW388">
-        <v>107.843715</v>
+        <v>110.843715</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70415,7 +70415,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>209.592269</v>
+        <v>212.592269</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70588,7 +70588,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>209.591806</v>
+        <v>212.591806</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70769,7 +70769,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>113.809329</v>
+        <v>116.809329</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70950,7 +70950,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW392">
-        <v>141.607211</v>
+        <v>144.607211</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -71131,7 +71131,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW393">
-        <v>128.70985</v>
+        <v>131.70985</v>
       </c>
     </row>
   </sheetData>

--- a/Relatório Construção.xlsx
+++ b/Relatório Construção.xlsx
@@ -844,7 +844,7 @@
         <v>45817.43766342592</v>
       </c>
       <c r="AW2">
-        <v>300.834282</v>
+        <v>301.834306</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>45974.32166768519</v>
       </c>
       <c r="AW3">
-        <v>143.950278</v>
+        <v>144.950301</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1203,7 +1203,7 @@
         <v>45986.56362434028</v>
       </c>
       <c r="AW4">
-        <v>131.708322</v>
+        <v>132.708345</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1379,7 +1379,7 @@
         <v>45862.49200517361</v>
       </c>
       <c r="AW5">
-        <v>255.779942</v>
+        <v>256.779965</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1560,7 +1560,7 @@
         <v>46051.33790607639</v>
       </c>
       <c r="AW6">
-        <v>66.934039</v>
+        <v>67.93406299999999</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>45859.70545487269</v>
       </c>
       <c r="AW7">
-        <v>258.566493</v>
+        <v>259.566516</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1919,7 +1919,7 @@
         <v>45975.64739481482</v>
       </c>
       <c r="AW8">
-        <v>142.62456</v>
+        <v>143.624583</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2097,7 +2097,7 @@
         <v>45824.66795922453</v>
       </c>
       <c r="AW9">
-        <v>293.603993</v>
+        <v>294.604016</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2281,7 +2281,7 @@
         <v>45875.62732515046</v>
       </c>
       <c r="AW10">
-        <v>242.64463</v>
+        <v>243.644653</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2462,7 +2462,7 @@
         <v>45890.64166144676</v>
       </c>
       <c r="AW11">
-        <v>227.630289</v>
+        <v>228.630313</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>45891.54403121528</v>
       </c>
       <c r="AW12">
-        <v>226.727917</v>
+        <v>227.72794</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2821,7 +2821,7 @@
         <v>45855.34298560185</v>
       </c>
       <c r="AW13">
-        <v>262.92897</v>
+        <v>263.928993</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2999,7 +2999,7 @@
         <v>45812.58396733797</v>
       </c>
       <c r="AW14">
-        <v>305.687986</v>
+        <v>306.688009</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3177,7 +3177,7 @@
         <v>45826.76881550926</v>
       </c>
       <c r="AW15">
-        <v>291.503137</v>
+        <v>292.50316</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3353,7 +3353,7 @@
         <v>45993.45690386574</v>
       </c>
       <c r="AW16">
-        <v>124.815046</v>
+        <v>125.815069</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -3534,7 +3534,7 @@
         <v>45975.69316193287</v>
       </c>
       <c r="AW17">
-        <v>142.578785</v>
+        <v>143.578808</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -3712,7 +3712,7 @@
         <v>45856.44733234953</v>
       </c>
       <c r="AW18">
-        <v>260.631667</v>
+        <v>261.63169</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -3893,7 +3893,7 @@
         <v>45895.66738841435</v>
       </c>
       <c r="AW19">
-        <v>222.60456</v>
+        <v>223.604583</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -4074,7 +4074,7 @@
         <v>45887.7561505787</v>
       </c>
       <c r="AW20">
-        <v>230.515799</v>
+        <v>231.515822</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -4255,7 +4255,7 @@
         <v>45974.32124640046</v>
       </c>
       <c r="AW21">
-        <v>143.950706</v>
+        <v>144.950729</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -4433,7 +4433,7 @@
         <v>46057.3192221875</v>
       </c>
       <c r="AW22">
-        <v>60.952731</v>
+        <v>61.952755</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -4614,7 +4614,7 @@
         <v>46058.5740270949</v>
       </c>
       <c r="AW23">
-        <v>59.697928</v>
+        <v>60.697951</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -4795,7 +4795,7 @@
         <v>46051.34049207176</v>
       </c>
       <c r="AW24">
-        <v>66.93145800000001</v>
+        <v>67.93148100000001</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -4971,7 +4971,7 @@
         <v>45862.49253582176</v>
       </c>
       <c r="AW25">
-        <v>255.77941</v>
+        <v>256.779433</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5152,7 +5152,7 @@
         <v>45975.54832606482</v>
       </c>
       <c r="AW26">
-        <v>142.723623</v>
+        <v>143.723646</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5330,7 +5330,7 @@
         <v>46077.69417114583</v>
       </c>
       <c r="AW27">
-        <v>40.577778</v>
+        <v>41.577801</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5511,7 +5511,7 @@
         <v>46027.33752056713</v>
       </c>
       <c r="AW28">
-        <v>90.934433</v>
+        <v>91.934456</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5689,7 +5689,7 @@
         <v>45905.67982599537</v>
       </c>
       <c r="AW29">
-        <v>212.59213</v>
+        <v>213.592153</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5875,7 +5875,7 @@
         <v>45826.76330768519</v>
       </c>
       <c r="AW30">
-        <v>291.508646</v>
+        <v>292.508669</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6056,7 +6056,7 @@
         <v>45896.58634196759</v>
       </c>
       <c r="AW31">
-        <v>221.685613</v>
+        <v>222.685637</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6237,7 +6237,7 @@
         <v>45966.44628628472</v>
       </c>
       <c r="AW32">
-        <v>151.82566</v>
+        <v>152.825683</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6415,7 +6415,7 @@
         <v>45824.67305528936</v>
       </c>
       <c r="AW33">
-        <v>293.5989</v>
+        <v>294.598924</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6596,7 +6596,7 @@
         <v>45888.44432909723</v>
       </c>
       <c r="AW34">
-        <v>229.827616</v>
+        <v>230.827639</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6777,7 +6777,7 @@
         <v>45967.66489237269</v>
       </c>
       <c r="AW35">
-        <v>150.60706</v>
+        <v>151.607083</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6958,7 +6958,7 @@
         <v>45979.54654831019</v>
       </c>
       <c r="AW36">
-        <v>138.725405</v>
+        <v>139.725428</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -7139,7 +7139,7 @@
         <v>45820.33365524306</v>
       </c>
       <c r="AW37">
-        <v>265.659155</v>
+        <v>266.659178</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -7317,7 +7317,7 @@
         <v>45860.39854054398</v>
       </c>
       <c r="AW38">
-        <v>257.873414</v>
+        <v>258.873438</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -7495,7 +7495,7 @@
         <v>46100.38240289352</v>
       </c>
       <c r="AW39">
-        <v>16.040197</v>
+        <v>17.04022</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -7676,7 +7676,7 @@
         <v>45965.38089574075</v>
       </c>
       <c r="AW40">
-        <v>152.891053</v>
+        <v>153.891076</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -7857,7 +7857,7 @@
         <v>45986.56665260416</v>
       </c>
       <c r="AW41">
-        <v>131.705301</v>
+        <v>132.705324</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8038,7 +8038,7 @@
         <v>46027.57691234954</v>
       </c>
       <c r="AW42">
-        <v>90.695035</v>
+        <v>91.695058</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -8219,7 +8219,7 @@
         <v>46078.55323623843</v>
       </c>
       <c r="AW43">
-        <v>39.718715</v>
+        <v>40.718738</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -8400,7 +8400,7 @@
         <v>46037.65326952546</v>
       </c>
       <c r="AW44">
-        <v>80.618681</v>
+        <v>81.61870399999999</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -8578,7 +8578,7 @@
         <v>46057.31722791667</v>
       </c>
       <c r="AW45">
-        <v>60.954722</v>
+        <v>61.954745</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -8759,7 +8759,7 @@
         <v>45903.36153759259</v>
       </c>
       <c r="AW46">
-        <v>214.910417</v>
+        <v>215.91044</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8940,7 +8940,7 @@
         <v>45888.44494424769</v>
       </c>
       <c r="AW47">
-        <v>229.827002</v>
+        <v>230.827025</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -9118,7 +9118,7 @@
         <v>46106.37582024305</v>
       </c>
       <c r="AW48">
-        <v>11.896134</v>
+        <v>12.896157</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9299,7 +9299,7 @@
         <v>45937.3293883912</v>
       </c>
       <c r="AW49">
-        <v>180.942558</v>
+        <v>181.942581</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -9480,7 +9480,7 @@
         <v>45924.33459813657</v>
       </c>
       <c r="AW50">
-        <v>180.943773</v>
+        <v>181.943796</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -9648,7 +9648,7 @@
         <v>46079.67913538194</v>
       </c>
       <c r="AW51">
-        <v>38.592813</v>
+        <v>39.592836</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -9829,7 +9829,7 @@
         <v>45846.48855997685</v>
       </c>
       <c r="AW52">
-        <v>271.783391</v>
+        <v>272.783414</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -10010,7 +10010,7 @@
         <v>45860.39754922454</v>
       </c>
       <c r="AW53">
-        <v>257.874398</v>
+        <v>258.874421</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -10188,7 +10188,7 @@
         <v>45859.70404015046</v>
       </c>
       <c r="AW54">
-        <v>258.567905</v>
+        <v>259.567928</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -10369,7 +10369,7 @@
         <v>45946.65447922454</v>
       </c>
       <c r="AW55">
-        <v>165.710521</v>
+        <v>166.710544</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -10547,7 +10547,7 @@
         <v>46079.67988275463</v>
       </c>
       <c r="AW56">
-        <v>38.592072</v>
+        <v>39.592095</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -10731,7 +10731,7 @@
         <v>45868.73102224537</v>
       </c>
       <c r="AW57">
-        <v>249.540926</v>
+        <v>250.540949</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -10909,7 +10909,7 @@
         <v>46100.38269733796</v>
       </c>
       <c r="AW58">
-        <v>17.889248</v>
+        <v>18.889271</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -11087,7 +11087,7 @@
         <v>45821.6263675</v>
       </c>
       <c r="AW59">
-        <v>296.645579</v>
+        <v>297.645602</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -11265,7 +11265,7 @@
         <v>45831.57755690972</v>
       </c>
       <c r="AW60">
-        <v>286.694398</v>
+        <v>287.694421</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -11446,7 +11446,7 @@
         <v>46001.47500929398</v>
       </c>
       <c r="AW61">
-        <v>116.796944</v>
+        <v>117.796968</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -11624,7 +11624,7 @@
         <v>46036.58371895833</v>
       </c>
       <c r="AW62">
-        <v>81.68822900000001</v>
+        <v>82.68825200000001</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -11802,7 +11802,7 @@
         <v>45859.70488313658</v>
       </c>
       <c r="AW63">
-        <v>258.567072</v>
+        <v>259.567095</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -11983,7 +11983,7 @@
         <v>45985.75714297454</v>
       </c>
       <c r="AW64">
-        <v>132.514803</v>
+        <v>133.514826</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -12164,7 +12164,7 @@
         <v>45965.37678740741</v>
       </c>
       <c r="AW65">
-        <v>152.895162</v>
+        <v>153.895185</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -12345,7 +12345,7 @@
         <v>45923.70330438657</v>
       </c>
       <c r="AW66">
-        <v>194.568646</v>
+        <v>195.568669</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -12523,7 +12523,7 @@
         <v>45856.44919015047</v>
       </c>
       <c r="AW67">
-        <v>261.822755</v>
+        <v>262.822778</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -12701,7 +12701,7 @@
         <v>45895.64805509259</v>
       </c>
       <c r="AW68">
-        <v>222.6239</v>
+        <v>223.623924</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -12885,7 +12885,7 @@
         <v>45975.64818255787</v>
       </c>
       <c r="AW69">
-        <v>142.623773</v>
+        <v>143.623796</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -13063,7 +13063,7 @@
         <v>46037.67363424769</v>
       </c>
       <c r="AW70">
-        <v>80.598322</v>
+        <v>81.59834499999999</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -13241,7 +13241,7 @@
         <v>45820.33324042824</v>
       </c>
       <c r="AW71">
-        <v>297.938715</v>
+        <v>298.938738</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -13419,7 +13419,7 @@
         <v>45817.44034118055</v>
       </c>
       <c r="AW72">
-        <v>300.831609</v>
+        <v>301.831632</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -13600,7 +13600,7 @@
         <v>46097.3925265625</v>
       </c>
       <c r="AW73">
-        <v>20.879421</v>
+        <v>21.879444</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -13781,7 +13781,7 @@
         <v>45959.55501203703</v>
       </c>
       <c r="AW74">
-        <v>158.716933</v>
+        <v>159.716956</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -13962,7 +13962,7 @@
         <v>45902.58757359954</v>
       </c>
       <c r="AW75">
-        <v>215.684375</v>
+        <v>216.684398</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -14140,7 +14140,7 @@
         <v>45859.68910778935</v>
       </c>
       <c r="AW76">
-        <v>258.582847</v>
+        <v>259.58287</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -14321,7 +14321,7 @@
         <v>46002.72977564814</v>
       </c>
       <c r="AW77">
-        <v>115.542176</v>
+        <v>116.542199</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -14502,7 +14502,7 @@
         <v>46057.49838530092</v>
       </c>
       <c r="AW78">
-        <v>60.773565</v>
+        <v>61.773588</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -14683,7 +14683,7 @@
         <v>46007.42731981481</v>
       </c>
       <c r="AW79">
-        <v>110.84463</v>
+        <v>111.844653</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -14861,7 +14861,7 @@
         <v>45966.55098307871</v>
       </c>
       <c r="AW80">
-        <v>151.720972</v>
+        <v>152.720995</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -15042,7 +15042,7 @@
         <v>45973.66445978009</v>
       </c>
       <c r="AW81">
-        <v>144.607488</v>
+        <v>145.607512</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -15220,7 +15220,7 @@
         <v>45908.5914516551</v>
       </c>
       <c r="AW82">
-        <v>209.680498</v>
+        <v>210.680521</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -15406,7 +15406,7 @@
         <v>45845.61766498843</v>
       </c>
       <c r="AW83">
-        <v>272.654282</v>
+        <v>273.654306</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -15587,7 +15587,7 @@
         <v>46097.39690710648</v>
       </c>
       <c r="AW84">
-        <v>20.875046</v>
+        <v>21.875069</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -15768,7 +15768,7 @@
         <v>45890.42079241898</v>
       </c>
       <c r="AW85">
-        <v>213.889144</v>
+        <v>214.889167</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -15949,7 +15949,7 @@
         <v>45986.57630509259</v>
       </c>
       <c r="AW86">
-        <v>131.695648</v>
+        <v>132.695671</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -16130,7 +16130,7 @@
         <v>45831.57415840278</v>
       </c>
       <c r="AW87">
-        <v>286.697789</v>
+        <v>287.697813</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -16308,7 +16308,7 @@
         <v>45952.41303611111</v>
       </c>
       <c r="AW88">
-        <v>165.858912</v>
+        <v>166.858935</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -16489,7 +16489,7 @@
         <v>45967.6662366088</v>
       </c>
       <c r="AW89">
-        <v>150.605718</v>
+        <v>151.605741</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -16670,7 +16670,7 @@
         <v>45957.71828232639</v>
       </c>
       <c r="AW90">
-        <v>160.553669</v>
+        <v>161.553692</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -16851,7 +16851,7 @@
         <v>45937.3283994213</v>
       </c>
       <c r="AW91">
-        <v>180.943553</v>
+        <v>181.943576</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -17032,7 +17032,7 @@
         <v>45923.7104591088</v>
       </c>
       <c r="AW92">
-        <v>194.561493</v>
+        <v>195.561516</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -17213,7 +17213,7 @@
         <v>45904.38451509259</v>
       </c>
       <c r="AW93">
-        <v>213.887431</v>
+        <v>214.887454</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -17399,7 +17399,7 @@
         <v>45873.70399680555</v>
       </c>
       <c r="AW94">
-        <v>244.567523</v>
+        <v>245.567546</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -17577,7 +17577,7 @@
         <v>45852.54883409722</v>
       </c>
       <c r="AW95">
-        <v>265.723113</v>
+        <v>266.723137</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -17755,7 +17755,7 @@
         <v>45821.67408983796</v>
       </c>
       <c r="AW96">
-        <v>296.597859</v>
+        <v>297.597882</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -17936,7 +17936,7 @@
         <v>46001.46563837962</v>
       </c>
       <c r="AW97">
-        <v>116.806308</v>
+        <v>117.806331</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -18117,7 +18117,7 @@
         <v>46111.63374820602</v>
       </c>
       <c r="AW98">
-        <v>6.638206</v>
+        <v>7.638229</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -18298,7 +18298,7 @@
         <v>45817.66125234954</v>
       </c>
       <c r="AW99">
-        <v>250.570035</v>
+        <v>251.570058</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -18476,7 +18476,7 @@
         <v>45826.76919975695</v>
       </c>
       <c r="AW100">
-        <v>291.502755</v>
+        <v>292.502778</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -18654,7 +18654,7 @@
         <v>45917.32877043981</v>
       </c>
       <c r="AW101">
-        <v>200.943183</v>
+        <v>201.943206</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -18832,7 +18832,7 @@
         <v>45859.7056584838</v>
       </c>
       <c r="AW102">
-        <v>258.566296</v>
+        <v>259.566319</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -19013,7 +19013,7 @@
         <v>46027.3338925</v>
       </c>
       <c r="AW103">
-        <v>90.938056</v>
+        <v>91.938079</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -19191,7 +19191,7 @@
         <v>45820.33284418982</v>
       </c>
       <c r="AW104">
-        <v>297.939109</v>
+        <v>298.939132</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -19369,7 +19369,7 @@
         <v>45908.71817314815</v>
       </c>
       <c r="AW105">
-        <v>209.553773</v>
+        <v>210.553796</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -19550,7 +19550,7 @@
         <v>45986.56307221065</v>
       </c>
       <c r="AW106">
-        <v>131.708877</v>
+        <v>132.7089</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -19731,7 +19731,7 @@
         <v>45890.64899726852</v>
       </c>
       <c r="AW107">
-        <v>227.622951</v>
+        <v>228.622975</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -19912,7 +19912,7 @@
         <v>45898.57314238426</v>
       </c>
       <c r="AW108">
-        <v>219.698808</v>
+        <v>220.698831</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -20090,7 +20090,7 @@
         <v>46058.54936295139</v>
       </c>
       <c r="AW109">
-        <v>59.722593</v>
+        <v>60.722616</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -20271,7 +20271,7 @@
         <v>45868.58624710648</v>
       </c>
       <c r="AW110">
-        <v>249.685706</v>
+        <v>250.685729</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -20449,7 +20449,7 @@
         <v>45824.58323728009</v>
       </c>
       <c r="AW111">
-        <v>293.688715</v>
+        <v>294.688738</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -20630,7 +20630,7 @@
         <v>45987.54818097223</v>
       </c>
       <c r="AW112">
-        <v>130.723773</v>
+        <v>131.723796</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -20811,7 +20811,7 @@
         <v>45875.68270515047</v>
       </c>
       <c r="AW113">
-        <v>188.944456</v>
+        <v>189.944479</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -20992,7 +20992,7 @@
         <v>45817.43553984954</v>
       </c>
       <c r="AW114">
-        <v>248.122581</v>
+        <v>249.122604</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -21173,7 +21173,7 @@
         <v>45986.5776178125</v>
       </c>
       <c r="AW115">
-        <v>131.694329</v>
+        <v>132.694352</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -21354,7 +21354,7 @@
         <v>45959.57354159722</v>
       </c>
       <c r="AW116">
-        <v>158.698414</v>
+        <v>159.698438</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -21535,7 +21535,7 @@
         <v>45908.66222837963</v>
       </c>
       <c r="AW117">
-        <v>209.609722</v>
+        <v>210.609745</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -21716,7 +21716,7 @@
         <v>45861.50585359953</v>
       </c>
       <c r="AW118">
-        <v>256.7661</v>
+        <v>257.766123</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -21897,7 +21897,7 @@
         <v>46050.54798530092</v>
       </c>
       <c r="AW119">
-        <v>67.72396999999999</v>
+        <v>68.72399299999999</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -22078,7 +22078,7 @@
         <v>46027.33527493056</v>
       </c>
       <c r="AW120">
-        <v>90.936678</v>
+        <v>91.936701</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -22256,7 +22256,7 @@
         <v>45817.43738373843</v>
       </c>
       <c r="AW121">
-        <v>300.834572</v>
+        <v>301.834595</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -22437,7 +22437,7 @@
         <v>45957.72764497685</v>
       </c>
       <c r="AW122">
-        <v>160.544306</v>
+        <v>161.544329</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -22618,7 +22618,7 @@
         <v>45975.54881452546</v>
       </c>
       <c r="AW123">
-        <v>142.723137</v>
+        <v>143.72316</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -22796,7 +22796,7 @@
         <v>46038.68340863426</v>
       </c>
       <c r="AW124">
-        <v>79.588542</v>
+        <v>80.588565</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -22977,7 +22977,7 @@
         <v>45821.67595234954</v>
       </c>
       <c r="AW125">
-        <v>296.595995</v>
+        <v>297.596019</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -23155,7 +23155,7 @@
         <v>45831.62649351852</v>
       </c>
       <c r="AW126">
-        <v>286.645451</v>
+        <v>287.645475</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
@@ -23336,7 +23336,7 @@
         <v>45929.32908571759</v>
       </c>
       <c r="AW127">
-        <v>188.942859</v>
+        <v>189.942882</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
@@ -23520,7 +23520,7 @@
         <v>45868.56623082176</v>
       </c>
       <c r="AW128">
-        <v>249.705718</v>
+        <v>250.705741</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
@@ -23698,7 +23698,7 @@
         <v>45890.69579123842</v>
       </c>
       <c r="AW129">
-        <v>227.576157</v>
+        <v>228.576181</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
@@ -23879,7 +23879,7 @@
         <v>45842.7072899537</v>
       </c>
       <c r="AW130">
-        <v>275.564664</v>
+        <v>276.564688</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
@@ -24060,7 +24060,7 @@
         <v>46086.6752787037</v>
       </c>
       <c r="AW131">
-        <v>31.596667</v>
+        <v>32.59669</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
@@ -24241,7 +24241,7 @@
         <v>45904.38667092593</v>
       </c>
       <c r="AW132">
-        <v>213.885278</v>
+        <v>214.885301</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
@@ -24419,7 +24419,7 @@
         <v>45826.76858534722</v>
       </c>
       <c r="AW133">
-        <v>291.503368</v>
+        <v>292.503391</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
@@ -24600,7 +24600,7 @@
         <v>45986.57620032407</v>
       </c>
       <c r="AW134">
-        <v>131.695752</v>
+        <v>132.695775</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -24781,7 +24781,7 @@
         <v>46002.7290687963</v>
       </c>
       <c r="AW135">
-        <v>115.542882</v>
+        <v>116.542905</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
@@ -24954,7 +24954,7 @@
         <v>45831.67398204861</v>
       </c>
       <c r="AW136">
-        <v>286.597963</v>
+        <v>287.597986</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
@@ -25135,7 +25135,7 @@
         <v>46001.47355491898</v>
       </c>
       <c r="AW137">
-        <v>116.798391</v>
+        <v>117.798414</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
@@ -25316,7 +25316,7 @@
         <v>46072.59686878472</v>
       </c>
       <c r="AW138">
-        <v>45.675081</v>
+        <v>46.675104</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
@@ -25497,7 +25497,7 @@
         <v>45923.31500230324</v>
       </c>
       <c r="AW139">
-        <v>194.956944</v>
+        <v>195.956968</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
@@ -25678,7 +25678,7 @@
         <v>45917.46641751158</v>
       </c>
       <c r="AW140">
-        <v>200.805532</v>
+        <v>201.805556</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
@@ -25856,7 +25856,7 @@
         <v>45812.58332680556</v>
       </c>
       <c r="AW141">
-        <v>304.647986</v>
+        <v>305.648009</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
@@ -26034,7 +26034,7 @@
         <v>45887.78360177083</v>
       </c>
       <c r="AW142">
-        <v>230.488345</v>
+        <v>231.488368</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
@@ -26215,7 +26215,7 @@
         <v>45929.32963659722</v>
       </c>
       <c r="AW143">
-        <v>188.942315</v>
+        <v>189.942338</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
@@ -26396,7 +26396,7 @@
         <v>46059.43619244212</v>
       </c>
       <c r="AW144">
-        <v>58.835752</v>
+        <v>59.835775</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
@@ -26572,7 +26572,7 @@
         <v>45993.4571319213</v>
       </c>
       <c r="AW145">
-        <v>124.814815</v>
+        <v>125.814838</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
@@ -26750,7 +26750,7 @@
         <v>45831.62328704861</v>
       </c>
       <c r="AW146">
-        <v>286.648657</v>
+        <v>287.648681</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
@@ -26928,7 +26928,7 @@
         <v>45826.76692778935</v>
       </c>
       <c r="AW147">
-        <v>291.505023</v>
+        <v>292.505046</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
@@ -27106,7 +27106,7 @@
         <v>46100.38703670139</v>
       </c>
       <c r="AW148">
-        <v>17.884919</v>
+        <v>18.884942</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
@@ -27287,7 +27287,7 @@
         <v>45890.58630611112</v>
       </c>
       <c r="AW149">
-        <v>227.685648</v>
+        <v>228.685671</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
@@ -27465,7 +27465,7 @@
         <v>45856.44962944444</v>
       </c>
       <c r="AW150">
-        <v>261.822326</v>
+        <v>262.82235</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
@@ -27646,7 +27646,7 @@
         <v>45896.58530709491</v>
       </c>
       <c r="AW151">
-        <v>221.686644</v>
+        <v>222.686667</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
@@ -27824,7 +27824,7 @@
         <v>45859.70515091435</v>
       </c>
       <c r="AW152">
-        <v>258.566794</v>
+        <v>259.566817</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
@@ -28005,7 +28005,7 @@
         <v>46037.6671268287</v>
       </c>
       <c r="AW153">
-        <v>80.604826</v>
+        <v>81.60485</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
@@ -28183,7 +28183,7 @@
         <v>46057.32008791667</v>
       </c>
       <c r="AW154">
-        <v>60.951863</v>
+        <v>61.951887</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
@@ -28364,7 +28364,7 @@
         <v>45924.45313572917</v>
       </c>
       <c r="AW155">
-        <v>193.818819</v>
+        <v>194.818843</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
@@ -28545,7 +28545,7 @@
         <v>45924.65307170139</v>
       </c>
       <c r="AW156">
-        <v>193.618877</v>
+        <v>194.6189</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
@@ -28729,7 +28729,7 @@
         <v>46001.4660153125</v>
       </c>
       <c r="AW157">
-        <v>116.805938</v>
+        <v>117.805961</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
@@ -28918,7 +28918,7 @@
         <v>45912.68970434028</v>
       </c>
       <c r="AW158">
-        <v>205.582245</v>
+        <v>206.582269</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
@@ -29096,7 +29096,7 @@
         <v>45898.61987270833</v>
       </c>
       <c r="AW159">
-        <v>215.517014</v>
+        <v>216.517037</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
@@ -29277,7 +29277,7 @@
         <v>45985.75649112268</v>
       </c>
       <c r="AW160">
-        <v>132.515463</v>
+        <v>133.515486</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
@@ -29458,7 +29458,7 @@
         <v>46044.64347104167</v>
       </c>
       <c r="AW161">
-        <v>73.628484</v>
+        <v>74.628507</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
@@ -29626,7 +29626,7 @@
         <v>45882.61953023148</v>
       </c>
       <c r="AW162">
-        <v>235.652419</v>
+        <v>236.652442</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
@@ -29807,7 +29807,7 @@
         <v>45929.33033346065</v>
       </c>
       <c r="AW163">
-        <v>188.94162</v>
+        <v>189.941644</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
@@ -29988,7 +29988,7 @@
         <v>45904.38106203704</v>
       </c>
       <c r="AW164">
-        <v>213.890891</v>
+        <v>214.890914</v>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
@@ -30169,7 +30169,7 @@
         <v>45980.73353560185</v>
       </c>
       <c r="AW165">
-        <v>137.538414</v>
+        <v>138.538438</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
@@ -30350,7 +30350,7 @@
         <v>45860.39774737268</v>
       </c>
       <c r="AW166">
-        <v>257.874201</v>
+        <v>258.874225</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
@@ -30528,7 +30528,7 @@
         <v>46057.31564032407</v>
       </c>
       <c r="AW167">
-        <v>60.956308</v>
+        <v>61.956331</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
@@ -30706,7 +30706,7 @@
         <v>45870.37493769676</v>
       </c>
       <c r="AW168">
-        <v>247.897014</v>
+        <v>248.897037</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
@@ -30887,7 +30887,7 @@
         <v>45954.62848792824</v>
       </c>
       <c r="AW169">
-        <v>163.643461</v>
+        <v>164.643484</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
@@ -31065,7 +31065,7 @@
         <v>45986.57927599538</v>
       </c>
       <c r="AW170">
-        <v>131.692674</v>
+        <v>132.692697</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
@@ -31246,7 +31246,7 @@
         <v>46086.67425099537</v>
       </c>
       <c r="AW171">
-        <v>31.597697</v>
+        <v>32.59772</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
@@ -31424,7 +31424,7 @@
         <v>45821.67315659721</v>
       </c>
       <c r="AW172">
-        <v>296.598796</v>
+        <v>297.598819</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
@@ -31605,7 +31605,7 @@
         <v>45845.32285525464</v>
       </c>
       <c r="AW173">
-        <v>272.949097</v>
+        <v>273.94912</v>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
@@ -31783,7 +31783,7 @@
         <v>46036.59229349537</v>
       </c>
       <c r="AW174">
-        <v>81.679653</v>
+        <v>82.679676</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
@@ -31961,7 +31961,7 @@
         <v>46063.54699333334</v>
       </c>
       <c r="AW175">
-        <v>54.724954</v>
+        <v>55.724977</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
@@ -32134,7 +32134,7 @@
         <v>45905.68003464121</v>
       </c>
       <c r="AW176">
-        <v>212.591921</v>
+        <v>213.591944</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
@@ -32315,7 +32315,7 @@
         <v>46027.33587091435</v>
       </c>
       <c r="AW177">
-        <v>90.936076</v>
+        <v>91.9361</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
@@ -32493,7 +32493,7 @@
         <v>46077.70038504629</v>
       </c>
       <c r="AW178">
-        <v>40.571563</v>
+        <v>41.571586</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
@@ -32671,7 +32671,7 @@
         <v>45817.43698824074</v>
       </c>
       <c r="AW179">
-        <v>300.834965</v>
+        <v>301.834988</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
@@ -32849,7 +32849,7 @@
         <v>45870.3699896875</v>
       </c>
       <c r="AW180">
-        <v>247.901956</v>
+        <v>248.901979</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
@@ -33027,7 +33027,7 @@
         <v>45895.66891309028</v>
       </c>
       <c r="AW181">
-        <v>222.603032</v>
+        <v>223.603056</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
@@ -33208,7 +33208,7 @@
         <v>46097.39300328704</v>
       </c>
       <c r="AW182">
-        <v>20.878947</v>
+        <v>21.87897</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
@@ -33386,7 +33386,7 @@
         <v>45824.67360026621</v>
       </c>
       <c r="AW183">
-        <v>293.598345</v>
+        <v>294.598368</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
@@ -33564,7 +33564,7 @@
         <v>45833.56676576388</v>
       </c>
       <c r="AW184">
-        <v>284.705185</v>
+        <v>285.705208</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
@@ -33745,7 +33745,7 @@
         <v>45966.55113974537</v>
       </c>
       <c r="AW185">
-        <v>151.72081</v>
+        <v>152.720833</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
@@ -33923,7 +33923,7 @@
         <v>45895.64817069445</v>
       </c>
       <c r="AW186">
-        <v>222.623785</v>
+        <v>223.623808</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
@@ -34101,7 +34101,7 @@
         <v>45824.67396405093</v>
       </c>
       <c r="AW187">
-        <v>293.597986</v>
+        <v>294.598009</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
@@ -34282,7 +34282,7 @@
         <v>45868.57042331019</v>
       </c>
       <c r="AW188">
-        <v>249.701528</v>
+        <v>250.701551</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
@@ -34463,7 +34463,7 @@
         <v>45890.75601248843</v>
       </c>
       <c r="AW189">
-        <v>227.515938</v>
+        <v>228.515961</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
@@ -34644,7 +34644,7 @@
         <v>45923.31572024305</v>
       </c>
       <c r="AW190">
-        <v>194.956227</v>
+        <v>195.95625</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
@@ -34825,7 +34825,7 @@
         <v>45979.60267356482</v>
       </c>
       <c r="AW191">
-        <v>138.669282</v>
+        <v>139.669306</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
@@ -35003,7 +35003,7 @@
         <v>46057.31766871527</v>
       </c>
       <c r="AW192">
-        <v>60.954282</v>
+        <v>61.954306</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
@@ -35181,7 +35181,7 @@
         <v>45817.4294139699</v>
       </c>
       <c r="AW193">
-        <v>300.842535</v>
+        <v>301.842558</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
@@ -35362,7 +35362,7 @@
         <v>45905.68518516204</v>
       </c>
       <c r="AW194">
-        <v>194.959769</v>
+        <v>195.959792</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
@@ -35546,7 +35546,7 @@
         <v>45868.56660532407</v>
       </c>
       <c r="AW195">
-        <v>249.705347</v>
+        <v>250.70537</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
@@ -35727,7 +35727,7 @@
         <v>46001.47424234953</v>
       </c>
       <c r="AW196">
-        <v>116.797708</v>
+        <v>117.797731</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
@@ -35908,7 +35908,7 @@
         <v>45904.38355210648</v>
       </c>
       <c r="AW197">
-        <v>213.888403</v>
+        <v>214.888426</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
@@ -36076,7 +36076,7 @@
         <v>45882.60734775463</v>
       </c>
       <c r="AW198">
-        <v>235.664606</v>
+        <v>236.66463</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
@@ -36254,7 +36254,7 @@
         <v>45930.59030788194</v>
       </c>
       <c r="AW199">
-        <v>187.681644</v>
+        <v>188.681667</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
@@ -36435,7 +36435,7 @@
         <v>45904.37770018518</v>
       </c>
       <c r="AW200">
-        <v>213.894248</v>
+        <v>214.894271</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
@@ -36613,7 +36613,7 @@
         <v>45824.58295356482</v>
       </c>
       <c r="AW201">
-        <v>293.688993</v>
+        <v>294.689016</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
@@ -36791,7 +36791,7 @@
         <v>45810.36211870371</v>
       </c>
       <c r="AW202">
-        <v>307.909826</v>
+        <v>308.90985</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
@@ -36969,7 +36969,7 @@
         <v>45898.66446734954</v>
       </c>
       <c r="AW203">
-        <v>219.607488</v>
+        <v>220.607512</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
@@ -37150,7 +37150,7 @@
         <v>45810.35108107638</v>
       </c>
       <c r="AW204">
-        <v>280.925532</v>
+        <v>281.925556</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
@@ -37328,7 +37328,7 @@
         <v>45826.76801165509</v>
       </c>
       <c r="AW205">
-        <v>291.503935</v>
+        <v>292.503958</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
@@ -37506,7 +37506,7 @@
         <v>46073.66776079861</v>
       </c>
       <c r="AW206">
-        <v>44.60419</v>
+        <v>45.604213</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
@@ -37684,7 +37684,7 @@
         <v>45880.4943486574</v>
       </c>
       <c r="AW207">
-        <v>223.530926</v>
+        <v>224.530949</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
@@ -37865,7 +37865,7 @@
         <v>45842.71044888889</v>
       </c>
       <c r="AW208">
-        <v>275.561505</v>
+        <v>276.561528</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -38043,7 +38043,7 @@
         <v>46036.58667920139</v>
       </c>
       <c r="AW209">
-        <v>81.685266</v>
+        <v>82.685289</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
@@ -38221,7 +38221,7 @@
         <v>45821.69981792824</v>
       </c>
       <c r="AW210">
-        <v>296.57213</v>
+        <v>297.572153</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
@@ -38399,7 +38399,7 @@
         <v>45824.58350305556</v>
       </c>
       <c r="AW211">
-        <v>293.688449</v>
+        <v>294.688472</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
@@ -38577,7 +38577,7 @@
         <v>46090.73012363426</v>
       </c>
       <c r="AW212">
-        <v>27.541829</v>
+        <v>28.541852</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -38755,7 +38755,7 @@
         <v>45825.66128076389</v>
       </c>
       <c r="AW213">
-        <v>292.610671</v>
+        <v>293.610694</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
@@ -38933,7 +38933,7 @@
         <v>45811.53830461806</v>
       </c>
       <c r="AW214">
-        <v>306.733646</v>
+        <v>307.733669</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
@@ -39111,7 +39111,7 @@
         <v>45813.67869909722</v>
       </c>
       <c r="AW215">
-        <v>304.593252</v>
+        <v>305.593275</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
@@ -39289,7 +39289,7 @@
         <v>45821.62512202546</v>
       </c>
       <c r="AW216">
-        <v>296.646829</v>
+        <v>297.646852</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -39467,7 +39467,7 @@
         <v>45859.70342961806</v>
       </c>
       <c r="AW217">
-        <v>258.568519</v>
+        <v>259.568542</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
@@ -39648,7 +39648,7 @@
         <v>45859.68545269676</v>
       </c>
       <c r="AW218">
-        <v>258.586493</v>
+        <v>259.586516</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
@@ -39829,7 +39829,7 @@
         <v>45954.36042099537</v>
       </c>
       <c r="AW219">
-        <v>163.911528</v>
+        <v>164.911551</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
@@ -40010,7 +40010,7 @@
         <v>46097.56800899305</v>
       </c>
       <c r="AW220">
-        <v>20.703947</v>
+        <v>21.70397</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
@@ -40191,7 +40191,7 @@
         <v>46051.33719802083</v>
       </c>
       <c r="AW221">
-        <v>66.934757</v>
+        <v>67.93478</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
@@ -40372,7 +40372,7 @@
         <v>46051.33887575231</v>
       </c>
       <c r="AW222">
-        <v>66.93307900000001</v>
+        <v>67.93310200000001</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
@@ -40553,7 +40553,7 @@
         <v>45979.57851665509</v>
       </c>
       <c r="AW223">
-        <v>138.693438</v>
+        <v>139.693461</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
@@ -40734,7 +40734,7 @@
         <v>45986.56036744213</v>
       </c>
       <c r="AW224">
-        <v>131.711586</v>
+        <v>132.711609</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
@@ -40912,7 +40912,7 @@
         <v>45821.68405166667</v>
       </c>
       <c r="AW225">
-        <v>296.587894</v>
+        <v>297.587917</v>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
@@ -41090,7 +41090,7 @@
         <v>45812.58297493056</v>
       </c>
       <c r="AW226">
-        <v>305.68897</v>
+        <v>306.688993</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
@@ -41268,7 +41268,7 @@
         <v>45812.58710694444</v>
       </c>
       <c r="AW227">
-        <v>305.684838</v>
+        <v>306.684861</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
@@ -41449,7 +41449,7 @@
         <v>45911.63280706019</v>
       </c>
       <c r="AW228">
-        <v>206.639144</v>
+        <v>207.639167</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -41630,7 +41630,7 @@
         <v>45820.33415019676</v>
       </c>
       <c r="AW229">
-        <v>265.659074</v>
+        <v>266.659097</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
@@ -41811,7 +41811,7 @@
         <v>45904.37834540509</v>
       </c>
       <c r="AW230">
-        <v>213.8936</v>
+        <v>214.893623</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
@@ -41992,7 +41992,7 @@
         <v>45895.60195914352</v>
       </c>
       <c r="AW231">
-        <v>222.669988</v>
+        <v>223.670012</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
@@ -42170,7 +42170,7 @@
         <v>45835.37156861111</v>
       </c>
       <c r="AW232">
-        <v>282.900382</v>
+        <v>283.900405</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -42351,7 +42351,7 @@
         <v>45923.31386627315</v>
       </c>
       <c r="AW233">
-        <v>194.958079</v>
+        <v>195.958102</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
@@ -42535,7 +42535,7 @@
         <v>45903.36175993056</v>
       </c>
       <c r="AW234">
-        <v>214.910185</v>
+        <v>215.910208</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
@@ -42713,7 +42713,7 @@
         <v>45972.38501128473</v>
       </c>
       <c r="AW235">
-        <v>145.886944</v>
+        <v>146.886968</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
@@ -42894,7 +42894,7 @@
         <v>46086.67639361111</v>
       </c>
       <c r="AW236">
-        <v>31.595556</v>
+        <v>32.595579</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
@@ -43075,7 +43075,7 @@
         <v>46001.47301980324</v>
       </c>
       <c r="AW237">
-        <v>116.798935</v>
+        <v>117.798958</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
@@ -43256,7 +43256,7 @@
         <v>45860.39721776621</v>
       </c>
       <c r="AW238">
-        <v>257.874734</v>
+        <v>258.874757</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
@@ -43437,7 +43437,7 @@
         <v>45904.51875018519</v>
       </c>
       <c r="AW239">
-        <v>213.753194</v>
+        <v>214.753218</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
@@ -43615,7 +43615,7 @@
         <v>46036.59334578704</v>
       </c>
       <c r="AW240">
-        <v>81.6786</v>
+        <v>82.678623</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
@@ -43796,7 +43796,7 @@
         <v>45985.7559840162</v>
       </c>
       <c r="AW241">
-        <v>132.515961</v>
+        <v>133.515984</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
@@ -43977,7 +43977,7 @@
         <v>45820.33046670139</v>
       </c>
       <c r="AW242">
-        <v>247.900729</v>
+        <v>248.900752</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
@@ -44161,7 +44161,7 @@
         <v>45895.67057834491</v>
       </c>
       <c r="AW243">
-        <v>222.601377</v>
+        <v>223.6014</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
@@ -44339,7 +44339,7 @@
         <v>45859.70464324074</v>
       </c>
       <c r="AW244">
-        <v>258.567303</v>
+        <v>259.567326</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
@@ -44512,7 +44512,7 @@
         <v>45824.69872459491</v>
       </c>
       <c r="AW245">
-        <v>293.573229</v>
+        <v>294.573252</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
@@ -44693,7 +44693,7 @@
         <v>45952.41598819445</v>
       </c>
       <c r="AW246">
-        <v>165.855961</v>
+        <v>166.855984</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
@@ -44874,7 +44874,7 @@
         <v>45923.56720940972</v>
       </c>
       <c r="AW247">
-        <v>194.660845</v>
+        <v>195.660868</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
@@ -45055,7 +45055,7 @@
         <v>45929.33121140047</v>
       </c>
       <c r="AW248">
-        <v>188.940741</v>
+        <v>189.940764</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -45236,7 +45236,7 @@
         <v>46078.55240465277</v>
       </c>
       <c r="AW249">
-        <v>39.719549</v>
+        <v>40.719572</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
@@ -45414,7 +45414,7 @@
         <v>45859.70424362268</v>
       </c>
       <c r="AW250">
-        <v>258.567708</v>
+        <v>259.567731</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
@@ -45595,7 +45595,7 @@
         <v>45888.4437121875</v>
       </c>
       <c r="AW251">
-        <v>229.828241</v>
+        <v>230.828264</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
@@ -45776,7 +45776,7 @@
         <v>46051.59352782407</v>
       </c>
       <c r="AW252">
-        <v>66.678426</v>
+        <v>67.678449</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -45957,7 +45957,7 @@
         <v>45839.55104972223</v>
       </c>
       <c r="AW253">
-        <v>278.720903</v>
+        <v>279.720926</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
@@ -46138,7 +46138,7 @@
         <v>46050.54756696759</v>
       </c>
       <c r="AW254">
-        <v>67.72438699999999</v>
+        <v>68.72441000000001</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
@@ -46319,7 +46319,7 @@
         <v>46111.70316528935</v>
       </c>
       <c r="AW255">
-        <v>6.568785</v>
+        <v>7.568808</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
@@ -46333,7 +46333,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -46349,11 +46349,14 @@
           <t>Construção de Cursos</t>
         </is>
       </c>
+      <c r="H256" s="2">
+        <v>46118.65642626157</v>
+      </c>
       <c r="I256" s="2">
         <v>46076.7099121875</v>
       </c>
       <c r="J256" s="2">
-        <v>46113.36898355324</v>
+        <v>46118.65642635417</v>
       </c>
       <c r="M256" s="2">
         <v>46106.70991219908</v>
@@ -46429,10 +46432,33 @@
           <t>https://docs.google.com/document/d/1ERSO1B7ZDvm0nQO6fx1fC6rTnKmNWXqnuUCTRdqjYbc/edit?tab=t.tqzjurqxgryn</t>
         </is>
       </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>Aprovado: Publicar !</t>
+        </is>
+      </c>
       <c r="AF256" t="inlineStr">
         <is>
           <t>Gestão</t>
         </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>01:22:00</t>
+        </is>
+      </c>
+      <c r="AH256">
+        <v>8</v>
       </c>
       <c r="AI256" s="2">
         <v>46076.70991956018</v>
@@ -46455,8 +46481,26 @@
       <c r="AO256" s="2">
         <v>46113.36897872685</v>
       </c>
+      <c r="AP256" s="2">
+        <v>46118.65567793982</v>
+      </c>
       <c r="AQ256">
-        <v>4.902975</v>
+        <v>5.28669</v>
+      </c>
+      <c r="AR256" s="2">
+        <v>46118.65567854166</v>
+      </c>
+      <c r="AS256" s="2">
+        <v>46118.65642714121</v>
+      </c>
+      <c r="AT256">
+        <v>0.000741</v>
+      </c>
+      <c r="AU256" s="2">
+        <v>46118.65642736111</v>
+      </c>
+      <c r="AW256">
+        <v>0.615544</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
@@ -46637,7 +46681,7 @@
         <v>46027.33658649305</v>
       </c>
       <c r="AW257">
-        <v>90.93535900000001</v>
+        <v>91.935382</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
@@ -46818,7 +46862,7 @@
         <v>45929.3236115625</v>
       </c>
       <c r="AW258">
-        <v>188.948333</v>
+        <v>189.948356</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
@@ -46999,7 +47043,7 @@
         <v>45860.43664048611</v>
       </c>
       <c r="AW259">
-        <v>257.835313</v>
+        <v>258.835336</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="1">
@@ -47177,7 +47221,7 @@
         <v>45929.32146375</v>
       </c>
       <c r="AW260">
-        <v>188.950486</v>
+        <v>189.950509</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="1">
@@ -47355,7 +47399,7 @@
         <v>45954.73906835648</v>
       </c>
       <c r="AW261">
-        <v>163.532882</v>
+        <v>164.532905</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
@@ -47531,7 +47575,7 @@
         <v>45862.4923733912</v>
       </c>
       <c r="AW262">
-        <v>255.779572</v>
+        <v>256.779595</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
@@ -47709,7 +47753,7 @@
         <v>46003.56398351852</v>
       </c>
       <c r="AW263">
-        <v>114.707963</v>
+        <v>115.707986</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
@@ -47887,7 +47931,7 @@
         <v>45938.33289437499</v>
       </c>
       <c r="AW264">
-        <v>179.939051</v>
+        <v>180.939074</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
@@ -48068,7 +48112,7 @@
         <v>45946.65440010416</v>
       </c>
       <c r="AW265">
-        <v>165.711273</v>
+        <v>166.711296</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
@@ -48246,7 +48290,7 @@
         <v>45821.62585732639</v>
       </c>
       <c r="AW266">
-        <v>296.646088</v>
+        <v>297.646111</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
@@ -48427,7 +48471,7 @@
         <v>45831.5739419676</v>
       </c>
       <c r="AW267">
-        <v>286.698009</v>
+        <v>287.698032</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
@@ -48608,7 +48652,7 @@
         <v>45842.71009863426</v>
       </c>
       <c r="AW268">
-        <v>275.561852</v>
+        <v>276.561875</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
@@ -48786,7 +48830,7 @@
         <v>45952.55986858797</v>
       </c>
       <c r="AW269">
-        <v>165.712083</v>
+        <v>166.712106</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
@@ -48967,7 +49011,7 @@
         <v>45966.55123927083</v>
       </c>
       <c r="AW270">
-        <v>151.720706</v>
+        <v>152.720729</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="1">
@@ -49148,7 +49192,7 @@
         <v>45986.57647679398</v>
       </c>
       <c r="AW271">
-        <v>131.695475</v>
+        <v>132.695498</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="1">
@@ -49329,7 +49373,7 @@
         <v>45842.7095575463</v>
       </c>
       <c r="AW272">
-        <v>275.562396</v>
+        <v>276.562419</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
@@ -49513,7 +49557,7 @@
         <v>45971.57262901621</v>
       </c>
       <c r="AW273">
-        <v>146.699317</v>
+        <v>147.69934</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
@@ -49691,7 +49735,7 @@
         <v>45923.31946878473</v>
       </c>
       <c r="AW274">
-        <v>194.952477</v>
+        <v>195.9525</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
@@ -49872,7 +49916,7 @@
         <v>45846.4887596412</v>
       </c>
       <c r="AW275">
-        <v>271.783194</v>
+        <v>272.783218</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
@@ -50053,7 +50097,7 @@
         <v>45832.68075126158</v>
       </c>
       <c r="AW276">
-        <v>285.591204</v>
+        <v>286.591227</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
@@ -50234,7 +50278,7 @@
         <v>45917.46522068288</v>
       </c>
       <c r="AW277">
-        <v>200.806725</v>
+        <v>201.806748</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
@@ -50415,7 +50459,7 @@
         <v>45965.37861903935</v>
       </c>
       <c r="AW278">
-        <v>152.893333</v>
+        <v>153.893356</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
@@ -50622,7 +50666,7 @@
         <v>45966.44556553241</v>
       </c>
       <c r="AW279">
-        <v>151.826389</v>
+        <v>152.826412</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
@@ -50800,7 +50844,7 @@
         <v>45975.64955575232</v>
       </c>
       <c r="AW280">
-        <v>142.622396</v>
+        <v>143.622419</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
@@ -50981,7 +51025,7 @@
         <v>45986.55970949074</v>
       </c>
       <c r="AW281">
-        <v>131.712245</v>
+        <v>132.712269</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
@@ -51162,7 +51206,7 @@
         <v>45924.33429111111</v>
       </c>
       <c r="AW282">
-        <v>180.942477</v>
+        <v>181.9425</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
@@ -51343,7 +51387,7 @@
         <v>45992.61684608796</v>
       </c>
       <c r="AW283">
-        <v>125.655104</v>
+        <v>126.655127</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
@@ -51521,7 +51565,7 @@
         <v>46100.38526741898</v>
       </c>
       <c r="AW284">
-        <v>17.886678</v>
+        <v>18.886701</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
@@ -51699,7 +51743,7 @@
         <v>45845.32248731481</v>
       </c>
       <c r="AW285">
-        <v>272.949468</v>
+        <v>273.949491</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
@@ -51877,7 +51921,7 @@
         <v>45833.56582039352</v>
       </c>
       <c r="AW286">
-        <v>284.706134</v>
+        <v>285.706157</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
@@ -52058,7 +52102,7 @@
         <v>45846.36008232638</v>
       </c>
       <c r="AW287">
-        <v>271.911863</v>
+        <v>272.911887</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
@@ -52239,7 +52283,7 @@
         <v>45890.64208997686</v>
       </c>
       <c r="AW288">
-        <v>227.629861</v>
+        <v>228.629884</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
@@ -52417,7 +52461,7 @@
         <v>45870.37016001157</v>
       </c>
       <c r="AW289">
-        <v>247.901794</v>
+        <v>248.901817</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
@@ -52598,7 +52642,7 @@
         <v>45971.57897849537</v>
       </c>
       <c r="AW290">
-        <v>146.692975</v>
+        <v>147.692998</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
@@ -52779,7 +52823,7 @@
         <v>45939.31507973379</v>
       </c>
       <c r="AW291">
-        <v>168.95728</v>
+        <v>169.957303</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
@@ -52960,7 +53004,7 @@
         <v>45887.75298732638</v>
       </c>
       <c r="AW292">
-        <v>230.518958</v>
+        <v>231.518981</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
@@ -53138,7 +53182,7 @@
         <v>45832.3608832176</v>
       </c>
       <c r="AW293">
-        <v>285.911065</v>
+        <v>286.911088</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
@@ -53316,7 +53360,7 @@
         <v>45826.76998138889</v>
       </c>
       <c r="AW294">
-        <v>291.501968</v>
+        <v>292.501991</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
@@ -53497,7 +53541,7 @@
         <v>45904.37713482638</v>
       </c>
       <c r="AW295">
-        <v>213.894815</v>
+        <v>214.894838</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
@@ -53678,7 +53722,7 @@
         <v>46097.39639761574</v>
       </c>
       <c r="AW296">
-        <v>20.875556</v>
+        <v>21.875579</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
@@ -53856,7 +53900,7 @@
         <v>45859.70231407408</v>
       </c>
       <c r="AW297">
-        <v>258.569641</v>
+        <v>259.569664</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
@@ -54037,7 +54081,7 @@
         <v>45986.70824453703</v>
       </c>
       <c r="AW298">
-        <v>131.563704</v>
+        <v>132.563727</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
@@ -54215,7 +54259,7 @@
         <v>46100.38306148148</v>
       </c>
       <c r="AW299">
-        <v>17.888889</v>
+        <v>18.888912</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
@@ -54404,7 +54448,7 @@
         <v>45835.37110386574</v>
       </c>
       <c r="AW300">
-        <v>282.900845</v>
+        <v>283.900868</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
@@ -54582,7 +54626,7 @@
         <v>45929.57279483796</v>
       </c>
       <c r="AW301">
-        <v>188.699155</v>
+        <v>189.699178</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
@@ -54763,7 +54807,7 @@
         <v>45904.38426976852</v>
       </c>
       <c r="AW302">
-        <v>213.887685</v>
+        <v>214.887708</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
@@ -54944,7 +54988,7 @@
         <v>46007.42707763889</v>
       </c>
       <c r="AW303">
-        <v>110.844873</v>
+        <v>111.844896</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
@@ -55125,7 +55169,7 @@
         <v>45930.65916848379</v>
       </c>
       <c r="AW304">
-        <v>187.612778</v>
+        <v>188.612801</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
@@ -55303,7 +55347,7 @@
         <v>45820.33137869213</v>
       </c>
       <c r="AW305">
-        <v>297.940567</v>
+        <v>298.94059</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
@@ -55489,7 +55533,7 @@
         <v>45894.61132443287</v>
       </c>
       <c r="AW306">
-        <v>223.660625</v>
+        <v>224.660648</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="1">
@@ -55670,7 +55714,7 @@
         <v>45975.54895935186</v>
       </c>
       <c r="AW307">
-        <v>142.722986</v>
+        <v>143.723009</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
@@ -55851,7 +55895,7 @@
         <v>46027.33476094907</v>
       </c>
       <c r="AW308">
-        <v>90.93718800000001</v>
+        <v>91.937211</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
@@ -56032,7 +56076,7 @@
         <v>46001.46150133102</v>
       </c>
       <c r="AW309">
-        <v>116.810451</v>
+        <v>117.810475</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
@@ -56213,7 +56257,7 @@
         <v>45930.65883226852</v>
       </c>
       <c r="AW310">
-        <v>187.613113</v>
+        <v>188.613137</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
@@ -56394,7 +56438,7 @@
         <v>45930.6606075926</v>
       </c>
       <c r="AW311">
-        <v>187.611343</v>
+        <v>188.611366</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
@@ -56575,7 +56619,7 @@
         <v>46111.63328278935</v>
       </c>
       <c r="AW312">
-        <v>6.638669</v>
+        <v>7.638692</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
@@ -56753,7 +56797,7 @@
         <v>45826.76959586806</v>
       </c>
       <c r="AW313">
-        <v>291.50235</v>
+        <v>292.502373</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
@@ -56931,7 +56975,7 @@
         <v>46057.31336575231</v>
       </c>
       <c r="AW314">
-        <v>60.958588</v>
+        <v>61.958611</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
@@ -57112,7 +57156,7 @@
         <v>45954.62754329861</v>
       </c>
       <c r="AW315">
-        <v>163.64441</v>
+        <v>164.644433</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
@@ -57293,7 +57337,7 @@
         <v>45873.70791493055</v>
       </c>
       <c r="AW316">
-        <v>244.564039</v>
+        <v>245.564063</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
@@ -57471,7 +57515,7 @@
         <v>46077.70090952546</v>
       </c>
       <c r="AW317">
-        <v>40.571042</v>
+        <v>41.571065</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
@@ -57649,7 +57693,7 @@
         <v>46100.38381973379</v>
       </c>
       <c r="AW318">
-        <v>17.888125</v>
+        <v>18.888148</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
@@ -57830,7 +57874,7 @@
         <v>46097.39592864583</v>
       </c>
       <c r="AW319">
-        <v>20.876019</v>
+        <v>21.876042</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
@@ -58008,7 +58052,7 @@
         <v>45873.70497479167</v>
       </c>
       <c r="AW320">
-        <v>244.566829</v>
+        <v>245.566852</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="1">
@@ -58189,7 +58233,7 @@
         <v>45840.40468760417</v>
       </c>
       <c r="AW321">
-        <v>257.872072</v>
+        <v>258.872095</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
@@ -58367,7 +58411,7 @@
         <v>46051.66997212963</v>
       </c>
       <c r="AW322">
-        <v>66.601979</v>
+        <v>67.602002</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="1">
@@ -58545,7 +58589,7 @@
         <v>45959.61025383102</v>
       </c>
       <c r="AW323">
-        <v>158.661701</v>
+        <v>159.661725</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
@@ -58723,7 +58767,7 @@
         <v>45817.43653768519</v>
       </c>
       <c r="AW324">
-        <v>300.835417</v>
+        <v>301.83544</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="1">
@@ -58904,7 +58948,7 @@
         <v>45923.32032945602</v>
       </c>
       <c r="AW325">
-        <v>194.95162</v>
+        <v>195.951644</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
@@ -59085,7 +59129,7 @@
         <v>45971.57499085648</v>
       </c>
       <c r="AW326">
-        <v>146.696956</v>
+        <v>147.696979</v>
       </c>
     </row>
     <row r="327" ht="18" customHeight="1">
@@ -59266,7 +59310,7 @@
         <v>45838.66248615741</v>
       </c>
       <c r="AW327">
-        <v>279.609468</v>
+        <v>280.609491</v>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
@@ -59447,7 +59491,7 @@
         <v>46001.4599725</v>
       </c>
       <c r="AW328">
-        <v>116.811979</v>
+        <v>117.812002</v>
       </c>
     </row>
     <row r="329" ht="18" customHeight="1">
@@ -59628,7 +59672,7 @@
         <v>46042.45735565972</v>
       </c>
       <c r="AW329">
-        <v>75.814595</v>
+        <v>76.814618</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
@@ -59809,7 +59853,7 @@
         <v>45883.60346527777</v>
       </c>
       <c r="AW330">
-        <v>234.668484</v>
+        <v>235.668507</v>
       </c>
     </row>
     <row r="331" ht="18" customHeight="1">
@@ -59987,7 +60031,7 @@
         <v>45890.69609947917</v>
       </c>
       <c r="AW331">
-        <v>227.575856</v>
+        <v>228.57588</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
@@ -60171,7 +60215,7 @@
         <v>45944.68359482639</v>
       </c>
       <c r="AW332">
-        <v>173.586574</v>
+        <v>174.586597</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
@@ -60352,7 +60396,7 @@
         <v>45965.38240310185</v>
       </c>
       <c r="AW333">
-        <v>152.889549</v>
+        <v>153.889572</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
@@ -60530,7 +60574,7 @@
         <v>45859.70298075231</v>
       </c>
       <c r="AW334">
-        <v>258.56897</v>
+        <v>259.568993</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
@@ -60711,7 +60755,7 @@
         <v>45975.64912039351</v>
       </c>
       <c r="AW335">
-        <v>142.622824</v>
+        <v>143.622847</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
@@ -60889,7 +60933,7 @@
         <v>45880.67850293982</v>
       </c>
       <c r="AW336">
-        <v>237.593449</v>
+        <v>238.593472</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
@@ -61070,7 +61114,7 @@
         <v>46034.69664187499</v>
       </c>
       <c r="AW337">
-        <v>83.57531299999999</v>
+        <v>84.57533599999999</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
@@ -61251,7 +61295,7 @@
         <v>45888.44706435185</v>
       </c>
       <c r="AW338">
-        <v>229.824884</v>
+        <v>230.824907</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
@@ -61427,7 +61471,7 @@
         <v>45954.62802541666</v>
       </c>
       <c r="AW339">
-        <v>163.643924</v>
+        <v>164.643947</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
@@ -61608,7 +61652,7 @@
         <v>46111.63441997685</v>
       </c>
       <c r="AW340">
-        <v>6.637535</v>
+        <v>7.637558</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
@@ -61789,7 +61833,7 @@
         <v>46097.39543481481</v>
       </c>
       <c r="AW341">
-        <v>20.876516</v>
+        <v>21.876539</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
@@ -61967,7 +62011,7 @@
         <v>45812.5781485301</v>
       </c>
       <c r="AW342">
-        <v>305.693796</v>
+        <v>306.693819</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
@@ -62148,7 +62192,7 @@
         <v>45923.31296491898</v>
       </c>
       <c r="AW343">
-        <v>194.958981</v>
+        <v>195.959005</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
@@ -62329,7 +62373,7 @@
         <v>45902.37917880787</v>
       </c>
       <c r="AW344">
-        <v>215.892766</v>
+        <v>216.892789</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -62510,7 +62554,7 @@
         <v>45973.66494252314</v>
       </c>
       <c r="AW345">
-        <v>144.607002</v>
+        <v>145.607025</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -62691,7 +62735,7 @@
         <v>45855.33980681713</v>
       </c>
       <c r="AW346">
-        <v>262.932141</v>
+        <v>263.932164</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -62872,7 +62916,7 @@
         <v>46057.49907950232</v>
       </c>
       <c r="AW347">
-        <v>60.77287</v>
+        <v>61.772894</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
@@ -63053,7 +63097,7 @@
         <v>46076.32663673611</v>
       </c>
       <c r="AW348">
-        <v>41.945313</v>
+        <v>42.945336</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
@@ -63234,7 +63278,7 @@
         <v>45992.61622836806</v>
       </c>
       <c r="AW349">
-        <v>125.655718</v>
+        <v>126.655741</v>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
@@ -63415,7 +63459,7 @@
         <v>45919.68091108797</v>
       </c>
       <c r="AW350">
-        <v>198.591042</v>
+        <v>199.591065</v>
       </c>
     </row>
     <row r="351" ht="18" customHeight="1">
@@ -63593,7 +63637,7 @@
         <v>45898.61942834491</v>
       </c>
       <c r="AW351">
-        <v>219.652523</v>
+        <v>220.652546</v>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
@@ -63774,7 +63818,7 @@
         <v>45973.66372342593</v>
       </c>
       <c r="AW352">
-        <v>144.608229</v>
+        <v>145.608252</v>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
@@ -63952,7 +63996,7 @@
         <v>45954.62691407408</v>
       </c>
       <c r="AW353">
-        <v>163.645035</v>
+        <v>164.645058</v>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
@@ -64133,7 +64177,7 @@
         <v>45846.35986268519</v>
       </c>
       <c r="AW354">
-        <v>271.912083</v>
+        <v>272.912106</v>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
@@ -64314,7 +64358,7 @@
         <v>45917.46567336806</v>
       </c>
       <c r="AW355">
-        <v>200.806273</v>
+        <v>201.806296</v>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
@@ -64495,7 +64539,7 @@
         <v>45929.33197420138</v>
       </c>
       <c r="AW356">
-        <v>188.939977</v>
+        <v>189.94</v>
       </c>
     </row>
     <row r="357" ht="18" customHeight="1">
@@ -64673,7 +64717,7 @@
         <v>45915.32586412037</v>
       </c>
       <c r="AW357">
-        <v>195.012488</v>
+        <v>196.012512</v>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
@@ -64854,7 +64898,7 @@
         <v>46037.66552774305</v>
       </c>
       <c r="AW358">
-        <v>80.606424</v>
+        <v>81.606447</v>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
@@ -65035,7 +65079,7 @@
         <v>45987.54471672454</v>
       </c>
       <c r="AW359">
-        <v>130.727234</v>
+        <v>131.727257</v>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
@@ -65216,7 +65260,7 @@
         <v>46006.54578523149</v>
       </c>
       <c r="AW360">
-        <v>111.726169</v>
+        <v>112.726192</v>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
@@ -65397,7 +65441,7 @@
         <v>46051.53146484954</v>
       </c>
       <c r="AW361">
-        <v>66.740486</v>
+        <v>67.740509</v>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
@@ -65575,7 +65619,7 @@
         <v>45820.3330696875</v>
       </c>
       <c r="AW362">
-        <v>297.938877</v>
+        <v>298.9389</v>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
@@ -65756,7 +65800,7 @@
         <v>45821.67524549768</v>
       </c>
       <c r="AW363">
-        <v>296.596701</v>
+        <v>297.596725</v>
       </c>
     </row>
     <row r="364" ht="18" customHeight="1">
@@ -65934,7 +65978,7 @@
         <v>45813.68440848379</v>
       </c>
       <c r="AW364">
-        <v>304.587546</v>
+        <v>305.587569</v>
       </c>
     </row>
     <row r="365" ht="18" customHeight="1">
@@ -66115,7 +66159,7 @@
         <v>45923.31175675926</v>
       </c>
       <c r="AW365">
-        <v>194.960197</v>
+        <v>195.96022</v>
       </c>
     </row>
     <row r="366" ht="18" customHeight="1">
@@ -66293,7 +66337,7 @@
         <v>46003.56407180555</v>
       </c>
       <c r="AW366">
-        <v>114.707882</v>
+        <v>115.707905</v>
       </c>
     </row>
     <row r="367" ht="18" customHeight="1">
@@ -66474,7 +66518,7 @@
         <v>45842.70903693287</v>
       </c>
       <c r="AW367">
-        <v>275.562917</v>
+        <v>276.56294</v>
       </c>
     </row>
     <row r="368" ht="18" customHeight="1">
@@ -66655,7 +66699,7 @@
         <v>45954.37944618055</v>
       </c>
       <c r="AW368">
-        <v>163.8925</v>
+        <v>164.892523</v>
       </c>
     </row>
     <row r="369" ht="18" customHeight="1">
@@ -66836,7 +66880,7 @@
         <v>45952.41448010417</v>
       </c>
       <c r="AW369">
-        <v>165.857465</v>
+        <v>166.857488</v>
       </c>
     </row>
     <row r="370" ht="18" customHeight="1">
@@ -67017,7 +67061,7 @@
         <v>45855.34249084491</v>
       </c>
       <c r="AW370">
-        <v>262.929456</v>
+        <v>263.929479</v>
       </c>
     </row>
     <row r="371" ht="18" customHeight="1">
@@ -67195,7 +67239,7 @@
         <v>45826.77024422454</v>
       </c>
       <c r="AW371">
-        <v>291.501701</v>
+        <v>292.501725</v>
       </c>
     </row>
     <row r="372" ht="18" customHeight="1">
@@ -67373,7 +67417,7 @@
         <v>45936.74229829861</v>
       </c>
       <c r="AW372">
-        <v>181.529653</v>
+        <v>182.529676</v>
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
@@ -67551,7 +67595,7 @@
         <v>45852.54993511573</v>
       </c>
       <c r="AW373">
-        <v>265.722014</v>
+        <v>266.722037</v>
       </c>
     </row>
     <row r="374" ht="18" customHeight="1">
@@ -67732,7 +67776,7 @@
         <v>45904.38291060185</v>
       </c>
       <c r="AW374">
-        <v>213.889039</v>
+        <v>214.889063</v>
       </c>
     </row>
     <row r="375" ht="18" customHeight="1">
@@ -67913,7 +67957,7 @@
         <v>46097.39673672454</v>
       </c>
       <c r="AW375">
-        <v>20.875208</v>
+        <v>21.875231</v>
       </c>
     </row>
     <row r="376" ht="18" customHeight="1">
@@ -68091,7 +68135,7 @@
         <v>45821.63864346065</v>
       </c>
       <c r="AW376">
-        <v>296.63331</v>
+        <v>297.633333</v>
       </c>
     </row>
     <row r="377" ht="18" customHeight="1">
@@ -68269,7 +68313,7 @@
         <v>45810.36123126157</v>
       </c>
       <c r="AW377">
-        <v>300.727454</v>
+        <v>301.727477</v>
       </c>
     </row>
     <row r="378" ht="18" customHeight="1">
@@ -68450,7 +68494,7 @@
         <v>45973.65832961806</v>
       </c>
       <c r="AW378">
-        <v>144.613623</v>
+        <v>145.613646</v>
       </c>
     </row>
     <row r="379" ht="18" customHeight="1">
@@ -68628,7 +68672,7 @@
         <v>45820.3322787037</v>
       </c>
       <c r="AW379">
-        <v>297.939676</v>
+        <v>298.939699</v>
       </c>
     </row>
     <row r="380" ht="18" customHeight="1">
@@ -68806,7 +68850,7 @@
         <v>45812.58675498843</v>
       </c>
       <c r="AW380">
-        <v>305.685197</v>
+        <v>306.68522</v>
       </c>
     </row>
     <row r="381" ht="18" customHeight="1">
@@ -68984,7 +69028,7 @@
         <v>45842.70851819444</v>
       </c>
       <c r="AW381">
-        <v>275.563438</v>
+        <v>276.563461</v>
       </c>
     </row>
     <row r="382" ht="18" customHeight="1">
@@ -69162,7 +69206,7 @@
         <v>45964.65037627315</v>
       </c>
       <c r="AW382">
-        <v>153.621574</v>
+        <v>154.621597</v>
       </c>
     </row>
     <row r="383" ht="18" customHeight="1">
@@ -69340,7 +69384,7 @@
         <v>45826.77171652778</v>
       </c>
       <c r="AW383">
-        <v>291.500231</v>
+        <v>292.500255</v>
       </c>
     </row>
     <row r="384" ht="18" customHeight="1">
@@ -69521,7 +69565,7 @@
         <v>45868.57320862269</v>
       </c>
       <c r="AW384">
-        <v>249.698738</v>
+        <v>250.698762</v>
       </c>
     </row>
     <row r="385" ht="18" customHeight="1">
@@ -69699,7 +69743,7 @@
         <v>45859.70584207177</v>
       </c>
       <c r="AW385">
-        <v>258.566111</v>
+        <v>259.566134</v>
       </c>
     </row>
     <row r="386" ht="18" customHeight="1">
@@ -69880,7 +69924,7 @@
         <v>46001.46105103009</v>
       </c>
       <c r="AW386">
-        <v>116.810903</v>
+        <v>117.810926</v>
       </c>
     </row>
     <row r="387" ht="18" customHeight="1">
@@ -70061,7 +70105,7 @@
         <v>45952.41516831018</v>
       </c>
       <c r="AW387">
-        <v>165.856782</v>
+        <v>166.856806</v>
       </c>
     </row>
     <row r="388" ht="18" customHeight="1">
@@ -70242,7 +70286,7 @@
         <v>46007.42823478009</v>
       </c>
       <c r="AW388">
-        <v>110.843715</v>
+        <v>111.843738</v>
       </c>
     </row>
     <row r="389" ht="18" customHeight="1">
@@ -70415,7 +70459,7 @@
         <v>45905.67968340278</v>
       </c>
       <c r="AW389">
-        <v>212.592269</v>
+        <v>213.592292</v>
       </c>
     </row>
     <row r="390" ht="18" customHeight="1">
@@ -70588,7 +70632,7 @@
         <v>45905.68014417824</v>
       </c>
       <c r="AW390">
-        <v>212.591806</v>
+        <v>213.591829</v>
       </c>
     </row>
     <row r="391" ht="18" customHeight="1">
@@ -70769,7 +70813,7 @@
         <v>46001.46262186342</v>
       </c>
       <c r="AW391">
-        <v>116.809329</v>
+        <v>117.809352</v>
       </c>
     </row>
     <row r="392" ht="18" customHeight="1">
@@ -70950,7 +70994,7 @@
         <v>45973.66474306713</v>
       </c>
       <c r="AW392">
-        <v>144.607211</v>
+        <v>145.607234</v>
       </c>
     </row>
     <row r="393" ht="18" customHeight="1">
@@ -71131,7 +71175,7 @@
         <v>45986.56209506944</v>
       </c>
       <c r="AW393">
-        <v>131.70985</v>
+        <v>132.709873</v>
       </c>
     </row>
   </sheetData>
